--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -55802,6 +55802,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2411">
+      <c r="A2411" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2411" t="n">
+        <v>47255</v>
+      </c>
+      <c r="C2411" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="D2411" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E2411" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="F2411" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2411" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -55825,6 +55825,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2412">
+      <c r="A2412" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2412" t="n">
+        <v>46445</v>
+      </c>
+      <c r="C2412" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="D2412" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2412" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2412" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G2412" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -55848,6 +55848,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2413" t="n">
+        <v>58401</v>
+      </c>
+      <c r="C2413" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2413" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2413" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -55871,6 +55871,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2414" t="n">
+        <v>66073</v>
+      </c>
+      <c r="C2414" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2414" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2414" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -55712,22 +55712,22 @@
     </row>
     <row r="2407">
       <c r="A2407" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2407" t="n">
-        <v>13754</v>
+        <v>1910</v>
       </c>
       <c r="C2407" t="n">
         <v>2.53999996185303</v>
       </c>
       <c r="D2407" t="n">
-        <v>2.5</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="E2407" t="n">
         <v>2.52999997138977</v>
       </c>
       <c r="F2407" t="n">
-        <v>2.5</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="G2407" t="s">
         <v>7</v>
@@ -55735,22 +55735,22 @@
     </row>
     <row r="2408">
       <c r="A2408" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2408" t="n">
-        <v>50389</v>
+        <v>13754</v>
       </c>
       <c r="C2408" t="n">
-        <v>2.54999995231628</v>
+        <v>2.53999996185303</v>
       </c>
       <c r="D2408" t="n">
-        <v>2.49000000953674</v>
+        <v>2.5</v>
       </c>
       <c r="E2408" t="n">
         <v>2.52999997138977</v>
       </c>
       <c r="F2408" t="n">
-        <v>2.54999995231628</v>
+        <v>2.5</v>
       </c>
       <c r="G2408" t="s">
         <v>7</v>
@@ -55758,19 +55758,19 @@
     </row>
     <row r="2409">
       <c r="A2409" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2409" t="n">
-        <v>57464</v>
+        <v>50389</v>
       </c>
       <c r="C2409" t="n">
-        <v>2.60999989509583</v>
+        <v>2.54999995231628</v>
       </c>
       <c r="D2409" t="n">
-        <v>2.53999996185303</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="E2409" t="n">
-        <v>2.54999995231628</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="F2409" t="n">
         <v>2.54999995231628</v>
@@ -55781,22 +55781,22 @@
     </row>
     <row r="2410">
       <c r="A2410" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2410" t="n">
-        <v>6227</v>
+        <v>57464</v>
       </c>
       <c r="C2410" t="n">
-        <v>2.57999992370605</v>
+        <v>2.60999989509583</v>
       </c>
       <c r="D2410" t="n">
-        <v>2.52999997138977</v>
+        <v>2.53999996185303</v>
       </c>
       <c r="E2410" t="n">
-        <v>2.52999997138977</v>
+        <v>2.54999995231628</v>
       </c>
       <c r="F2410" t="n">
-        <v>2.5699999332428</v>
+        <v>2.54999995231628</v>
       </c>
       <c r="G2410" t="s">
         <v>7</v>
@@ -55804,22 +55804,22 @@
     </row>
     <row r="2411">
       <c r="A2411" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2411" t="n">
-        <v>47255</v>
+        <v>6227</v>
       </c>
       <c r="C2411" t="n">
-        <v>2.61999988555908</v>
+        <v>2.57999992370605</v>
       </c>
       <c r="D2411" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="E2411" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="F2411" t="n">
         <v>2.5699999332428</v>
-      </c>
-      <c r="E2411" t="n">
-        <v>2.57999992370605</v>
-      </c>
-      <c r="F2411" t="n">
-        <v>2.59999990463257</v>
       </c>
       <c r="G2411" t="s">
         <v>7</v>
@@ -55827,22 +55827,22 @@
     </row>
     <row r="2412">
       <c r="A2412" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2412" t="n">
-        <v>46445</v>
+        <v>47255</v>
       </c>
       <c r="C2412" t="n">
         <v>2.61999988555908</v>
       </c>
       <c r="D2412" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E2412" t="n">
         <v>2.57999992370605</v>
       </c>
-      <c r="E2412" t="n">
-        <v>2.61999988555908</v>
-      </c>
       <c r="F2412" t="n">
-        <v>2.60999989509583</v>
+        <v>2.59999990463257</v>
       </c>
       <c r="G2412" t="s">
         <v>7</v>
@@ -55850,22 +55850,22 @@
     </row>
     <row r="2413">
       <c r="A2413" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2413" t="n">
-        <v>58401</v>
+        <v>46445</v>
       </c>
       <c r="C2413" t="n">
-        <v>2.64000010490417</v>
+        <v>2.61999988555908</v>
       </c>
       <c r="D2413" t="n">
-        <v>2.59999990463257</v>
+        <v>2.57999992370605</v>
       </c>
       <c r="E2413" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2413" t="n">
         <v>2.60999989509583</v>
-      </c>
-      <c r="F2413" t="n">
-        <v>2.64000010490417</v>
       </c>
       <c r="G2413" t="s">
         <v>7</v>
@@ -55873,24 +55873,47 @@
     </row>
     <row r="2414">
       <c r="A2414" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2414" t="n">
-        <v>66073</v>
+        <v>58401</v>
       </c>
       <c r="C2414" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2414" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2414" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2415" t="n">
+        <v>40456</v>
+      </c>
+      <c r="C2415" t="n">
         <v>2.70000004768372</v>
       </c>
-      <c r="D2414" t="n">
-        <v>2.64000010490417</v>
-      </c>
-      <c r="E2414" t="n">
-        <v>2.64000010490417</v>
-      </c>
-      <c r="F2414" t="n">
-        <v>2.70000004768372</v>
-      </c>
-      <c r="G2414" t="s">
+      <c r="D2415" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G2415" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G2" t="n">
-        <v>7.36839532852173</v>
+        <v>7.36839580535889</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269540786743</v>
+        <v>7.41269588470459</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007827758789</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G11" t="n">
-        <v>7.36839532852173</v>
+        <v>7.36839580535889</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.34914016723633</v>
       </c>
       <c r="G13" t="n">
-        <v>7.35363054275513</v>
+        <v>7.35363006591797</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.56503295898438</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5234432220459</v>
+        <v>7.52344226837158</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302261352539</v>
+        <v>7.31302213668823</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G31" t="n">
-        <v>7.39054536819458</v>
+        <v>7.3905463218689</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.47914361953735</v>
+        <v>7.47914409637451</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.47914361953735</v>
+        <v>7.47914409637451</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.5972752571106</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G37" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559278488159</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559278488159</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G40" t="n">
-        <v>7.53820896148682</v>
+        <v>7.53820848464966</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.47914361953735</v>
+        <v>7.47914409637451</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559278488159</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G57" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G58" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G60" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G61" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587160110474</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.94050121307373</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8187689781189</v>
+        <v>7.81877040863037</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970363616943</v>
+        <v>7.75970411300659</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568523406982</v>
+        <v>7.85568475723267</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568523406982</v>
+        <v>7.85568475723267</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G68" t="n">
-        <v>7.87045192718506</v>
+        <v>7.87045240402222</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G70" t="n">
-        <v>7.86306667327881</v>
+        <v>7.86306858062744</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86306667327881</v>
+        <v>7.86306858062744</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G72" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998245239258</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G74" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998245239258</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998245239258</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G78" t="n">
-        <v>7.87045192718506</v>
+        <v>7.87045240402222</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.78923606872559</v>
+        <v>7.7892370223999</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G80" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G81" t="n">
-        <v>7.66372299194336</v>
+        <v>7.6637225151062</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>10.0249805450439</v>
       </c>
       <c r="G85" t="n">
-        <v>7.88521766662598</v>
+        <v>7.88521718978882</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80400323867798</v>
+        <v>7.80400276184082</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830236434937</v>
+        <v>7.84830141067505</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G94" t="n">
-        <v>7.80400323867798</v>
+        <v>7.80400276184082</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278738021851</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755502700806</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77447032928467</v>
+        <v>7.77446985244751</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755502700806</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.78092670440674</v>
       </c>
       <c r="G100" t="n">
-        <v>7.69325590133667</v>
+        <v>7.69325542449951</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G101" t="n">
-        <v>7.73017168045044</v>
+        <v>7.7301721572876</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278738021851</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587160110474</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G106" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G107" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G108" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7080225944519</v>
+        <v>7.70802307128906</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755502700806</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G111" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G112" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755502700806</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755502700806</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755502700806</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G117" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063734054565</v>
+        <v>7.70063829421997</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G119" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G120" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278738021851</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278738021851</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G125" t="n">
-        <v>7.66372299194336</v>
+        <v>7.6637225151062</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G127" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G128" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G129" t="n">
-        <v>7.73017168045044</v>
+        <v>7.7301721572876</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G130" t="n">
-        <v>7.73017168045044</v>
+        <v>7.7301721572876</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.54625988006592</v>
       </c>
       <c r="G138" t="n">
-        <v>7.50867605209351</v>
+        <v>7.50867652893066</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.5972752571106</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.5972752571106</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58250761032104</v>
+        <v>7.58250856399536</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G144" t="n">
-        <v>7.53820896148682</v>
+        <v>7.53820848464966</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G152" t="n">
-        <v>7.53820896148682</v>
+        <v>7.53820848464966</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.5972752571106</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.60258007049561</v>
       </c>
       <c r="G155" t="n">
-        <v>7.55297470092773</v>
+        <v>7.55297517776489</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G159" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942529678345</v>
+        <v>7.61942481994629</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942529678345</v>
+        <v>7.61942481994629</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G162" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063734054565</v>
+        <v>7.70063829421997</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G164" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540403366089</v>
+        <v>7.71540451049805</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G169" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G170" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587160110474</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587160110474</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540403366089</v>
+        <v>7.71540451049805</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G174" t="n">
-        <v>7.53820896148682</v>
+        <v>7.53820848464966</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.5972752571106</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G179" t="n">
-        <v>7.53820896148682</v>
+        <v>7.53820848464966</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559278488159</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559278488159</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G184" t="n">
-        <v>7.53820896148682</v>
+        <v>7.53820848464966</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58250761032104</v>
+        <v>7.58250856399536</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.61196708679199</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56035804748535</v>
+        <v>7.56035900115967</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.47116661071777</v>
       </c>
       <c r="G191" t="n">
-        <v>7.4496111869812</v>
+        <v>7.44961166381836</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G196" t="n">
-        <v>7.39054536819458</v>
+        <v>7.3905463218689</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G197" t="n">
-        <v>7.39054536819458</v>
+        <v>7.3905463218689</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007827758789</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G219" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G221" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998245239258</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G222" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998245239258</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232028961182</v>
+        <v>7.7523193359375</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G229" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G230" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G234" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G237" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G238" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G239" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G240" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082418441772</v>
+        <v>7.53082466125488</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241468429565</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.23549890518188</v>
+        <v>7.2354998588562</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.15201854705811</v>
       </c>
       <c r="G283" t="n">
-        <v>7.19858312606812</v>
+        <v>7.19858264923096</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.23549890518188</v>
+        <v>7.2354998588562</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.15201854705811</v>
       </c>
       <c r="G285" t="n">
-        <v>7.19858312606812</v>
+        <v>7.19858264923096</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30932950973511</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G287" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G288" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G289" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G290" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G291" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G292" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G293" t="n">
-        <v>7.12475204467773</v>
+        <v>7.12475061416626</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G294" t="n">
-        <v>7.12475204467773</v>
+        <v>7.12475061416626</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G295" t="n">
-        <v>7.12475204467773</v>
+        <v>7.12475061416626</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G296" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G297" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G298" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G299" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G301" t="n">
-        <v>7.12475204467773</v>
+        <v>7.12475061416626</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G302" t="n">
-        <v>7.08783578872681</v>
+        <v>7.08783626556396</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400518417358</v>
+        <v>7.01400375366211</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G304" t="n">
-        <v>7.1616678237915</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G305" t="n">
-        <v>7.08783578872681</v>
+        <v>7.08783626556396</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017219543457</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017219543457</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.72961807250977</v>
       </c>
       <c r="G313" t="n">
-        <v>6.86634111404419</v>
+        <v>6.86634063720703</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017219543457</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017219543457</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.63575077056885</v>
       </c>
       <c r="G320" t="n">
-        <v>6.79251003265381</v>
+        <v>6.79250907897949</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G325" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G326" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260299682617</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G327" t="n">
-        <v>6.34951972961426</v>
+        <v>6.3495192527771</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G329" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G330" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G331" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260299682617</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G334" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.30721664428711</v>
       </c>
       <c r="G335" t="n">
-        <v>6.53409767150879</v>
+        <v>6.53409814834595</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G336" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G337" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G338" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G339" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G340" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G341" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G342" t="n">
-        <v>6.49718284606934</v>
+        <v>6.49718379974365</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G343" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260299682617</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G344" t="n">
-        <v>6.23877239227295</v>
+        <v>6.23877191543579</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G345" t="n">
-        <v>6.23877239227295</v>
+        <v>6.23877191543579</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G346" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260299682617</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G347" t="n">
-        <v>6.34951972961426</v>
+        <v>6.3495192527771</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G349" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G351" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G352" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G356" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G357" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G358" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494083404541</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G361" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G363" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494083404541</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G365" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494083404541</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G378" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G379" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G384" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G385" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G386" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G387" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G388" t="n">
-        <v>6.09110832214355</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G393" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G400" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G402" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G405" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G408" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G415" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G416" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G420" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G425" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G446" t="n">
-        <v>5.90653038024902</v>
+        <v>5.90652990341187</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G447" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G456" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G464" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G467" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G468" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737258911133</v>
+        <v>5.53737211227417</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G482" t="n">
-        <v>5.46354055404663</v>
+        <v>5.46354007720947</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G483" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G484" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G485" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G486" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G487" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G488" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G489" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G490" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G491" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G492" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G493" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G494" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G495" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G496" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G497" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G498" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G500" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G501" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G503" t="n">
-        <v>5.24204540252686</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G504" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G505" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G507" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G508" t="n">
-        <v>5.35279178619385</v>
+        <v>5.35279226303101</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G509" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G510" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G511" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821336746216</v>
+        <v>5.16821432113647</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821336746216</v>
+        <v>5.16821432113647</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G514" t="n">
-        <v>5.24204540252686</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24204540252686</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.83350801467896</v>
       </c>
       <c r="G524" t="n">
-        <v>5.3749418258667</v>
+        <v>5.37494325637817</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G525" t="n">
-        <v>5.43400716781616</v>
+        <v>5.434006690979</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G526" t="n">
-        <v>5.46354055404663</v>
+        <v>5.46354007720947</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737258911133</v>
+        <v>5.53737211227417</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49307298660278</v>
+        <v>5.49307346343994</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G530" t="n">
-        <v>5.65550231933594</v>
+        <v>5.6555027961731</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G531" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G533" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.28406810760498</v>
       </c>
       <c r="G534" t="n">
-        <v>5.72933340072632</v>
+        <v>5.72933387756348</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.30284214019775</v>
       </c>
       <c r="G536" t="n">
-        <v>5.74410057067871</v>
+        <v>5.74410104751587</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G537" t="n">
-        <v>5.65550231933594</v>
+        <v>5.6555027961731</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G542" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G543" t="n">
-        <v>5.49307298660278</v>
+        <v>5.49307346343994</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G545" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G546" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G548" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970899581909</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.48405265808105</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.48405265808105</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G554" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G555" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G561" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G562" t="n">
-        <v>5.5148606300354</v>
+        <v>5.51486110687256</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G563" t="n">
-        <v>5.5148606300354</v>
+        <v>5.51486110687256</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G568" t="n">
-        <v>5.5148606300354</v>
+        <v>5.51486110687256</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G572" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.82295417785645</v>
+        <v>5.82295370101929</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G575" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G576" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G577" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G578" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G582" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593067169189</v>
+        <v>5.74593114852905</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G586" t="n">
-        <v>5.68431186676025</v>
+        <v>5.68431234359741</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G592" t="n">
-        <v>5.65350341796875</v>
+        <v>5.65350389480591</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6.77718687057495</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56107473373413</v>
+        <v>5.56107425689697</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G604" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G605" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G606" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G607" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.30785322189331</v>
       </c>
       <c r="G608" t="n">
-        <v>5.17595911026001</v>
+        <v>5.17595863342285</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G613" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G614" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G615" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G616" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G617" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G618" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G619" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G620" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G625" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G626" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G627" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G628" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G630" t="n">
-        <v>5.68431186676025</v>
+        <v>5.68431234359741</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G638" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G639" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G643" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G646" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G647" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G648" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G649" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G653" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G655" t="n">
-        <v>5.25298309326172</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G656" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G657" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G658" t="n">
-        <v>5.19136333465576</v>
+        <v>5.19136381149292</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G659" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G660" t="n">
-        <v>5.19136333465576</v>
+        <v>5.19136381149292</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G665" t="n">
-        <v>5.14514923095703</v>
+        <v>5.14514970779419</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G666" t="n">
-        <v>5.0989351272583</v>
+        <v>5.09893560409546</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650835037231</v>
+        <v>5.00650787353516</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06812572479248</v>
+        <v>5.06812620162964</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676803588867</v>
+        <v>5.20676851272583</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G672" t="n">
-        <v>5.0989351272583</v>
+        <v>5.09893560409546</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G674" t="n">
-        <v>5.14514923095703</v>
+        <v>5.14514970779419</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G675" t="n">
-        <v>5.25298309326172</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G677" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G678" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G679" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G682" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G684" t="n">
-        <v>5.25298309326172</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G688" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G690" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G694" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.60822677612305</v>
       </c>
       <c r="G695" t="n">
-        <v>5.4224328994751</v>
+        <v>5.42243337631226</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G696" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G700" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G702" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G707" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G708" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G709" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G711" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G713" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G714" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162397384644</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G718" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G719" t="n">
-        <v>5.25298309326172</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G720" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G721" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G723" t="n">
-        <v>5.23757839202881</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>6.12011909484863</v>
       </c>
       <c r="G728" t="n">
-        <v>5.02191305160522</v>
+        <v>5.02191209793091</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G729" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434078216553</v>
+        <v>5.11434125900269</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434078216553</v>
+        <v>5.11434125900269</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G735" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G736" t="n">
-        <v>5.06812572479248</v>
+        <v>5.06812620162964</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G738" t="n">
-        <v>5.0989351272583</v>
+        <v>5.09893560409546</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G739" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G740" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.98870611190796</v>
       </c>
       <c r="G741" t="n">
-        <v>4.91408061981201</v>
+        <v>4.91408014297485</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>6.13889312744141</v>
       </c>
       <c r="G744" t="n">
-        <v>5.03731727600098</v>
+        <v>5.03731775283813</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>5.9136118888855</v>
       </c>
       <c r="G745" t="n">
-        <v>4.85246086120605</v>
+        <v>4.85246181488037</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.83851909637451</v>
       </c>
       <c r="G746" t="n">
-        <v>4.79084348678589</v>
+        <v>4.79084300994873</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436874389648</v>
+        <v>4.54436922073364</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.63201189041138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.62139177322388</v>
+        <v>4.62139225006104</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02061128616333</v>
+        <v>4.02061080932617</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.88196873664856</v>
+        <v>3.88196921348572</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468578338623</v>
+        <v>3.60468626022339</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G759" t="n">
-        <v>3.59698343276978</v>
+        <v>3.5969831943512</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G762" t="n">
-        <v>3.06552338600159</v>
+        <v>3.06552314758301</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G763" t="n">
-        <v>3.06552338600159</v>
+        <v>3.06552314758301</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G765" t="n">
-        <v>3.25808095932007</v>
+        <v>3.25808119773865</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.39672255516052</v>
+        <v>3.39672231674194</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G778" t="n">
-        <v>3.48915100097656</v>
+        <v>3.48915123939514</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306697845459</v>
+        <v>3.54306674003601</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G780" t="n">
-        <v>3.3890209197998</v>
+        <v>3.38902115821838</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G781" t="n">
-        <v>3.45063877105713</v>
+        <v>3.45063900947571</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G784" t="n">
-        <v>3.3890209197998</v>
+        <v>3.38902115821838</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G785" t="n">
-        <v>3.43523478507996</v>
+        <v>3.43523454666138</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G786" t="n">
-        <v>3.44293761253357</v>
+        <v>3.44293737411499</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.7741367816925</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G790" t="n">
-        <v>3.86656403541565</v>
+        <v>3.86656451225281</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.81264805793762</v>
+        <v>3.81264781951904</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.7741367816925</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.83575582504272</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G794" t="n">
-        <v>3.86656403541565</v>
+        <v>3.86656451225281</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G796" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116052627563</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G797" t="n">
-        <v>3.89737343788147</v>
+        <v>3.89737367630005</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.83575582504272</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116052627563</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291434288025</v>
+        <v>3.84291386604309</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.57131576538086</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01609182357788</v>
+        <v>4.01609230041504</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G809" t="n">
-        <v>4.0903115272522</v>
+        <v>4.09031200408936</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.60886287689209</v>
       </c>
       <c r="G811" t="n">
-        <v>4.04907846450806</v>
+        <v>4.04907894134521</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G824" t="n">
-        <v>4.28822994232178</v>
+        <v>4.28822946548462</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G830" t="n">
-        <v>4.0903115272522</v>
+        <v>4.09031200408936</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G831" t="n">
-        <v>4.0903115272522</v>
+        <v>4.09031200408936</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G833" t="n">
-        <v>4.15628385543823</v>
+        <v>4.15628433227539</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G835" t="n">
-        <v>4.13979053497314</v>
+        <v>4.1397910118103</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G836" t="n">
-        <v>4.13979053497314</v>
+        <v>4.1397910118103</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G838" t="n">
-        <v>4.15628385543823</v>
+        <v>4.15628433227539</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28822994232178</v>
+        <v>4.28822946548462</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23875093460083</v>
+        <v>4.23875045776367</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G846" t="n">
-        <v>4.15628385543823</v>
+        <v>4.15628433227539</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G858" t="n">
-        <v>4.13979053497314</v>
+        <v>4.1397910118103</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23875093460083</v>
+        <v>4.23875045776367</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G868" t="n">
-        <v>4.23875093460083</v>
+        <v>4.23875045776367</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G870" t="n">
-        <v>4.28822994232178</v>
+        <v>4.28822946548462</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G872" t="n">
-        <v>4.23875093460083</v>
+        <v>4.23875045776367</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23875093460083</v>
+        <v>4.23875045776367</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G886" t="n">
-        <v>4.15628385543823</v>
+        <v>4.15628433227539</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G889" t="n">
-        <v>4.15628385543823</v>
+        <v>4.15628433227539</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258466720581</v>
+        <v>4.03258514404297</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959921836853</v>
+        <v>3.99959969520569</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959921836853</v>
+        <v>3.99959969520569</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G901" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G903" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168056488037</v>
+        <v>3.80168032646179</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G909" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G911" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G912" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G919" t="n">
-        <v>3.31513166427612</v>
+        <v>3.3151319026947</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G920" t="n">
-        <v>3.31513166427612</v>
+        <v>3.3151319026947</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.75467395782471</v>
       </c>
       <c r="G923" t="n">
-        <v>3.29863810539246</v>
+        <v>3.29863786697388</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G925" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G927" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G932" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G934" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G937" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G941" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G942" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G943" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G946" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G947" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G950" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G952" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G953" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G954" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G957" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G958" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G959" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G961" t="n">
-        <v>3.83466744422913</v>
+        <v>3.83466696739197</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959921836853</v>
+        <v>3.99959969520569</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G966" t="n">
-        <v>3.85116052627563</v>
+        <v>3.85116004943848</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.8594069480896</v>
+        <v>3.85940742492676</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.8594069480896</v>
+        <v>3.85940742492676</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G972" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518748283386</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G973" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G974" t="n">
-        <v>3.83466744422913</v>
+        <v>3.83466696739197</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G975" t="n">
-        <v>3.85116052627563</v>
+        <v>3.85116004943848</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G978" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G979" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G982" t="n">
-        <v>3.68622899055481</v>
+        <v>3.68622875213623</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G984" t="n">
-        <v>3.68622899055481</v>
+        <v>3.68622875213623</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G985" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G991" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G992" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G994" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518748283386</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G995" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518748283386</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G999" t="n">
-        <v>3.68622899055481</v>
+        <v>3.68622875213623</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.71921420097351</v>
+        <v>3.71921467781067</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518748283386</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518748283386</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.68622899055481</v>
+        <v>3.68622875213623</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.45532369613647</v>
+        <v>3.4553234577179</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.45532369613647</v>
+        <v>3.4553234577179</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285757064819</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.45532369613647</v>
+        <v>3.4553234577179</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220084190369</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.71921420097351</v>
+        <v>3.71921467781067</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570799827576</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.7769410610199</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.83466744422913</v>
+        <v>3.83466696739197</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272135734558</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.69447445869446</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.68622899055481</v>
+        <v>3.68622875213623</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.68622899055481</v>
+        <v>3.68622875213623</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.61200857162476</v>
+        <v>3.61200881004333</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.54603624343872</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.45532369613647</v>
+        <v>3.4553234577179</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.38110399246216</v>
+        <v>3.38110423088074</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.34811735153198</v>
+        <v>3.34811758995056</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285757064819</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.34811735153198</v>
+        <v>3.34811758995056</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.35636425018311</v>
+        <v>3.35636448860168</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.28214526176453</v>
+        <v>3.28214502334595</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493915557861</v>
+        <v>3.17493939399719</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721277236938</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721277236938</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.21617197990417</v>
+        <v>3.2161717414856</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493915557861</v>
+        <v>3.17493939399719</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.21617197990417</v>
+        <v>3.2161717414856</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.59510111808777</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.15844631195068</v>
+        <v>3.15844655036926</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351406097412</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.32288694381714</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.91929507255554</v>
+        <v>2.91929531097412</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351406097412</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.05948686599731</v>
+        <v>3.05948662757874</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.08422660827637</v>
+        <v>3.08422684669495</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.08422660827637</v>
+        <v>3.08422684669495</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.41675400733948</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.00176095962524</v>
+        <v>3.0017614364624</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.4636869430542</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.04299378395081</v>
+        <v>3.04299402236938</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.05948686599731</v>
+        <v>3.05948662757874</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.05948686599731</v>
+        <v>3.05948662757874</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630843162537</v>
+        <v>2.88630867004395</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.35636425018311</v>
+        <v>3.35636448860168</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.38110399246216</v>
+        <v>3.38110423088074</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.47181701660156</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -63214,6 +63214,32 @@
         <v>2.66000008583069</v>
       </c>
       <c r="H2417" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2418" t="n">
+        <v>112047</v>
+      </c>
+      <c r="C2418" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2418" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="H2418" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -603,7 +603,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437644958496</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.47914409637451</v>
+        <v>7.4791431427002</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.47914409637451</v>
+        <v>7.4791431427002</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559278488159</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559278488159</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.47914409637451</v>
+        <v>7.4791431427002</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559278488159</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437644958496</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G57" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G60" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G61" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.94050121307373</v>
       </c>
       <c r="G63" t="n">
-        <v>7.81877040863037</v>
+        <v>7.81876945495605</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.7892370223999</v>
+        <v>7.78923606872559</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830141067505</v>
+        <v>7.84830236434937</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278928756714</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77446985244751</v>
+        <v>7.77447080612183</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278928756714</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G106" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G107" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G108" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G109" t="n">
-        <v>7.70802307128906</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278928756714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278928756714</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774091720581</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559278488159</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559278488159</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615184783936</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.7523193359375</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699262619019</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082466125488</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.2354998588562</v>
+        <v>7.23549890518188</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.2354998588562</v>
+        <v>7.23549890518188</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.90325736999512</v>
+        <v>6.9032564163208</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400375366211</v>
+        <v>7.01400327682495</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.90325736999512</v>
+        <v>6.9032564163208</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017219543457</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017219543457</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017219543457</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.90325736999512</v>
+        <v>6.9032564163208</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.90325736999512</v>
+        <v>6.9032564163208</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017219543457</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.90325736999512</v>
+        <v>6.9032564163208</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867799758911</v>
+        <v>6.71867895126343</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G326" t="n">
-        <v>6.31260299682617</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G331" t="n">
-        <v>6.31260299682617</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G343" t="n">
-        <v>6.31260299682617</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G346" t="n">
-        <v>6.31260299682617</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G358" t="n">
-        <v>6.16494083404541</v>
+        <v>6.16494035720825</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G363" t="n">
-        <v>6.16494083404541</v>
+        <v>6.16494035720825</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G365" t="n">
-        <v>6.16494083404541</v>
+        <v>6.16494035720825</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587648391724</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587648391724</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821432113647</v>
+        <v>5.16821384429932</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821432113647</v>
+        <v>5.16821384429932</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.81473398208618</v>
       </c>
       <c r="G523" t="n">
-        <v>5.36017560958862</v>
+        <v>5.36017608642578</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49307346343994</v>
+        <v>5.49307298660278</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.28406810760498</v>
       </c>
       <c r="G534" t="n">
-        <v>5.72933387756348</v>
+        <v>5.72933340072632</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G540" t="n">
-        <v>5.5816707611084</v>
+        <v>5.58167123794556</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.50783920288086</v>
+        <v>5.5078387260437</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G543" t="n">
-        <v>5.49307346343994</v>
+        <v>5.49307298660278</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G550" t="n">
-        <v>5.34540987014771</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405170440674</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405170440674</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G554" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G561" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57648038864136</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57648038864136</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57648038864136</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.82295370101929</v>
+        <v>5.82295417785645</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593114852905</v>
+        <v>5.74593067169189</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G586" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57648038864136</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G604" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G605" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G609" t="n">
-        <v>5.22217321395874</v>
+        <v>5.22217273712158</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G611" t="n">
-        <v>5.22217321395874</v>
+        <v>5.22217273712158</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G613" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G614" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G615" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G616" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G617" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G618" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G619" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G620" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G623" t="n">
-        <v>5.34540987014771</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G625" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G626" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G627" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G628" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G630" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G632" t="n">
-        <v>5.43783760070801</v>
+        <v>5.43783712387085</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G638" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G639" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G643" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379201889038</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G654" t="n">
-        <v>5.22217321395874</v>
+        <v>5.22217273712158</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G655" t="n">
-        <v>5.25298166275024</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G658" t="n">
-        <v>5.19136381149292</v>
+        <v>5.19136333465576</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G660" t="n">
-        <v>5.19136381149292</v>
+        <v>5.19136333465576</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G665" t="n">
-        <v>5.14514970779419</v>
+        <v>5.14514923095703</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650787353516</v>
+        <v>5.00650835037231</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676851272583</v>
+        <v>5.20676803588867</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G674" t="n">
-        <v>5.14514970779419</v>
+        <v>5.14514923095703</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G675" t="n">
-        <v>5.25298166275024</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G676" t="n">
-        <v>5.22217321395874</v>
+        <v>5.22217273712158</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G684" t="n">
-        <v>5.25298166275024</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G690" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G694" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G699" t="n">
-        <v>5.34540987014771</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G707" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G708" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G711" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G713" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G714" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G716" t="n">
-        <v>5.34540987014771</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379201889038</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G719" t="n">
-        <v>5.25298166275024</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379201889038</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379201889038</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G725" t="n">
-        <v>5.22217321395874</v>
+        <v>5.22217273712158</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G729" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G735" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G739" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G740" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>6.13889312744141</v>
       </c>
       <c r="G744" t="n">
-        <v>5.03731775283813</v>
+        <v>5.03731822967529</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>5.9136118888855</v>
       </c>
       <c r="G745" t="n">
-        <v>4.85246181488037</v>
+        <v>4.85246133804321</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760635375977</v>
+        <v>4.66760587692261</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760635375977</v>
+        <v>4.66760587692261</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.4442777633667</v>
       </c>
       <c r="G753" t="n">
-        <v>4.46734523773193</v>
+        <v>4.46734571456909</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08223009109497</v>
+        <v>4.08222961425781</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468626022339</v>
+        <v>3.60468578338623</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G761" t="n">
-        <v>3.20416474342346</v>
+        <v>3.20416498184204</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G762" t="n">
-        <v>3.06552314758301</v>
+        <v>3.06552338600159</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G763" t="n">
-        <v>3.06552314758301</v>
+        <v>3.06552338600159</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G772" t="n">
-        <v>3.20416474342346</v>
+        <v>3.20416498184204</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.39672231674194</v>
+        <v>3.39672255516052</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G783" t="n">
-        <v>3.46604418754578</v>
+        <v>3.4660439491272</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G787" t="n">
-        <v>3.46604418754578</v>
+        <v>3.4660439491272</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.77413654327393</v>
+        <v>3.77413606643677</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035064697266</v>
+        <v>3.8203501701355</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.77413654327393</v>
+        <v>3.77413606643677</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.82035064697266</v>
+        <v>3.8203501701355</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818260192871</v>
+        <v>3.92818307876587</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G805" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G808" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G809" t="n">
-        <v>4.09031200408936</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G815" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G820" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.95617008209229</v>
       </c>
       <c r="G823" t="n">
-        <v>4.35420274734497</v>
+        <v>4.35420227050781</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G828" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G830" t="n">
-        <v>4.09031200408936</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G831" t="n">
-        <v>4.09031200408936</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G834" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G849" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G851" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G852" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G853" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G854" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G855" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G856" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G857" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G859" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G861" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G876" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G877" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G878" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G880" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G883" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G884" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258514404297</v>
+        <v>4.03258466720581</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G893" t="n">
-        <v>4.04083204269409</v>
+        <v>4.04083156585693</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G898" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.89239311218262</v>
+        <v>3.89239358901978</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168032646179</v>
+        <v>3.80168056488037</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G912" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G916" t="n">
-        <v>3.43058371543884</v>
+        <v>3.43058395385742</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G927" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G948" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G951" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G955" t="n">
-        <v>3.63674831390381</v>
+        <v>3.63674855232239</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G956" t="n">
-        <v>3.63674831390381</v>
+        <v>3.63674855232239</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G957" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G958" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G959" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85940742492676</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.85940742492676</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G978" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G980" t="n">
-        <v>3.63674831390381</v>
+        <v>3.63674855232239</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G983" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G986" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G988" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G989" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.65324211120605</v>
+        <v>3.65324234962463</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.74395442008972</v>
+        <v>3.74395418167114</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.63674831390381</v>
+        <v>3.63674855232239</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.65324211120605</v>
+        <v>3.65324234962463</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.63674831390381</v>
+        <v>3.63674855232239</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252908706665</v>
+        <v>3.56252932548523</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252908706665</v>
+        <v>3.56252932548523</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.52129650115967</v>
+        <v>3.52129626274109</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883037567139</v>
+        <v>3.43883061408997</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883037567139</v>
+        <v>3.43883061408997</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285757064819</v>
+        <v>3.37285733222961</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220131874084</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570847511292</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694034576416</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.65324211120605</v>
+        <v>3.65324234962463</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.65324211120605</v>
+        <v>3.65324234962463</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71096849441528</v>
+        <v>3.7109682559967</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.63674831390381</v>
+        <v>3.63674855232239</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.62025594711304</v>
+        <v>3.62025570869446</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428290367126</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252908706665</v>
+        <v>3.56252932548523</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43058371543884</v>
+        <v>3.43058395385742</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077598571777</v>
+        <v>3.57077622413635</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.52129650115967</v>
+        <v>3.52129626274109</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.52129650115967</v>
+        <v>3.52129626274109</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428290367126</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.52129650115967</v>
+        <v>3.52129626274109</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428290367126</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.43058371543884</v>
+        <v>3.43058395385742</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.82976794242859</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.36461114883423</v>
+        <v>3.36461091041565</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.38110423088074</v>
+        <v>3.38110399246216</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285757064819</v>
+        <v>3.37285733222961</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.35636448860168</v>
+        <v>3.35636425018311</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.28214502334595</v>
+        <v>3.28214526176453</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12545990943909</v>
+        <v>3.12546014785767</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247326850891</v>
+        <v>3.09247303009033</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247326850891</v>
+        <v>3.09247303009033</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721277236938</v>
+        <v>3.11721301078796</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721277236938</v>
+        <v>3.11721301078796</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.99351406097412</v>
+        <v>2.9935142993927</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.93578815460205</v>
+        <v>2.93578791618347</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.98526740074158</v>
+        <v>2.98526763916016</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877431869507</v>
+        <v>2.96877455711365</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.99351406097412</v>
+        <v>2.9935142993927</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.93578815460205</v>
+        <v>2.93578791618347</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.06773376464844</v>
+        <v>3.06773352622986</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.07598042488098</v>
+        <v>3.0759801864624</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.08422684669495</v>
+        <v>3.08422660827637</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.08422684669495</v>
+        <v>3.08422660827637</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12545990943909</v>
+        <v>3.12546014785767</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.06773376464844</v>
+        <v>3.06773352622986</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.06773376464844</v>
+        <v>3.06773352622986</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.07598042488098</v>
+        <v>3.0759801864624</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.4636869430542</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.04299402236938</v>
+        <v>3.04299378395081</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.98526740074158</v>
+        <v>2.98526763916016</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877431869507</v>
+        <v>2.96877455711365</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.24779295921326</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.85332179069519</v>
+        <v>2.85332202911377</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630867004395</v>
+        <v>2.88630843162537</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.35636448860168</v>
+        <v>3.35636425018311</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.38110423088074</v>
+        <v>3.38110399246216</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.56433200836182</v>
+        <v>3.56433176994324</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.56433200836182</v>
+        <v>3.56433176994324</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>4.06560802459717</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.61598873138428</v>
+        <v>3.61598896980286</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.96880793571472</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.52989387512207</v>
+        <v>3.52989411354065</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.50406551361084</v>
+        <v>3.50406575202942</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.50406551361084</v>
+        <v>3.50406575202942</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.98816800117493</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.54711318016052</v>
+        <v>3.54711294174194</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.98816800117493</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.54711318016052</v>
+        <v>3.54711294174194</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.88168811798096</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.45240879058838</v>
+        <v>3.45240902900696</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.85264801979065</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.42658019065857</v>
+        <v>3.42658042907715</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.16829514503479</v>
+        <v>3.16829490661621</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21995186805725</v>
+        <v>3.21995210647583</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21995186805725</v>
+        <v>3.21995210647583</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.63968706130981</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.2371711730957</v>
+        <v>3.23717093467712</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.72921061515808</v>
+        <v>2.72921085357666</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.08792591094971</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.74642968177795</v>
+        <v>2.74642944335938</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.72921061515808</v>
+        <v>2.72921085357666</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.14600610733032</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.79808640480042</v>
+        <v>2.79808664321899</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.7684850692749</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.46231603622437</v>
+        <v>2.46231579780579</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.35039258003235</v>
+        <v>2.35039234161377</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.33317351341248</v>
+        <v>2.33317375183105</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.33317351341248</v>
+        <v>2.33317375183105</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.27290749549866</v>
+        <v>2.27290725708008</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.26429772377014</v>
+        <v>2.26429796218872</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.27290749549866</v>
+        <v>2.27290725708008</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.26429772377014</v>
+        <v>2.26429796218872</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542193412781</v>
+        <v>2.19542169570923</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542193412781</v>
+        <v>2.19542169570923</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.10071754455566</v>
+        <v>2.10071778297424</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.03280401229858</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.80799436569214</v>
+        <v>1.80799448490143</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.13928389549255</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.9026985168457</v>
+        <v>1.90269863605499</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.11024403572083</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.87687027454376</v>
+        <v>1.87687039375305</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>2.29416394233704</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.04045057296753</v>
+        <v>2.04045033454895</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157454490662</v>
+        <v>1.97157430648804</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157454490662</v>
+        <v>1.97157430648804</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574642181396</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574642181396</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157454490662</v>
+        <v>1.97157430648804</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.96296501159668</v>
+        <v>1.9629647731781</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.96296501159668</v>
+        <v>1.9629647731781</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574642181396</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713665008545</v>
+        <v>1.93713688850403</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.10056400299072</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.86826074123383</v>
+        <v>1.86826086044312</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.91130793094635</v>
+        <v>1.91130816936493</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713665008545</v>
+        <v>1.93713688850403</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.91130793094635</v>
+        <v>1.91130816936493</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.91130793094635</v>
+        <v>1.91130816936493</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.96296501159668</v>
+        <v>1.9629647731781</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.29416394233704</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.04045057296753</v>
+        <v>2.04045033454895</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.10071754455566</v>
+        <v>2.10071778297424</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178304672241</v>
+        <v>2.34178328514099</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.49675440788269</v>
+        <v>2.49675464630127</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49675440788269</v>
+        <v>2.49675464630127</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.49675440788269</v>
+        <v>2.49675464630127</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.7491250038147</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.44509696960449</v>
+        <v>2.44509673118591</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.35039258003235</v>
+        <v>2.35039234161377</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.35039258003235</v>
+        <v>2.35039234161377</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -63240,6 +63240,32 @@
         <v>2.59999990463257</v>
       </c>
       <c r="H2418" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2419" t="n">
+        <v>40713</v>
+      </c>
+      <c r="C2419" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2419" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G2419" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="H2419" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G2" t="n">
-        <v>7.36839580535889</v>
+        <v>7.3683967590332</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G3" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269588470459</v>
+        <v>7.41269636154175</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007923126221</v>
+        <v>7.42007875442505</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G7" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G11" t="n">
-        <v>7.36839580535889</v>
+        <v>7.3683967590332</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G12" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.34914016723633</v>
       </c>
       <c r="G13" t="n">
-        <v>7.35363006591797</v>
+        <v>7.35363101959229</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G15" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G16" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302213668823</v>
+        <v>7.31302261352539</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G19" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G22" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484449386597</v>
+        <v>7.43484401702881</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G25" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437644958496</v>
+        <v>7.46437740325928</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727430343628</v>
+        <v>7.5972728729248</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437644958496</v>
+        <v>7.46437740325928</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G58" t="n">
-        <v>7.64895677566528</v>
+        <v>7.64895582199097</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970411300659</v>
+        <v>7.75970315933228</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568523406982</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568523406982</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G68" t="n">
-        <v>7.87045240402222</v>
+        <v>7.8704514503479</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G72" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G74" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G78" t="n">
-        <v>7.87045240402222</v>
+        <v>7.8704514503479</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.78923606872559</v>
+        <v>7.78923749923706</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G81" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372156143188</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830236434937</v>
+        <v>7.84830141067505</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77447080612183</v>
+        <v>7.77446985244751</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063829421997</v>
+        <v>7.70063924789429</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278833389282</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G125" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372156143188</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633964538574</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G127" t="n">
-        <v>7.64895677566528</v>
+        <v>7.64895582199097</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G128" t="n">
-        <v>7.64895677566528</v>
+        <v>7.64895582199097</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67110538482666</v>
+        <v>7.67110443115234</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727430343628</v>
+        <v>7.5972728729248</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727430343628</v>
+        <v>7.5972728729248</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727430343628</v>
+        <v>7.5972728729248</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633964538574</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942481994629</v>
+        <v>7.61942386627197</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942481994629</v>
+        <v>7.61942386627197</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063829421997</v>
+        <v>7.70063924789429</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G164" t="n">
-        <v>7.64895677566528</v>
+        <v>7.64895582199097</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633964538574</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633964538574</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633964538574</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727430343628</v>
+        <v>7.5972728729248</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633964538574</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774091720581</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.61196708679199</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56035900115967</v>
+        <v>7.56035852432251</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.47116661071777</v>
       </c>
       <c r="G191" t="n">
-        <v>7.44961166381836</v>
+        <v>7.4496111869812</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G193" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G194" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G195" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G198" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G199" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007923126221</v>
+        <v>7.42007875442505</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G205" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G208" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G210" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G213" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G214" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G221" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G222" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232076644897</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.45699262619019</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082513809204</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G249" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G253" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G254" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.23549890518188</v>
+        <v>7.2354998588562</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.23549890518188</v>
+        <v>7.2354998588562</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30932998657227</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G293" t="n">
-        <v>7.12475061416626</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G294" t="n">
-        <v>7.12475061416626</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G295" t="n">
-        <v>7.12475061416626</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G301" t="n">
-        <v>7.12475061416626</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400327682495</v>
+        <v>7.01400423049927</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867895126343</v>
+        <v>6.71867799758911</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G321" t="n">
-        <v>6.75559329986572</v>
+        <v>6.75559377670288</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G322" t="n">
-        <v>6.75559329986572</v>
+        <v>6.75559377670288</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.60793018341064</v>
+        <v>6.6079306602478</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.30721664428711</v>
       </c>
       <c r="G335" t="n">
-        <v>6.53409814834595</v>
+        <v>6.53409862518311</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G358" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494131088257</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G363" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494131088257</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G365" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494131088257</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G393" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G405" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G408" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G416" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G420" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811897277832</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G446" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90653038024902</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811897277832</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811897277832</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811897277832</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G491" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G492" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G493" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G495" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G496" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G497" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.89921379089355</v>
       </c>
       <c r="G499" t="n">
-        <v>5.42662382125854</v>
+        <v>5.42662334442139</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587600708008</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G503" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G504" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G505" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587600708008</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G508" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821384429932</v>
+        <v>5.16821432113647</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821384429932</v>
+        <v>5.16821432113647</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G514" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G518" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G520" t="n">
-        <v>5.21251201629639</v>
+        <v>5.21251249313354</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.81473398208618</v>
       </c>
       <c r="G523" t="n">
-        <v>5.36017608642578</v>
+        <v>5.36017560958862</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.83350801467896</v>
       </c>
       <c r="G524" t="n">
-        <v>5.37494325637817</v>
+        <v>5.37494277954102</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G525" t="n">
-        <v>5.434006690979</v>
+        <v>5.43400716781616</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49307298660278</v>
+        <v>5.49307346343994</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G530" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550327301025</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.28406810760498</v>
       </c>
       <c r="G534" t="n">
-        <v>5.72933340072632</v>
+        <v>5.72933435440063</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G537" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550327301025</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G540" t="n">
-        <v>5.58167123794556</v>
+        <v>5.5816707611084</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.5078387260437</v>
+        <v>5.50783920288086</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G542" t="n">
-        <v>5.47830629348755</v>
+        <v>5.47830677032471</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G543" t="n">
-        <v>5.49307298660278</v>
+        <v>5.49307346343994</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G545" t="n">
-        <v>5.47830629348755</v>
+        <v>5.47830677032471</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G546" t="n">
-        <v>5.47830629348755</v>
+        <v>5.47830677032471</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G550" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.48405170440674</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.48405170440674</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G554" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G555" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G561" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G562" t="n">
-        <v>5.51486110687256</v>
+        <v>5.5148606300354</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G563" t="n">
-        <v>5.51486110687256</v>
+        <v>5.5148606300354</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G568" t="n">
-        <v>5.51486110687256</v>
+        <v>5.5148606300354</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G572" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G575" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G576" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G577" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G578" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G580" t="n">
-        <v>5.85376358032227</v>
+        <v>5.85376405715942</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G582" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G586" t="n">
-        <v>5.68431186676025</v>
+        <v>5.68431234359741</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G588" t="n">
-        <v>5.62269353866577</v>
+        <v>5.62269401550293</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G595" t="n">
-        <v>5.62269353866577</v>
+        <v>5.62269401550293</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G596" t="n">
-        <v>5.53026628494263</v>
+        <v>5.53026580810547</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G597" t="n">
-        <v>5.53026628494263</v>
+        <v>5.53026580810547</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G603" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G604" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G605" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G609" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G610" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G611" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G613" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G614" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G615" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G616" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G617" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G618" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G619" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G620" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G623" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540939331055</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G625" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G626" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G627" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G628" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G630" t="n">
-        <v>5.68431186676025</v>
+        <v>5.68431234359741</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G632" t="n">
-        <v>5.43783712387085</v>
+        <v>5.43783760070801</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G638" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G639" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G643" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G644" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G650" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G654" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G658" t="n">
-        <v>5.19136333465576</v>
+        <v>5.19136381149292</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G660" t="n">
-        <v>5.19136333465576</v>
+        <v>5.19136381149292</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353137969971</v>
+        <v>5.08353090286255</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G665" t="n">
-        <v>5.14514923095703</v>
+        <v>5.14514970779419</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650835037231</v>
+        <v>5.00650787353516</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676803588867</v>
+        <v>5.20676851272583</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G674" t="n">
-        <v>5.14514923095703</v>
+        <v>5.14514970779419</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G676" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G683" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G688" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G690" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G693" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G694" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G699" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540939331055</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G701" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G704" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G707" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G708" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G709" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G711" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G712" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31459999084473</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G713" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G714" t="n">
-        <v>5.39162349700928</v>
+        <v>5.39162445068359</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G716" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540939331055</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379154205322</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G725" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>6.12011909484863</v>
       </c>
       <c r="G728" t="n">
-        <v>5.02191209793091</v>
+        <v>5.02191257476807</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434125900269</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434125900269</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353137969971</v>
+        <v>5.08353090286255</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353137969971</v>
+        <v>5.08353090286255</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>6.13889312744141</v>
       </c>
       <c r="G744" t="n">
-        <v>5.03731822967529</v>
+        <v>5.03731775283813</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436922073364</v>
+        <v>4.54436874389648</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.4442777633667</v>
       </c>
       <c r="G753" t="n">
-        <v>4.46734571456909</v>
+        <v>4.46734523773193</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08222961425781</v>
+        <v>4.08223009109497</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468578338623</v>
+        <v>3.60468602180481</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G759" t="n">
-        <v>3.5969831943512</v>
+        <v>3.59698295593262</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G761" t="n">
-        <v>3.20416498184204</v>
+        <v>3.20416474342346</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G762" t="n">
-        <v>3.06552338600159</v>
+        <v>3.06552314758301</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G763" t="n">
-        <v>3.06552338600159</v>
+        <v>3.06552314758301</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G766" t="n">
-        <v>3.30429482460022</v>
+        <v>3.3042950630188</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G770" t="n">
-        <v>3.26578378677368</v>
+        <v>3.2657835483551</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G772" t="n">
-        <v>3.20416498184204</v>
+        <v>3.20416474342346</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G775" t="n">
-        <v>3.30429482460022</v>
+        <v>3.3042950630188</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.39672255516052</v>
+        <v>3.39672231674194</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306674003601</v>
+        <v>3.54306650161743</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G781" t="n">
-        <v>3.45063900947571</v>
+        <v>3.45063877105713</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G783" t="n">
-        <v>3.4660439491272</v>
+        <v>3.46604418754578</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G785" t="n">
-        <v>3.43523454666138</v>
+        <v>3.4352343082428</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G787" t="n">
-        <v>3.4660439491272</v>
+        <v>3.46604418754578</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.77413606643677</v>
+        <v>3.7741367816925</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.8203501701355</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.81264781951904</v>
+        <v>3.8126482963562</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.77413606643677</v>
+        <v>3.7741367816925</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.83575558662415</v>
+        <v>3.8357560634613</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.8203501701355</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G799" t="n">
-        <v>3.97439765930176</v>
+        <v>3.9743971824646</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.83575558662415</v>
+        <v>3.8357560634613</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G805" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G808" t="n">
-        <v>4.11505126953125</v>
+        <v>4.11505079269409</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G809" t="n">
-        <v>4.0903115272522</v>
+        <v>4.09031200408936</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G815" t="n">
-        <v>4.11505126953125</v>
+        <v>4.11505079269409</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G820" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.95617008209229</v>
       </c>
       <c r="G823" t="n">
-        <v>4.35420227050781</v>
+        <v>4.35420274734497</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G828" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G830" t="n">
-        <v>4.0903115272522</v>
+        <v>4.09031200408936</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G831" t="n">
-        <v>4.0903115272522</v>
+        <v>4.09031200408936</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G834" t="n">
-        <v>4.11505126953125</v>
+        <v>4.11505079269409</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G849" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G851" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G852" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G853" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G854" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G855" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G856" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G857" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G859" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G861" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G876" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G877" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G878" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G880" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G883" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G884" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576333999634</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258466720581</v>
+        <v>4.03258514404297</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G893" t="n">
-        <v>4.04083156585693</v>
+        <v>4.04083204269409</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G898" t="n">
-        <v>4.11505126953125</v>
+        <v>4.11505079269409</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.89239358901978</v>
+        <v>3.89239311218262</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168056488037</v>
+        <v>3.80168032646179</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G912" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G916" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058371543884</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G927" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G948" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G951" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G955" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G956" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G957" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G958" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G959" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.8594069480896</v>
+        <v>3.85940742492676</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.8594069480896</v>
+        <v>3.85940742492676</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G978" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G980" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G983" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G988" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G989" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324211120605</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324211120605</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285757064819</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324211120605</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324211120605</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.12075519561768</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.62025570869446</v>
+        <v>3.62025594711304</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058371543884</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077622413635</v>
+        <v>3.57077598571777</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058371543884</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.82976794242859</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.36461091041565</v>
+        <v>3.36461114883423</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.38110399246216</v>
+        <v>3.38110423088074</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285757064819</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.35636425018311</v>
+        <v>3.35636448860168</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.28214526176453</v>
+        <v>3.28214502334595</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721277236938</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721277236938</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351406097412</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351406097412</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.0759801864624</v>
+        <v>3.07598042488098</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.08422660827637</v>
+        <v>3.08422684669495</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.08422660827637</v>
+        <v>3.08422684669495</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.0759801864624</v>
+        <v>3.07598042488098</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.4636869430542</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.04299378395081</v>
+        <v>3.04299402236938</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.24779295921326</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.85332202911377</v>
+        <v>2.85332179069519</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630843162537</v>
+        <v>2.88630867004395</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.35636425018311</v>
+        <v>3.35636448860168</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.38110399246216</v>
+        <v>3.38110423088074</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.56433176994324</v>
+        <v>3.56433200836182</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.56433176994324</v>
+        <v>3.56433200836182</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>4.06560802459717</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.61598896980286</v>
+        <v>3.61598873138428</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.96880793571472</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.52989411354065</v>
+        <v>3.52989387512207</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.98816800117493</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.54711294174194</v>
+        <v>3.54711318016052</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.98816800117493</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.54711294174194</v>
+        <v>3.54711318016052</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.88168811798096</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.45240902900696</v>
+        <v>3.45240879058838</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.85264801979065</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.42658042907715</v>
+        <v>3.42658019065857</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.16829490661621</v>
+        <v>3.16829514503479</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21995210647583</v>
+        <v>3.21995186805725</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21995210647583</v>
+        <v>3.21995186805725</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.63968706130981</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.23717093467712</v>
+        <v>3.2371711730957</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.67755341529846</v>
+        <v>2.67755365371704</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.67755341529846</v>
+        <v>2.67755365371704</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.08792591094971</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.74642944335938</v>
+        <v>2.74642968177795</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.67755341529846</v>
+        <v>2.67755365371704</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.14600610733032</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.79808664321899</v>
+        <v>2.79808640480042</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.67755341529846</v>
+        <v>2.67755365371704</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423996925354</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.7684850692749</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.46231579780579</v>
+        <v>2.46231603622437</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.27290725708008</v>
+        <v>2.27290749549866</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.27290725708008</v>
+        <v>2.27290749549866</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542169570923</v>
+        <v>2.19542193412781</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542169570923</v>
+        <v>2.19542193412781</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.10071778297424</v>
+        <v>2.10071754455566</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.03280401229858</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.80799448490143</v>
+        <v>1.80799436569214</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.13928389549255</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.90269863605499</v>
+        <v>1.9026985168457</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.11024403572083</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.87687039375305</v>
+        <v>1.87687027454376</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>2.29416394233704</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.04045033454895</v>
+        <v>2.04045057296753</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.94574642181396</v>
+        <v>1.94574618339539</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.94574642181396</v>
+        <v>1.94574618339539</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.94574642181396</v>
+        <v>1.94574618339539</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713688850403</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.10056400299072</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.86826086044312</v>
+        <v>1.86826074123383</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130793094635</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713688850403</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130793094635</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130793094635</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.29416394233704</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.04045033454895</v>
+        <v>2.04045057296753</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.10071778297424</v>
+        <v>2.10071754455566</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178328514099</v>
+        <v>2.34178304672241</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.7491250038147</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.44509673118591</v>
+        <v>2.44509696960449</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065907478333</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -63251,7 +63251,7 @@
         <v>40713</v>
       </c>
       <c r="C2419" t="n">
-        <v>2.66000008583069</v>
+        <v>2.67000007629395</v>
       </c>
       <c r="D2419" t="n">
         <v>2.60999989509583</v>
@@ -63266,6 +63266,32 @@
         <v>2.67000007629395</v>
       </c>
       <c r="H2419" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2420" t="n">
+        <v>22378</v>
+      </c>
+      <c r="C2420" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2420" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2420" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F2420" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2420" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="H2420" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3683967590332</v>
+        <v>7.36839628219604</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269588470459</v>
+        <v>7.41269493103027</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007970809937</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3683967590332</v>
+        <v>7.36839628219604</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.34914016723633</v>
       </c>
       <c r="G13" t="n">
-        <v>7.35363054275513</v>
+        <v>7.35363006591797</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302309036255</v>
+        <v>7.31302213668823</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512331008911</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484401702881</v>
+        <v>7.43484544754028</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G31" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054584503174</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437692642212</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727382659912</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G37" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559087753296</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559087753296</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559087753296</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437692642212</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157390594482</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G57" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G58" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895725250244</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157390594482</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G60" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G61" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587207794189</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.94050121307373</v>
       </c>
       <c r="G63" t="n">
-        <v>7.81876993179321</v>
+        <v>7.8187689781189</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970411300659</v>
+        <v>7.75970315933228</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568428039551</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568428039551</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G70" t="n">
-        <v>7.86306858062744</v>
+        <v>7.8630690574646</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86306858062744</v>
+        <v>7.8630690574646</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.94428396224976</v>
+        <v>7.94428300857544</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.87479400634766</v>
       </c>
       <c r="G77" t="n">
-        <v>7.76708745956421</v>
+        <v>7.76708698272705</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.78923654556274</v>
+        <v>7.78923606872559</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G80" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>10.0249805450439</v>
       </c>
       <c r="G85" t="n">
-        <v>7.88521814346313</v>
+        <v>7.88521718978882</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G87" t="n">
-        <v>7.8040018081665</v>
+        <v>7.80400228500366</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830236434937</v>
+        <v>7.84830284118652</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.93111419677734</v>
       </c>
       <c r="G92" t="n">
-        <v>7.81138610839844</v>
+        <v>7.81138515472412</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G94" t="n">
-        <v>7.8040018081665</v>
+        <v>7.80400228500366</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278785705566</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77447032928467</v>
+        <v>7.77446985244751</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.78092670440674</v>
       </c>
       <c r="G100" t="n">
-        <v>7.69325542449951</v>
+        <v>7.6932544708252</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G101" t="n">
-        <v>7.73017168045044</v>
+        <v>7.73017263412476</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278785705566</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587207794189</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G106" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G107" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G108" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G109" t="n">
-        <v>7.70802068710327</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G111" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G112" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157390594482</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755407333374</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G117" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063924789429</v>
+        <v>7.70063781738281</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G120" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157390594482</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278785705566</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278785705566</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G127" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895725250244</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G128" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895725250244</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G129" t="n">
-        <v>7.73017168045044</v>
+        <v>7.73017263412476</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G130" t="n">
-        <v>7.73017168045044</v>
+        <v>7.73017263412476</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157390594482</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G132" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680625915527</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G133" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680625915527</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.6711049079895</v>
+        <v>7.67110538482666</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157247543335</v>
+        <v>7.64157390594482</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512331008911</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727382659912</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727382659912</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58250856399536</v>
+        <v>7.5825080871582</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G153" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680625915527</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727382659912</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G157" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680625915527</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G158" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680625915527</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942338943481</v>
+        <v>7.61942386627197</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942338943481</v>
+        <v>7.61942386627197</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G162" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063924789429</v>
+        <v>7.70063781738281</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G164" t="n">
-        <v>7.64895629882812</v>
+        <v>7.64895725250244</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G169" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G170" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587207794189</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587207794189</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727382659912</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559087753296</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559087753296</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49391078948975</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58250856399536</v>
+        <v>7.5825080871582</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512331008911</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.61196708679199</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56035947799683</v>
+        <v>7.56035900115967</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.47116661071777</v>
       </c>
       <c r="G191" t="n">
-        <v>7.44961071014404</v>
+        <v>7.44961023330688</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G196" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054584503174</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G197" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054584503174</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007970809937</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G219" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615327835083</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232172012329</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G229" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G239" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.45699310302734</v>
+        <v>7.45699453353882</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241563796997</v>
+        <v>7.2724142074585</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.23549890518188</v>
+        <v>7.2354998588562</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.15201854705811</v>
       </c>
       <c r="G283" t="n">
-        <v>7.19858312606812</v>
+        <v>7.1985821723938</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.23549890518188</v>
+        <v>7.2354998588562</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.15201854705811</v>
       </c>
       <c r="G285" t="n">
-        <v>7.19858312606812</v>
+        <v>7.1985821723938</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G293" t="n">
-        <v>7.12475109100342</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G294" t="n">
-        <v>7.12475109100342</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G295" t="n">
-        <v>7.12475109100342</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G301" t="n">
-        <v>7.12475109100342</v>
+        <v>7.12475156784058</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G302" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400423049927</v>
+        <v>7.01400470733643</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G305" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.72961807250977</v>
       </c>
       <c r="G313" t="n">
-        <v>6.86634063720703</v>
+        <v>6.86634111404419</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867895126343</v>
+        <v>6.71867847442627</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G321" t="n">
-        <v>6.75559377670288</v>
+        <v>6.75559282302856</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G322" t="n">
-        <v>6.75559377670288</v>
+        <v>6.75559282302856</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.6079306602478</v>
+        <v>6.60792970657349</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G327" t="n">
-        <v>6.3495192527771</v>
+        <v>6.34951972961426</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G347" t="n">
-        <v>6.3495192527771</v>
+        <v>6.34951972961426</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G355" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G356" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G357" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G358" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494083404541</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G359" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G361" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G363" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494083404541</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G365" t="n">
-        <v>6.16494035720825</v>
+        <v>6.16494083404541</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G373" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G376" t="n">
-        <v>6.01727676391602</v>
+        <v>6.01727724075317</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G378" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G379" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G380" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G381" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G382" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G383" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G384" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G385" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G386" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G387" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G388" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G392" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G394" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G395" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G396" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G397" t="n">
-        <v>5.86961460113525</v>
+        <v>5.8696141242981</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G399" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G400" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G401" t="n">
-        <v>5.79578304290771</v>
+        <v>5.79578256607056</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G402" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G404" t="n">
-        <v>5.57428789138794</v>
+        <v>5.57428741455078</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G406" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G409" t="n">
-        <v>5.86961460113525</v>
+        <v>5.8696141242981</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G410" t="n">
-        <v>5.79578304290771</v>
+        <v>5.79578256607056</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G411" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G412" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86961460113525</v>
+        <v>5.8696141242981</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G415" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G421" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G423" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G425" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G426" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G427" t="n">
-        <v>5.86961460113525</v>
+        <v>5.8696141242981</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G429" t="n">
-        <v>5.57428789138794</v>
+        <v>5.57428741455078</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G430" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G431" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G432" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G433" t="n">
-        <v>5.86961460113525</v>
+        <v>5.8696141242981</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G434" t="n">
-        <v>5.79578304290771</v>
+        <v>5.79578256607056</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G438" t="n">
-        <v>6.01727676391602</v>
+        <v>6.01727724075317</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.97868299484253</v>
       </c>
       <c r="G439" t="n">
-        <v>6.27568769454956</v>
+        <v>6.27568817138672</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.97868299484253</v>
       </c>
       <c r="G440" t="n">
-        <v>6.27568769454956</v>
+        <v>6.27568817138672</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G442" t="n">
-        <v>5.86961460113525</v>
+        <v>5.8696141242981</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G443" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G444" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G445" t="n">
-        <v>5.79578304290771</v>
+        <v>5.79578256607056</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G447" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G449" t="n">
-        <v>5.57428789138794</v>
+        <v>5.57428741455078</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G450" t="n">
-        <v>5.57428789138794</v>
+        <v>5.57428741455078</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G451" t="n">
-        <v>5.57428789138794</v>
+        <v>5.57428741455078</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G452" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G453" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G454" t="n">
-        <v>5.57428789138794</v>
+        <v>5.57428741455078</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G455" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G456" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G457" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G459" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G461" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G462" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G463" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G464" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G465" t="n">
-        <v>5.79578304290771</v>
+        <v>5.79578256607056</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G466" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G467" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G468" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G471" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G472" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G473" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G474" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G475" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G476" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G477" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G478" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G480" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737211227417</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G483" t="n">
-        <v>5.50045680999756</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G484" t="n">
-        <v>5.50045680999756</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G485" t="n">
-        <v>5.50045680999756</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G486" t="n">
-        <v>5.50045680999756</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G487" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G488" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G489" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G490" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G491" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G492" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G493" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G494" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G495" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G496" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G497" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G498" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G500" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G501" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G503" t="n">
-        <v>5.24204444885254</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G504" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G505" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G507" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G508" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G509" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G510" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G511" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821384429932</v>
+        <v>5.16821336746216</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821384429932</v>
+        <v>5.16821336746216</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G514" t="n">
-        <v>5.24204444885254</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G515" t="n">
-        <v>5.20512914657593</v>
+        <v>5.20512962341309</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G516" t="n">
-        <v>5.20512914657593</v>
+        <v>5.20512962341309</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G517" t="n">
-        <v>5.20512914657593</v>
+        <v>5.20512962341309</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24204444885254</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G519" t="n">
-        <v>5.28634452819824</v>
+        <v>5.28634405136108</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G521" t="n">
-        <v>5.28634452819824</v>
+        <v>5.28634405136108</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>6.70209407806396</v>
       </c>
       <c r="G522" t="n">
-        <v>5.27157783508301</v>
+        <v>5.27157831192017</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.81473398208618</v>
       </c>
       <c r="G523" t="n">
-        <v>5.36017560958862</v>
+        <v>5.36017608642578</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G525" t="n">
-        <v>5.43400764465332</v>
+        <v>5.43400716781616</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737211227417</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G529" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G530" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550327301025</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G531" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G532" t="n">
-        <v>5.68503427505493</v>
+        <v>5.68503475189209</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>7.32161521911621</v>
       </c>
       <c r="G533" t="n">
-        <v>5.75886631011963</v>
+        <v>5.75886678695679</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.37793493270874</v>
       </c>
       <c r="G535" t="n">
-        <v>5.8031644821167</v>
+        <v>5.80316543579102</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G537" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550327301025</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G538" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G540" t="n">
-        <v>5.58167123794556</v>
+        <v>5.5816707611084</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.50783920288086</v>
+        <v>5.50784015655518</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G542" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G545" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G546" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G548" t="n">
-        <v>5.38970851898193</v>
+        <v>5.38970804214478</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405265808105</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405265808105</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G553" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G555" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G556" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G557" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G558" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G559" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G560" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G571" t="n">
-        <v>5.77674007415771</v>
+        <v>5.77674055099487</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.8229546546936</v>
+        <v>5.82295417785645</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G574" t="n">
-        <v>5.77674007415771</v>
+        <v>5.77674055099487</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G580" t="n">
-        <v>5.85376405715942</v>
+        <v>5.85376310348511</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.07756090164185</v>
       </c>
       <c r="G581" t="n">
-        <v>5.80754947662354</v>
+        <v>5.80754852294922</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G583" t="n">
-        <v>5.77674007415771</v>
+        <v>5.77674055099487</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593114852905</v>
+        <v>5.74593162536621</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G596" t="n">
-        <v>5.53026580810547</v>
+        <v>5.53026628494263</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G597" t="n">
-        <v>5.53026580810547</v>
+        <v>5.53026628494263</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G598" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G599" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G600" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G602" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G607" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G609" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G611" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G612" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G621" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G623" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G624" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G636" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G637" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G641" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G642" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G645" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G646" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G649" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G653" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G654" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G655" t="n">
-        <v>5.25298261642456</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G665" t="n">
-        <v>5.14514970779419</v>
+        <v>5.14514923095703</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650835037231</v>
+        <v>5.00650787353516</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G669" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676851272583</v>
+        <v>5.20676803588867</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G673" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G674" t="n">
-        <v>5.14514970779419</v>
+        <v>5.14514923095703</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G675" t="n">
-        <v>5.25298261642456</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G676" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G682" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G684" t="n">
-        <v>5.25298261642456</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G686" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G688" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G691" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G692" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G696" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G697" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G698" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G699" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G706" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G709" t="n">
-        <v>5.4070291519165</v>
+        <v>5.40702867507935</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G710" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G716" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G718" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G719" t="n">
-        <v>5.25298261642456</v>
+        <v>5.2529821395874</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G720" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G721" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919624328613</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G725" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G726" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G727" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434030532837</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G731" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G732" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434030532837</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.98870611190796</v>
       </c>
       <c r="G741" t="n">
-        <v>4.91408014297485</v>
+        <v>4.91408061981201</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>6.00747919082642</v>
       </c>
       <c r="G742" t="n">
-        <v>4.92948436737061</v>
+        <v>4.92948484420776</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>6.00747919082642</v>
       </c>
       <c r="G743" t="n">
-        <v>4.92948436737061</v>
+        <v>4.92948484420776</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.83851909637451</v>
       </c>
       <c r="G746" t="n">
-        <v>4.79084348678589</v>
+        <v>4.79084253311157</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.65078496932983</v>
       </c>
       <c r="G749" t="n">
-        <v>4.63679647445679</v>
+        <v>4.63679695129395</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436922073364</v>
+        <v>4.54436874389648</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.55691814422607</v>
       </c>
       <c r="G752" t="n">
-        <v>4.55977296829224</v>
+        <v>4.55977344512939</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.4442777633667</v>
       </c>
       <c r="G753" t="n">
-        <v>4.46734523773193</v>
+        <v>4.46734571456909</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.29409122467041</v>
       </c>
       <c r="G754" t="n">
-        <v>4.34410858154297</v>
+        <v>4.34410810470581</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08223009109497</v>
+        <v>4.08222961425781</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02061033248901</v>
+        <v>4.02061080932617</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.88196897506714</v>
+        <v>3.88196873664856</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G759" t="n">
-        <v>3.59698295593262</v>
+        <v>3.59698343276978</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G760" t="n">
-        <v>3.23497462272644</v>
+        <v>3.23497438430786</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G762" t="n">
-        <v>3.06552338600159</v>
+        <v>3.06552314758301</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G763" t="n">
-        <v>3.06552338600159</v>
+        <v>3.06552314758301</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G764" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G766" t="n">
-        <v>3.30429482460022</v>
+        <v>3.3042950630188</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G767" t="n">
-        <v>3.31970000267029</v>
+        <v>3.31970024108887</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G768" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G769" t="n">
-        <v>3.31970000267029</v>
+        <v>3.31970024108887</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G773" t="n">
-        <v>3.23497462272644</v>
+        <v>3.23497438430786</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G774" t="n">
-        <v>3.23497462272644</v>
+        <v>3.23497438430786</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G775" t="n">
-        <v>3.30429482460022</v>
+        <v>3.3042950630188</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.3967227935791</v>
+        <v>3.39672231674194</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306674003601</v>
+        <v>3.54306650161743</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G782" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G785" t="n">
-        <v>3.43523478507996</v>
+        <v>3.43523454666138</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G786" t="n">
-        <v>3.44293737411499</v>
+        <v>3.44293713569641</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.77413654327393</v>
+        <v>3.7741367816925</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.8203501701355</v>
+        <v>3.82035040855408</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.8126482963562</v>
+        <v>3.81264805793762</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.77413654327393</v>
+        <v>3.7741367816925</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.83575582504272</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.8203501701355</v>
+        <v>3.82035040855408</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G796" t="n">
-        <v>3.85116028785706</v>
+        <v>3.85116004943848</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G797" t="n">
-        <v>3.89737391471863</v>
+        <v>3.89737343788147</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818307876587</v>
+        <v>3.92818260192871</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G799" t="n">
-        <v>3.9743971824646</v>
+        <v>3.97439742088318</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.83575582504272</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85116028785706</v>
+        <v>3.85116004943848</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.40235614776611</v>
       </c>
       <c r="G802" t="n">
-        <v>3.86765384674072</v>
+        <v>3.8676540851593</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G805" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291434288025</v>
+        <v>3.84291458129883</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.57131576538086</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01609182357788</v>
+        <v>4.01609230041504</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G809" t="n">
-        <v>4.09031105041504</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G817" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.03126382827759</v>
       </c>
       <c r="G819" t="n">
-        <v>4.42017555236816</v>
+        <v>4.42017602920532</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G824" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G825" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G827" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G830" t="n">
-        <v>4.09031105041504</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G831" t="n">
-        <v>4.09031105041504</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G850" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G860" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G866" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G870" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G871" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G881" t="n">
-        <v>4.22225713729858</v>
+        <v>4.22225666046143</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258466720581</v>
+        <v>4.03258514404297</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.61824893951416</v>
       </c>
       <c r="G895" t="n">
-        <v>4.05732440948486</v>
+        <v>4.05732488632202</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.54315614700317</v>
       </c>
       <c r="G896" t="n">
-        <v>3.99135255813599</v>
+        <v>3.99135231971741</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G901" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G903" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.8923933506012</v>
+        <v>3.89239311218262</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.41174221038818</v>
       </c>
       <c r="G905" t="n">
-        <v>3.87590026855469</v>
+        <v>3.87589979171753</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168056488037</v>
+        <v>3.80168032646179</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G909" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G913" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G916" t="n">
-        <v>3.43058347702026</v>
+        <v>3.43058371543884</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G925" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G926" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G929" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G931" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G933" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G935" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G936" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G940" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G943" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G945" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148781776428</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G946" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G948" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G951" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G953" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G954" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G955" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G956" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.61824893951416</v>
       </c>
       <c r="G962" t="n">
-        <v>4.05732440948486</v>
+        <v>4.05732488632202</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G964" t="n">
-        <v>3.96661305427551</v>
+        <v>3.96661281585693</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.50560903549194</v>
       </c>
       <c r="G965" t="n">
-        <v>3.95836591720581</v>
+        <v>3.95836615562439</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.56192922592163</v>
       </c>
       <c r="G967" t="n">
-        <v>4.00784587860107</v>
+        <v>4.00784540176392</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96661305427551</v>
+        <v>3.96661281585693</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.48683595657349</v>
       </c>
       <c r="G969" t="n">
-        <v>3.94187259674072</v>
+        <v>3.94187307357788</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85940718650818</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.85940718650818</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G972" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G973" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992770195007</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G980" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G982" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G983" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G984" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G986" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G988" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G989" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G990" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044845581055</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G991" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G992" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992770195007</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G994" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G995" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G997" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044845581055</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G999" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921443939209</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044845581055</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044845581055</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044845581055</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044845581055</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.74395418167114</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883037567139</v>
+        <v>3.43883061408997</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883037567139</v>
+        <v>3.43883061408997</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285709381104</v>
+        <v>3.37285733222961</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921443939209</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570823669434</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694058418274</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.34603595733643</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.81817436218262</v>
+        <v>3.81817388534546</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>4.3554220199585</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.826420545578</v>
+        <v>3.82642030715942</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.79343390464783</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869344711304</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148781776428</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71096849441528</v>
+        <v>3.71096873283386</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148781776428</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428338050842</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43058347702026</v>
+        <v>3.43058371543884</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077622413635</v>
+        <v>3.57077598571777</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428338050842</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428338050842</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.43058347702026</v>
+        <v>3.43058371543884</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.82976794242859</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.36461138725281</v>
+        <v>3.36461114883423</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.34811758995056</v>
+        <v>3.34811735153198</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285709381104</v>
+        <v>3.37285733222961</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.89547491073608</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.42233777046204</v>
+        <v>3.42233753204346</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.34811758995056</v>
+        <v>3.34811735153198</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.35636448860168</v>
+        <v>3.35636425018311</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.28214550018311</v>
+        <v>3.28214526176453</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493915557861</v>
+        <v>3.17493939399719</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493915557861</v>
+        <v>3.17493939399719</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.56694102287292</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.13370680809021</v>
+        <v>3.13370704650879</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351453781128</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.32288694381714</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.91929483413696</v>
+        <v>2.91929507255554</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877479553223</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351453781128</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.07598042488098</v>
+        <v>3.07598066329956</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.08422636985779</v>
+        <v>3.08422660827637</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.08422636985779</v>
+        <v>3.08422660827637</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.07598042488098</v>
+        <v>3.07598066329956</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.35104703903198</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.94403481483459</v>
+        <v>2.94403505325317</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877479553223</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.31349992752075</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.91104817390442</v>
+        <v>2.91104793548584</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.24779295921326</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.85332202911377</v>
+        <v>2.85332179069519</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.35636448860168</v>
+        <v>3.35636425018311</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.4635705947876</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.05592823028564</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.6073796749115</v>
+        <v>3.60737943649292</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.05592823028564</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.6073796749115</v>
+        <v>3.60737943649292</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.52128481864929</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.504065990448</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.504065990448</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.52128481864929</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.9494481086731</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.51267528533936</v>
+        <v>3.51267504692078</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.52128481864929</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.52128481864929</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.52128481864929</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.97848796844482</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.53850364685059</v>
+        <v>3.53850340843201</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.9494481086731</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.51267528533936</v>
+        <v>3.51267504692078</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.88168811798096</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.45240879058838</v>
+        <v>3.45240902900696</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.86232805252075</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.43518996238708</v>
+        <v>3.43518972396851</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.16829490661621</v>
+        <v>3.16829514503479</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21995186805725</v>
+        <v>3.21995210647583</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21995186805725</v>
+        <v>3.21995210647583</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.20273280143738</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.28152704238892</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.91861987113953</v>
+        <v>2.91862034797668</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.10728597640991</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.76364874839783</v>
+        <v>2.76364850997925</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.08792591094971</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.74642968177795</v>
+        <v>2.74642944335938</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.62589693069458</v>
+        <v>2.625896692276</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.62589693069458</v>
+        <v>2.625896692276</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.82656598091125</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.51397371292114</v>
+        <v>2.51397347450256</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.05888605117798</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.72060108184814</v>
+        <v>2.72060132026672</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.62589693069458</v>
+        <v>2.625896692276</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.62589693069458</v>
+        <v>2.625896692276</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.62589693069458</v>
+        <v>2.625896692276</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.62589693069458</v>
+        <v>2.625896692276</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1549" t="n">
-        <v>2.60006856918335</v>
+        <v>2.60006833076477</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.86528611183167</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.54841160774231</v>
+        <v>2.54841136932373</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.778165102005</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.4709255695343</v>
+        <v>2.47092533111572</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.29012608528137</v>
+        <v>2.29012632369995</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.29012608528137</v>
+        <v>2.29012632369995</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.27290725708008</v>
+        <v>2.27290749549866</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.53616499900818</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.25568819046021</v>
+        <v>2.25568842887878</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.29012608528137</v>
+        <v>2.29012632369995</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.27290725708008</v>
+        <v>2.27290749549866</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.53616499900818</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.25568819046021</v>
+        <v>2.25568842887878</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.29012608528137</v>
+        <v>2.29012632369995</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.29012608528137</v>
+        <v>2.29012632369995</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>2.53616499900818</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.25568819046021</v>
+        <v>2.25568842887878</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.22125053405762</v>
+        <v>2.2212507724762</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542193412781</v>
+        <v>2.19542217254639</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542193412781</v>
+        <v>2.19542217254639</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>2.42968511581421</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.16098403930664</v>
+        <v>2.16098427772522</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.42968511581421</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.16098403930664</v>
+        <v>2.16098427772522</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>2.3812849521637</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.11793661117554</v>
+        <v>2.11793684959412</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.3812849521637</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.11793661117554</v>
+        <v>2.11793684959412</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.09210824966431</v>
+        <v>2.09210848808289</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.30384397506714</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.04905986785889</v>
+        <v>2.04906010627747</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.13928389549255</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.90269863605499</v>
+        <v>1.9026985168457</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.11024403572083</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.87687039375305</v>
+        <v>1.87687027454376</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.236083984375</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.9887934923172</v>
+        <v>1.98879361152649</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.30384397506714</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.04905986785889</v>
+        <v>2.04906010627747</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157442569733</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157442569733</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574630260468</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574630260468</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157442569733</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574630260468</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713676929474</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.10056400299072</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.86826086044312</v>
+        <v>1.86826074123383</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.9285272359848</v>
+        <v>1.92852711677551</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.9285272359848</v>
+        <v>1.92852711677551</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713676929474</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.9285272359848</v>
+        <v>1.92852711677551</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.9285272359848</v>
+        <v>1.92852711677551</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.99740290641785</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.30384397506714</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.04905986785889</v>
+        <v>2.04906010627747</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.02323150634766</v>
+        <v>2.02323174476624</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.18681240081787</v>
+        <v>2.18681263923645</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>2.42968511581421</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.16098403930664</v>
+        <v>2.16098427772522</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.22125053405762</v>
+        <v>2.2212507724762</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.22125053405762</v>
+        <v>2.2212507724762</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178328514099</v>
+        <v>2.34178304672241</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.778165102005</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.4709255695343</v>
+        <v>2.47092533111572</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.7588050365448</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.45370650291443</v>
+        <v>2.45370626449585</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204930305481</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.68136501312256</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.38483071327209</v>
+        <v>2.38483047485352</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.37622117996216</v>
+        <v>2.376220703125</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.41065907478333</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -63370,6 +63370,32 @@
         <v>2.58999991416931</v>
       </c>
       <c r="H2423" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2424" t="n">
+        <v>25620</v>
+      </c>
+      <c r="C2424" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D2424" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E2424" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G2424" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H2424" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -56186,8 +56186,31 @@
       <c r="E2427" t="n">
         <v>2.47000002861023</v>
       </c>
-      <c r="F2427"/>
+      <c r="F2427" t="n">
+        <v>2.53999996185303</v>
+      </c>
       <c r="G2427" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2428" t="n">
+        <v>35175</v>
+      </c>
+      <c r="C2428" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D2428" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="E2428" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F2428"/>
+      <c r="G2428" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -56201,7 +56201,7 @@
         <v>35175</v>
       </c>
       <c r="C2428" t="n">
-        <v>2.57999992370605</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="D2428" t="n">
         <v>2.52999997138977</v>
@@ -56209,8 +56209,31 @@
       <c r="E2428" t="n">
         <v>2.53999996185303</v>
       </c>
-      <c r="F2428"/>
+      <c r="F2428" t="n">
+        <v>2.58999991416931</v>
+      </c>
       <c r="G2428" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2429" t="n">
+        <v>50461</v>
+      </c>
+      <c r="C2429" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="D2429" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2429" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="F2429"/>
+      <c r="G2429" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -56232,8 +56232,31 @@
       <c r="E2429" t="n">
         <v>2.55999994277954</v>
       </c>
-      <c r="F2429"/>
+      <c r="F2429" t="n">
+        <v>2.59999990463257</v>
+      </c>
       <c r="G2429" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2430" t="n">
+        <v>75619</v>
+      </c>
+      <c r="C2430" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2430"/>
+      <c r="G2430" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -56255,8 +56255,31 @@
       <c r="E2430" t="n">
         <v>2.59999990463257</v>
       </c>
-      <c r="F2430"/>
+      <c r="F2430" t="n">
+        <v>2.66000008583069</v>
+      </c>
       <c r="G2430" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2431" t="n">
+        <v>21630</v>
+      </c>
+      <c r="C2431" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F2431"/>
+      <c r="G2431" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -56285,6 +56285,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2432">
+      <c r="A2432" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2432" t="n">
+        <v>108806</v>
+      </c>
+      <c r="C2432" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="G2432" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3683967590332</v>
+        <v>7.36839628219604</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G3" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269540786743</v>
+        <v>7.41269636154175</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007970809937</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G7" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3683967590332</v>
+        <v>7.36839628219604</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G12" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G15" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G16" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302309036255</v>
+        <v>7.31302165985107</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G19" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.3585262298584</v>
       </c>
       <c r="G20" t="n">
-        <v>7.36101293563843</v>
+        <v>7.36101245880127</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G22" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484401702881</v>
+        <v>7.43484449386597</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.44300556182861</v>
       </c>
       <c r="G24" t="n">
-        <v>7.42746019363403</v>
+        <v>7.42746067047119</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G25" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437692642212</v>
+        <v>7.46437740325928</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G37" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437692642212</v>
+        <v>7.46437740325928</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.94050121307373</v>
       </c>
       <c r="G63" t="n">
-        <v>7.81876945495605</v>
+        <v>7.81876993179321</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970506668091</v>
+        <v>7.75970315933228</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568380355835</v>
+        <v>7.85568618774414</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568380355835</v>
+        <v>7.85568618774414</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>10.1188478469849</v>
       </c>
       <c r="G67" t="n">
-        <v>7.95904874801636</v>
+        <v>7.95904922485352</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G68" t="n">
-        <v>7.8704514503479</v>
+        <v>7.87045192718506</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G70" t="n">
-        <v>7.86306953430176</v>
+        <v>7.86306810379028</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86306953430176</v>
+        <v>7.86306810379028</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.94428300857544</v>
+        <v>7.94428396224976</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G78" t="n">
-        <v>7.8704514503479</v>
+        <v>7.87045192718506</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G80" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G81" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372203826904</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80400276184082</v>
+        <v>7.80400228500366</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830236434937</v>
+        <v>7.84830093383789</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.93111419677734</v>
       </c>
       <c r="G92" t="n">
-        <v>7.81138563156128</v>
+        <v>7.81138610839844</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G94" t="n">
-        <v>7.80400276184082</v>
+        <v>7.80400228500366</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755359649658</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755359649658</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G101" t="n">
-        <v>7.7301721572876</v>
+        <v>7.73017263412476</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755359649658</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G111" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G112" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755359649658</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755359649658</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755311965942</v>
+        <v>7.73755359649658</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G117" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063924789429</v>
+        <v>7.70063877105713</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G119" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G120" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G125" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372203826904</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G129" t="n">
-        <v>7.7301721572876</v>
+        <v>7.73017263412476</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G130" t="n">
-        <v>7.7301721572876</v>
+        <v>7.73017263412476</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G132" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680673599243</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G133" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680673599243</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67110538482666</v>
+        <v>7.67110586166382</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58250856399536</v>
+        <v>7.5825080871582</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G153" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680673599243</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.60258007049561</v>
       </c>
       <c r="G155" t="n">
-        <v>7.55297517776489</v>
+        <v>7.55297470092773</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G157" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680673599243</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G158" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680673599243</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G159" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942386627197</v>
+        <v>7.61942338943481</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942386627197</v>
+        <v>7.61942338943481</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G162" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063924789429</v>
+        <v>7.70063877105713</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540498733521</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G169" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G170" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540498733521</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58250856399536</v>
+        <v>7.5825080871582</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G193" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G194" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G195" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G198" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G199" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007970809937</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G205" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G208" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G210" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G213" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G214" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G219" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615280151367</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G229" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G230" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G234" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G237" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G238" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G239" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848873138428</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G240" t="n">
-        <v>7.60465669631958</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.4569935798645</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G249" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G253" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G254" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624624252319</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.2354998588562</v>
+        <v>7.23549938201904</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.2354998588562</v>
+        <v>7.23549938201904</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30933046340942</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G287" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G288" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G289" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G290" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G291" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G292" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G296" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G297" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G298" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G299" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G302" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783531188965</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400375366211</v>
+        <v>7.01400470733643</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G304" t="n">
-        <v>7.16166830062866</v>
+        <v>7.16166877746582</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G305" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783531188965</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G306" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G308" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G309" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G311" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.72961807250977</v>
       </c>
       <c r="G313" t="n">
-        <v>6.86634063720703</v>
+        <v>6.86634111404419</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017314910889</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.9032564163208</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867895126343</v>
+        <v>6.71867847442627</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.6079306602478</v>
+        <v>6.60793018341064</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G326" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G327" t="n">
-        <v>6.3495192527771</v>
+        <v>6.34951972961426</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G331" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G334" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G339" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G343" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G346" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G347" t="n">
-        <v>6.3495192527771</v>
+        <v>6.34951972961426</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G349" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G351" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G352" t="n">
-        <v>6.42335176467896</v>
+        <v>6.4233512878418</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G353" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G354" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G355" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G358" t="n">
-        <v>6.16493988037109</v>
+        <v>6.16494035720825</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G359" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G360" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G362" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G363" t="n">
-        <v>6.16493988037109</v>
+        <v>6.16494035720825</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G364" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.83788299560547</v>
       </c>
       <c r="G365" t="n">
-        <v>6.16493988037109</v>
+        <v>6.16494035720825</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G366" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G367" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G368" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G369" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G370" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G371" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G372" t="n">
-        <v>6.20185613632202</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G373" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G376" t="n">
-        <v>6.01727724075317</v>
+        <v>6.01727676391602</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G380" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G381" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G382" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G383" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G397" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G398" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G403" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G406" t="n">
-        <v>6.12802505493164</v>
+        <v>6.1280255317688</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G409" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G414" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G422" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G424" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G427" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G433" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G438" t="n">
-        <v>6.01727724075317</v>
+        <v>6.01727676391602</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344472885132</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G442" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G448" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G458" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G469" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195053100586</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737258911133</v>
+        <v>5.53737211227417</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G482" t="n">
-        <v>5.46354007720947</v>
+        <v>5.46354055404663</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G487" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G488" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G489" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G490" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G491" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G492" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G493" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G494" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G495" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G496" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G497" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G498" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G500" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G501" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587648391724</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G504" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G505" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587648391724</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G507" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G508" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G509" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G510" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G511" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821384429932</v>
+        <v>5.16821336746216</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821384429932</v>
+        <v>5.16821336746216</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G520" t="n">
-        <v>5.21251201629639</v>
+        <v>5.21251249313354</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G526" t="n">
-        <v>5.46354007720947</v>
+        <v>5.46354055404663</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737258911133</v>
+        <v>5.53737211227417</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G530" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550327301025</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.28406810760498</v>
       </c>
       <c r="G534" t="n">
-        <v>5.72933387756348</v>
+        <v>5.72933435440063</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.30284214019775</v>
       </c>
       <c r="G536" t="n">
-        <v>5.74410009384155</v>
+        <v>5.74410057067871</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G537" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550327301025</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.17142820358276</v>
       </c>
       <c r="G539" t="n">
-        <v>5.64073657989502</v>
+        <v>5.6407356262207</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G540" t="n">
-        <v>5.58167123794556</v>
+        <v>5.5816707611084</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.50783920288086</v>
+        <v>5.50783967971802</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G542" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830724716187</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G544" t="n">
-        <v>5.41924238204956</v>
+        <v>5.41924142837524</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G545" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830724716187</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G546" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830724716187</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G547" t="n">
-        <v>5.41924238204956</v>
+        <v>5.41924142837524</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G548" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G549" t="n">
-        <v>5.41924238204956</v>
+        <v>5.41924142837524</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G550" t="n">
-        <v>5.34540987014771</v>
+        <v>5.34540939331055</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405265808105</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405265808105</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G556" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G557" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G558" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G570" t="n">
-        <v>5.69971704483032</v>
+        <v>5.69971656799316</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G571" t="n">
-        <v>5.77674102783203</v>
+        <v>5.77673959732056</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G572" t="n">
-        <v>5.79214429855347</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.8229546546936</v>
+        <v>5.82295370101929</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G574" t="n">
-        <v>5.77674102783203</v>
+        <v>5.77673959732056</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G575" t="n">
-        <v>5.79214429855347</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G576" t="n">
-        <v>5.79214429855347</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G577" t="n">
-        <v>5.79214429855347</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G578" t="n">
-        <v>5.79214429855347</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.07756090164185</v>
       </c>
       <c r="G581" t="n">
-        <v>5.80754947662354</v>
+        <v>5.80754899978638</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G582" t="n">
-        <v>5.79214429855347</v>
+        <v>5.79214382171631</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G583" t="n">
-        <v>5.77674102783203</v>
+        <v>5.77673959732056</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593067169189</v>
+        <v>5.74593114852905</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G587" t="n">
-        <v>5.66890716552734</v>
+        <v>5.6689076423645</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G588" t="n">
-        <v>5.62269401550293</v>
+        <v>5.62269353866577</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G590" t="n">
-        <v>5.66890716552734</v>
+        <v>5.6689076423645</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6.77718687057495</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56107425689697</v>
+        <v>5.56107473373413</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G595" t="n">
-        <v>5.62269401550293</v>
+        <v>5.62269353866577</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G596" t="n">
-        <v>5.53026580810547</v>
+        <v>5.53026628494263</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G597" t="n">
-        <v>5.53026580810547</v>
+        <v>5.53026628494263</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G602" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G606" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.30785322189331</v>
       </c>
       <c r="G608" t="n">
-        <v>5.17595863342285</v>
+        <v>5.17595911026001</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G612" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G621" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G624" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G632" t="n">
-        <v>5.43783712387085</v>
+        <v>5.43783760070801</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54566955566406</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G640" t="n">
-        <v>5.33000516891479</v>
+        <v>5.33000564575195</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G641" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G642" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G645" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G647" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G648" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.42049312591553</v>
       </c>
       <c r="G652" t="n">
-        <v>5.26838684082031</v>
+        <v>5.26838636398315</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G655" t="n">
-        <v>5.25298261642456</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G656" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G657" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G659" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G666" t="n">
-        <v>5.0989351272583</v>
+        <v>5.09893560409546</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650835037231</v>
+        <v>5.00650787353516</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06812620162964</v>
+        <v>5.06812572479248</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G669" t="n">
-        <v>5.12974500656128</v>
+        <v>5.1297459602356</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.1605544090271</v>
+        <v>5.16055488586426</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676803588867</v>
+        <v>5.20676898956299</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G672" t="n">
-        <v>5.0989351272583</v>
+        <v>5.09893560409546</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G673" t="n">
-        <v>5.12974500656128</v>
+        <v>5.1297459602356</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G675" t="n">
-        <v>5.25298261642456</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G677" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G678" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G679" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G680" t="n">
-        <v>5.33000516891479</v>
+        <v>5.33000564575195</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.42049312591553</v>
       </c>
       <c r="G681" t="n">
-        <v>5.26838684082031</v>
+        <v>5.26838636398315</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G684" t="n">
-        <v>5.25298261642456</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G685" t="n">
-        <v>5.33000516891479</v>
+        <v>5.33000564575195</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G691" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G692" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.60822677612305</v>
       </c>
       <c r="G695" t="n">
-        <v>5.42243337631226</v>
+        <v>5.4224328994751</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G697" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G698" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G700" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G702" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G703" t="n">
-        <v>5.33000516891479</v>
+        <v>5.33000564575195</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G706" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G710" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G715" t="n">
-        <v>5.33000516891479</v>
+        <v>5.33000564575195</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G719" t="n">
-        <v>5.25298261642456</v>
+        <v>5.25298166275024</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G723" t="n">
-        <v>5.23757791519165</v>
+        <v>5.23757743835449</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G726" t="n">
-        <v>5.12974500656128</v>
+        <v>5.1297459602356</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G727" t="n">
-        <v>5.12974500656128</v>
+        <v>5.1297459602356</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G729" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434078216553</v>
+        <v>5.11434125900269</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G731" t="n">
-        <v>5.12974500656128</v>
+        <v>5.1297459602356</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G732" t="n">
-        <v>5.12974500656128</v>
+        <v>5.1297459602356</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434078216553</v>
+        <v>5.11434125900269</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G735" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G736" t="n">
-        <v>5.06812620162964</v>
+        <v>5.06812572479248</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G738" t="n">
-        <v>5.0989351272583</v>
+        <v>5.09893560409546</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G739" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G740" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.98870611190796</v>
       </c>
       <c r="G741" t="n">
-        <v>4.91408014297485</v>
+        <v>4.91408061981201</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>6.00747919082642</v>
       </c>
       <c r="G742" t="n">
-        <v>4.92948436737061</v>
+        <v>4.92948532104492</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>6.00747919082642</v>
       </c>
       <c r="G743" t="n">
-        <v>4.92948436737061</v>
+        <v>4.92948532104492</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.65078496932983</v>
       </c>
       <c r="G749" t="n">
-        <v>4.63679647445679</v>
+        <v>4.63679695129395</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436922073364</v>
+        <v>4.54436874389648</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.55691814422607</v>
       </c>
       <c r="G752" t="n">
-        <v>4.55977296829224</v>
+        <v>4.55977344512939</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.4442777633667</v>
       </c>
       <c r="G753" t="n">
-        <v>4.46734571456909</v>
+        <v>4.46734523773193</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08222961425781</v>
+        <v>4.08223009109497</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.88196921348572</v>
+        <v>3.88196969032288</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468578338623</v>
+        <v>3.60468602180481</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G766" t="n">
-        <v>3.3042950630188</v>
+        <v>3.30429482460022</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G767" t="n">
-        <v>3.31970000267029</v>
+        <v>3.31970024108887</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G769" t="n">
-        <v>3.31970000267029</v>
+        <v>3.31970024108887</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G770" t="n">
-        <v>3.2657835483551</v>
+        <v>3.26578378677368</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G775" t="n">
-        <v>3.3042950630188</v>
+        <v>3.30429482460022</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G778" t="n">
-        <v>3.48915123939514</v>
+        <v>3.48915100097656</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G781" t="n">
-        <v>3.45063900947571</v>
+        <v>3.45063924789429</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035064697266</v>
+        <v>3.82035040855408</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.8126482963562</v>
+        <v>3.81264781951904</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.82035064697266</v>
+        <v>3.82035040855408</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G796" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G797" t="n">
-        <v>3.89737367630005</v>
+        <v>3.89737343788147</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G799" t="n">
-        <v>3.97439670562744</v>
+        <v>3.97439694404602</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G805" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291386604309</v>
+        <v>3.84291434288025</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G810" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10680532455444</v>
+        <v>4.1068058013916</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.10680532455444</v>
+        <v>4.1068058013916</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.66518306732178</v>
       </c>
       <c r="G814" t="n">
-        <v>4.09855842590332</v>
+        <v>4.09855794906616</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.66518306732178</v>
       </c>
       <c r="G816" t="n">
-        <v>4.09855842590332</v>
+        <v>4.09855794906616</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.05003690719604</v>
       </c>
       <c r="G818" t="n">
-        <v>4.43666887283325</v>
+        <v>4.43666839599609</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G820" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G821" t="n">
-        <v>4.30472326278687</v>
+        <v>4.30472278594971</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.95617008209229</v>
       </c>
       <c r="G823" t="n">
-        <v>4.35420227050781</v>
+        <v>4.35420274734497</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G824" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G826" t="n">
-        <v>4.25524425506592</v>
+        <v>4.25524377822876</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G828" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G829" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G832" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G839" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G844" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G849" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G851" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G852" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G853" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G854" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G855" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G856" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G857" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G859" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G861" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G862" t="n">
-        <v>4.25524425506592</v>
+        <v>4.25524377822876</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G863" t="n">
-        <v>4.25524425506592</v>
+        <v>4.25524377822876</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G864" t="n">
-        <v>4.25524425506592</v>
+        <v>4.25524377822876</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G870" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G873" t="n">
-        <v>4.25524425506592</v>
+        <v>4.25524377822876</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G876" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G877" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G878" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G879" t="n">
-        <v>4.25524425506592</v>
+        <v>4.25524377822876</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G880" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G883" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G884" t="n">
-        <v>4.2057638168335</v>
+        <v>4.20576429367065</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G887" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G888" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G890" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G891" t="n">
-        <v>4.10680532455444</v>
+        <v>4.1068058013916</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258466720581</v>
+        <v>4.03258562088013</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G893" t="n">
-        <v>4.04083156585693</v>
+        <v>4.04083204269409</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G894" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.54315614700317</v>
       </c>
       <c r="G896" t="n">
-        <v>3.99135279655457</v>
+        <v>3.99135231971741</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959993362427</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959993362427</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.52438306808472</v>
       </c>
       <c r="G900" t="n">
-        <v>3.97485971450806</v>
+        <v>3.97485947608948</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.89239358901978</v>
+        <v>3.89239263534546</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.41174221038818</v>
       </c>
       <c r="G905" t="n">
-        <v>3.87590003013611</v>
+        <v>3.87590026855469</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168056488037</v>
+        <v>3.80168032646179</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G912" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G913" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G916" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.78283405303955</v>
       </c>
       <c r="G918" t="n">
-        <v>3.32337760925293</v>
+        <v>3.32337784767151</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.75467395782471</v>
       </c>
       <c r="G923" t="n">
-        <v>3.29863786697388</v>
+        <v>3.29863810539246</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G925" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G927" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G932" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G934" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G937" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G938" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G939" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G940" t="n">
-        <v>3.60376286506653</v>
+        <v>3.60376262664795</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G945" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148781776428</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G947" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G950" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G951" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G953" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G954" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G955" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G956" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G958" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G959" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G961" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466720581055</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959993362427</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G964" t="n">
-        <v>3.96661305427551</v>
+        <v>3.96661329269409</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G966" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.56192922592163</v>
       </c>
       <c r="G967" t="n">
-        <v>4.00784587860107</v>
+        <v>4.00784540176392</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96661305427551</v>
+        <v>3.96661329269409</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.8594069480896</v>
+        <v>3.85940742492676</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.8594069480896</v>
+        <v>3.85940742492676</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G974" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466720581055</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G975" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992794036865</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G978" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G980" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G982" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G983" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G984" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G985" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G988" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G989" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G990" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992794036865</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G997" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G999" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.60376286506653</v>
+        <v>3.60376262664795</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.64499497413635</v>
+        <v>3.64499521255493</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694034576416</v>
+        <v>3.77694082260132</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466720581055</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.34603595733643</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.81817436218262</v>
+        <v>3.81817412376404</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>4.3554220199585</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.826420545578</v>
+        <v>3.82642030715942</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148781776428</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447493553162</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148781776428</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.64499497413635</v>
+        <v>3.64499521255493</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.64499497413635</v>
+        <v>3.64499521255493</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.62850260734558</v>
+        <v>3.62850284576416</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.60376286506653</v>
+        <v>3.60376262664795</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.64499497413635</v>
+        <v>3.64499521255493</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.58726906776428</v>
+        <v>3.5872688293457</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077622413635</v>
+        <v>3.57077574729919</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.82976794242859</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.36461091041565</v>
+        <v>3.36461114883423</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.38110399246216</v>
+        <v>3.38110423088074</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493939399719</v>
+        <v>3.17493963241577</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247350692749</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247350692749</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.2161717414856</v>
+        <v>3.21617197990417</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493939399719</v>
+        <v>3.17493963241577</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124044418335</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.2161717414856</v>
+        <v>3.21617197990417</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.59510111808777</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.15844655036926</v>
+        <v>3.15844678878784</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124044418335</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.36043310165405</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.95228099822998</v>
+        <v>2.95228123664856</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.43552708625793</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.01825428009033</v>
+        <v>3.01825404167175</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.0759801864624</v>
+        <v>3.07598066329956</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124044418335</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.0759801864624</v>
+        <v>3.07598066329956</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.38859295845032</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.97702050209045</v>
+        <v>2.97702026367188</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.41675400733948</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.0017614364624</v>
+        <v>3.00176119804382</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124044418335</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124044418335</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.38859295845032</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.97702050209045</v>
+        <v>2.97702026367188</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.43552708625793</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.01825428009033</v>
+        <v>3.01825404167175</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124044418335</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.24779295921326</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.85332202911377</v>
+        <v>2.85332179069519</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630843162537</v>
+        <v>2.88630867004395</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.38110399246216</v>
+        <v>3.38110423088074</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181749343872</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.50480270385742</v>
+        <v>3.504802942276</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.48006296157837</v>
+        <v>3.48006319999695</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.03656816482544</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.59016060829163</v>
+        <v>3.59016084671021</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.03656816482544</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.59016060829163</v>
+        <v>3.59016084671021</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.05592823028564</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.6073796749115</v>
+        <v>3.60737943649292</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.05592823028564</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.6073796749115</v>
+        <v>3.60737943649292</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.97848796844482</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.53850364685059</v>
+        <v>3.53850340843201</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.85264801979065</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.42658042907715</v>
+        <v>3.42658019065857</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.77520799636841</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.35770440101624</v>
+        <v>3.35770463943481</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.16829490661621</v>
+        <v>3.16829514503479</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21995210647583</v>
+        <v>3.21995186805725</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21995210647583</v>
+        <v>3.21995186805725</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.14600610733032</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.79808664321899</v>
+        <v>2.79808640480042</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.03952598571777</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.70338201522827</v>
+        <v>2.70338225364685</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.7684850692749</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.46231579780579</v>
+        <v>2.46231603622437</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.65232491493225</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.35900187492371</v>
+        <v>2.35900211334229</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.65232491493225</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.35900187492371</v>
+        <v>2.35900211334229</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>2.65232491493225</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.35900187492371</v>
+        <v>2.35900211334229</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542169570923</v>
+        <v>2.19542217254639</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542169570923</v>
+        <v>2.19542217254639</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>2.3812849521637</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.11793661117554</v>
+        <v>2.11793684959412</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.10071778297424</v>
+        <v>2.10071754455566</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.3812849521637</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.11793661117554</v>
+        <v>2.11793684959412</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.09210848808289</v>
+        <v>2.09210824966431</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.37160491943359</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.1093270778656</v>
+        <v>2.10932683944702</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.06627893447876</v>
+        <v>2.06627869606018</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>2.34256505966187</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.08349895477295</v>
+        <v>2.08349871635437</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>2.28448390960693</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.03184080123901</v>
+        <v>2.03184103965759</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.13928389549255</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.90269863605499</v>
+        <v>1.9026985168457</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.11024403572083</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.87687039375305</v>
+        <v>1.87687027454376</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.06627893447876</v>
+        <v>2.06627869606018</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.94574642181396</v>
+        <v>1.9457460641861</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.94574642181396</v>
+        <v>1.9457460641861</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.19736409187317</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.95435547828674</v>
+        <v>1.95435559749603</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.94574642181396</v>
+        <v>1.9457460641861</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713688850403</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.10056400299072</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.86826086044312</v>
+        <v>1.86826074123383</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130805015564</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713688850403</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130805015564</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130805015564</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>2.19736409187317</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.95435547828674</v>
+        <v>1.95435559749603</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.06627893447876</v>
+        <v>2.06627869606018</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.10071778297424</v>
+        <v>2.10071754455566</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178328514099</v>
+        <v>2.34178304672241</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.78784489631653</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.47953462600708</v>
+        <v>2.47953486442566</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.78784489631653</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.47953462600708</v>
+        <v>2.47953486442566</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -63638,7 +63638,7 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B2434" t="n">
-        <v>23931</v>
+        <v>24455</v>
       </c>
       <c r="C2434" t="n">
         <v>2.66000008583069</v>
@@ -63656,6 +63656,32 @@
         <v>2.65000009536743</v>
       </c>
       <c r="H2434" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2435" t="n">
+        <v>61008</v>
+      </c>
+      <c r="C2435" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2435" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="H2435" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G3" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269636154175</v>
+        <v>7.41269540786743</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007923126221</v>
+        <v>7.42007827758789</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G7" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G12" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.56503295898438</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52344274520874</v>
+        <v>7.52344226837158</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G15" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G16" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302165985107</v>
+        <v>7.31302213668823</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G19" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.3585262298584</v>
       </c>
       <c r="G20" t="n">
-        <v>7.36101245880127</v>
+        <v>7.36101293563843</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G22" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484449386597</v>
+        <v>7.43484497070312</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G25" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G31" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054536819458</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437692642212</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.47914361953735</v>
+        <v>7.4791431427002</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.47914361953735</v>
+        <v>7.4791431427002</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.70583438873291</v>
       </c>
       <c r="G36" t="n">
-        <v>7.63419055938721</v>
+        <v>7.63419103622437</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G37" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G40" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820991516113</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.47914361953735</v>
+        <v>7.4791431427002</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437692642212</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568618774414</v>
+        <v>7.85568523406982</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568618774414</v>
+        <v>7.85568523406982</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G70" t="n">
-        <v>7.86306810379028</v>
+        <v>7.8630690574646</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86306810379028</v>
+        <v>7.8630690574646</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.94428396224976</v>
+        <v>7.94428300857544</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G80" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G81" t="n">
-        <v>7.66372203826904</v>
+        <v>7.66372299194336</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80400228500366</v>
+        <v>7.80400323867798</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830093383789</v>
+        <v>7.84830188751221</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G94" t="n">
-        <v>7.80400228500366</v>
+        <v>7.80400323867798</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755359649658</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77447080612183</v>
+        <v>7.77446985244751</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755359649658</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.78092670440674</v>
       </c>
       <c r="G100" t="n">
-        <v>7.69325542449951</v>
+        <v>7.69325494766235</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G101" t="n">
-        <v>7.73017263412476</v>
+        <v>7.73017168045044</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755359649658</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G111" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G112" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755359649658</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755359649658</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755359649658</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G117" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G120" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G125" t="n">
-        <v>7.66372203826904</v>
+        <v>7.66372299194336</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G129" t="n">
-        <v>7.73017263412476</v>
+        <v>7.73017168045044</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G130" t="n">
-        <v>7.73017263412476</v>
+        <v>7.73017168045044</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67110586166382</v>
+        <v>7.6711049079895</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.54625988006592</v>
       </c>
       <c r="G138" t="n">
-        <v>7.50867652893066</v>
+        <v>7.50867605209351</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G142" t="n">
-        <v>7.5825080871582</v>
+        <v>7.58250761032104</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G144" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820991516113</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G152" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820991516113</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.60258007049561</v>
       </c>
       <c r="G155" t="n">
-        <v>7.55297470092773</v>
+        <v>7.55297517776489</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G162" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540498733521</v>
+        <v>7.71540403366089</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G169" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G170" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540498733521</v>
+        <v>7.71540403366089</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G174" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820991516113</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727430343628</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633916854858</v>
+        <v>7.6563401222229</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G179" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820991516113</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559183120728</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G184" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820991516113</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G187" t="n">
-        <v>7.5825080871582</v>
+        <v>7.58250761032104</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.47116661071777</v>
       </c>
       <c r="G191" t="n">
-        <v>7.4496111869812</v>
+        <v>7.44961166381836</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G193" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G194" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G195" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G196" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054536819458</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G197" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054536819458</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G198" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G199" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007923126221</v>
+        <v>7.42007827758789</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G205" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G208" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G210" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G213" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G214" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G219" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232124328613</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G229" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G239" t="n">
-        <v>7.67848873138428</v>
+        <v>7.67848825454712</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.45699405670166</v>
+        <v>7.45699310302734</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082609176636</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G249" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G253" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G254" t="n">
-        <v>7.38316249847412</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624624252319</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241468429565</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.23549938201904</v>
+        <v>7.23550033569336</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.15201854705811</v>
       </c>
       <c r="G283" t="n">
-        <v>7.19858312606812</v>
+        <v>7.19858264923096</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.23549938201904</v>
+        <v>7.23550033569336</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.15201854705811</v>
       </c>
       <c r="G285" t="n">
-        <v>7.19858312606812</v>
+        <v>7.19858264923096</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30933046340942</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G287" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G288" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G289" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G290" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G291" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G292" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G293" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G294" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G295" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G296" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G297" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G298" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G299" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325784683228</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G301" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G302" t="n">
-        <v>7.08783531188965</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G304" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G305" t="n">
-        <v>7.08783531188965</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G306" t="n">
-        <v>6.97708892822266</v>
+        <v>6.9770884513855</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325784683228</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G308" t="n">
-        <v>6.97708892822266</v>
+        <v>6.9770884513855</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G309" t="n">
-        <v>6.97708892822266</v>
+        <v>6.9770884513855</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G311" t="n">
-        <v>6.97708892822266</v>
+        <v>6.9770884513855</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325784683228</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325784683228</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325784683228</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867847442627</v>
+        <v>6.71867799758911</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.63575077056885</v>
       </c>
       <c r="G320" t="n">
-        <v>6.79250907897949</v>
+        <v>6.79250955581665</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G321" t="n">
-        <v>6.75559377670288</v>
+        <v>6.75559329986572</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G322" t="n">
-        <v>6.75559377670288</v>
+        <v>6.75559329986572</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.35415077209473</v>
       </c>
       <c r="G323" t="n">
-        <v>6.57101488113403</v>
+        <v>6.57101535797119</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.60793018341064</v>
+        <v>6.60792970657349</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G325" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G329" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G330" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G334" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.30721664428711</v>
       </c>
       <c r="G335" t="n">
-        <v>6.53409814834595</v>
+        <v>6.53409862518311</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G336" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G337" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G338" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G339" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G340" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G341" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G342" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G344" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G345" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G349" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G351" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G352" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G353" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G354" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G355" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G356" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G357" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G359" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G360" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G361" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G362" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G364" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G366" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G367" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G368" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G369" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G370" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G371" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G372" t="n">
-        <v>6.20185661315918</v>
+        <v>6.20185565948486</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G373" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G378" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G379" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G380" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G381" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G382" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G383" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G384" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G385" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G386" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G387" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G388" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G392" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G394" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G395" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G396" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G398" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G399" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G401" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G403" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G404" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G406" t="n">
-        <v>6.1280255317688</v>
+        <v>6.12802505493164</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G410" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G411" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G412" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G414" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G421" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G422" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G423" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G424" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G426" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811992645264</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G429" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G432" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G434" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.97868299484253</v>
       </c>
       <c r="G439" t="n">
-        <v>6.27568817138672</v>
+        <v>6.27568769454956</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.97868299484253</v>
       </c>
       <c r="G440" t="n">
-        <v>6.27568817138672</v>
+        <v>6.27568769454956</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G443" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G445" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G448" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G449" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G450" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G451" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G452" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G454" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G455" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G457" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G458" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811992645264</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G461" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G463" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G465" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G466" t="n">
-        <v>5.83269786834717</v>
+        <v>5.83269834518433</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G469" t="n">
-        <v>5.72195053100586</v>
+        <v>5.72195100784302</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811992645264</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G472" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G473" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G474" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G475" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G476" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G477" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G478" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811944961548</v>
+        <v>5.64811992645264</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737211227417</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G482" t="n">
-        <v>5.46354055404663</v>
+        <v>5.46354007720947</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587648391724</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587648391724</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G519" t="n">
-        <v>5.28634357452393</v>
+        <v>5.28634405136108</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G520" t="n">
-        <v>5.21251249313354</v>
+        <v>5.21251201629639</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G521" t="n">
-        <v>5.28634357452393</v>
+        <v>5.28634405136108</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.83350801467896</v>
       </c>
       <c r="G524" t="n">
-        <v>5.37494277954102</v>
+        <v>5.37494230270386</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G525" t="n">
-        <v>5.43400716781616</v>
+        <v>5.43400764465332</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G526" t="n">
-        <v>5.46354055404663</v>
+        <v>5.46354007720947</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737211227417</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G530" t="n">
-        <v>5.65550327301025</v>
+        <v>5.6555027961731</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G532" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G537" t="n">
-        <v>5.65550327301025</v>
+        <v>5.6555027961731</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.17142820358276</v>
       </c>
       <c r="G539" t="n">
-        <v>5.6407356262207</v>
+        <v>5.64073610305786</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G540" t="n">
-        <v>5.5816707611084</v>
+        <v>5.58167123794556</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.50783967971802</v>
+        <v>5.50783920288086</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G542" t="n">
-        <v>5.47830724716187</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G545" t="n">
-        <v>5.47830724716187</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G546" t="n">
-        <v>5.47830724716187</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G550" t="n">
-        <v>5.34540939331055</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.48405265808105</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.48405265808105</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G570" t="n">
-        <v>5.69971656799316</v>
+        <v>5.69971704483032</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G571" t="n">
-        <v>5.77673959732056</v>
+        <v>5.77674007415771</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G572" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.82295370101929</v>
+        <v>5.82295417785645</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G574" t="n">
-        <v>5.77673959732056</v>
+        <v>5.77674007415771</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G575" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G576" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G577" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G578" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.11510801315308</v>
       </c>
       <c r="G579" t="n">
-        <v>5.83835887908936</v>
+        <v>5.8383584022522</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G580" t="n">
-        <v>5.85376405715942</v>
+        <v>5.85376358032227</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G582" t="n">
-        <v>5.79214382171631</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G583" t="n">
-        <v>5.77673959732056</v>
+        <v>5.77674007415771</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G592" t="n">
-        <v>5.65350389480591</v>
+        <v>5.65350341796875</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G596" t="n">
-        <v>5.53026628494263</v>
+        <v>5.53026580810547</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.7396411895752</v>
       </c>
       <c r="G597" t="n">
-        <v>5.53026628494263</v>
+        <v>5.53026580810547</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G603" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G606" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G607" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.30785322189331</v>
       </c>
       <c r="G608" t="n">
-        <v>5.17595911026001</v>
+        <v>5.17595863342285</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G609" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G610" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G611" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G621" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G640" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G642" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G644" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G645" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G646" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G647" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G648" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G649" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G650" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.42049312591553</v>
       </c>
       <c r="G652" t="n">
-        <v>5.26838636398315</v>
+        <v>5.26838684082031</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G653" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G654" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G655" t="n">
-        <v>5.25298166275024</v>
+        <v>5.25298261642456</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G656" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G657" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G659" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353137969971</v>
+        <v>5.08353090286255</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650787353516</v>
+        <v>5.00650835037231</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G669" t="n">
-        <v>5.1297459602356</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676898956299</v>
+        <v>5.20676851272583</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G673" t="n">
-        <v>5.1297459602356</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G675" t="n">
-        <v>5.25298166275024</v>
+        <v>5.25298261642456</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G676" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G677" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G678" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G679" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G680" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.42049312591553</v>
       </c>
       <c r="G681" t="n">
-        <v>5.26838636398315</v>
+        <v>5.26838684082031</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G682" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G683" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G684" t="n">
-        <v>5.25298166275024</v>
+        <v>5.25298261642456</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G685" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G691" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G697" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G698" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G700" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G701" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G702" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G703" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G704" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G706" t="n">
-        <v>5.36081552505493</v>
+        <v>5.36081504821777</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G712" t="n">
-        <v>5.31460046768188</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G715" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G718" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.40172004699707</v>
       </c>
       <c r="G719" t="n">
-        <v>5.25298166275024</v>
+        <v>5.25298261642456</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G720" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G721" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.38294696807861</v>
       </c>
       <c r="G723" t="n">
-        <v>5.23757743835449</v>
+        <v>5.23757791519165</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.36417293548584</v>
       </c>
       <c r="G725" t="n">
-        <v>5.22217273712158</v>
+        <v>5.22217321395874</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G726" t="n">
-        <v>5.1297459602356</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G727" t="n">
-        <v>5.1297459602356</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>6.12011909484863</v>
       </c>
       <c r="G728" t="n">
-        <v>5.02191209793091</v>
+        <v>5.02191257476807</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434125900269</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G731" t="n">
-        <v>5.1297459602356</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G732" t="n">
-        <v>5.1297459602356</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434125900269</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353137969971</v>
+        <v>5.08353090286255</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353137969971</v>
+        <v>5.08353090286255</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>6.00747919082642</v>
       </c>
       <c r="G742" t="n">
-        <v>4.92948532104492</v>
+        <v>4.92948484420776</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>6.00747919082642</v>
       </c>
       <c r="G743" t="n">
-        <v>4.92948532104492</v>
+        <v>4.92948484420776</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.83851909637451</v>
       </c>
       <c r="G746" t="n">
-        <v>4.79084300994873</v>
+        <v>4.79084348678589</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.65078496932983</v>
       </c>
       <c r="G749" t="n">
-        <v>4.63679695129395</v>
+        <v>4.63679647445679</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.63201189041138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.62139225006104</v>
+        <v>4.62139177322388</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.55691814422607</v>
       </c>
       <c r="G752" t="n">
-        <v>4.55977344512939</v>
+        <v>4.55977296829224</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.29409122467041</v>
       </c>
       <c r="G754" t="n">
-        <v>4.34410858154297</v>
+        <v>4.34410810470581</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.88196969032288</v>
+        <v>3.88196921348572</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468602180481</v>
+        <v>3.60468554496765</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G771" t="n">
-        <v>3.31199741363525</v>
+        <v>3.31199765205383</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.39672255516052</v>
+        <v>3.39672231674194</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G777" t="n">
-        <v>3.31199741363525</v>
+        <v>3.31199765205383</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306674003601</v>
+        <v>3.54306697845459</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G780" t="n">
-        <v>3.38902115821838</v>
+        <v>3.3890209197998</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G781" t="n">
-        <v>3.45063924789429</v>
+        <v>3.45063900947571</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G784" t="n">
-        <v>3.38902115821838</v>
+        <v>3.3890209197998</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G785" t="n">
-        <v>3.43523454666138</v>
+        <v>3.43523478507996</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.7741367816925</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035040855408</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G790" t="n">
-        <v>3.86656451225281</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.81264781951904</v>
+        <v>3.81264805793762</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.7741367816925</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G794" t="n">
-        <v>3.86656451225281</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.82035040855408</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818307876587</v>
+        <v>3.92818260192871</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G799" t="n">
-        <v>3.97439694404602</v>
+        <v>3.97439742088318</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291434288025</v>
+        <v>3.84291458129883</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.57131576538086</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01609230041504</v>
+        <v>4.01609182357788</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G812" t="n">
-        <v>4.1068058013916</v>
+        <v>4.10680532455444</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.1068058013916</v>
+        <v>4.10680532455444</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G820" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G822" t="n">
-        <v>4.27173614501953</v>
+        <v>4.27173662185669</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G826" t="n">
-        <v>4.25524377822876</v>
+        <v>4.25524425506592</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G828" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G833" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G835" t="n">
-        <v>4.1397910118103</v>
+        <v>4.13979053497314</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G836" t="n">
-        <v>4.1397910118103</v>
+        <v>4.13979053497314</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G838" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G846" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G849" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G851" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G852" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G853" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G854" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G855" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G856" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G857" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G858" t="n">
-        <v>4.1397910118103</v>
+        <v>4.13979053497314</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G859" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G861" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G862" t="n">
-        <v>4.25524377822876</v>
+        <v>4.25524425506592</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G863" t="n">
-        <v>4.25524377822876</v>
+        <v>4.25524425506592</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G864" t="n">
-        <v>4.25524377822876</v>
+        <v>4.25524425506592</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G865" t="n">
-        <v>4.27173614501953</v>
+        <v>4.27173662185669</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G868" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G872" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G873" t="n">
-        <v>4.25524377822876</v>
+        <v>4.25524425506592</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G876" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G877" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G878" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G879" t="n">
-        <v>4.25524377822876</v>
+        <v>4.25524425506592</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G880" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G883" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G884" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G886" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G889" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G891" t="n">
-        <v>4.1068058013916</v>
+        <v>4.10680532455444</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258562088013</v>
+        <v>4.03258466720581</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G893" t="n">
-        <v>4.04083204269409</v>
+        <v>4.04083156585693</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.54315614700317</v>
       </c>
       <c r="G896" t="n">
-        <v>3.99135231971741</v>
+        <v>3.99135279655457</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959993362427</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959993362427</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G901" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G903" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.89239263534546</v>
+        <v>3.89239311218262</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.41174221038818</v>
       </c>
       <c r="G905" t="n">
-        <v>3.87590026855469</v>
+        <v>3.87589979171753</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168032646179</v>
+        <v>3.80168056488037</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G911" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G912" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G913" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G915" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G919" t="n">
-        <v>3.3151319026947</v>
+        <v>3.31513166427612</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G920" t="n">
-        <v>3.3151319026947</v>
+        <v>3.31513166427612</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G924" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G925" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G927" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G932" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G934" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G937" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G938" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G940" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G941" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G942" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G943" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G945" t="n">
-        <v>3.66148781776428</v>
+        <v>3.66148805618286</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G946" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G952" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G953" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G954" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G958" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G959" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G961" t="n">
-        <v>3.83466720581055</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959993362427</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G964" t="n">
-        <v>3.96661329269409</v>
+        <v>3.96661281585693</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96661329269409</v>
+        <v>3.96661281585693</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85940742492676</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.85940742492676</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G972" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G973" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G974" t="n">
-        <v>3.83466720581055</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992746353149</v>
+        <v>3.80992770195007</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G978" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G979" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G985" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G991" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G992" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992746353149</v>
+        <v>3.80992770195007</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G994" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G995" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921420097351</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285709381104</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220108032227</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921420097351</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694082260132</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.83466720581055</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.34603595733643</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.81817412376404</v>
+        <v>3.81817436218262</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>4.3554220199585</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.82642030715942</v>
+        <v>3.826420545578</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.66148781776428</v>
+        <v>3.66148805618286</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.66148781776428</v>
+        <v>3.66148805618286</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.62850284576416</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.08320808410645</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.5872688293457</v>
+        <v>3.58726906776428</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077574729919</v>
+        <v>3.57077598571777</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.38110423088074</v>
+        <v>3.38110399246216</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.34811758995056</v>
+        <v>3.34811735153198</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285709381104</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.34811758995056</v>
+        <v>3.34811735153198</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493963241577</v>
+        <v>3.17493915557861</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247350692749</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247350692749</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721324920654</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721324920654</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493963241577</v>
+        <v>3.17493915557861</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.05124044418335</v>
+        <v>3.05124068260193</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.59510111808777</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.15844678878784</v>
+        <v>3.15844655036926</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.05124044418335</v>
+        <v>3.05124068260193</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.36043310165405</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.95228123664856</v>
+        <v>2.95228099822998</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.93578815460205</v>
+        <v>2.93578791618347</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.32288694381714</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.91929531097412</v>
+        <v>2.91929507255554</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.93578815460205</v>
+        <v>2.93578791618347</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.43552708625793</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.01825404167175</v>
+        <v>3.01825428009033</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.07598066329956</v>
+        <v>3.07598042488098</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.05124044418335</v>
+        <v>3.05124068260193</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.07598066329956</v>
+        <v>3.07598042488098</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.38859295845032</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.97702026367188</v>
+        <v>2.97702050209045</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.41675400733948</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.00176119804382</v>
+        <v>3.00176095962524</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.05124044418335</v>
+        <v>3.05124068260193</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.05124044418335</v>
+        <v>3.05124068260193</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.38859295845032</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.97702026367188</v>
+        <v>2.97702050209045</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.43552708625793</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.01825404167175</v>
+        <v>3.01825428009033</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.47307395935059</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.05124044418335</v>
+        <v>3.05124068260193</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.35104703903198</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.94403481483459</v>
+        <v>2.94403505325317</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.38110423088074</v>
+        <v>3.38110399246216</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.47181749343872</v>
+        <v>3.47181725502014</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.96118092536926</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.48006319999695</v>
+        <v>3.48006296157837</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -63682,6 +63682,32 @@
         <v>2.63000011444092</v>
       </c>
       <c r="H2435" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2436" t="n">
+        <v>5926</v>
+      </c>
+      <c r="C2436" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="D2436" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E2436" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2436" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="G2436" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="H2436" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G2" t="n">
-        <v>7.36839580535889</v>
+        <v>7.36839628219604</v>
       </c>
       <c r="H2" t="n">
         <v>8309</v>
@@ -456,7 +456,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G3" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H3" t="n">
         <v>6711</v>
@@ -485,7 +485,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269588470459</v>
+        <v>7.41269540786743</v>
       </c>
       <c r="H4" t="n">
         <v>14488</v>
@@ -543,7 +543,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H6" t="n">
         <v>3089</v>
@@ -572,7 +572,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G7" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H8" t="n">
         <v>532</v>
@@ -659,7 +659,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H10" t="n">
         <v>1917</v>
@@ -688,7 +688,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G11" t="n">
-        <v>7.36839580535889</v>
+        <v>7.36839628219604</v>
       </c>
       <c r="H11" t="n">
         <v>1384</v>
@@ -717,7 +717,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G12" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H12" t="n">
         <v>1065</v>
@@ -775,7 +775,7 @@
         <v>9.56503295898438</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52344274520874</v>
+        <v>7.52344226837158</v>
       </c>
       <c r="H14" t="n">
         <v>532</v>
@@ -804,7 +804,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G15" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H15" t="n">
         <v>1384</v>
@@ -833,7 +833,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G16" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H16" t="n">
         <v>213</v>
@@ -862,7 +862,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H17" t="n">
         <v>106</v>
@@ -920,7 +920,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G19" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H19" t="n">
         <v>7776</v>
@@ -949,7 +949,7 @@
         <v>9.3585262298584</v>
       </c>
       <c r="G20" t="n">
-        <v>7.36101198196411</v>
+        <v>7.36101293563843</v>
       </c>
       <c r="H20" t="n">
         <v>1065</v>
@@ -978,7 +978,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512378692627</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H21" t="n">
         <v>3302</v>
@@ -1007,7 +1007,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G22" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H22" t="n">
         <v>2450</v>
@@ -1036,7 +1036,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484449386597</v>
+        <v>7.43484497070312</v>
       </c>
       <c r="H23" t="n">
         <v>1065</v>
@@ -1065,7 +1065,7 @@
         <v>9.44300556182861</v>
       </c>
       <c r="G24" t="n">
-        <v>7.42746067047119</v>
+        <v>7.42745971679688</v>
       </c>
       <c r="H24" t="n">
         <v>319</v>
@@ -1094,7 +1094,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G25" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H25" t="n">
         <v>1384</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H26" t="n">
         <v>4154</v>
@@ -1152,7 +1152,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H27" t="n">
         <v>639</v>
@@ -1181,7 +1181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G31" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054536819458</v>
       </c>
       <c r="H31" t="n">
         <v>2237</v>
@@ -1297,7 +1297,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437644958496</v>
+        <v>7.46437788009644</v>
       </c>
       <c r="H32" t="n">
         <v>4580</v>
@@ -1326,7 +1326,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H33" t="n">
         <v>426</v>
@@ -1355,7 +1355,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>9.70583438873291</v>
       </c>
       <c r="G36" t="n">
-        <v>7.63419055938721</v>
+        <v>7.63419151306152</v>
       </c>
       <c r="H36" t="n">
         <v>3196</v>
@@ -1442,7 +1442,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G37" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H37" t="n">
         <v>3089</v>
@@ -1471,7 +1471,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H38" t="n">
         <v>21413</v>
@@ -1500,7 +1500,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H39" t="n">
         <v>11186</v>
@@ -1529,7 +1529,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G40" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H40" t="n">
         <v>1598</v>
@@ -1558,7 +1558,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H41" t="n">
         <v>15021</v>
@@ -1587,7 +1587,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H42" t="n">
         <v>12784</v>
@@ -1616,7 +1616,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H43" t="n">
         <v>5326</v>
@@ -1645,7 +1645,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H44" t="n">
         <v>12357</v>
@@ -1732,7 +1732,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H47" t="n">
         <v>3089</v>
@@ -1761,7 +1761,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H48" t="n">
         <v>3941</v>
@@ -1819,7 +1819,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H50" t="n">
         <v>2556</v>
@@ -1848,7 +1848,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H51" t="n">
         <v>13103</v>
@@ -1877,7 +1877,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437644958496</v>
+        <v>7.46437788009644</v>
       </c>
       <c r="H52" t="n">
         <v>2982</v>
@@ -1906,7 +1906,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H53" t="n">
         <v>7776</v>
@@ -1935,7 +1935,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H54" t="n">
         <v>319</v>
@@ -1964,7 +1964,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H55" t="n">
         <v>21306</v>
@@ -1993,7 +1993,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H56" t="n">
         <v>4261</v>
@@ -2022,7 +2022,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G57" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H57" t="n">
         <v>9694</v>
@@ -2051,7 +2051,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G58" t="n">
-        <v>7.64895725250244</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H58" t="n">
         <v>11186</v>
@@ -2080,7 +2080,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H59" t="n">
         <v>106</v>
@@ -2109,7 +2109,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G60" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H60" t="n">
         <v>639</v>
@@ -2138,7 +2138,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G61" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H61" t="n">
         <v>9481</v>
@@ -2167,7 +2167,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H62" t="n">
         <v>1065</v>
@@ -2196,7 +2196,7 @@
         <v>9.94050121307373</v>
       </c>
       <c r="G63" t="n">
-        <v>7.81876945495605</v>
+        <v>7.8187689781189</v>
       </c>
       <c r="H63" t="n">
         <v>16725</v>
@@ -2225,7 +2225,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970411300659</v>
+        <v>7.75970315933228</v>
       </c>
       <c r="H64" t="n">
         <v>12570</v>
@@ -2254,7 +2254,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568618774414</v>
       </c>
       <c r="H65" t="n">
         <v>22052</v>
@@ -2283,7 +2283,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568618774414</v>
       </c>
       <c r="H66" t="n">
         <v>4261</v>
@@ -2312,7 +2312,7 @@
         <v>10.1188478469849</v>
       </c>
       <c r="G67" t="n">
-        <v>7.95904970169067</v>
+        <v>7.95904922485352</v>
       </c>
       <c r="H67" t="n">
         <v>7137</v>
@@ -2341,7 +2341,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G68" t="n">
-        <v>7.8704514503479</v>
+        <v>7.87045097351074</v>
       </c>
       <c r="H68" t="n">
         <v>1704</v>
@@ -2370,7 +2370,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H69" t="n">
         <v>2343</v>
@@ -2399,7 +2399,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G70" t="n">
-        <v>7.86306953430176</v>
+        <v>7.86306810379028</v>
       </c>
       <c r="H70" t="n">
         <v>8842</v>
@@ -2428,7 +2428,7 @@
         <v>9.99682140350342</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86306953430176</v>
+        <v>7.86306810379028</v>
       </c>
       <c r="H71" t="n">
         <v>4580</v>
@@ -2486,7 +2486,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.94428396224976</v>
+        <v>7.94428300857544</v>
       </c>
       <c r="H73" t="n">
         <v>5326</v>
@@ -2573,7 +2573,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H76" t="n">
         <v>852</v>
@@ -2631,7 +2631,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G78" t="n">
-        <v>7.8704514503479</v>
+        <v>7.87045097351074</v>
       </c>
       <c r="H78" t="n">
         <v>639</v>
@@ -2660,7 +2660,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.78923606872559</v>
+        <v>7.7892370223999</v>
       </c>
       <c r="H79" t="n">
         <v>5007</v>
@@ -2689,7 +2689,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G80" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H80" t="n">
         <v>18430</v>
@@ -2718,7 +2718,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G81" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372299194336</v>
       </c>
       <c r="H81" t="n">
         <v>6072</v>
@@ -2747,7 +2747,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H82" t="n">
         <v>4367</v>
@@ -2776,7 +2776,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H84" t="n">
         <v>10653</v>
@@ -2863,7 +2863,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H86" t="n">
         <v>33664</v>
@@ -2892,7 +2892,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80400276184082</v>
+        <v>7.80400323867798</v>
       </c>
       <c r="H87" t="n">
         <v>2130</v>
@@ -2921,7 +2921,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830236434937</v>
+        <v>7.84830188751221</v>
       </c>
       <c r="H88" t="n">
         <v>2982</v>
@@ -2950,7 +2950,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H89" t="n">
         <v>15021</v>
@@ -2979,7 +2979,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H90" t="n">
         <v>5859</v>
@@ -3008,7 +3008,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H91" t="n">
         <v>2450</v>
@@ -3037,7 +3037,7 @@
         <v>9.93111419677734</v>
       </c>
       <c r="G92" t="n">
-        <v>7.81138563156128</v>
+        <v>7.81138610839844</v>
       </c>
       <c r="H92" t="n">
         <v>7457</v>
@@ -3066,7 +3066,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H93" t="n">
         <v>958</v>
@@ -3095,7 +3095,7 @@
         <v>9.92172718048096</v>
       </c>
       <c r="G94" t="n">
-        <v>7.80400276184082</v>
+        <v>7.80400323867798</v>
       </c>
       <c r="H94" t="n">
         <v>3728</v>
@@ -3124,7 +3124,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H95" t="n">
         <v>2556</v>
@@ -3153,7 +3153,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H96" t="n">
         <v>1598</v>
@@ -3182,7 +3182,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H97" t="n">
         <v>2556</v>
@@ -3211,7 +3211,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77447080612183</v>
+        <v>7.77446985244751</v>
       </c>
       <c r="H98" t="n">
         <v>1278</v>
@@ -3240,7 +3240,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H99" t="n">
         <v>11612</v>
@@ -3269,7 +3269,7 @@
         <v>9.78092670440674</v>
       </c>
       <c r="G100" t="n">
-        <v>7.69325542449951</v>
+        <v>7.69325590133667</v>
       </c>
       <c r="H100" t="n">
         <v>1811</v>
@@ -3298,7 +3298,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G101" t="n">
-        <v>7.7301721572876</v>
+        <v>7.73017168045044</v>
       </c>
       <c r="H101" t="n">
         <v>1491</v>
@@ -3327,7 +3327,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H102" t="n">
         <v>1065</v>
@@ -3356,7 +3356,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H103" t="n">
         <v>852</v>
@@ -3385,7 +3385,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H104" t="n">
         <v>1065</v>
@@ -3414,7 +3414,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G106" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H106" t="n">
         <v>852</v>
@@ -3472,7 +3472,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G107" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H107" t="n">
         <v>3302</v>
@@ -3501,7 +3501,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G108" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G109" t="n">
-        <v>7.70802116394043</v>
+        <v>7.70802211761475</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H110" t="n">
         <v>319</v>
@@ -3588,7 +3588,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G111" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H111" t="n">
         <v>4794</v>
@@ -3617,7 +3617,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G112" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H113" t="n">
         <v>2237</v>
@@ -3675,7 +3675,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H114" t="n">
         <v>4687</v>
@@ -3704,7 +3704,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H115" t="n">
         <v>213</v>
@@ -3733,7 +3733,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H116" t="n">
         <v>319</v>
@@ -3762,7 +3762,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G117" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H117" t="n">
         <v>319</v>
@@ -3791,7 +3791,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063829421997</v>
+        <v>7.70063781738281</v>
       </c>
       <c r="H118" t="n">
         <v>50070</v>
@@ -3820,7 +3820,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G119" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H119" t="n">
         <v>5326</v>
@@ -3849,7 +3849,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G120" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H120" t="n">
         <v>852</v>
@@ -3878,7 +3878,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H121" t="n">
         <v>4580</v>
@@ -3907,7 +3907,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H122" t="n">
         <v>213</v>
@@ -3936,7 +3936,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278928756714</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H124" t="n">
         <v>7137</v>
@@ -3994,7 +3994,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G125" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372299194336</v>
       </c>
       <c r="H125" t="n">
         <v>426</v>
@@ -4023,7 +4023,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H126" t="n">
         <v>426</v>
@@ -4052,7 +4052,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G127" t="n">
-        <v>7.64895725250244</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H127" t="n">
         <v>1384</v>
@@ -4081,7 +4081,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G128" t="n">
-        <v>7.64895725250244</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H128" t="n">
         <v>2130</v>
@@ -4110,7 +4110,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G129" t="n">
-        <v>7.7301721572876</v>
+        <v>7.73017168045044</v>
       </c>
       <c r="H129" t="n">
         <v>1065</v>
@@ -4139,7 +4139,7 @@
         <v>9.82786083221436</v>
       </c>
       <c r="G130" t="n">
-        <v>7.7301721572876</v>
+        <v>7.73017168045044</v>
       </c>
       <c r="H130" t="n">
         <v>745</v>
@@ -4168,7 +4168,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H131" t="n">
         <v>1811</v>
@@ -4197,7 +4197,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G132" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H132" t="n">
         <v>1704</v>
@@ -4226,7 +4226,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G133" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H133" t="n">
         <v>2769</v>
@@ -4255,7 +4255,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67110538482666</v>
+        <v>7.6711049079895</v>
       </c>
       <c r="H134" t="n">
         <v>852</v>
@@ -4284,7 +4284,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H135" t="n">
         <v>1384</v>
@@ -4313,7 +4313,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512378692627</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H136" t="n">
         <v>2556</v>
@@ -4342,7 +4342,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H137" t="n">
         <v>10440</v>
@@ -4371,7 +4371,7 @@
         <v>9.54625988006592</v>
       </c>
       <c r="G138" t="n">
-        <v>7.50867652893066</v>
+        <v>7.50867605209351</v>
       </c>
       <c r="H138" t="n">
         <v>3302</v>
@@ -4400,7 +4400,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H139" t="n">
         <v>6498</v>
@@ -4516,7 +4516,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H143" t="n">
         <v>8629</v>
@@ -4545,7 +4545,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G144" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H144" t="n">
         <v>213</v>
@@ -4574,7 +4574,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H145" t="n">
         <v>1065</v>
@@ -4603,7 +4603,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H146" t="n">
         <v>106</v>
@@ -4632,7 +4632,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H149" t="n">
         <v>2663</v>
@@ -4719,7 +4719,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H150" t="n">
         <v>2769</v>
@@ -4748,7 +4748,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H151" t="n">
         <v>12997</v>
@@ -4777,7 +4777,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G152" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H152" t="n">
         <v>13742</v>
@@ -4806,7 +4806,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G153" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H153" t="n">
         <v>639</v>
@@ -4893,7 +4893,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H156" t="n">
         <v>426</v>
@@ -4922,7 +4922,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G157" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H157" t="n">
         <v>2343</v>
@@ -4951,7 +4951,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G158" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G159" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H159" t="n">
         <v>22691</v>
@@ -5009,7 +5009,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942481994629</v>
+        <v>7.61942338943481</v>
       </c>
       <c r="H160" t="n">
         <v>26953</v>
@@ -5038,7 +5038,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942481994629</v>
+        <v>7.61942338943481</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G162" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H162" t="n">
         <v>745</v>
@@ -5096,7 +5096,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063829421997</v>
+        <v>7.70063781738281</v>
       </c>
       <c r="H163" t="n">
         <v>1171</v>
@@ -5125,7 +5125,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G164" t="n">
-        <v>7.64895725250244</v>
+        <v>7.64895677566528</v>
       </c>
       <c r="H164" t="n">
         <v>1384</v>
@@ -5154,7 +5154,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H165" t="n">
         <v>2343</v>
@@ -5183,7 +5183,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540403366089</v>
       </c>
       <c r="H167" t="n">
         <v>745</v>
@@ -5241,7 +5241,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H168" t="n">
         <v>46022</v>
@@ -5270,7 +5270,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G169" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H169" t="n">
         <v>4367</v>
@@ -5299,7 +5299,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G170" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H170" t="n">
         <v>106</v>
@@ -5328,7 +5328,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H171" t="n">
         <v>21519</v>
@@ -5357,7 +5357,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587207794189</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540403366089</v>
       </c>
       <c r="H173" t="n">
         <v>5433</v>
@@ -5415,7 +5415,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G174" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H174" t="n">
         <v>32918</v>
@@ -5444,7 +5444,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H175" t="n">
         <v>1278</v>
@@ -5502,7 +5502,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65633916854858</v>
       </c>
       <c r="H177" t="n">
         <v>5859</v>
@@ -5531,7 +5531,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H178" t="n">
         <v>10653</v>
@@ -5560,7 +5560,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G179" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H179" t="n">
         <v>13210</v>
@@ -5589,7 +5589,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H180" t="n">
         <v>11079</v>
@@ -5618,7 +5618,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774187088013</v>
+        <v>7.56774234771729</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H182" t="n">
         <v>6072</v>
@@ -5676,7 +5676,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559135437012</v>
+        <v>7.54559230804443</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G184" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H184" t="n">
         <v>7457</v>
@@ -5734,7 +5734,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49391031265259</v>
+        <v>7.49390983581543</v>
       </c>
       <c r="H185" t="n">
         <v>11718</v>
@@ -5850,7 +5850,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512378692627</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H189" t="n">
         <v>106</v>
@@ -5879,7 +5879,7 @@
         <v>9.61196708679199</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56035852432251</v>
+        <v>7.56035757064819</v>
       </c>
       <c r="H190" t="n">
         <v>1065</v>
@@ -5908,7 +5908,7 @@
         <v>9.47116661071777</v>
       </c>
       <c r="G191" t="n">
-        <v>7.44961071014404</v>
+        <v>7.44961166381836</v>
       </c>
       <c r="H191" t="n">
         <v>106</v>
@@ -5966,7 +5966,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G193" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H193" t="n">
         <v>9481</v>
@@ -5995,7 +5995,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G194" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H194" t="n">
         <v>8735</v>
@@ -6024,7 +6024,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G195" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H195" t="n">
         <v>3196</v>
@@ -6053,7 +6053,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G196" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054536819458</v>
       </c>
       <c r="H196" t="n">
         <v>12784</v>
@@ -6082,7 +6082,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G197" t="n">
-        <v>7.3905463218689</v>
+        <v>7.39054536819458</v>
       </c>
       <c r="H197" t="n">
         <v>9055</v>
@@ -6111,7 +6111,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G198" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H198" t="n">
         <v>10653</v>
@@ -6140,7 +6140,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G199" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H199" t="n">
         <v>15553</v>
@@ -6169,7 +6169,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G205" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H205" t="n">
         <v>106</v>
@@ -6343,7 +6343,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H206" t="n">
         <v>5220</v>
@@ -6372,7 +6372,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H207" t="n">
         <v>3728</v>
@@ -6401,7 +6401,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G208" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H208" t="n">
         <v>2130</v>
@@ -6430,7 +6430,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H209" t="n">
         <v>319</v>
@@ -6459,7 +6459,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G210" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H210" t="n">
         <v>1171</v>
@@ -6546,7 +6546,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G213" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H213" t="n">
         <v>27379</v>
@@ -6575,7 +6575,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G214" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H214" t="n">
         <v>12357</v>
@@ -6633,7 +6633,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H216" t="n">
         <v>11612</v>
@@ -6662,7 +6662,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H217" t="n">
         <v>192826</v>
@@ -6691,7 +6691,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H218" t="n">
         <v>82563</v>
@@ -6720,7 +6720,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G219" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H219" t="n">
         <v>55504</v>
@@ -6749,7 +6749,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H220" t="n">
         <v>61683</v>
@@ -6836,7 +6836,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H223" t="n">
         <v>7883</v>
@@ -6865,7 +6865,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H224" t="n">
         <v>21519</v>
@@ -6894,7 +6894,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615184783936</v>
+        <v>7.82615375518799</v>
       </c>
       <c r="H225" t="n">
         <v>1491</v>
@@ -6923,7 +6923,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H226" t="n">
         <v>16086</v>
@@ -6952,7 +6952,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H227" t="n">
         <v>63174</v>
@@ -6981,7 +6981,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232076644897</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H228" t="n">
         <v>21200</v>
@@ -7010,7 +7010,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G229" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H229" t="n">
         <v>34623</v>
@@ -7039,7 +7039,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G230" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H230" t="n">
         <v>24076</v>
@@ -7068,7 +7068,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H231" t="n">
         <v>3089</v>
@@ -7097,7 +7097,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H232" t="n">
         <v>7883</v>
@@ -7126,7 +7126,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H233" t="n">
         <v>23970</v>
@@ -7155,7 +7155,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G234" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H234" t="n">
         <v>54864</v>
@@ -7184,7 +7184,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H235" t="n">
         <v>9055</v>
@@ -7213,7 +7213,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H236" t="n">
         <v>8203</v>
@@ -7242,7 +7242,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G237" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H237" t="n">
         <v>4794</v>
@@ -7271,7 +7271,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G238" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H238" t="n">
         <v>14062</v>
@@ -7300,7 +7300,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G239" t="n">
-        <v>7.67848825454712</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H239" t="n">
         <v>29829</v>
@@ -7329,7 +7329,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G240" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465812683105</v>
       </c>
       <c r="H240" t="n">
         <v>21413</v>
@@ -7358,7 +7358,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H241" t="n">
         <v>39630</v>
@@ -7387,7 +7387,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H242" t="n">
         <v>19495</v>
@@ -7416,7 +7416,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H243" t="n">
         <v>23650</v>
@@ -7445,7 +7445,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H244" t="n">
         <v>36967</v>
@@ -7503,7 +7503,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H246" t="n">
         <v>35688</v>
@@ -7532,7 +7532,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H247" t="n">
         <v>25674</v>
@@ -7561,7 +7561,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H248" t="n">
         <v>1598</v>
@@ -7590,7 +7590,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G249" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H249" t="n">
         <v>42400</v>
@@ -7619,7 +7619,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H250" t="n">
         <v>13742</v>
@@ -7648,7 +7648,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H251" t="n">
         <v>2982</v>
@@ -7677,7 +7677,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H252" t="n">
         <v>3089</v>
@@ -7706,7 +7706,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G253" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H253" t="n">
         <v>2769</v>
@@ -7735,7 +7735,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G254" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316345214844</v>
       </c>
       <c r="H254" t="n">
         <v>1065</v>
@@ -7764,7 +7764,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H255" t="n">
         <v>24502</v>
@@ -7793,7 +7793,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H256" t="n">
         <v>53586</v>
@@ -7822,7 +7822,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H258" t="n">
         <v>1384</v>
@@ -7880,7 +7880,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H259" t="n">
         <v>29296</v>
@@ -7909,7 +7909,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H260" t="n">
         <v>2343</v>
@@ -7938,7 +7938,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H261" t="n">
         <v>319</v>
@@ -7967,7 +7967,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H262" t="n">
         <v>14062</v>
@@ -7996,7 +7996,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H263" t="n">
         <v>1598</v>
@@ -8025,7 +8025,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H264" t="n">
         <v>532</v>
@@ -8054,7 +8054,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H265" t="n">
         <v>6498</v>
@@ -8083,7 +8083,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H266" t="n">
         <v>36114</v>
@@ -8112,7 +8112,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H267" t="n">
         <v>7457</v>
@@ -8141,7 +8141,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H268" t="n">
         <v>11825</v>
@@ -8170,7 +8170,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624719619751</v>
       </c>
       <c r="H269" t="n">
         <v>4474</v>
@@ -8199,7 +8199,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H270" t="n">
         <v>22478</v>
@@ -8228,7 +8228,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H271" t="n">
         <v>2130</v>
@@ -8257,7 +8257,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H272" t="n">
         <v>20880</v>
@@ -8286,7 +8286,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H273" t="n">
         <v>5326</v>
@@ -8315,7 +8315,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H274" t="n">
         <v>6072</v>
@@ -8344,7 +8344,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H275" t="n">
         <v>2663</v>
@@ -8373,7 +8373,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H276" t="n">
         <v>426</v>
@@ -8402,7 +8402,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H277" t="n">
         <v>19176</v>
@@ -8431,7 +8431,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H278" t="n">
         <v>532</v>
@@ -8460,7 +8460,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H279" t="n">
         <v>6392</v>
@@ -8489,7 +8489,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H280" t="n">
         <v>1171</v>
@@ -8518,7 +8518,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241516113281</v>
+        <v>7.27241563796997</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.23549890518188</v>
+        <v>7.23550033569336</v>
       </c>
       <c r="H282" t="n">
         <v>39097</v>
@@ -8605,7 +8605,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.23549890518188</v>
+        <v>7.23550033569336</v>
       </c>
       <c r="H284" t="n">
         <v>19389</v>
@@ -8663,7 +8663,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932998657227</v>
       </c>
       <c r="H286" t="n">
         <v>106</v>
@@ -8692,7 +8692,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G287" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H287" t="n">
         <v>7244</v>
@@ -8721,7 +8721,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G288" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H288" t="n">
         <v>1065</v>
@@ -8750,7 +8750,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G289" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H289" t="n">
         <v>745</v>
@@ -8779,7 +8779,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G290" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H290" t="n">
         <v>6818</v>
@@ -8808,7 +8808,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G291" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H291" t="n">
         <v>1065</v>
@@ -8837,7 +8837,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G292" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H292" t="n">
         <v>3728</v>
@@ -8866,7 +8866,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G293" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H293" t="n">
         <v>1917</v>
@@ -8895,7 +8895,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G294" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H294" t="n">
         <v>4474</v>
@@ -8924,7 +8924,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G295" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G296" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H296" t="n">
         <v>14595</v>
@@ -8982,7 +8982,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G297" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H297" t="n">
         <v>8629</v>
@@ -9011,7 +9011,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G298" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H298" t="n">
         <v>532</v>
@@ -9040,7 +9040,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G299" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.90325593948364</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H300" t="n">
         <v>23011</v>
@@ -9098,7 +9098,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G301" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475204467773</v>
       </c>
       <c r="H301" t="n">
         <v>2237</v>
@@ -9127,7 +9127,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G302" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H302" t="n">
         <v>4474</v>
@@ -9156,7 +9156,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400327682495</v>
+        <v>7.01400470733643</v>
       </c>
       <c r="H303" t="n">
         <v>639</v>
@@ -9185,7 +9185,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G304" t="n">
-        <v>7.16166877746582</v>
+        <v>7.1616678237915</v>
       </c>
       <c r="H304" t="n">
         <v>3941</v>
@@ -9214,7 +9214,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G305" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H305" t="n">
         <v>19282</v>
@@ -9272,7 +9272,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.90325593948364</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H307" t="n">
         <v>2130</v>
@@ -9359,7 +9359,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017362594604</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H310" t="n">
         <v>4048</v>
@@ -9417,7 +9417,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017362594604</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H312" t="n">
         <v>2663</v>
@@ -9446,7 +9446,7 @@
         <v>8.72961807250977</v>
       </c>
       <c r="G313" t="n">
-        <v>6.86634063720703</v>
+        <v>6.86634159088135</v>
       </c>
       <c r="H313" t="n">
         <v>5326</v>
@@ -9475,7 +9475,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017362594604</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H314" t="n">
         <v>51349</v>
@@ -9504,7 +9504,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.90325593948364</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H315" t="n">
         <v>958</v>
@@ -9533,7 +9533,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.90325593948364</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H316" t="n">
         <v>213</v>
@@ -9562,7 +9562,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017362594604</v>
+        <v>6.94017267227173</v>
       </c>
       <c r="H317" t="n">
         <v>54438</v>
@@ -9591,7 +9591,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.90325593948364</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H318" t="n">
         <v>27379</v>
@@ -9620,7 +9620,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867895126343</v>
+        <v>6.71867799758911</v>
       </c>
       <c r="H319" t="n">
         <v>12144</v>
@@ -9649,7 +9649,7 @@
         <v>8.63575077056885</v>
       </c>
       <c r="G320" t="n">
-        <v>6.79250907897949</v>
+        <v>6.79251003265381</v>
       </c>
       <c r="H320" t="n">
         <v>9907</v>
@@ -9765,7 +9765,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.6079306602478</v>
+        <v>6.60792970657349</v>
       </c>
       <c r="H324" t="n">
         <v>5859</v>
@@ -9794,7 +9794,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G325" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H325" t="n">
         <v>9161</v>
@@ -9852,7 +9852,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G327" t="n">
-        <v>6.3495192527771</v>
+        <v>6.34951972961426</v>
       </c>
       <c r="H327" t="n">
         <v>3089</v>
@@ -9881,7 +9881,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H328" t="n">
         <v>25568</v>
@@ -9910,7 +9910,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G329" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H329" t="n">
         <v>958</v>
@@ -9939,7 +9939,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G330" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H332" t="n">
         <v>4367</v>
@@ -10026,7 +10026,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H333" t="n">
         <v>6924</v>
@@ -10055,7 +10055,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G334" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H334" t="n">
         <v>2343</v>
@@ -10084,7 +10084,7 @@
         <v>8.30721664428711</v>
       </c>
       <c r="G335" t="n">
-        <v>6.53409767150879</v>
+        <v>6.53409814834595</v>
       </c>
       <c r="H335" t="n">
         <v>3089</v>
@@ -10113,7 +10113,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G336" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H336" t="n">
         <v>2556</v>
@@ -10142,7 +10142,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G337" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H337" t="n">
         <v>7563</v>
@@ -10171,7 +10171,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G338" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G339" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H339" t="n">
         <v>6285</v>
@@ -10229,7 +10229,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G340" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H340" t="n">
         <v>532</v>
@@ -10258,7 +10258,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G341" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H341" t="n">
         <v>5539</v>
@@ -10287,7 +10287,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G342" t="n">
-        <v>6.49718427658081</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H342" t="n">
         <v>2556</v>
@@ -10345,7 +10345,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G344" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H344" t="n">
         <v>3409</v>
@@ -10374,7 +10374,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G345" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G347" t="n">
-        <v>6.3495192527771</v>
+        <v>6.34951972961426</v>
       </c>
       <c r="H347" t="n">
         <v>852</v>
@@ -10461,7 +10461,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H348" t="n">
         <v>12677</v>
@@ -10490,7 +10490,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G349" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H349" t="n">
         <v>19389</v>
@@ -10519,7 +10519,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H350" t="n">
         <v>6605</v>
@@ -10548,7 +10548,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G351" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H351" t="n">
         <v>13316</v>
@@ -10577,7 +10577,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G352" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G356" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H356" t="n">
         <v>1065</v>
@@ -10722,7 +10722,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G357" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G361" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H361" t="n">
         <v>532</v>
@@ -11215,7 +11215,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H374" t="n">
         <v>2556</v>
@@ -11244,7 +11244,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H375" t="n">
         <v>3196</v>
@@ -11273,7 +11273,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G376" t="n">
-        <v>6.01727724075317</v>
+        <v>6.01727676391602</v>
       </c>
       <c r="H376" t="n">
         <v>213</v>
@@ -11302,7 +11302,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H377" t="n">
         <v>15340</v>
@@ -11331,7 +11331,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G378" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H378" t="n">
         <v>74147</v>
@@ -11360,7 +11360,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G379" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G384" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H384" t="n">
         <v>532</v>
@@ -11534,7 +11534,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G385" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H385" t="n">
         <v>532</v>
@@ -11563,7 +11563,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G386" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G387" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H387" t="n">
         <v>532</v>
@@ -11621,7 +11621,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G388" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110832214355</v>
       </c>
       <c r="H388" t="n">
         <v>2663</v>
@@ -11650,7 +11650,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.05419301986694</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H389" t="n">
         <v>3196</v>
@@ -11737,7 +11737,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G392" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H392" t="n">
         <v>9374</v>
@@ -11795,7 +11795,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G394" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H394" t="n">
         <v>22265</v>
@@ -11824,7 +11824,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G395" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H395" t="n">
         <v>28018</v>
@@ -11853,7 +11853,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G396" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H396" t="n">
         <v>32812</v>
@@ -11882,7 +11882,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G397" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H397" t="n">
         <v>7244</v>
@@ -11940,7 +11940,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G399" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H399" t="n">
         <v>18323</v>
@@ -11998,7 +11998,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G401" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H401" t="n">
         <v>958</v>
@@ -12085,7 +12085,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G404" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H404" t="n">
         <v>20454</v>
@@ -12230,7 +12230,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G409" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H409" t="n">
         <v>319</v>
@@ -12259,7 +12259,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G410" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H410" t="n">
         <v>9588</v>
@@ -12288,7 +12288,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G411" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H411" t="n">
         <v>106</v>
@@ -12317,7 +12317,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G412" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H412" t="n">
         <v>11292</v>
@@ -12346,7 +12346,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H413" t="n">
         <v>532</v>
@@ -12578,7 +12578,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G421" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H421" t="n">
         <v>3302</v>
@@ -12636,7 +12636,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G423" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H423" t="n">
         <v>2343</v>
@@ -12723,7 +12723,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G426" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H426" t="n">
         <v>3515</v>
@@ -12752,7 +12752,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G427" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H427" t="n">
         <v>22904</v>
@@ -12810,7 +12810,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G429" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H429" t="n">
         <v>7990</v>
@@ -12839,7 +12839,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G430" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H430" t="n">
         <v>2024</v>
@@ -12868,7 +12868,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G431" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H431" t="n">
         <v>13955</v>
@@ -12897,7 +12897,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G432" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H432" t="n">
         <v>7776</v>
@@ -12926,7 +12926,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G433" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H433" t="n">
         <v>5220</v>
@@ -12955,7 +12955,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G434" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H434" t="n">
         <v>6498</v>
@@ -13071,7 +13071,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G438" t="n">
-        <v>6.01727724075317</v>
+        <v>6.01727676391602</v>
       </c>
       <c r="H438" t="n">
         <v>1278</v>
@@ -13187,7 +13187,7 @@
         <v>7.46241617202759</v>
       </c>
       <c r="G442" t="n">
-        <v>5.86961507797241</v>
+        <v>5.86961460113525</v>
       </c>
       <c r="H442" t="n">
         <v>1491</v>
@@ -13216,7 +13216,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G443" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H443" t="n">
         <v>30149</v>
@@ -13245,7 +13245,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G444" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H444" t="n">
         <v>958</v>
@@ -13274,7 +13274,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G445" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H445" t="n">
         <v>5007</v>
@@ -13390,7 +13390,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G449" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H449" t="n">
         <v>4261</v>
@@ -13419,7 +13419,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G450" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H450" t="n">
         <v>5752</v>
@@ -13448,7 +13448,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G451" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H451" t="n">
         <v>8735</v>
@@ -13477,7 +13477,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G452" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H452" t="n">
         <v>16512</v>
@@ -13506,7 +13506,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G453" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H453" t="n">
         <v>2343</v>
@@ -13535,7 +13535,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G454" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H454" t="n">
         <v>2769</v>
@@ -13564,7 +13564,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G455" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H455" t="n">
         <v>7350</v>
@@ -13622,7 +13622,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G457" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H457" t="n">
         <v>20347</v>
@@ -13680,7 +13680,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G459" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H459" t="n">
         <v>3089</v>
@@ -13738,7 +13738,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G461" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H461" t="n">
         <v>106</v>
@@ -13767,7 +13767,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G462" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H462" t="n">
         <v>1065</v>
@@ -13796,7 +13796,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G463" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H463" t="n">
         <v>2556</v>
@@ -13854,7 +13854,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G465" t="n">
-        <v>5.79578256607056</v>
+        <v>5.7957820892334</v>
       </c>
       <c r="H465" t="n">
         <v>1065</v>
@@ -13883,7 +13883,7 @@
         <v>7.41548204421997</v>
       </c>
       <c r="G466" t="n">
-        <v>5.83269834518433</v>
+        <v>5.83269882202148</v>
       </c>
       <c r="H466" t="n">
         <v>3728</v>
@@ -14028,7 +14028,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G471" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H471" t="n">
         <v>2343</v>
@@ -14057,7 +14057,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G472" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H472" t="n">
         <v>106</v>
@@ -14086,7 +14086,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G473" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H473" t="n">
         <v>21626</v>
@@ -14115,7 +14115,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G474" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H474" t="n">
         <v>1917</v>
@@ -14144,7 +14144,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G475" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H475" t="n">
         <v>7670</v>
@@ -14173,7 +14173,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G476" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H476" t="n">
         <v>4900</v>
@@ -14202,7 +14202,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G477" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H477" t="n">
         <v>4900</v>
@@ -14231,7 +14231,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G478" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H478" t="n">
         <v>5539</v>
@@ -14289,7 +14289,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G480" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H480" t="n">
         <v>2130</v>
@@ -14492,7 +14492,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G487" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H487" t="n">
         <v>26846</v>
@@ -14521,7 +14521,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G488" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H488" t="n">
         <v>11931</v>
@@ -14550,7 +14550,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G489" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H489" t="n">
         <v>2556</v>
@@ -14579,7 +14579,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G490" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H490" t="n">
         <v>13849</v>
@@ -14695,7 +14695,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G494" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H494" t="n">
         <v>15873</v>
@@ -14811,7 +14811,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G498" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H498" t="n">
         <v>6392</v>
@@ -14840,7 +14840,7 @@
         <v>6.89921379089355</v>
       </c>
       <c r="G499" t="n">
-        <v>5.42662334442139</v>
+        <v>5.4266242980957</v>
       </c>
       <c r="H499" t="n">
         <v>106533</v>
@@ -14869,7 +14869,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G500" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H500" t="n">
         <v>50603</v>
@@ -14898,7 +14898,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G501" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H501" t="n">
         <v>18856</v>
@@ -14927,7 +14927,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587648391724</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H502" t="n">
         <v>12251</v>
@@ -14956,7 +14956,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G503" t="n">
-        <v>5.24204540252686</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H503" t="n">
         <v>20561</v>
@@ -15043,7 +15043,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587648391724</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H506" t="n">
         <v>11399</v>
@@ -15072,7 +15072,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G507" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H507" t="n">
         <v>45703</v>
@@ -15130,7 +15130,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G509" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H509" t="n">
         <v>39417</v>
@@ -15159,7 +15159,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G510" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H510" t="n">
         <v>33345</v>
@@ -15188,7 +15188,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G511" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H511" t="n">
         <v>12251</v>
@@ -15275,7 +15275,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G514" t="n">
-        <v>5.24204540252686</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H514" t="n">
         <v>35582</v>
@@ -15391,7 +15391,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24204540252686</v>
+        <v>5.2420449256897</v>
       </c>
       <c r="H518" t="n">
         <v>33451</v>
@@ -15449,7 +15449,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G520" t="n">
-        <v>5.21251201629639</v>
+        <v>5.21251249313354</v>
       </c>
       <c r="H520" t="n">
         <v>16619</v>
@@ -15565,7 +15565,7 @@
         <v>6.83350801467896</v>
       </c>
       <c r="G524" t="n">
-        <v>5.37494277954102</v>
+        <v>5.3749418258667</v>
       </c>
       <c r="H524" t="n">
         <v>3302</v>
@@ -15594,7 +15594,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G525" t="n">
-        <v>5.43400716781616</v>
+        <v>5.43400764465332</v>
       </c>
       <c r="H525" t="n">
         <v>20028</v>
@@ -15710,7 +15710,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G529" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H529" t="n">
         <v>9791</v>
@@ -15797,7 +15797,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G532" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H532" t="n">
         <v>15759</v>
@@ -15884,7 +15884,7 @@
         <v>7.37793493270874</v>
       </c>
       <c r="G535" t="n">
-        <v>5.80316495895386</v>
+        <v>5.80316543579102</v>
       </c>
       <c r="H535" t="n">
         <v>4634</v>
@@ -15971,7 +15971,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G538" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120414733887</v>
       </c>
       <c r="H538" t="n">
         <v>8909</v>
@@ -16058,7 +16058,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.5078387260437</v>
+        <v>5.50783967971802</v>
       </c>
       <c r="H541" t="n">
         <v>31068</v>
@@ -16087,7 +16087,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G542" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H542" t="n">
         <v>13665</v>
@@ -16174,7 +16174,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G545" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H545" t="n">
         <v>11633</v>
@@ -16203,7 +16203,7 @@
         <v>6.96492099761963</v>
       </c>
       <c r="G546" t="n">
-        <v>5.47830677032471</v>
+        <v>5.47830629348755</v>
       </c>
       <c r="H546" t="n">
         <v>14669</v>
@@ -16261,7 +16261,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G548" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H548" t="n">
         <v>3390</v>
@@ -16348,7 +16348,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.48405170440674</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H551" t="n">
         <v>3089</v>
@@ -16377,7 +16377,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.48405170440674</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H552" t="n">
         <v>9976</v>
@@ -16493,7 +16493,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G556" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H556" t="n">
         <v>4442</v>
@@ -16522,7 +16522,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G557" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H557" t="n">
         <v>13819</v>
@@ -16551,7 +16551,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G558" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H558" t="n">
         <v>20885</v>
@@ -16754,7 +16754,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H565" t="n">
         <v>6946</v>
@@ -16783,7 +16783,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H566" t="n">
         <v>6002</v>
@@ -16870,7 +16870,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H569" t="n">
         <v>8874</v>
@@ -16928,7 +16928,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G571" t="n">
-        <v>5.77674055099487</v>
+        <v>5.77674007415771</v>
       </c>
       <c r="H571" t="n">
         <v>3259</v>
@@ -16986,7 +16986,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.8229546546936</v>
+        <v>5.82295417785645</v>
       </c>
       <c r="H573" t="n">
         <v>2375</v>
@@ -17015,7 +17015,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G574" t="n">
-        <v>5.77674055099487</v>
+        <v>5.77674007415771</v>
       </c>
       <c r="H574" t="n">
         <v>4794</v>
@@ -17189,7 +17189,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G580" t="n">
-        <v>5.85376405715942</v>
+        <v>5.85376358032227</v>
       </c>
       <c r="H580" t="n">
         <v>2840</v>
@@ -17276,7 +17276,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G583" t="n">
-        <v>5.77674055099487</v>
+        <v>5.77674007415771</v>
       </c>
       <c r="H583" t="n">
         <v>1715</v>
@@ -17334,7 +17334,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593019485474</v>
+        <v>5.74593114852905</v>
       </c>
       <c r="H585" t="n">
         <v>1301</v>
@@ -17392,7 +17392,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G587" t="n">
-        <v>5.66890716552734</v>
+        <v>5.6689076423645</v>
       </c>
       <c r="H587" t="n">
         <v>10990</v>
@@ -17421,7 +17421,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G588" t="n">
-        <v>5.62269401550293</v>
+        <v>5.62269353866577</v>
       </c>
       <c r="H588" t="n">
         <v>2162</v>
@@ -17479,7 +17479,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G590" t="n">
-        <v>5.66890716552734</v>
+        <v>5.6689076423645</v>
       </c>
       <c r="H590" t="n">
         <v>7426</v>
@@ -17508,7 +17508,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.57648038864136</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H591" t="n">
         <v>11995</v>
@@ -17537,7 +17537,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G592" t="n">
-        <v>5.65350389480591</v>
+        <v>5.65350341796875</v>
       </c>
       <c r="H592" t="n">
         <v>12357</v>
@@ -17566,7 +17566,7 @@
         <v>6.77718687057495</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56107425689697</v>
+        <v>5.56107473373413</v>
       </c>
       <c r="H593" t="n">
         <v>10592</v>
@@ -17624,7 +17624,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G595" t="n">
-        <v>5.62269401550293</v>
+        <v>5.62269353866577</v>
       </c>
       <c r="H595" t="n">
         <v>33809</v>
@@ -17827,7 +17827,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G602" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H602" t="n">
         <v>5214</v>
@@ -17856,7 +17856,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G603" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H603" t="n">
         <v>31770</v>
@@ -17972,7 +17972,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G607" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H607" t="n">
         <v>7436</v>
@@ -18059,7 +18059,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G610" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H610" t="n">
         <v>5007</v>
@@ -18117,7 +18117,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G612" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H612" t="n">
         <v>17032</v>
@@ -18465,7 +18465,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G624" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H624" t="n">
         <v>11485</v>
@@ -18697,7 +18697,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G632" t="n">
-        <v>5.43783712387085</v>
+        <v>5.43783760070801</v>
       </c>
       <c r="H632" t="n">
         <v>294825</v>
@@ -18958,7 +18958,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G641" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H641" t="n">
         <v>12988</v>
@@ -19045,7 +19045,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G644" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H644" t="n">
         <v>37013</v>
@@ -19103,7 +19103,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G646" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H646" t="n">
         <v>12266</v>
@@ -19190,7 +19190,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G649" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H649" t="n">
         <v>1693</v>
@@ -19219,7 +19219,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G650" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H650" t="n">
         <v>18052</v>
@@ -19248,7 +19248,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H651" t="n">
         <v>8630</v>
@@ -19306,7 +19306,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G653" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H653" t="n">
         <v>3865</v>
@@ -19538,7 +19538,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H661" t="n">
         <v>10675</v>
@@ -19567,7 +19567,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H662" t="n">
         <v>33870</v>
@@ -19596,7 +19596,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H663" t="n">
         <v>10127</v>
@@ -19741,7 +19741,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06812620162964</v>
+        <v>5.06812572479248</v>
       </c>
       <c r="H668" t="n">
         <v>18182</v>
@@ -19770,7 +19770,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G669" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H669" t="n">
         <v>4938</v>
@@ -19799,7 +19799,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H670" t="n">
         <v>5550</v>
@@ -19828,7 +19828,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676803588867</v>
+        <v>5.20676851272583</v>
       </c>
       <c r="H671" t="n">
         <v>10523</v>
@@ -19886,7 +19886,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G673" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H673" t="n">
         <v>7144</v>
@@ -20147,7 +20147,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G682" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H682" t="n">
         <v>7075</v>
@@ -20176,7 +20176,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G683" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H683" t="n">
         <v>7878</v>
@@ -20437,7 +20437,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G692" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H692" t="n">
         <v>9073</v>
@@ -20524,7 +20524,7 @@
         <v>6.60822677612305</v>
       </c>
       <c r="G695" t="n">
-        <v>5.42243337631226</v>
+        <v>5.4224328994751</v>
       </c>
       <c r="H695" t="n">
         <v>13441</v>
@@ -20698,7 +20698,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G701" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H701" t="n">
         <v>1549</v>
@@ -20785,7 +20785,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G704" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H704" t="n">
         <v>16985</v>
@@ -20814,7 +20814,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H705" t="n">
         <v>4626</v>
@@ -20959,7 +20959,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G710" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H710" t="n">
         <v>22162</v>
@@ -21017,7 +21017,7 @@
         <v>6.47681283950806</v>
       </c>
       <c r="G712" t="n">
-        <v>5.31459999084473</v>
+        <v>5.31460094451904</v>
       </c>
       <c r="H712" t="n">
         <v>10762</v>
@@ -21162,7 +21162,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H717" t="n">
         <v>11988</v>
@@ -21191,7 +21191,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G718" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H718" t="n">
         <v>2084</v>
@@ -21249,7 +21249,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G720" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H720" t="n">
         <v>3936</v>
@@ -21278,7 +21278,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G721" t="n">
-        <v>5.29919624328613</v>
+        <v>5.29919672012329</v>
       </c>
       <c r="H721" t="n">
         <v>3313</v>
@@ -21307,7 +21307,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H722" t="n">
         <v>8101</v>
@@ -21365,7 +21365,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H724" t="n">
         <v>158873</v>
@@ -21423,7 +21423,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G726" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H726" t="n">
         <v>34937</v>
@@ -21452,7 +21452,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G727" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H727" t="n">
         <v>45598</v>
@@ -21510,7 +21510,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G729" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H729" t="n">
         <v>214334</v>
@@ -21568,7 +21568,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G731" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H731" t="n">
         <v>7136</v>
@@ -21597,7 +21597,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G732" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974548339844</v>
       </c>
       <c r="H732" t="n">
         <v>47543</v>
@@ -21684,7 +21684,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G735" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H735" t="n">
         <v>12753</v>
@@ -21713,7 +21713,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G736" t="n">
-        <v>5.06812620162964</v>
+        <v>5.06812572479248</v>
       </c>
       <c r="H736" t="n">
         <v>5420</v>
@@ -21800,7 +21800,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G739" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H739" t="n">
         <v>9338</v>
@@ -21829,7 +21829,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G740" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272150039673</v>
       </c>
       <c r="H740" t="n">
         <v>18125</v>
@@ -21858,7 +21858,7 @@
         <v>5.98870611190796</v>
       </c>
       <c r="G741" t="n">
-        <v>4.91408014297485</v>
+        <v>4.91408061981201</v>
       </c>
       <c r="H741" t="n">
         <v>84527</v>
@@ -21945,7 +21945,7 @@
         <v>6.13889312744141</v>
       </c>
       <c r="G744" t="n">
-        <v>5.03731822967529</v>
+        <v>5.03731775283813</v>
       </c>
       <c r="H744" t="n">
         <v>78631</v>
@@ -22003,7 +22003,7 @@
         <v>5.83851909637451</v>
       </c>
       <c r="G746" t="n">
-        <v>4.79084300994873</v>
+        <v>4.79084348678589</v>
       </c>
       <c r="H746" t="n">
         <v>6996</v>
@@ -22032,7 +22032,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H747" t="n">
         <v>45629</v>
@@ -22061,7 +22061,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760587692261</v>
+        <v>4.66760635375977</v>
       </c>
       <c r="H748" t="n">
         <v>24857</v>
@@ -22148,7 +22148,7 @@
         <v>5.63201189041138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.62139225006104</v>
+        <v>4.62139177322388</v>
       </c>
       <c r="H751" t="n">
         <v>11601</v>
@@ -22177,7 +22177,7 @@
         <v>5.55691814422607</v>
       </c>
       <c r="G752" t="n">
-        <v>4.55977344512939</v>
+        <v>4.55977296829224</v>
       </c>
       <c r="H752" t="n">
         <v>19277</v>
@@ -22206,7 +22206,7 @@
         <v>5.4442777633667</v>
       </c>
       <c r="G753" t="n">
-        <v>4.46734571456909</v>
+        <v>4.46734523773193</v>
       </c>
       <c r="H753" t="n">
         <v>30856</v>
@@ -22235,7 +22235,7 @@
         <v>5.29409122467041</v>
       </c>
       <c r="G754" t="n">
-        <v>4.34410858154297</v>
+        <v>4.34410810470581</v>
       </c>
       <c r="H754" t="n">
         <v>96598</v>
@@ -22264,7 +22264,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08222961425781</v>
+        <v>4.08223009109497</v>
       </c>
       <c r="H755" t="n">
         <v>42542</v>
@@ -22351,7 +22351,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468578338623</v>
+        <v>3.60468554496765</v>
       </c>
       <c r="H758" t="n">
         <v>114780</v>
@@ -22380,7 +22380,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G759" t="n">
-        <v>3.59698295593262</v>
+        <v>3.5969831943512</v>
       </c>
       <c r="H759" t="n">
         <v>59239</v>
@@ -22583,7 +22583,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G766" t="n">
-        <v>3.3042950630188</v>
+        <v>3.30429482460022</v>
       </c>
       <c r="H766" t="n">
         <v>13344</v>
@@ -22612,7 +22612,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G767" t="n">
-        <v>3.31969976425171</v>
+        <v>3.31970024108887</v>
       </c>
       <c r="H767" t="n">
         <v>9480</v>
@@ -22670,7 +22670,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G769" t="n">
-        <v>3.31969976425171</v>
+        <v>3.31970024108887</v>
       </c>
       <c r="H769" t="n">
         <v>6925</v>
@@ -22699,7 +22699,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G770" t="n">
-        <v>3.2657835483551</v>
+        <v>3.26578378677368</v>
       </c>
       <c r="H770" t="n">
         <v>7733</v>
@@ -22728,7 +22728,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G771" t="n">
-        <v>3.31199741363525</v>
+        <v>3.31199765205383</v>
       </c>
       <c r="H771" t="n">
         <v>19489</v>
@@ -22844,7 +22844,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G775" t="n">
-        <v>3.3042950630188</v>
+        <v>3.30429482460022</v>
       </c>
       <c r="H775" t="n">
         <v>11885</v>
@@ -22873,7 +22873,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.39672255516052</v>
+        <v>3.39672231674194</v>
       </c>
       <c r="H776" t="n">
         <v>23048</v>
@@ -22902,7 +22902,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G777" t="n">
-        <v>3.31199741363525</v>
+        <v>3.31199765205383</v>
       </c>
       <c r="H777" t="n">
         <v>10983</v>
@@ -22931,7 +22931,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G778" t="n">
-        <v>3.48915147781372</v>
+        <v>3.48915100097656</v>
       </c>
       <c r="H778" t="n">
         <v>94813</v>
@@ -22960,7 +22960,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306650161743</v>
+        <v>3.54306697845459</v>
       </c>
       <c r="H779" t="n">
         <v>19181</v>
@@ -22989,7 +22989,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G780" t="n">
-        <v>3.38902115821838</v>
+        <v>3.3890209197998</v>
       </c>
       <c r="H780" t="n">
         <v>14969</v>
@@ -23018,7 +23018,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G781" t="n">
-        <v>3.45063877105713</v>
+        <v>3.45063900947571</v>
       </c>
       <c r="H781" t="n">
         <v>5436</v>
@@ -23076,7 +23076,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G783" t="n">
-        <v>3.4660439491272</v>
+        <v>3.46604418754578</v>
       </c>
       <c r="H783" t="n">
         <v>30728</v>
@@ -23105,7 +23105,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G784" t="n">
-        <v>3.38902115821838</v>
+        <v>3.3890209197998</v>
       </c>
       <c r="H784" t="n">
         <v>15845</v>
@@ -23134,7 +23134,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G785" t="n">
-        <v>3.4352343082428</v>
+        <v>3.43523478507996</v>
       </c>
       <c r="H785" t="n">
         <v>31274</v>
@@ -23163,7 +23163,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G786" t="n">
-        <v>3.44293737411499</v>
+        <v>3.44293761253357</v>
       </c>
       <c r="H786" t="n">
         <v>21547</v>
@@ -23192,7 +23192,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G787" t="n">
-        <v>3.4660439491272</v>
+        <v>3.46604418754578</v>
       </c>
       <c r="H787" t="n">
         <v>46280</v>
@@ -23221,7 +23221,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.77413630485535</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H788" t="n">
         <v>79040</v>
@@ -23250,7 +23250,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.8203501701355</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H789" t="n">
         <v>103597</v>
@@ -23279,7 +23279,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G790" t="n">
-        <v>3.86656451225281</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H790" t="n">
         <v>21030</v>
@@ -23308,7 +23308,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.8126482963562</v>
+        <v>3.81264805793762</v>
       </c>
       <c r="H791" t="n">
         <v>43347</v>
@@ -23337,7 +23337,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.77413630485535</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H792" t="n">
         <v>60664</v>
@@ -23366,7 +23366,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H793" t="n">
         <v>20249</v>
@@ -23395,7 +23395,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G794" t="n">
-        <v>3.86656451225281</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H794" t="n">
         <v>52761</v>
@@ -23424,7 +23424,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.8203501701355</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H795" t="n">
         <v>37010</v>
@@ -23453,7 +23453,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G796" t="n">
-        <v>3.85116052627563</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H796" t="n">
         <v>6620</v>
@@ -23482,7 +23482,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G797" t="n">
-        <v>3.89737367630005</v>
+        <v>3.89737343788147</v>
       </c>
       <c r="H797" t="n">
         <v>14230</v>
@@ -23511,7 +23511,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818355560303</v>
+        <v>3.92818260192871</v>
       </c>
       <c r="H798" t="n">
         <v>44285</v>
@@ -23540,7 +23540,7 @@
         <v>4.84353017807007</v>
       </c>
       <c r="G799" t="n">
-        <v>3.9743971824646</v>
+        <v>3.97439742088318</v>
       </c>
       <c r="H799" t="n">
         <v>50963</v>
@@ -23569,7 +23569,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H800" t="n">
         <v>42258</v>
@@ -23598,7 +23598,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85116052627563</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H801" t="n">
         <v>45469</v>
@@ -23656,7 +23656,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H803" t="n">
         <v>26953</v>
@@ -23714,7 +23714,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G805" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H805" t="n">
         <v>26480</v>
@@ -23743,7 +23743,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291386604309</v>
+        <v>3.84291458129883</v>
       </c>
       <c r="H806" t="n">
         <v>94227</v>
@@ -23772,7 +23772,7 @@
         <v>4.57131576538086</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01609230041504</v>
+        <v>4.01609182357788</v>
       </c>
       <c r="H807" t="n">
         <v>66075</v>
@@ -23859,7 +23859,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G810" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H810" t="n">
         <v>33575</v>
@@ -23975,7 +23975,7 @@
         <v>4.66518306732178</v>
       </c>
       <c r="G814" t="n">
-        <v>4.09855842590332</v>
+        <v>4.09855794906616</v>
       </c>
       <c r="H814" t="n">
         <v>59049</v>
@@ -24033,7 +24033,7 @@
         <v>4.66518306732178</v>
       </c>
       <c r="G816" t="n">
-        <v>4.09855842590332</v>
+        <v>4.09855794906616</v>
       </c>
       <c r="H816" t="n">
         <v>42310</v>
@@ -24091,7 +24091,7 @@
         <v>5.05003690719604</v>
       </c>
       <c r="G818" t="n">
-        <v>4.43666887283325</v>
+        <v>4.43666839599609</v>
       </c>
       <c r="H818" t="n">
         <v>171756</v>
@@ -24178,7 +24178,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G821" t="n">
-        <v>4.30472326278687</v>
+        <v>4.30472278594971</v>
       </c>
       <c r="H821" t="n">
         <v>71502</v>
@@ -24207,7 +24207,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G822" t="n">
-        <v>4.27173614501953</v>
+        <v>4.27173662185669</v>
       </c>
       <c r="H822" t="n">
         <v>24302</v>
@@ -24236,7 +24236,7 @@
         <v>4.95617008209229</v>
       </c>
       <c r="G823" t="n">
-        <v>4.35420227050781</v>
+        <v>4.35420274734497</v>
       </c>
       <c r="H823" t="n">
         <v>29222</v>
@@ -24265,7 +24265,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G824" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H824" t="n">
         <v>56130</v>
@@ -24410,7 +24410,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G829" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H829" t="n">
         <v>13352</v>
@@ -24497,7 +24497,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G832" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H832" t="n">
         <v>24015</v>
@@ -24526,7 +24526,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G833" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H833" t="n">
         <v>13815</v>
@@ -24584,7 +24584,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G835" t="n">
-        <v>4.1397910118103</v>
+        <v>4.13979053497314</v>
       </c>
       <c r="H835" t="n">
         <v>12122</v>
@@ -24613,7 +24613,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G836" t="n">
-        <v>4.1397910118103</v>
+        <v>4.13979053497314</v>
       </c>
       <c r="H836" t="n">
         <v>40720</v>
@@ -24642,7 +24642,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H837" t="n">
         <v>17076</v>
@@ -24671,7 +24671,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G838" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H838" t="n">
         <v>6395</v>
@@ -24700,7 +24700,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G839" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H839" t="n">
         <v>12092</v>
@@ -24729,7 +24729,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H840" t="n">
         <v>4918</v>
@@ -24758,7 +24758,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H841" t="n">
         <v>29013</v>
@@ -24787,7 +24787,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H842" t="n">
         <v>14939</v>
@@ -24816,7 +24816,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H843" t="n">
         <v>12791</v>
@@ -24845,7 +24845,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G844" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H844" t="n">
         <v>12779</v>
@@ -24874,7 +24874,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H845" t="n">
         <v>6786</v>
@@ -24903,7 +24903,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G846" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H846" t="n">
         <v>4454</v>
@@ -24932,7 +24932,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H847" t="n">
         <v>5286</v>
@@ -24961,7 +24961,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H848" t="n">
         <v>24096</v>
@@ -25251,7 +25251,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G858" t="n">
-        <v>4.1397910118103</v>
+        <v>4.13979053497314</v>
       </c>
       <c r="H858" t="n">
         <v>20200</v>
@@ -25454,7 +25454,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G865" t="n">
-        <v>4.27173614501953</v>
+        <v>4.27173662185669</v>
       </c>
       <c r="H865" t="n">
         <v>17734</v>
@@ -25512,7 +25512,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H867" t="n">
         <v>1044</v>
@@ -25541,7 +25541,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G868" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H868" t="n">
         <v>7727</v>
@@ -25570,7 +25570,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H869" t="n">
         <v>6800</v>
@@ -25599,7 +25599,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G870" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H870" t="n">
         <v>12725</v>
@@ -25657,7 +25657,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G872" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H872" t="n">
         <v>7867</v>
@@ -25715,7 +25715,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H874" t="n">
         <v>23224</v>
@@ -25947,7 +25947,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277669906616</v>
       </c>
       <c r="H882" t="n">
         <v>10955</v>
@@ -26034,7 +26034,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H885" t="n">
         <v>4939</v>
@@ -26063,7 +26063,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G886" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H886" t="n">
         <v>10193</v>
@@ -26092,7 +26092,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G887" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H887" t="n">
         <v>31366</v>
@@ -26121,7 +26121,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G888" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H888" t="n">
         <v>20954</v>
@@ -26150,7 +26150,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G889" t="n">
-        <v>4.15628433227539</v>
+        <v>4.15628385543823</v>
       </c>
       <c r="H889" t="n">
         <v>31506</v>
@@ -26179,7 +26179,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G890" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H890" t="n">
         <v>4171</v>
@@ -26295,7 +26295,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G894" t="n">
-        <v>4.12329816818237</v>
+        <v>4.12329864501953</v>
       </c>
       <c r="H894" t="n">
         <v>10355</v>
@@ -26382,7 +26382,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H897" t="n">
         <v>21516</v>
@@ -26440,7 +26440,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H899" t="n">
         <v>13100</v>
@@ -26469,7 +26469,7 @@
         <v>4.52438306808472</v>
       </c>
       <c r="G900" t="n">
-        <v>3.97485971450806</v>
+        <v>3.97485947608948</v>
       </c>
       <c r="H900" t="n">
         <v>7883</v>
@@ -26498,7 +26498,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G901" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H901" t="n">
         <v>23762</v>
@@ -26527,7 +26527,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H902" t="n">
         <v>27440</v>
@@ -26556,7 +26556,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G903" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H903" t="n">
         <v>30505</v>
@@ -26585,7 +26585,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.89239358901978</v>
+        <v>3.89239311218262</v>
       </c>
       <c r="H904" t="n">
         <v>57694</v>
@@ -26614,7 +26614,7 @@
         <v>4.41174221038818</v>
       </c>
       <c r="G905" t="n">
-        <v>3.87590003013611</v>
+        <v>3.87589979171753</v>
       </c>
       <c r="H905" t="n">
         <v>14193</v>
@@ -26672,7 +26672,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H907" t="n">
         <v>21206</v>
@@ -26730,7 +26730,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H909" t="n">
         <v>12272</v>
@@ -26759,7 +26759,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H910" t="n">
         <v>221384</v>
@@ -26788,7 +26788,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G911" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H911" t="n">
         <v>26515</v>
@@ -26904,7 +26904,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G915" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H915" t="n">
         <v>239972</v>
@@ -26933,7 +26933,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G916" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H916" t="n">
         <v>30575</v>
@@ -26991,7 +26991,7 @@
         <v>3.78283405303955</v>
       </c>
       <c r="G918" t="n">
-        <v>3.32337760925293</v>
+        <v>3.32337784767151</v>
       </c>
       <c r="H918" t="n">
         <v>20342</v>
@@ -27020,7 +27020,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G919" t="n">
-        <v>3.3151319026947</v>
+        <v>3.31513166427612</v>
       </c>
       <c r="H919" t="n">
         <v>19199</v>
@@ -27049,7 +27049,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G920" t="n">
-        <v>3.3151319026947</v>
+        <v>3.31513166427612</v>
       </c>
       <c r="H920" t="n">
         <v>6182</v>
@@ -27136,7 +27136,7 @@
         <v>3.75467395782471</v>
       </c>
       <c r="G923" t="n">
-        <v>3.29863786697388</v>
+        <v>3.29863810539246</v>
       </c>
       <c r="H923" t="n">
         <v>6991</v>
@@ -27165,7 +27165,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G924" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H924" t="n">
         <v>19579</v>
@@ -27281,7 +27281,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H928" t="n">
         <v>18937</v>
@@ -27339,7 +27339,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H930" t="n">
         <v>14164</v>
@@ -27600,7 +27600,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G939" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H939" t="n">
         <v>25861</v>
@@ -27658,7 +27658,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G941" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H941" t="n">
         <v>84865</v>
@@ -27687,7 +27687,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G942" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H942" t="n">
         <v>31672</v>
@@ -27716,7 +27716,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G943" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H943" t="n">
         <v>39520</v>
@@ -27745,7 +27745,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H944" t="n">
         <v>39463</v>
@@ -27803,7 +27803,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G946" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H946" t="n">
         <v>23231</v>
@@ -27832,7 +27832,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G947" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H947" t="n">
         <v>47814</v>
@@ -27890,7 +27890,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H949" t="n">
         <v>106760</v>
@@ -27919,7 +27919,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G950" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H950" t="n">
         <v>10561</v>
@@ -27948,7 +27948,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G951" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H951" t="n">
         <v>23800</v>
@@ -27977,7 +27977,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G952" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H952" t="n">
         <v>37331</v>
@@ -28064,7 +28064,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G955" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H955" t="n">
         <v>15820</v>
@@ -28093,7 +28093,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G956" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H956" t="n">
         <v>4348</v>
@@ -28209,7 +28209,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H960" t="n">
         <v>23384</v>
@@ -28238,7 +28238,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G961" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H961" t="n">
         <v>231929</v>
@@ -28296,7 +28296,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959945678711</v>
       </c>
       <c r="H963" t="n">
         <v>98447</v>
@@ -28325,7 +28325,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G964" t="n">
-        <v>3.96661305427551</v>
+        <v>3.96661281585693</v>
       </c>
       <c r="H964" t="n">
         <v>39821</v>
@@ -28383,7 +28383,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G966" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H966" t="n">
         <v>80934</v>
@@ -28412,7 +28412,7 @@
         <v>4.56192922592163</v>
       </c>
       <c r="G967" t="n">
-        <v>4.00784587860107</v>
+        <v>4.00784540176392</v>
       </c>
       <c r="H967" t="n">
         <v>56555</v>
@@ -28441,7 +28441,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96661305427551</v>
+        <v>3.96661281585693</v>
       </c>
       <c r="H968" t="n">
         <v>98913</v>
@@ -28557,7 +28557,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G972" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H972" t="n">
         <v>13653</v>
@@ -28586,7 +28586,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G973" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H973" t="n">
         <v>30963</v>
@@ -28615,7 +28615,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G974" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H974" t="n">
         <v>14226</v>
@@ -28644,7 +28644,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G975" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116028785706</v>
       </c>
       <c r="H975" t="n">
         <v>12119</v>
@@ -28673,7 +28673,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992794036865</v>
+        <v>3.80992770195007</v>
       </c>
       <c r="H976" t="n">
         <v>12393</v>
@@ -28702,7 +28702,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H977" t="n">
         <v>18818</v>
@@ -28760,7 +28760,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G979" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H979" t="n">
         <v>17023</v>
@@ -28789,7 +28789,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G980" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H980" t="n">
         <v>10952</v>
@@ -28847,7 +28847,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G982" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H982" t="n">
         <v>14851</v>
@@ -28876,7 +28876,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G983" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H983" t="n">
         <v>19501</v>
@@ -28905,7 +28905,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G984" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H984" t="n">
         <v>14074</v>
@@ -28963,7 +28963,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H986" t="n">
         <v>14453</v>
@@ -28992,7 +28992,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H987" t="n">
         <v>32827</v>
@@ -29021,7 +29021,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G988" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H988" t="n">
         <v>105272</v>
@@ -29050,7 +29050,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G989" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H989" t="n">
         <v>29551</v>
@@ -29079,7 +29079,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G990" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H990" t="n">
         <v>34076</v>
@@ -29108,7 +29108,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G991" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H991" t="n">
         <v>31203</v>
@@ -29137,7 +29137,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G992" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H992" t="n">
         <v>77453</v>
@@ -29166,7 +29166,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992794036865</v>
+        <v>3.80992770195007</v>
       </c>
       <c r="H993" t="n">
         <v>25930</v>
@@ -29195,7 +29195,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G994" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H994" t="n">
         <v>29512</v>
@@ -29224,7 +29224,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G995" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H995" t="n">
         <v>32878</v>
@@ -29253,7 +29253,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H996" t="n">
         <v>22397</v>
@@ -29282,7 +29282,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G997" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H997" t="n">
         <v>27938</v>
@@ -29311,7 +29311,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H998" t="n">
         <v>7194</v>
@@ -29340,7 +29340,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G999" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H999" t="n">
         <v>12906</v>
@@ -29369,7 +29369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1000" t="n">
         <v>15235</v>
@@ -29427,7 +29427,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1002" t="n">
         <v>35487</v>
@@ -29456,7 +29456,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1003" t="n">
         <v>38443</v>
@@ -29543,7 +29543,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1006" t="n">
         <v>54190</v>
@@ -29630,7 +29630,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1009" t="n">
         <v>21917</v>
@@ -29688,7 +29688,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1011" t="n">
         <v>16281</v>
@@ -29746,7 +29746,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1013" t="n">
         <v>21737</v>
@@ -29775,7 +29775,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1014" t="n">
         <v>18825</v>
@@ -29804,7 +29804,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1015" t="n">
         <v>18095</v>
@@ -29833,7 +29833,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1016" t="n">
         <v>29025</v>
@@ -29920,7 +29920,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1019" t="n">
         <v>21560</v>
@@ -29949,7 +29949,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1020" t="n">
         <v>23255</v>
@@ -30007,7 +30007,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1022" t="n">
         <v>23587</v>
@@ -30036,7 +30036,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1023" t="n">
         <v>100775</v>
@@ -30065,7 +30065,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1024" t="n">
         <v>24801</v>
@@ -30094,7 +30094,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1025" t="n">
         <v>37874</v>
@@ -30123,7 +30123,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1026" t="n">
         <v>14221</v>
@@ -30152,7 +30152,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1027" t="n">
         <v>25372</v>
@@ -30239,7 +30239,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1030" t="n">
         <v>28499</v>
@@ -30297,7 +30297,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1032" t="n">
         <v>39883</v>
@@ -30355,7 +30355,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1034" t="n">
         <v>41320</v>
@@ -30384,7 +30384,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1035" t="n">
         <v>20652</v>
@@ -30413,7 +30413,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1036" t="n">
         <v>25907</v>
@@ -30442,7 +30442,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1037" t="n">
         <v>103283</v>
@@ -30471,7 +30471,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921420097351</v>
       </c>
       <c r="H1038" t="n">
         <v>51341</v>
@@ -30500,7 +30500,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1039" t="n">
         <v>43496</v>
@@ -30529,7 +30529,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1040" t="n">
         <v>37918</v>
@@ -30558,7 +30558,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1041" t="n">
         <v>33432</v>
@@ -30616,7 +30616,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1043" t="n">
         <v>11883</v>
@@ -30645,7 +30645,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1044" t="n">
         <v>60916</v>
@@ -30674,7 +30674,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1045" t="n">
         <v>26734</v>
@@ -30703,7 +30703,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1046" t="n">
         <v>8805</v>
@@ -30732,7 +30732,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1047" t="n">
         <v>25237</v>
@@ -30761,7 +30761,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H1048" t="n">
         <v>18325</v>
@@ -30790,7 +30790,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1049" t="n">
         <v>11760</v>
@@ -30819,7 +30819,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1050" t="n">
         <v>3012</v>
@@ -30848,7 +30848,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1051" t="n">
         <v>3548</v>
@@ -30877,7 +30877,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1052" t="n">
         <v>6158</v>
@@ -30906,7 +30906,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1053" t="n">
         <v>8465</v>
@@ -30964,7 +30964,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1055" t="n">
         <v>12152</v>
@@ -30993,7 +30993,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1056" t="n">
         <v>13789</v>
@@ -31051,7 +31051,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1058" t="n">
         <v>12928</v>
@@ -31080,7 +31080,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1059" t="n">
         <v>5829</v>
@@ -31138,7 +31138,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1061" t="n">
         <v>16774</v>
@@ -31167,7 +31167,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1062" t="n">
         <v>48219</v>
@@ -31196,7 +31196,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1063" t="n">
         <v>25919</v>
@@ -31225,7 +31225,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1064" t="n">
         <v>11044</v>
@@ -31254,7 +31254,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1065" t="n">
         <v>24230</v>
@@ -31283,7 +31283,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1066" t="n">
         <v>19508</v>
@@ -31312,7 +31312,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1067" t="n">
         <v>39186</v>
@@ -31341,7 +31341,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1068" t="n">
         <v>17426</v>
@@ -31370,7 +31370,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1069" t="n">
         <v>58800</v>
@@ -31428,7 +31428,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.78518748283386</v>
+        <v>3.78518772125244</v>
       </c>
       <c r="H1071" t="n">
         <v>50468</v>
@@ -31457,7 +31457,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1072" t="n">
         <v>42884</v>
@@ -31486,7 +31486,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1073" t="n">
         <v>22042</v>
@@ -31515,7 +31515,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1074" t="n">
         <v>65157</v>
@@ -31544,7 +31544,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1075" t="n">
         <v>26677</v>
@@ -31573,7 +31573,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1076" t="n">
         <v>80824</v>
@@ -31602,7 +31602,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1077" t="n">
         <v>94343</v>
@@ -31631,7 +31631,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1078" t="n">
         <v>6907</v>
@@ -31660,7 +31660,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1079" t="n">
         <v>14510</v>
@@ -31747,7 +31747,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1082" t="n">
         <v>21043</v>
@@ -31776,7 +31776,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1083" t="n">
         <v>17577</v>
@@ -31834,7 +31834,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1085" t="n">
         <v>9140</v>
@@ -31892,7 +31892,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1087" t="n">
         <v>42401</v>
@@ -31921,7 +31921,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1088" t="n">
         <v>11524</v>
@@ -31950,7 +31950,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1089" t="n">
         <v>6676</v>
@@ -31979,7 +31979,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H1090" t="n">
         <v>13072</v>
@@ -32008,7 +32008,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1091" t="n">
         <v>1611</v>
@@ -32037,7 +32037,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1092" t="n">
         <v>27747</v>
@@ -32066,7 +32066,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1093" t="n">
         <v>24635</v>
@@ -32211,7 +32211,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1098" t="n">
         <v>5347</v>
@@ -32269,7 +32269,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1100" t="n">
         <v>19929</v>
@@ -32298,7 +32298,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1101" t="n">
         <v>18207</v>
@@ -32356,7 +32356,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1103" t="n">
         <v>8811</v>
@@ -32443,7 +32443,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1106" t="n">
         <v>12193</v>
@@ -32559,7 +32559,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1110" t="n">
         <v>6715</v>
@@ -32588,7 +32588,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1111" t="n">
         <v>8326</v>
@@ -32617,7 +32617,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1112" t="n">
         <v>3066</v>
@@ -32704,7 +32704,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285709381104</v>
       </c>
       <c r="H1115" t="n">
         <v>45530</v>
@@ -32733,7 +32733,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1116" t="n">
         <v>10368</v>
@@ -32820,7 +32820,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1119" t="n">
         <v>119353</v>
@@ -32849,7 +32849,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220084190369</v>
       </c>
       <c r="H1120" t="n">
         <v>74582</v>
@@ -32907,7 +32907,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921420097351</v>
       </c>
       <c r="H1122" t="n">
         <v>40624</v>
@@ -32936,7 +32936,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570847511292</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1123" t="n">
         <v>50758</v>
@@ -32965,7 +32965,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1124" t="n">
         <v>70251</v>
@@ -32994,7 +32994,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1125" t="n">
         <v>30453</v>
@@ -33023,7 +33023,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694034576416</v>
+        <v>3.7769410610199</v>
       </c>
       <c r="H1126" t="n">
         <v>56617</v>
@@ -33052,7 +33052,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H1127" t="n">
         <v>98755</v>
@@ -33081,7 +33081,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1128" t="n">
         <v>62441</v>
@@ -33168,7 +33168,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.79343366622925</v>
+        <v>3.79343414306641</v>
       </c>
       <c r="H1131" t="n">
         <v>33720</v>
@@ -33197,7 +33197,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.76869368553162</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1132" t="n">
         <v>13639</v>
@@ -33226,7 +33226,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1133" t="n">
         <v>63296</v>
@@ -33255,7 +33255,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1134" t="n">
         <v>26915</v>
@@ -33284,7 +33284,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1135" t="n">
         <v>25711</v>
@@ -33313,7 +33313,7 @@
         <v>4.15830183029175</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.65324234962463</v>
+        <v>3.65324187278748</v>
       </c>
       <c r="H1136" t="n">
         <v>9914</v>
@@ -33371,7 +33371,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.7109682559967</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1138" t="n">
         <v>28849</v>
@@ -33458,7 +33458,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1141" t="n">
         <v>18975</v>
@@ -33487,7 +33487,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1142" t="n">
         <v>70144</v>
@@ -33516,7 +33516,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1143" t="n">
         <v>71574</v>
@@ -33574,7 +33574,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1145" t="n">
         <v>11043</v>
@@ -33632,7 +33632,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1147" t="n">
         <v>5028</v>
@@ -33806,7 +33806,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.68622875213623</v>
+        <v>3.68622899055481</v>
       </c>
       <c r="H1153" t="n">
         <v>18247</v>
@@ -33864,7 +33864,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1155" t="n">
         <v>8816</v>
@@ -33951,7 +33951,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1158" t="n">
         <v>16226</v>
@@ -34009,7 +34009,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.63674855232239</v>
+        <v>3.63674831390381</v>
       </c>
       <c r="H1160" t="n">
         <v>6366</v>
@@ -34096,7 +34096,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1163" t="n">
         <v>36527</v>
@@ -34125,7 +34125,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1164" t="n">
         <v>32377</v>
@@ -34183,7 +34183,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1166" t="n">
         <v>8226</v>
@@ -34212,7 +34212,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.57902312278748</v>
+        <v>3.57902264595032</v>
       </c>
       <c r="H1167" t="n">
         <v>10482</v>
@@ -34241,7 +34241,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1168" t="n">
         <v>10241</v>
@@ -34270,7 +34270,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1169" t="n">
         <v>8390</v>
@@ -34299,7 +34299,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1170" t="n">
         <v>23775</v>
@@ -34328,7 +34328,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1171" t="n">
         <v>4856</v>
@@ -34357,7 +34357,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1172" t="n">
         <v>22682</v>
@@ -34415,7 +34415,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1174" t="n">
         <v>82581</v>
@@ -34560,7 +34560,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1179" t="n">
         <v>10695</v>
@@ -34618,7 +34618,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H1181" t="n">
         <v>8590</v>
@@ -34705,7 +34705,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1184" t="n">
         <v>30559</v>
@@ -34792,7 +34792,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1187" t="n">
         <v>17346</v>
@@ -34821,7 +34821,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1188" t="n">
         <v>64523</v>
@@ -34850,7 +34850,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.67798161506653</v>
+        <v>3.67798185348511</v>
       </c>
       <c r="H1189" t="n">
         <v>48866</v>
@@ -34879,7 +34879,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1190" t="n">
         <v>25104</v>
@@ -34908,7 +34908,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077622413635</v>
+        <v>3.57077598571777</v>
       </c>
       <c r="H1191" t="n">
         <v>5698</v>
@@ -34937,7 +34937,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1192" t="n">
         <v>7688</v>
@@ -34995,7 +34995,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1194" t="n">
         <v>16241</v>
@@ -35053,7 +35053,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1196" t="n">
         <v>6031</v>
@@ -35111,7 +35111,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1198" t="n">
         <v>11291</v>
@@ -35169,7 +35169,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1200" t="n">
         <v>7176</v>
@@ -35198,7 +35198,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1201" t="n">
         <v>8294</v>
@@ -35227,7 +35227,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1202" t="n">
         <v>5435</v>
@@ -35256,7 +35256,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1203" t="n">
         <v>7859</v>
@@ -35343,7 +35343,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1206" t="n">
         <v>10703</v>
@@ -35372,7 +35372,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1207" t="n">
         <v>26510</v>
@@ -35401,7 +35401,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1208" t="n">
         <v>1693</v>
@@ -35430,7 +35430,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1209" t="n">
         <v>10093</v>
@@ -35488,7 +35488,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1211" t="n">
         <v>51874</v>
@@ -35517,7 +35517,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1212" t="n">
         <v>12870</v>
@@ -35546,7 +35546,7 @@
         <v>4.0081148147583</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.52129626274109</v>
+        <v>3.52129650115967</v>
       </c>
       <c r="H1213" t="n">
         <v>2326</v>
@@ -35604,7 +35604,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1215" t="n">
         <v>22828</v>
@@ -35633,7 +35633,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1216" t="n">
         <v>8971</v>
@@ -35662,7 +35662,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1217" t="n">
         <v>3168</v>
@@ -35720,7 +35720,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428290367126</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1219" t="n">
         <v>41335</v>
@@ -35778,7 +35778,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1221" t="n">
         <v>5316</v>
@@ -35807,7 +35807,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1222" t="n">
         <v>6029</v>
@@ -35836,7 +35836,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1223" t="n">
         <v>22676</v>
@@ -35865,7 +35865,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1224" t="n">
         <v>10519</v>
@@ -35894,7 +35894,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1225" t="n">
         <v>9180</v>
@@ -35923,7 +35923,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1226" t="n">
         <v>12826</v>
@@ -35952,7 +35952,7 @@
         <v>3.99872803688049</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.51304984092712</v>
+        <v>3.51304960250854</v>
       </c>
       <c r="H1227" t="n">
         <v>11090</v>
@@ -35981,7 +35981,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1228" t="n">
         <v>9896</v>
@@ -36039,7 +36039,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1230" t="n">
         <v>20614</v>
@@ -36068,7 +36068,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1231" t="n">
         <v>12772</v>
@@ -36097,7 +36097,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532369613647</v>
       </c>
       <c r="H1232" t="n">
         <v>23015</v>
@@ -36126,7 +36126,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.43058395385742</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H1233" t="n">
         <v>26288</v>
@@ -36184,7 +36184,7 @@
         <v>3.82976794242859</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.36461091041565</v>
+        <v>3.36461114883423</v>
       </c>
       <c r="H1235" t="n">
         <v>21167</v>
@@ -36242,7 +36242,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.34811758995056</v>
+        <v>3.34811735153198</v>
       </c>
       <c r="H1237" t="n">
         <v>6542</v>
@@ -36271,7 +36271,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285709381104</v>
       </c>
       <c r="H1238" t="n">
         <v>1560</v>
@@ -36358,7 +36358,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1241" t="n">
         <v>8107</v>
@@ -36474,7 +36474,7 @@
         <v>3.81099390983582</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.34811758995056</v>
+        <v>3.34811735153198</v>
       </c>
       <c r="H1245" t="n">
         <v>16269</v>
@@ -36561,7 +36561,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493939399719</v>
+        <v>3.17493915557861</v>
       </c>
       <c r="H1248" t="n">
         <v>97339</v>
@@ -36590,7 +36590,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1249" t="n">
         <v>48472</v>
@@ -36619,7 +36619,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1250" t="n">
         <v>14068</v>
@@ -36648,7 +36648,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1251" t="n">
         <v>38843</v>
@@ -36677,7 +36677,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247303009033</v>
+        <v>3.09247326850891</v>
       </c>
       <c r="H1252" t="n">
         <v>10004</v>
@@ -36706,7 +36706,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721324920654</v>
       </c>
       <c r="H1253" t="n">
         <v>6186</v>
@@ -36735,7 +36735,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721324920654</v>
       </c>
       <c r="H1254" t="n">
         <v>7022</v>
@@ -36764,7 +36764,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.2161717414856</v>
+        <v>3.21617197990417</v>
       </c>
       <c r="H1255" t="n">
         <v>41768</v>
@@ -36793,7 +36793,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493939399719</v>
+        <v>3.17493915557861</v>
       </c>
       <c r="H1256" t="n">
         <v>43078</v>
@@ -36851,7 +36851,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.2161717414856</v>
+        <v>3.21617197990417</v>
       </c>
       <c r="H1258" t="n">
         <v>26713</v>
@@ -36880,7 +36880,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1259" t="n">
         <v>13331</v>
@@ -37054,7 +37054,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1265" t="n">
         <v>33527</v>
@@ -37083,7 +37083,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1266" t="n">
         <v>13521</v>
@@ -37170,7 +37170,7 @@
         <v>3.32288694381714</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.91929531097412</v>
+        <v>2.91929507255554</v>
       </c>
       <c r="H1269" t="n">
         <v>2212</v>
@@ -37199,7 +37199,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1270" t="n">
         <v>2889</v>
@@ -37228,7 +37228,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1271" t="n">
         <v>8955</v>
@@ -37286,7 +37286,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280103683472</v>
       </c>
       <c r="H1273" t="n">
         <v>76645</v>
@@ -37431,7 +37431,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.0759801864624</v>
+        <v>3.07598042488098</v>
       </c>
       <c r="H1278" t="n">
         <v>2623</v>
@@ -37518,7 +37518,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1281" t="n">
         <v>186455</v>
@@ -37547,7 +37547,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1282" t="n">
         <v>37331</v>
@@ -37576,7 +37576,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1283" t="n">
         <v>6914</v>
@@ -37605,7 +37605,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072016716003</v>
       </c>
       <c r="H1284" t="n">
         <v>4412</v>
@@ -37750,7 +37750,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.0759801864624</v>
+        <v>3.07598042488098</v>
       </c>
       <c r="H1289" t="n">
         <v>6377</v>
@@ -37808,7 +37808,7 @@
         <v>3.41675400733948</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.0017614364624</v>
+        <v>3.00176095962524</v>
       </c>
       <c r="H1291" t="n">
         <v>10469</v>
@@ -38011,7 +38011,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1298" t="n">
         <v>2308</v>
@@ -38127,7 +38127,7 @@
         <v>3.35104703903198</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.94403481483459</v>
+        <v>2.94403505325317</v>
       </c>
       <c r="H1302" t="n">
         <v>14106</v>
@@ -38156,7 +38156,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1303" t="n">
         <v>16267</v>
@@ -38214,7 +38214,7 @@
         <v>3.24779295921326</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.85332202911377</v>
+        <v>2.85332179069519</v>
       </c>
       <c r="H1305" t="n">
         <v>46001</v>
@@ -38243,7 +38243,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630843162537</v>
+        <v>2.88630867004395</v>
       </c>
       <c r="H1306" t="n">
         <v>18867</v>
@@ -38417,7 +38417,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1312" t="n">
         <v>43094</v>
@@ -38562,7 +38562,7 @@
         <v>4.03656816482544</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.59016060829163</v>
+        <v>3.59016084671021</v>
       </c>
       <c r="H1317" t="n">
         <v>51551</v>
@@ -38649,7 +38649,7 @@
         <v>4.03656816482544</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.59016060829163</v>
+        <v>3.59016084671021</v>
       </c>
       <c r="H1320" t="n">
         <v>32773</v>
@@ -38678,7 +38678,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1321" t="n">
         <v>19899</v>
@@ -38736,7 +38736,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1323" t="n">
         <v>8362</v>
@@ -38765,7 +38765,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1324" t="n">
         <v>8377</v>
@@ -38794,7 +38794,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1325" t="n">
         <v>624</v>
@@ -38852,7 +38852,7 @@
         <v>4.05592823028564</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.6073796749115</v>
+        <v>3.60737943649292</v>
       </c>
       <c r="H1327" t="n">
         <v>2238</v>
@@ -38881,7 +38881,7 @@
         <v>4.05592823028564</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.6073796749115</v>
+        <v>3.60737943649292</v>
       </c>
       <c r="H1328" t="n">
         <v>8560</v>
@@ -38997,7 +38997,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1332" t="n">
         <v>36069</v>
@@ -39055,7 +39055,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1334" t="n">
         <v>13459</v>
@@ -39113,7 +39113,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1336" t="n">
         <v>37524</v>
@@ -39432,7 +39432,7 @@
         <v>3.97848796844482</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.53850364685059</v>
+        <v>3.53850340843201</v>
       </c>
       <c r="H1347" t="n">
         <v>7133</v>
@@ -39519,7 +39519,7 @@
         <v>3.85264801979065</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.42658042907715</v>
+        <v>3.42658019065857</v>
       </c>
       <c r="H1350" t="n">
         <v>51255</v>
@@ -39577,7 +39577,7 @@
         <v>3.77520799636841</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.35770440101624</v>
+        <v>3.35770463943481</v>
       </c>
       <c r="H1352" t="n">
         <v>2129</v>
@@ -39780,7 +39780,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1359" t="n">
         <v>170543</v>
@@ -39809,7 +39809,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1360" t="n">
         <v>31480</v>
@@ -39838,7 +39838,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1361" t="n">
         <v>9312</v>
@@ -39896,7 +39896,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1363" t="n">
         <v>10464</v>
@@ -39925,7 +39925,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1364" t="n">
         <v>23356</v>
@@ -39954,7 +39954,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1365" t="n">
         <v>6332</v>
@@ -39983,7 +39983,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1366" t="n">
         <v>6495</v>
@@ -40012,7 +40012,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1367" t="n">
         <v>24029</v>
@@ -40128,7 +40128,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.16829490661621</v>
+        <v>3.16829514503479</v>
       </c>
       <c r="H1371" t="n">
         <v>4983</v>
@@ -40157,7 +40157,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1372" t="n">
         <v>6436</v>
@@ -40215,7 +40215,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1374" t="n">
         <v>434</v>
@@ -40302,7 +40302,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1377" t="n">
         <v>16484</v>
@@ -40331,7 +40331,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1378" t="n">
         <v>10186</v>
@@ -40360,7 +40360,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1379" t="n">
         <v>42590</v>
@@ -40389,7 +40389,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1380" t="n">
         <v>1765</v>
@@ -40418,7 +40418,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1381" t="n">
         <v>37987</v>
@@ -40447,7 +40447,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1382" t="n">
         <v>73173</v>
@@ -40476,7 +40476,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1383" t="n">
         <v>14226</v>
@@ -40505,7 +40505,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1384" t="n">
         <v>415</v>
@@ -40534,7 +40534,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1385" t="n">
         <v>52993</v>
@@ -40563,7 +40563,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1386" t="n">
         <v>55695</v>
@@ -40592,7 +40592,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1387" t="n">
         <v>55</v>
@@ -40679,7 +40679,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1390" t="n">
         <v>212</v>
@@ -40708,7 +40708,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1391" t="n">
         <v>4819</v>
@@ -40737,7 +40737,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1392" t="n">
         <v>24899</v>
@@ -40766,7 +40766,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1393" t="n">
         <v>29155</v>
@@ -40795,7 +40795,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1394" t="n">
         <v>9851</v>
@@ -40824,7 +40824,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21995210647583</v>
+        <v>3.21995186805725</v>
       </c>
       <c r="H1395" t="n">
         <v>1030</v>
@@ -40882,7 +40882,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21995210647583</v>
+        <v>3.21995186805725</v>
       </c>
       <c r="H1397" t="n">
         <v>13064</v>
@@ -40911,7 +40911,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1398" t="n">
         <v>25070</v>
@@ -41114,7 +41114,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.21134257316589</v>
+        <v>3.21134233474731</v>
       </c>
       <c r="H1405" t="n">
         <v>27111</v>
@@ -41143,7 +41143,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1406" t="n">
         <v>31073</v>
@@ -41172,7 +41172,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1407" t="n">
         <v>2987</v>
@@ -41201,7 +41201,7 @@
         <v>3.6009669303894</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273280143738</v>
       </c>
       <c r="H1408" t="n">
         <v>35107</v>
@@ -41230,7 +41230,7 @@
         <v>3.58160710334778</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.18551397323608</v>
+        <v>3.18551421165466</v>
       </c>
       <c r="H1409" t="n">
         <v>200392</v>
@@ -41578,7 +41578,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1421" t="n">
         <v>294760</v>
@@ -41607,7 +41607,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1422" t="n">
         <v>35450</v>
@@ -41636,7 +41636,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1423" t="n">
         <v>9366</v>
@@ -41665,7 +41665,7 @@
         <v>3.04920601844788</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.71199178695679</v>
+        <v>2.71199154853821</v>
       </c>
       <c r="H1424" t="n">
         <v>53755</v>
@@ -41694,7 +41694,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1425" t="n">
         <v>51368</v>
@@ -41752,7 +41752,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1427" t="n">
         <v>44531</v>
@@ -41781,7 +41781,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1428" t="n">
         <v>64646</v>
@@ -41810,7 +41810,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1429" t="n">
         <v>11887</v>
@@ -41839,7 +41839,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1430" t="n">
         <v>9533</v>
@@ -41926,7 +41926,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1433" t="n">
         <v>10331</v>
@@ -41955,7 +41955,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1434" t="n">
         <v>98460</v>
@@ -41984,7 +41984,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1435" t="n">
         <v>11831</v>
@@ -42042,7 +42042,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.72921085357666</v>
+        <v>2.72921061515808</v>
       </c>
       <c r="H1437" t="n">
         <v>11573</v>
@@ -42071,7 +42071,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1438" t="n">
         <v>12728</v>
@@ -42129,7 +42129,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.6861629486084</v>
+        <v>2.68616318702698</v>
       </c>
       <c r="H1440" t="n">
         <v>12710</v>
@@ -42158,7 +42158,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1441" t="n">
         <v>7860</v>
@@ -42187,7 +42187,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1442" t="n">
         <v>13772</v>
@@ -42274,7 +42274,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1445" t="n">
         <v>14504</v>
@@ -42419,7 +42419,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1450" t="n">
         <v>20</v>
@@ -42535,7 +42535,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1454" t="n">
         <v>18616</v>
@@ -42564,7 +42564,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1455" t="n">
         <v>24438</v>
@@ -42593,7 +42593,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1456" t="n">
         <v>9511</v>
@@ -42651,7 +42651,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1458" t="n">
         <v>7087</v>
@@ -42680,7 +42680,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1459" t="n">
         <v>0</v>
@@ -42767,7 +42767,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1462" t="n">
         <v>8485</v>
@@ -42825,7 +42825,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1464" t="n">
         <v>7001</v>
@@ -42854,7 +42854,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1465" t="n">
         <v>35035</v>
@@ -42912,7 +42912,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1467" t="n">
         <v>39470</v>
@@ -42941,7 +42941,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1468" t="n">
         <v>26594</v>
@@ -42970,7 +42970,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1469" t="n">
         <v>4860</v>
@@ -42999,7 +42999,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1470" t="n">
         <v>14149</v>
@@ -43028,7 +43028,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1471" t="n">
         <v>7824</v>
@@ -43057,7 +43057,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1472" t="n">
         <v>309</v>
@@ -43086,7 +43086,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1473" t="n">
         <v>4257</v>
@@ -43115,7 +43115,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1474" t="n">
         <v>4029</v>
@@ -43260,7 +43260,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1479" t="n">
         <v>198</v>
@@ -43289,7 +43289,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1480" t="n">
         <v>17076</v>
@@ -43318,7 +43318,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1481" t="n">
         <v>8595</v>
@@ -43347,7 +43347,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1482" t="n">
         <v>13838</v>
@@ -43405,7 +43405,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1484" t="n">
         <v>24519</v>
@@ -43434,7 +43434,7 @@
         <v>3.14600610733032</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.79808664321899</v>
+        <v>2.79808640480042</v>
       </c>
       <c r="H1485" t="n">
         <v>143477</v>
@@ -43463,7 +43463,7 @@
         <v>3.03952598571777</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.70338201522827</v>
+        <v>2.70338225364685</v>
       </c>
       <c r="H1486" t="n">
         <v>67478</v>
@@ -43492,7 +43492,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1487" t="n">
         <v>26058</v>
@@ -43579,7 +43579,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1490" t="n">
         <v>8748</v>
@@ -43608,7 +43608,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1491" t="n">
         <v>29823</v>
@@ -43666,7 +43666,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1493" t="n">
         <v>68569</v>
@@ -43695,7 +43695,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.7378203868866</v>
+        <v>2.73782014846802</v>
       </c>
       <c r="H1494" t="n">
         <v>57457</v>
@@ -43724,7 +43724,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.69477248191833</v>
+        <v>2.69477272033691</v>
       </c>
       <c r="H1495" t="n">
         <v>7764</v>
@@ -43753,7 +43753,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1496" t="n">
         <v>28832</v>
@@ -43927,7 +43927,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1502" t="n">
         <v>30040</v>
@@ -44014,7 +44014,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1505" t="n">
         <v>14841</v>
@@ -44043,7 +44043,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1506" t="n">
         <v>20996</v>
@@ -44072,7 +44072,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1507" t="n">
         <v>3357</v>
@@ -44101,7 +44101,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1508" t="n">
         <v>6712</v>
@@ -44130,7 +44130,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1509" t="n">
         <v>1581</v>
@@ -44159,7 +44159,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1510" t="n">
         <v>8075</v>
@@ -44246,7 +44246,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1513" t="n">
         <v>8695</v>
@@ -44449,7 +44449,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1520" t="n">
         <v>17400</v>
@@ -44565,7 +44565,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1524" t="n">
         <v>40680</v>
@@ -44652,7 +44652,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1527" t="n">
         <v>21079</v>
@@ -44768,7 +44768,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1531" t="n">
         <v>13812</v>
@@ -44855,7 +44855,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1534" t="n">
         <v>3396</v>
@@ -44884,7 +44884,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1535" t="n">
         <v>298</v>
@@ -44942,7 +44942,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1537" t="n">
         <v>47394</v>
@@ -44971,7 +44971,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1538" t="n">
         <v>53293</v>
@@ -45000,7 +45000,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.6689441204071</v>
+        <v>2.66894435882568</v>
       </c>
       <c r="H1539" t="n">
         <v>1340</v>
@@ -45058,7 +45058,7 @@
         <v>2.99112606048584</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.66033482551575</v>
+        <v>2.66033506393433</v>
       </c>
       <c r="H1541" t="n">
         <v>64824</v>
@@ -45203,7 +45203,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1546" t="n">
         <v>1556</v>
@@ -45348,7 +45348,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1551" t="n">
         <v>12634</v>
@@ -45377,7 +45377,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1552" t="n">
         <v>42728</v>
@@ -45406,7 +45406,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.56563067436218</v>
+        <v>2.5656304359436</v>
       </c>
       <c r="H1553" t="n">
         <v>7867</v>
@@ -45435,7 +45435,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1554" t="n">
         <v>20594</v>
@@ -45464,7 +45464,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1555" t="n">
         <v>2918</v>
@@ -45493,7 +45493,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1556" t="n">
         <v>2071</v>
@@ -45522,7 +45522,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1557" t="n">
         <v>8550</v>
@@ -45580,7 +45580,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1559" t="n">
         <v>5144</v>
@@ -45609,7 +45609,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.57424020767212</v>
+        <v>2.57423973083496</v>
       </c>
       <c r="H1560" t="n">
         <v>5682</v>
@@ -45638,7 +45638,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1561" t="n">
         <v>4172</v>
@@ -45667,7 +45667,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1562" t="n">
         <v>3173</v>
@@ -45725,7 +45725,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.55702114105225</v>
+        <v>2.55702090263367</v>
       </c>
       <c r="H1564" t="n">
         <v>60925</v>
@@ -45783,7 +45783,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1566" t="n">
         <v>15762</v>
@@ -45812,7 +45812,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1567" t="n">
         <v>4363</v>
@@ -45870,7 +45870,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1569" t="n">
         <v>52254</v>
@@ -45899,7 +45899,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1570" t="n">
         <v>24597</v>
@@ -45986,7 +45986,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1573" t="n">
         <v>9765</v>
@@ -46015,7 +46015,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1574" t="n">
         <v>13419</v>
@@ -46044,7 +46044,7 @@
         <v>2.7684850692749</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.46231579780579</v>
+        <v>2.46231603622437</v>
       </c>
       <c r="H1575" t="n">
         <v>2078</v>
@@ -46073,7 +46073,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1576" t="n">
         <v>14992</v>
@@ -46131,7 +46131,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1578" t="n">
         <v>3766</v>
@@ -46160,7 +46160,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1579" t="n">
         <v>4333</v>
@@ -46189,7 +46189,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1580" t="n">
         <v>3340</v>
@@ -46218,7 +46218,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1581" t="n">
         <v>32796</v>
@@ -46276,7 +46276,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1583" t="n">
         <v>4884</v>
@@ -46392,7 +46392,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1587" t="n">
         <v>9909</v>
@@ -46421,7 +46421,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1588" t="n">
         <v>3414</v>
@@ -46450,7 +46450,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1589" t="n">
         <v>10979</v>
@@ -46479,7 +46479,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1590" t="n">
         <v>4907</v>
@@ -46508,7 +46508,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1591" t="n">
         <v>10038</v>
@@ -46537,7 +46537,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1592" t="n">
         <v>2788</v>
@@ -46566,7 +46566,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1593" t="n">
         <v>1012</v>
@@ -46595,7 +46595,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1594" t="n">
         <v>2066</v>
@@ -46682,7 +46682,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1597" t="n">
         <v>15617</v>
@@ -46769,7 +46769,7 @@
         <v>2.65232491493225</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.35900187492371</v>
+        <v>2.35900211334229</v>
       </c>
       <c r="H1600" t="n">
         <v>9429</v>
@@ -46798,7 +46798,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1601" t="n">
         <v>10946</v>
@@ -46827,7 +46827,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1602" t="n">
         <v>344</v>
@@ -46856,7 +46856,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1603" t="n">
         <v>1960</v>
@@ -46943,7 +46943,7 @@
         <v>2.65232491493225</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.35900187492371</v>
+        <v>2.35900211334229</v>
       </c>
       <c r="H1606" t="n">
         <v>3746</v>
@@ -46972,7 +46972,7 @@
         <v>2.65232491493225</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.35900187492371</v>
+        <v>2.35900211334229</v>
       </c>
       <c r="H1607" t="n">
         <v>2247</v>
@@ -47001,7 +47001,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1608" t="n">
         <v>17007</v>
@@ -47030,7 +47030,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1609" t="n">
         <v>2565</v>
@@ -47088,7 +47088,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1611" t="n">
         <v>32982</v>
@@ -47204,7 +47204,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1615" t="n">
         <v>7674</v>
@@ -47320,7 +47320,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1619" t="n">
         <v>51766</v>
@@ -47407,7 +47407,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1622" t="n">
         <v>10065</v>
@@ -47668,7 +47668,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1631" t="n">
         <v>47603</v>
@@ -47697,7 +47697,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1632" t="n">
         <v>2350</v>
@@ -47726,7 +47726,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542169570923</v>
+        <v>2.19542217254639</v>
       </c>
       <c r="H1633" t="n">
         <v>21458</v>
@@ -47784,7 +47784,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542169570923</v>
+        <v>2.19542217254639</v>
       </c>
       <c r="H1635" t="n">
         <v>12502</v>
@@ -47929,7 +47929,7 @@
         <v>2.3812849521637</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.11793661117554</v>
+        <v>2.11793684959412</v>
       </c>
       <c r="H1640" t="n">
         <v>21898</v>
@@ -47958,7 +47958,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.10071778297424</v>
+        <v>2.10071754455566</v>
       </c>
       <c r="H1641" t="n">
         <v>12225</v>
@@ -47987,7 +47987,7 @@
         <v>2.3812849521637</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.11793661117554</v>
+        <v>2.11793684959412</v>
       </c>
       <c r="H1642" t="n">
         <v>11329</v>
@@ -48016,7 +48016,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.09210848808289</v>
+        <v>2.09210824966431</v>
       </c>
       <c r="H1643" t="n">
         <v>3904</v>
@@ -48045,7 +48045,7 @@
         <v>2.37160491943359</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.1093270778656</v>
+        <v>2.10932683944702</v>
       </c>
       <c r="H1644" t="n">
         <v>17777</v>
@@ -48074,7 +48074,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.06627893447876</v>
+        <v>2.06627869606018</v>
       </c>
       <c r="H1645" t="n">
         <v>26535</v>
@@ -48132,7 +48132,7 @@
         <v>2.34256505966187</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.08349895477295</v>
+        <v>2.08349871635437</v>
       </c>
       <c r="H1647" t="n">
         <v>19328</v>
@@ -48161,7 +48161,7 @@
         <v>2.28448390960693</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.03184080123901</v>
+        <v>2.03184103965759</v>
       </c>
       <c r="H1648" t="n">
         <v>23903</v>
@@ -48219,7 +48219,7 @@
         <v>2.13928389549255</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.90269863605499</v>
+        <v>1.9026985168457</v>
       </c>
       <c r="H1650" t="n">
         <v>284242</v>
@@ -48277,7 +48277,7 @@
         <v>2.11024403572083</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.87687039375305</v>
+        <v>1.87687027454376</v>
       </c>
       <c r="H1652" t="n">
         <v>30327</v>
@@ -48335,7 +48335,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1654" t="n">
         <v>16354</v>
@@ -48422,7 +48422,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1657" t="n">
         <v>22469</v>
@@ -48509,7 +48509,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.06627893447876</v>
+        <v>2.06627869606018</v>
       </c>
       <c r="H1660" t="n">
         <v>12975</v>
@@ -48567,7 +48567,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1662" t="n">
         <v>33081</v>
@@ -48654,7 +48654,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1665" t="n">
         <v>13211</v>
@@ -48683,7 +48683,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1666" t="n">
         <v>1802</v>
@@ -48712,7 +48712,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1667" t="n">
         <v>14537</v>
@@ -48741,7 +48741,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.94574642181396</v>
+        <v>1.9457460641861</v>
       </c>
       <c r="H1668" t="n">
         <v>5866</v>
@@ -48770,7 +48770,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.94574642181396</v>
+        <v>1.9457460641861</v>
       </c>
       <c r="H1669" t="n">
         <v>16104</v>
@@ -48799,7 +48799,7 @@
         <v>2.19736409187317</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.95435547828674</v>
+        <v>1.95435559749603</v>
       </c>
       <c r="H1670" t="n">
         <v>12022</v>
@@ -48857,7 +48857,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1672" t="n">
         <v>15156</v>
@@ -48915,7 +48915,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1674" t="n">
         <v>1074</v>
@@ -48944,7 +48944,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1675" t="n">
         <v>10649</v>
@@ -48973,7 +48973,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1676" t="n">
         <v>11045</v>
@@ -49002,7 +49002,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1677" t="n">
         <v>5075</v>
@@ -49060,7 +49060,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157430648804</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1679" t="n">
         <v>11494</v>
@@ -49089,7 +49089,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1680" t="n">
         <v>5364</v>
@@ -49118,7 +49118,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1681" t="n">
         <v>2066</v>
@@ -49205,7 +49205,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.94574642181396</v>
+        <v>1.9457460641861</v>
       </c>
       <c r="H1684" t="n">
         <v>37</v>
@@ -49234,7 +49234,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713688850403</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1685" t="n">
         <v>2206</v>
@@ -49263,7 +49263,7 @@
         <v>2.10056400299072</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.86826086044312</v>
+        <v>1.86826074123383</v>
       </c>
       <c r="H1686" t="n">
         <v>3905</v>
@@ -49292,7 +49292,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1687" t="n">
         <v>8509</v>
@@ -49321,7 +49321,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1688" t="n">
         <v>1787</v>
@@ -49350,7 +49350,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130805015564</v>
       </c>
       <c r="H1689" t="n">
         <v>2827</v>
@@ -49379,7 +49379,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713688850403</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1690" t="n">
         <v>6351</v>
@@ -49408,7 +49408,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130805015564</v>
       </c>
       <c r="H1691" t="n">
         <v>11205</v>
@@ -49437,7 +49437,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1692" t="n">
         <v>13</v>
@@ -49524,7 +49524,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.92852735519409</v>
+        <v>1.9285272359848</v>
       </c>
       <c r="H1695" t="n">
         <v>4200</v>
@@ -49553,7 +49553,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130805015564</v>
       </c>
       <c r="H1696" t="n">
         <v>8700</v>
@@ -49582,7 +49582,7 @@
         <v>2.19736409187317</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.95435547828674</v>
+        <v>1.95435559749603</v>
       </c>
       <c r="H1697" t="n">
         <v>7025</v>
@@ -49611,7 +49611,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.9629647731781</v>
+        <v>1.96296501159668</v>
       </c>
       <c r="H1698" t="n">
         <v>11966</v>
@@ -49640,7 +49640,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1699" t="n">
         <v>12812</v>
@@ -49727,7 +49727,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1702" t="n">
         <v>37919</v>
@@ -49756,7 +49756,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1703" t="n">
         <v>31668</v>
@@ -49785,7 +49785,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1704" t="n">
         <v>8447</v>
@@ -49843,7 +49843,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1706" t="n">
         <v>10454</v>
@@ -49872,7 +49872,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1707" t="n">
         <v>15181</v>
@@ -49901,7 +49901,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1708" t="n">
         <v>31126</v>
@@ -49930,7 +49930,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1709" t="n">
         <v>1022</v>
@@ -49959,7 +49959,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1710" t="n">
         <v>35480</v>
@@ -49988,7 +49988,7 @@
         <v>2.2264039516449</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.98018383979797</v>
+        <v>1.98018395900726</v>
       </c>
       <c r="H1711" t="n">
         <v>9213</v>
@@ -50046,7 +50046,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1713" t="n">
         <v>23525</v>
@@ -50075,7 +50075,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1714" t="n">
         <v>20154</v>
@@ -50104,7 +50104,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1715" t="n">
         <v>7005</v>
@@ -50133,7 +50133,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1716" t="n">
         <v>3434</v>
@@ -50191,7 +50191,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1718" t="n">
         <v>41646</v>
@@ -50220,7 +50220,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.99740302562714</v>
+        <v>1.99740314483643</v>
       </c>
       <c r="H1719" t="n">
         <v>15121</v>
@@ -50336,7 +50336,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1723" t="n">
         <v>65810</v>
@@ -50423,7 +50423,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1726" t="n">
         <v>7626</v>
@@ -50481,7 +50481,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1728" t="n">
         <v>22331</v>
@@ -50539,7 +50539,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1730" t="n">
         <v>79797</v>
@@ -50568,7 +50568,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1731" t="n">
         <v>7710</v>
@@ -50626,7 +50626,7 @@
         <v>2.26512408256531</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.01462197303772</v>
+        <v>2.0146222114563</v>
       </c>
       <c r="H1733" t="n">
         <v>18450</v>
@@ -50916,7 +50916,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.06627893447876</v>
+        <v>2.06627869606018</v>
       </c>
       <c r="H1743" t="n">
         <v>23959</v>
@@ -50945,7 +50945,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.10071778297424</v>
+        <v>2.10071754455566</v>
       </c>
       <c r="H1744" t="n">
         <v>16458</v>
@@ -50974,7 +50974,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1745" t="n">
         <v>73553</v>
@@ -51003,7 +51003,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1746" t="n">
         <v>21182</v>
@@ -51177,7 +51177,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.20403122901917</v>
+        <v>2.20403146743774</v>
       </c>
       <c r="H1752" t="n">
         <v>66956</v>
@@ -51351,7 +51351,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.31595468521118</v>
+        <v>2.31595492362976</v>
       </c>
       <c r="H1758" t="n">
         <v>35729</v>
@@ -51438,7 +51438,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1761" t="n">
         <v>46109</v>
@@ -51467,7 +51467,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178328514099</v>
+        <v>2.34178304672241</v>
       </c>
       <c r="H1762" t="n">
         <v>39976</v>
@@ -51525,7 +51525,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1764" t="n">
         <v>25977</v>
@@ -51612,7 +51612,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1767" t="n">
         <v>46462</v>
@@ -51641,7 +51641,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1768" t="n">
         <v>78393</v>
@@ -51670,7 +51670,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1769" t="n">
         <v>37445</v>
@@ -51699,7 +51699,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1770" t="n">
         <v>35917</v>
@@ -51757,7 +51757,7 @@
         <v>2.83624601364136</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.5225830078125</v>
+        <v>2.52258324623108</v>
       </c>
       <c r="H1772" t="n">
         <v>17402</v>
@@ -51815,7 +51815,7 @@
         <v>2.78784489631653</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.47953462600708</v>
+        <v>2.47953486442566</v>
       </c>
       <c r="H1774" t="n">
         <v>4649</v>
@@ -51902,7 +51902,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1777" t="n">
         <v>19559</v>
@@ -51931,7 +51931,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1778" t="n">
         <v>39347</v>
@@ -51989,7 +51989,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1780" t="n">
         <v>21413</v>
@@ -52047,7 +52047,7 @@
         <v>2.78784489631653</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.47953462600708</v>
+        <v>2.47953486442566</v>
       </c>
       <c r="H1782" t="n">
         <v>38259</v>
@@ -52076,7 +52076,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1783" t="n">
         <v>84665</v>
@@ -52134,7 +52134,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1785" t="n">
         <v>36419</v>
@@ -52163,7 +52163,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1786" t="n">
         <v>20786</v>
@@ -52221,7 +52221,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1788" t="n">
         <v>16442</v>
@@ -52250,7 +52250,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1789" t="n">
         <v>12324</v>
@@ -52366,7 +52366,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1793" t="n">
         <v>3563</v>
@@ -52395,7 +52395,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1794" t="n">
         <v>4978</v>
@@ -52424,7 +52424,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1795" t="n">
         <v>15184</v>
@@ -52453,7 +52453,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1796" t="n">
         <v>9261</v>
@@ -52482,7 +52482,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1797" t="n">
         <v>8670</v>
@@ -52511,7 +52511,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1798" t="n">
         <v>277</v>
@@ -52540,7 +52540,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1799" t="n">
         <v>8141</v>
@@ -52569,7 +52569,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1800" t="n">
         <v>4610</v>
@@ -52598,7 +52598,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1801" t="n">
         <v>10103</v>
@@ -52627,7 +52627,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1802" t="n">
         <v>5605</v>
@@ -52656,7 +52656,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1803" t="n">
         <v>9157</v>
@@ -52685,7 +52685,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1804" t="n">
         <v>1740</v>
@@ -52743,7 +52743,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1806" t="n">
         <v>13043</v>
@@ -52772,7 +52772,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1807" t="n">
         <v>1109</v>
@@ -52801,7 +52801,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1808" t="n">
         <v>13121</v>
@@ -52859,7 +52859,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.35039234161377</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1810" t="n">
         <v>982</v>
@@ -52917,7 +52917,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1812" t="n">
         <v>8492</v>
@@ -52946,7 +52946,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1813" t="n">
         <v>28535</v>
@@ -52975,7 +52975,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1814" t="n">
         <v>3215</v>
@@ -53004,7 +53004,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.40204977989197</v>
+        <v>2.40204954147339</v>
       </c>
       <c r="H1815" t="n">
         <v>3758</v>
@@ -53062,7 +53062,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1817" t="n">
         <v>21384</v>
@@ -53091,7 +53091,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.43648719787598</v>
+        <v>2.43648743629456</v>
       </c>
       <c r="H1818" t="n">
         <v>22026</v>
@@ -53120,7 +53120,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1819" t="n">
         <v>15508</v>
@@ -53149,7 +53149,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1820" t="n">
         <v>60205</v>
@@ -53178,7 +53178,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.37622117996216</v>
+        <v>2.37622094154358</v>
       </c>
       <c r="H1821" t="n">
         <v>18850</v>
@@ -53207,7 +53207,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.39344024658203</v>
+        <v>2.39344000816345</v>
       </c>
       <c r="H1822" t="n">
         <v>32573</v>
@@ -53236,7 +53236,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.4106593132019</v>
+        <v>2.41065883636475</v>
       </c>
       <c r="H1823" t="n">
         <v>8939</v>
@@ -53265,7 +53265,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.41926836967468</v>
+        <v>2.41926860809326</v>
       </c>
       <c r="H1824" t="n">
         <v>2472</v>
@@ -71048,6 +71048,35 @@
         <v>3236</v>
       </c>
       <c r="I2437" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2438" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2438" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="G2438" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="H2438" t="n">
+        <v>18632</v>
+      </c>
+      <c r="I2438" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G2" t="n">
-        <v>7.36839628219604</v>
+        <v>7.36839580535889</v>
       </c>
       <c r="H2" t="n">
         <v>8309</v>
@@ -456,7 +456,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G3" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H3" t="n">
         <v>6711</v>
@@ -485,7 +485,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269540786743</v>
+        <v>7.41269493103027</v>
       </c>
       <c r="H4" t="n">
         <v>14488</v>
@@ -514,7 +514,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007875442505</v>
+        <v>7.42007970809937</v>
       </c>
       <c r="H5" t="n">
         <v>319</v>
@@ -543,7 +543,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H6" t="n">
         <v>3089</v>
@@ -572,7 +572,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G7" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H8" t="n">
         <v>532</v>
@@ -630,7 +630,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H9" t="n">
         <v>213</v>
@@ -659,7 +659,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H10" t="n">
         <v>1917</v>
@@ -688,7 +688,7 @@
         <v>9.36791324615479</v>
       </c>
       <c r="G11" t="n">
-        <v>7.36839628219604</v>
+        <v>7.36839580535889</v>
       </c>
       <c r="H11" t="n">
         <v>1384</v>
@@ -717,7 +717,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G12" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H12" t="n">
         <v>1065</v>
@@ -746,7 +746,7 @@
         <v>9.34914016723633</v>
       </c>
       <c r="G13" t="n">
-        <v>7.35363054275513</v>
+        <v>7.35363006591797</v>
       </c>
       <c r="H13" t="n">
         <v>2450</v>
@@ -775,7 +775,7 @@
         <v>9.56503295898438</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52344179153442</v>
+        <v>7.52344226837158</v>
       </c>
       <c r="H14" t="n">
         <v>532</v>
@@ -804,7 +804,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G15" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H15" t="n">
         <v>1384</v>
@@ -833,7 +833,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G16" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H16" t="n">
         <v>213</v>
@@ -862,7 +862,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H17" t="n">
         <v>106</v>
@@ -920,7 +920,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G19" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H19" t="n">
         <v>7776</v>
@@ -978,7 +978,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H21" t="n">
         <v>3302</v>
@@ -1007,7 +1007,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G22" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H22" t="n">
         <v>2450</v>
@@ -1036,7 +1036,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484401702881</v>
+        <v>7.43484449386597</v>
       </c>
       <c r="H23" t="n">
         <v>1065</v>
@@ -1094,7 +1094,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G25" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H25" t="n">
         <v>1384</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H26" t="n">
         <v>4154</v>
@@ -1152,7 +1152,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H27" t="n">
         <v>639</v>
@@ -1181,7 +1181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H30" t="n">
         <v>1704</v>
@@ -1268,7 +1268,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G31" t="n">
-        <v>7.39054536819458</v>
+        <v>7.39054489135742</v>
       </c>
       <c r="H31" t="n">
         <v>2237</v>
@@ -1297,7 +1297,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437692642212</v>
       </c>
       <c r="H32" t="n">
         <v>4580</v>
@@ -1326,7 +1326,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.47914266586304</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H33" t="n">
         <v>426</v>
@@ -1355,7 +1355,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.47914266586304</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H35" t="n">
         <v>2769</v>
@@ -1413,7 +1413,7 @@
         <v>9.70583438873291</v>
       </c>
       <c r="G36" t="n">
-        <v>7.63419198989868</v>
+        <v>7.63419103622437</v>
       </c>
       <c r="H36" t="n">
         <v>3196</v>
@@ -1442,7 +1442,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G37" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H37" t="n">
         <v>3089</v>
@@ -1471,7 +1471,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559087753296</v>
       </c>
       <c r="H38" t="n">
         <v>21413</v>
@@ -1500,7 +1500,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559087753296</v>
       </c>
       <c r="H39" t="n">
         <v>11186</v>
@@ -1529,7 +1529,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G40" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820896148682</v>
       </c>
       <c r="H40" t="n">
         <v>1598</v>
@@ -1558,7 +1558,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H41" t="n">
         <v>15021</v>
@@ -1587,7 +1587,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H42" t="n">
         <v>12784</v>
@@ -1616,7 +1616,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H43" t="n">
         <v>5326</v>
@@ -1645,7 +1645,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H44" t="n">
         <v>12357</v>
@@ -1674,7 +1674,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H45" t="n">
         <v>10014</v>
@@ -1703,7 +1703,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H46" t="n">
         <v>1598</v>
@@ -1761,7 +1761,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.47914266586304</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H48" t="n">
         <v>3941</v>
@@ -1790,7 +1790,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H49" t="n">
         <v>9588</v>
@@ -1819,7 +1819,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559087753296</v>
       </c>
       <c r="H50" t="n">
         <v>2556</v>
@@ -1877,7 +1877,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437692642212</v>
       </c>
       <c r="H52" t="n">
         <v>2982</v>
@@ -1964,7 +1964,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H55" t="n">
         <v>21306</v>
@@ -1993,7 +1993,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H56" t="n">
         <v>4261</v>
@@ -2022,7 +2022,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G57" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H57" t="n">
         <v>9694</v>
@@ -2051,7 +2051,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G58" t="n">
-        <v>7.64895677566528</v>
+        <v>7.6489577293396</v>
       </c>
       <c r="H58" t="n">
         <v>11186</v>
@@ -2080,7 +2080,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H59" t="n">
         <v>106</v>
@@ -2109,7 +2109,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G60" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H60" t="n">
         <v>639</v>
@@ -2138,7 +2138,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G61" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H61" t="n">
         <v>9481</v>
@@ -2167,7 +2167,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587303161621</v>
       </c>
       <c r="H62" t="n">
         <v>1065</v>
@@ -2225,7 +2225,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970363616943</v>
+        <v>7.75970268249512</v>
       </c>
       <c r="H64" t="n">
         <v>12570</v>
@@ -2254,7 +2254,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568523406982</v>
+        <v>7.85568571090698</v>
       </c>
       <c r="H65" t="n">
         <v>22052</v>
@@ -2283,7 +2283,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568523406982</v>
+        <v>7.85568571090698</v>
       </c>
       <c r="H66" t="n">
         <v>4261</v>
@@ -2341,7 +2341,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G68" t="n">
-        <v>7.87045097351074</v>
+        <v>7.8704514503479</v>
       </c>
       <c r="H68" t="n">
         <v>1704</v>
@@ -2370,7 +2370,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G69" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H69" t="n">
         <v>2343</v>
@@ -2457,7 +2457,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G72" t="n">
-        <v>7.89998435974121</v>
+        <v>7.89998388290405</v>
       </c>
       <c r="H72" t="n">
         <v>2343</v>
@@ -2486,7 +2486,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.9442834854126</v>
+        <v>7.94428253173828</v>
       </c>
       <c r="H73" t="n">
         <v>5326</v>
@@ -2515,7 +2515,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G74" t="n">
-        <v>7.89998435974121</v>
+        <v>7.89998388290405</v>
       </c>
       <c r="H74" t="n">
         <v>6924</v>
@@ -2544,7 +2544,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89998435974121</v>
+        <v>7.89998388290405</v>
       </c>
       <c r="H75" t="n">
         <v>1065</v>
@@ -2573,7 +2573,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G76" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H76" t="n">
         <v>852</v>
@@ -2602,7 +2602,7 @@
         <v>9.87479400634766</v>
       </c>
       <c r="G77" t="n">
-        <v>7.76708650588989</v>
+        <v>7.76708698272705</v>
       </c>
       <c r="H77" t="n">
         <v>7244</v>
@@ -2631,7 +2631,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G78" t="n">
-        <v>7.87045097351074</v>
+        <v>7.8704514503479</v>
       </c>
       <c r="H78" t="n">
         <v>639</v>
@@ -2660,7 +2660,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.78923606872559</v>
+        <v>7.7892370223999</v>
       </c>
       <c r="H79" t="n">
         <v>5007</v>
@@ -2689,7 +2689,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G80" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H80" t="n">
         <v>18430</v>
@@ -2747,7 +2747,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H82" t="n">
         <v>4367</v>
@@ -2776,7 +2776,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H84" t="n">
         <v>10653</v>
@@ -2834,7 +2834,7 @@
         <v>10.0249805450439</v>
       </c>
       <c r="G85" t="n">
-        <v>7.88521766662598</v>
+        <v>7.88521718978882</v>
       </c>
       <c r="H85" t="n">
         <v>6072</v>
@@ -2863,7 +2863,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H86" t="n">
         <v>33664</v>
@@ -2950,7 +2950,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H89" t="n">
         <v>15021</v>
@@ -2979,7 +2979,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H90" t="n">
         <v>5859</v>
@@ -3008,7 +3008,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H91" t="n">
         <v>2450</v>
@@ -3066,7 +3066,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H93" t="n">
         <v>958</v>
@@ -3124,7 +3124,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H95" t="n">
         <v>2556</v>
@@ -3182,7 +3182,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H97" t="n">
         <v>2556</v>
@@ -3211,7 +3211,7 @@
         <v>9.88418102264404</v>
       </c>
       <c r="G98" t="n">
-        <v>7.77447128295898</v>
+        <v>7.77447032928467</v>
       </c>
       <c r="H98" t="n">
         <v>1278</v>
@@ -3240,7 +3240,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H99" t="n">
         <v>11612</v>
@@ -3269,7 +3269,7 @@
         <v>9.78092670440674</v>
       </c>
       <c r="G100" t="n">
-        <v>7.69325542449951</v>
+        <v>7.69325590133667</v>
       </c>
       <c r="H100" t="n">
         <v>1811</v>
@@ -3356,7 +3356,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587303161621</v>
       </c>
       <c r="H103" t="n">
         <v>852</v>
@@ -3385,7 +3385,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H104" t="n">
         <v>1065</v>
@@ -3414,7 +3414,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G106" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H106" t="n">
         <v>852</v>
@@ -3472,7 +3472,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G107" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H107" t="n">
         <v>3302</v>
@@ -3501,7 +3501,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G108" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>9.79970073699951</v>
       </c>
       <c r="G109" t="n">
-        <v>7.70802211761475</v>
+        <v>7.70802164077759</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H110" t="n">
         <v>319</v>
@@ -3588,7 +3588,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G111" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H111" t="n">
         <v>4794</v>
@@ -3617,7 +3617,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G112" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H113" t="n">
         <v>2237</v>
@@ -3675,7 +3675,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H114" t="n">
         <v>4687</v>
@@ -3704,7 +3704,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H115" t="n">
         <v>213</v>
@@ -3733,7 +3733,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755407333374</v>
+        <v>7.7375545501709</v>
       </c>
       <c r="H116" t="n">
         <v>319</v>
@@ -3762,7 +3762,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G117" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H117" t="n">
         <v>319</v>
@@ -3791,7 +3791,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063829421997</v>
+        <v>7.70063781738281</v>
       </c>
       <c r="H118" t="n">
         <v>50070</v>
@@ -3849,7 +3849,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G120" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H120" t="n">
         <v>852</v>
@@ -3878,7 +3878,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H121" t="n">
         <v>4580</v>
@@ -3965,7 +3965,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H124" t="n">
         <v>7137</v>
@@ -4023,7 +4023,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633916854858</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H126" t="n">
         <v>426</v>
@@ -4052,7 +4052,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G127" t="n">
-        <v>7.64895677566528</v>
+        <v>7.6489577293396</v>
       </c>
       <c r="H127" t="n">
         <v>1384</v>
@@ -4081,7 +4081,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G128" t="n">
-        <v>7.64895677566528</v>
+        <v>7.6489577293396</v>
       </c>
       <c r="H128" t="n">
         <v>2130</v>
@@ -4168,7 +4168,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H131" t="n">
         <v>1811</v>
@@ -4197,7 +4197,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G132" t="n">
-        <v>7.62680578231812</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H132" t="n">
         <v>1704</v>
@@ -4226,7 +4226,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G133" t="n">
-        <v>7.62680578231812</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H133" t="n">
         <v>2769</v>
@@ -4255,7 +4255,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.6711049079895</v>
+        <v>7.67110538482666</v>
       </c>
       <c r="H134" t="n">
         <v>852</v>
@@ -4284,7 +4284,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157342910767</v>
+        <v>7.64157295227051</v>
       </c>
       <c r="H135" t="n">
         <v>1384</v>
@@ -4313,7 +4313,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H136" t="n">
         <v>2556</v>
@@ -4342,7 +4342,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H137" t="n">
         <v>10440</v>
@@ -4400,7 +4400,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H139" t="n">
         <v>6498</v>
@@ -4429,7 +4429,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H140" t="n">
         <v>7457</v>
@@ -4458,7 +4458,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H141" t="n">
         <v>18323</v>
@@ -4487,7 +4487,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G142" t="n">
-        <v>7.5825080871582</v>
+        <v>7.58250856399536</v>
       </c>
       <c r="H142" t="n">
         <v>639</v>
@@ -4516,7 +4516,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H143" t="n">
         <v>8629</v>
@@ -4545,7 +4545,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G144" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820896148682</v>
       </c>
       <c r="H144" t="n">
         <v>213</v>
@@ -4574,7 +4574,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H145" t="n">
         <v>1065</v>
@@ -4690,7 +4690,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H149" t="n">
         <v>2663</v>
@@ -4748,7 +4748,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H151" t="n">
         <v>12997</v>
@@ -4777,7 +4777,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G152" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820896148682</v>
       </c>
       <c r="H152" t="n">
         <v>13742</v>
@@ -4806,7 +4806,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G153" t="n">
-        <v>7.62680578231812</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H153" t="n">
         <v>639</v>
@@ -4835,7 +4835,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H154" t="n">
         <v>3409</v>
@@ -4893,7 +4893,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633916854858</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H156" t="n">
         <v>426</v>
@@ -4922,7 +4922,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G157" t="n">
-        <v>7.62680578231812</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H157" t="n">
         <v>2343</v>
@@ -4951,7 +4951,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G158" t="n">
-        <v>7.62680578231812</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942434310913</v>
+        <v>7.61942338943481</v>
       </c>
       <c r="H160" t="n">
         <v>26953</v>
@@ -5038,7 +5038,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942434310913</v>
+        <v>7.61942338943481</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G162" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H162" t="n">
         <v>745</v>
@@ -5096,7 +5096,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063829421997</v>
+        <v>7.70063781738281</v>
       </c>
       <c r="H163" t="n">
         <v>1171</v>
@@ -5125,7 +5125,7 @@
         <v>9.72460746765137</v>
       </c>
       <c r="G164" t="n">
-        <v>7.64895677566528</v>
+        <v>7.6489577293396</v>
       </c>
       <c r="H164" t="n">
         <v>1384</v>
@@ -5154,7 +5154,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633916854858</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H165" t="n">
         <v>2343</v>
@@ -5183,7 +5183,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633916854858</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540498733521</v>
+        <v>7.71540451049805</v>
       </c>
       <c r="H167" t="n">
         <v>745</v>
@@ -5241,7 +5241,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633916854858</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H168" t="n">
         <v>46022</v>
@@ -5270,7 +5270,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G169" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H169" t="n">
         <v>4367</v>
@@ -5299,7 +5299,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G170" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H170" t="n">
         <v>106</v>
@@ -5328,7 +5328,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587303161621</v>
       </c>
       <c r="H171" t="n">
         <v>21519</v>
@@ -5357,7 +5357,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587303161621</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540498733521</v>
+        <v>7.71540451049805</v>
       </c>
       <c r="H173" t="n">
         <v>5433</v>
@@ -5415,7 +5415,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G174" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820896148682</v>
       </c>
       <c r="H174" t="n">
         <v>32918</v>
@@ -5473,7 +5473,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727430343628</v>
+        <v>7.59727334976196</v>
       </c>
       <c r="H176" t="n">
         <v>745</v>
@@ -5502,7 +5502,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633916854858</v>
+        <v>7.65633869171143</v>
       </c>
       <c r="H177" t="n">
         <v>5859</v>
@@ -5560,7 +5560,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G179" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820896148682</v>
       </c>
       <c r="H179" t="n">
         <v>13210</v>
@@ -5647,7 +5647,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559087753296</v>
       </c>
       <c r="H182" t="n">
         <v>6072</v>
@@ -5676,7 +5676,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559087753296</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G184" t="n">
-        <v>7.53820943832397</v>
+        <v>7.53820896148682</v>
       </c>
       <c r="H184" t="n">
         <v>7457</v>
@@ -5763,7 +5763,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H186" t="n">
         <v>7137</v>
@@ -5792,7 +5792,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G187" t="n">
-        <v>7.5825080871582</v>
+        <v>7.58250856399536</v>
       </c>
       <c r="H187" t="n">
         <v>10014</v>
@@ -5821,7 +5821,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H188" t="n">
         <v>3196</v>
@@ -5850,7 +5850,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512426376343</v>
+        <v>7.57512521743774</v>
       </c>
       <c r="H189" t="n">
         <v>106</v>
@@ -5937,7 +5937,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H192" t="n">
         <v>213</v>
@@ -5966,7 +5966,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G193" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H193" t="n">
         <v>9481</v>
@@ -5995,7 +5995,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G194" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H194" t="n">
         <v>8735</v>
@@ -6024,7 +6024,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G195" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H195" t="n">
         <v>3196</v>
@@ -6053,7 +6053,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G196" t="n">
-        <v>7.39054536819458</v>
+        <v>7.39054489135742</v>
       </c>
       <c r="H196" t="n">
         <v>12784</v>
@@ -6082,7 +6082,7 @@
         <v>9.39607334136963</v>
       </c>
       <c r="G197" t="n">
-        <v>7.39054536819458</v>
+        <v>7.39054489135742</v>
       </c>
       <c r="H197" t="n">
         <v>9055</v>
@@ -6111,7 +6111,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G198" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H198" t="n">
         <v>10653</v>
@@ -6140,7 +6140,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G199" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H199" t="n">
         <v>15553</v>
@@ -6169,7 +6169,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H201" t="n">
         <v>745</v>
@@ -6227,7 +6227,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H203" t="n">
         <v>1384</v>
@@ -6285,7 +6285,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007875442505</v>
+        <v>7.42007970809937</v>
       </c>
       <c r="H204" t="n">
         <v>958</v>
@@ -6314,7 +6314,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G205" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H205" t="n">
         <v>106</v>
@@ -6343,7 +6343,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H206" t="n">
         <v>5220</v>
@@ -6401,7 +6401,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G208" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H208" t="n">
         <v>2130</v>
@@ -6430,7 +6430,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H209" t="n">
         <v>319</v>
@@ -6459,7 +6459,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G210" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H210" t="n">
         <v>1171</v>
@@ -6488,7 +6488,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H211" t="n">
         <v>3728</v>
@@ -6517,7 +6517,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H212" t="n">
         <v>958</v>
@@ -6546,7 +6546,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G213" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H213" t="n">
         <v>27379</v>
@@ -6575,7 +6575,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G214" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H214" t="n">
         <v>12357</v>
@@ -6604,7 +6604,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H215" t="n">
         <v>639</v>
@@ -6633,7 +6633,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H216" t="n">
         <v>11612</v>
@@ -6662,7 +6662,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H217" t="n">
         <v>192826</v>
@@ -6691,7 +6691,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G218" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H218" t="n">
         <v>82563</v>
@@ -6720,7 +6720,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G219" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H219" t="n">
         <v>55504</v>
@@ -6749,7 +6749,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H220" t="n">
         <v>61683</v>
@@ -6778,7 +6778,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G221" t="n">
-        <v>7.89998435974121</v>
+        <v>7.89998388290405</v>
       </c>
       <c r="H221" t="n">
         <v>44637</v>
@@ -6807,7 +6807,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G222" t="n">
-        <v>7.89998435974121</v>
+        <v>7.89998388290405</v>
       </c>
       <c r="H222" t="n">
         <v>38565</v>
@@ -6836,7 +6836,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G223" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H223" t="n">
         <v>7883</v>
@@ -6865,7 +6865,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G224" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H224" t="n">
         <v>21519</v>
@@ -6894,7 +6894,7 @@
         <v>9.94988822937012</v>
       </c>
       <c r="G225" t="n">
-        <v>7.82615280151367</v>
+        <v>7.82615232467651</v>
       </c>
       <c r="H225" t="n">
         <v>1491</v>
@@ -6923,7 +6923,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H226" t="n">
         <v>16086</v>
@@ -6952,7 +6952,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H227" t="n">
         <v>63174</v>
@@ -6981,7 +6981,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75231981277466</v>
+        <v>7.75232028961182</v>
       </c>
       <c r="H228" t="n">
         <v>21200</v>
@@ -7010,7 +7010,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G229" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H229" t="n">
         <v>34623</v>
@@ -7068,7 +7068,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H231" t="n">
         <v>3089</v>
@@ -7097,7 +7097,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H232" t="n">
         <v>7883</v>
@@ -7126,7 +7126,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H233" t="n">
         <v>23970</v>
@@ -7184,7 +7184,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H235" t="n">
         <v>9055</v>
@@ -7213,7 +7213,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H236" t="n">
         <v>8203</v>
@@ -7300,7 +7300,7 @@
         <v>9.76215362548828</v>
       </c>
       <c r="G239" t="n">
-        <v>7.67848968505859</v>
+        <v>7.67848920822144</v>
       </c>
       <c r="H239" t="n">
         <v>29829</v>
@@ -7358,7 +7358,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H241" t="n">
         <v>39630</v>
@@ -7387,7 +7387,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H242" t="n">
         <v>19495</v>
@@ -7416,7 +7416,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H243" t="n">
         <v>23650</v>
@@ -7445,7 +7445,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H244" t="n">
         <v>36967</v>
@@ -7474,7 +7474,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.45699453353882</v>
+        <v>7.45699405670166</v>
       </c>
       <c r="H245" t="n">
         <v>35049</v>
@@ -7503,7 +7503,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.5308256149292</v>
+        <v>7.53082609176636</v>
       </c>
       <c r="H246" t="n">
         <v>35688</v>
@@ -7532,7 +7532,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H247" t="n">
         <v>25674</v>
@@ -7561,7 +7561,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H248" t="n">
         <v>1598</v>
@@ -7590,7 +7590,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G249" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H249" t="n">
         <v>42400</v>
@@ -7619,7 +7619,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H250" t="n">
         <v>13742</v>
@@ -7706,7 +7706,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G253" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H253" t="n">
         <v>2769</v>
@@ -7735,7 +7735,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G254" t="n">
-        <v>7.38316202163696</v>
+        <v>7.38316297531128</v>
       </c>
       <c r="H254" t="n">
         <v>1065</v>
@@ -7793,7 +7793,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H256" t="n">
         <v>53586</v>
@@ -7822,7 +7822,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H258" t="n">
         <v>1384</v>
@@ -7909,7 +7909,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H260" t="n">
         <v>2343</v>
@@ -7967,7 +7967,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H262" t="n">
         <v>14062</v>
@@ -7996,7 +7996,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H263" t="n">
         <v>1598</v>
@@ -8112,7 +8112,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H267" t="n">
         <v>7457</v>
@@ -8141,7 +8141,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H268" t="n">
         <v>11825</v>
@@ -8170,7 +8170,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H269" t="n">
         <v>4474</v>
@@ -8257,7 +8257,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H272" t="n">
         <v>20880</v>
@@ -8344,7 +8344,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H275" t="n">
         <v>2663</v>
@@ -8373,7 +8373,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H276" t="n">
         <v>426</v>
@@ -8402,7 +8402,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H277" t="n">
         <v>19176</v>
@@ -8431,7 +8431,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H278" t="n">
         <v>532</v>
@@ -8460,7 +8460,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H279" t="n">
         <v>6392</v>
@@ -8489,7 +8489,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H280" t="n">
         <v>1171</v>
@@ -8518,7 +8518,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.27241563796997</v>
+        <v>7.27241468429565</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G282" t="n">
-        <v>7.23549890518188</v>
+        <v>7.23549938201904</v>
       </c>
       <c r="H282" t="n">
         <v>39097</v>
@@ -8605,7 +8605,7 @@
         <v>9.19895267486572</v>
       </c>
       <c r="G284" t="n">
-        <v>7.23549890518188</v>
+        <v>7.23549938201904</v>
       </c>
       <c r="H284" t="n">
         <v>19389</v>
@@ -9069,7 +9069,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H300" t="n">
         <v>23011</v>
@@ -9127,7 +9127,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G302" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H302" t="n">
         <v>4474</v>
@@ -9156,7 +9156,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400423049927</v>
+        <v>7.01400470733643</v>
       </c>
       <c r="H303" t="n">
         <v>639</v>
@@ -9214,7 +9214,7 @@
         <v>9.0112190246582</v>
       </c>
       <c r="G305" t="n">
-        <v>7.08783626556396</v>
+        <v>7.08783578872681</v>
       </c>
       <c r="H305" t="n">
         <v>19282</v>
@@ -9272,7 +9272,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H307" t="n">
         <v>2130</v>
@@ -9359,7 +9359,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H310" t="n">
         <v>4048</v>
@@ -9417,7 +9417,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H312" t="n">
         <v>2663</v>
@@ -9446,7 +9446,7 @@
         <v>8.72961807250977</v>
       </c>
       <c r="G313" t="n">
-        <v>6.86634159088135</v>
+        <v>6.86634063720703</v>
       </c>
       <c r="H313" t="n">
         <v>5326</v>
@@ -9475,7 +9475,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H314" t="n">
         <v>51349</v>
@@ -9504,7 +9504,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H315" t="n">
         <v>958</v>
@@ -9533,7 +9533,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H316" t="n">
         <v>213</v>
@@ -9562,7 +9562,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H317" t="n">
         <v>54438</v>
@@ -9591,7 +9591,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.90325689315796</v>
+        <v>6.90325736999512</v>
       </c>
       <c r="H318" t="n">
         <v>27379</v>
@@ -9649,7 +9649,7 @@
         <v>8.63575077056885</v>
       </c>
       <c r="G320" t="n">
-        <v>6.79250907897949</v>
+        <v>6.79250860214233</v>
       </c>
       <c r="H320" t="n">
         <v>9907</v>
@@ -9765,7 +9765,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.60792970657349</v>
+        <v>6.60793018341064</v>
       </c>
       <c r="H324" t="n">
         <v>5859</v>
@@ -9794,7 +9794,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G325" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H325" t="n">
         <v>9161</v>
@@ -9881,7 +9881,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H328" t="n">
         <v>25568</v>
@@ -9910,7 +9910,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G329" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H329" t="n">
         <v>958</v>
@@ -9939,7 +9939,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G330" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H332" t="n">
         <v>4367</v>
@@ -10026,7 +10026,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H333" t="n">
         <v>6924</v>
@@ -10055,7 +10055,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G334" t="n">
-        <v>6.42335176467896</v>
+        <v>6.42335081100464</v>
       </c>
       <c r="H334" t="n">
         <v>2343</v>
@@ -10113,7 +10113,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G336" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H336" t="n">
         <v>2556</v>
@@ -10142,7 +10142,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G337" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H337" t="n">
         <v>7563</v>
@@ -10171,7 +10171,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G338" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G339" t="n">
-        <v>6.42335176467896</v>
+        <v>6.42335081100464</v>
       </c>
       <c r="H339" t="n">
         <v>6285</v>
@@ -10229,7 +10229,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G340" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H340" t="n">
         <v>532</v>
@@ -10258,7 +10258,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G341" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H341" t="n">
         <v>5539</v>
@@ -10287,7 +10287,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G342" t="n">
-        <v>6.49718332290649</v>
+        <v>6.49718284606934</v>
       </c>
       <c r="H342" t="n">
         <v>2556</v>
@@ -10461,7 +10461,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H348" t="n">
         <v>12677</v>
@@ -10490,7 +10490,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G349" t="n">
-        <v>6.42335176467896</v>
+        <v>6.42335081100464</v>
       </c>
       <c r="H349" t="n">
         <v>19389</v>
@@ -10519,7 +10519,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643550872803</v>
+        <v>6.38643598556519</v>
       </c>
       <c r="H350" t="n">
         <v>6605</v>
@@ -10548,7 +10548,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G351" t="n">
-        <v>6.42335176467896</v>
+        <v>6.42335081100464</v>
       </c>
       <c r="H351" t="n">
         <v>13316</v>
@@ -10577,7 +10577,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G352" t="n">
-        <v>6.42335176467896</v>
+        <v>6.42335081100464</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G353" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H353" t="n">
         <v>2663</v>
@@ -10635,7 +10635,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G354" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H354" t="n">
         <v>7670</v>
@@ -10664,7 +10664,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G355" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H355" t="n">
         <v>8948</v>
@@ -10780,7 +10780,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G359" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H359" t="n">
         <v>2982</v>
@@ -10809,7 +10809,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G360" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H360" t="n">
         <v>6178</v>
@@ -10867,7 +10867,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G362" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H362" t="n">
         <v>3196</v>
@@ -10925,7 +10925,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G364" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H364" t="n">
         <v>3409</v>
@@ -10983,7 +10983,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G366" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H366" t="n">
         <v>532</v>
@@ -11012,7 +11012,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G367" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G368" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H368" t="n">
         <v>1065</v>
@@ -11070,7 +11070,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G369" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H369" t="n">
         <v>9268</v>
@@ -11099,7 +11099,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G370" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G371" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>7.88481616973877</v>
       </c>
       <c r="G372" t="n">
-        <v>6.20185565948486</v>
+        <v>6.20185661315918</v>
       </c>
       <c r="H372" t="n">
         <v>3196</v>
@@ -11186,7 +11186,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G373" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H373" t="n">
         <v>6392</v>
@@ -11215,7 +11215,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H374" t="n">
         <v>2556</v>
@@ -11244,7 +11244,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H375" t="n">
         <v>3196</v>
@@ -11302,7 +11302,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H377" t="n">
         <v>15340</v>
@@ -11389,7 +11389,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G380" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H380" t="n">
         <v>1598</v>
@@ -11418,7 +11418,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G381" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G382" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H382" t="n">
         <v>1278</v>
@@ -11476,7 +11476,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G383" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H383" t="n">
         <v>14169</v>
@@ -11650,7 +11650,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H389" t="n">
         <v>3196</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H390" t="n">
         <v>8203</v>
@@ -11708,7 +11708,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H391" t="n">
         <v>5433</v>
@@ -11766,7 +11766,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G393" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H393" t="n">
         <v>30042</v>
@@ -11940,7 +11940,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G399" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H399" t="n">
         <v>18323</v>
@@ -11998,7 +11998,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G401" t="n">
-        <v>5.7957820892334</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H401" t="n">
         <v>958</v>
@@ -12085,7 +12085,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G404" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H404" t="n">
         <v>20454</v>
@@ -12114,7 +12114,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G405" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H405" t="n">
         <v>34197</v>
@@ -12143,7 +12143,7 @@
         <v>7.79094982147217</v>
       </c>
       <c r="G406" t="n">
-        <v>6.12802505493164</v>
+        <v>6.12802457809448</v>
       </c>
       <c r="H406" t="n">
         <v>5326</v>
@@ -12201,7 +12201,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G408" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H408" t="n">
         <v>9801</v>
@@ -12259,7 +12259,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G410" t="n">
-        <v>5.7957820892334</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H410" t="n">
         <v>9588</v>
@@ -12433,7 +12433,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G416" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H416" t="n">
         <v>3089</v>
@@ -12462,7 +12462,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H417" t="n">
         <v>106</v>
@@ -12491,7 +12491,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H418" t="n">
         <v>639</v>
@@ -12520,7 +12520,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H419" t="n">
         <v>3089</v>
@@ -12549,7 +12549,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G420" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H420" t="n">
         <v>532</v>
@@ -12810,7 +12810,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G429" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H429" t="n">
         <v>7990</v>
@@ -12897,7 +12897,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G432" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H432" t="n">
         <v>7776</v>
@@ -12955,7 +12955,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G434" t="n">
-        <v>5.7957820892334</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H434" t="n">
         <v>6498</v>
@@ -12984,7 +12984,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H435" t="n">
         <v>13103</v>
@@ -13013,7 +13013,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H436" t="n">
         <v>13636</v>
@@ -13042,7 +13042,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H437" t="n">
         <v>1598</v>
@@ -13158,7 +13158,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344568252563</v>
+        <v>5.94344520568848</v>
       </c>
       <c r="H441" t="n">
         <v>33664</v>
@@ -13216,7 +13216,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G443" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H443" t="n">
         <v>30149</v>
@@ -13274,7 +13274,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G445" t="n">
-        <v>5.7957820892334</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H445" t="n">
         <v>5007</v>
@@ -13303,7 +13303,7 @@
         <v>7.50934886932373</v>
       </c>
       <c r="G446" t="n">
-        <v>5.90652990341187</v>
+        <v>5.90652942657471</v>
       </c>
       <c r="H446" t="n">
         <v>21732</v>
@@ -13390,7 +13390,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G449" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H449" t="n">
         <v>4261</v>
@@ -13419,7 +13419,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G450" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H450" t="n">
         <v>5752</v>
@@ -13448,7 +13448,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G451" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H451" t="n">
         <v>8735</v>
@@ -13477,7 +13477,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G452" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H452" t="n">
         <v>16512</v>
@@ -13535,7 +13535,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G454" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428693771362</v>
       </c>
       <c r="H454" t="n">
         <v>2769</v>
@@ -13622,7 +13622,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G457" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H457" t="n">
         <v>20347</v>
@@ -13738,7 +13738,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G461" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H461" t="n">
         <v>106</v>
@@ -13796,7 +13796,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G463" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H463" t="n">
         <v>2556</v>
@@ -13854,7 +13854,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G465" t="n">
-        <v>5.7957820892334</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H465" t="n">
         <v>1065</v>
@@ -14057,7 +14057,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G472" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H472" t="n">
         <v>106</v>
@@ -14086,7 +14086,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G473" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H473" t="n">
         <v>21626</v>
@@ -14115,7 +14115,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G474" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H474" t="n">
         <v>1917</v>
@@ -14144,7 +14144,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G475" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H475" t="n">
         <v>7670</v>
@@ -14173,7 +14173,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G476" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H476" t="n">
         <v>4900</v>
@@ -14202,7 +14202,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G477" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H477" t="n">
         <v>4900</v>
@@ -14231,7 +14231,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G478" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H478" t="n">
         <v>5539</v>
@@ -14318,7 +14318,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737163543701</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H481" t="n">
         <v>20241</v>
@@ -14376,7 +14376,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G483" t="n">
-        <v>5.50045537948608</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H483" t="n">
         <v>3409</v>
@@ -14405,7 +14405,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G484" t="n">
-        <v>5.50045537948608</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H484" t="n">
         <v>2343</v>
@@ -14434,7 +14434,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G485" t="n">
-        <v>5.50045537948608</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H485" t="n">
         <v>19176</v>
@@ -14463,7 +14463,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G486" t="n">
-        <v>5.50045537948608</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H486" t="n">
         <v>4154</v>
@@ -14869,7 +14869,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G500" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H500" t="n">
         <v>50603</v>
@@ -14898,7 +14898,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G501" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H501" t="n">
         <v>18856</v>
@@ -14927,7 +14927,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587743759155</v>
       </c>
       <c r="H502" t="n">
         <v>12251</v>
@@ -14956,7 +14956,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G503" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H503" t="n">
         <v>20561</v>
@@ -15043,7 +15043,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587743759155</v>
       </c>
       <c r="H506" t="n">
         <v>11399</v>
@@ -15130,7 +15130,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G509" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H509" t="n">
         <v>39417</v>
@@ -15159,7 +15159,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G510" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H510" t="n">
         <v>33345</v>
@@ -15188,7 +15188,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G511" t="n">
-        <v>5.27896165847778</v>
+        <v>5.27896118164062</v>
       </c>
       <c r="H511" t="n">
         <v>12251</v>
@@ -15217,7 +15217,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821336746216</v>
+        <v>5.168212890625</v>
       </c>
       <c r="H512" t="n">
         <v>25248</v>
@@ -15246,7 +15246,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821336746216</v>
+        <v>5.168212890625</v>
       </c>
       <c r="H513" t="n">
         <v>33877</v>
@@ -15275,7 +15275,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G514" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H514" t="n">
         <v>35582</v>
@@ -15304,7 +15304,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G515" t="n">
-        <v>5.20512962341309</v>
+        <v>5.20512914657593</v>
       </c>
       <c r="H515" t="n">
         <v>9374</v>
@@ -15333,7 +15333,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G516" t="n">
-        <v>5.20512962341309</v>
+        <v>5.20512914657593</v>
       </c>
       <c r="H516" t="n">
         <v>8203</v>
@@ -15362,7 +15362,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G517" t="n">
-        <v>5.20512962341309</v>
+        <v>5.20512914657593</v>
       </c>
       <c r="H517" t="n">
         <v>11931</v>
@@ -15391,7 +15391,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G518" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H518" t="n">
         <v>33451</v>
@@ -15420,7 +15420,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G519" t="n">
-        <v>5.28634405136108</v>
+        <v>5.28634452819824</v>
       </c>
       <c r="H519" t="n">
         <v>9268</v>
@@ -15478,7 +15478,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G521" t="n">
-        <v>5.28634405136108</v>
+        <v>5.28634452819824</v>
       </c>
       <c r="H521" t="n">
         <v>22691</v>
@@ -15565,7 +15565,7 @@
         <v>6.83350801467896</v>
       </c>
       <c r="G524" t="n">
-        <v>5.37494277954102</v>
+        <v>5.37494230270386</v>
       </c>
       <c r="H524" t="n">
         <v>3302</v>
@@ -15652,7 +15652,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737163543701</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H527" t="n">
         <v>16193</v>
@@ -15681,7 +15681,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49307346343994</v>
+        <v>5.49307298660278</v>
       </c>
       <c r="H528" t="n">
         <v>4048</v>
@@ -15739,7 +15739,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G530" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550231933594</v>
       </c>
       <c r="H530" t="n">
         <v>14591</v>
@@ -15797,7 +15797,7 @@
         <v>7.22774791717529</v>
       </c>
       <c r="G532" t="n">
-        <v>5.68503475189209</v>
+        <v>5.68503427505493</v>
       </c>
       <c r="H532" t="n">
         <v>15759</v>
@@ -15884,7 +15884,7 @@
         <v>7.37793493270874</v>
       </c>
       <c r="G535" t="n">
-        <v>5.80316543579102</v>
+        <v>5.80316495895386</v>
       </c>
       <c r="H535" t="n">
         <v>4634</v>
@@ -15942,7 +15942,7 @@
         <v>7.19020223617554</v>
       </c>
       <c r="G537" t="n">
-        <v>5.6555027961731</v>
+        <v>5.65550231933594</v>
       </c>
       <c r="H537" t="n">
         <v>22654</v>
@@ -16000,7 +16000,7 @@
         <v>7.17142820358276</v>
       </c>
       <c r="G539" t="n">
-        <v>5.64073610305786</v>
+        <v>5.6407356262207</v>
       </c>
       <c r="H539" t="n">
         <v>7267</v>
@@ -16058,7 +16058,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.50783920288086</v>
+        <v>5.50783967971802</v>
       </c>
       <c r="H541" t="n">
         <v>31068</v>
@@ -16116,7 +16116,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G543" t="n">
-        <v>5.49307346343994</v>
+        <v>5.49307298660278</v>
       </c>
       <c r="H543" t="n">
         <v>13326</v>
@@ -16348,7 +16348,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.48405170440674</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H551" t="n">
         <v>3089</v>
@@ -16377,7 +16377,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.48405170440674</v>
+        <v>5.4840521812439</v>
       </c>
       <c r="H552" t="n">
         <v>9976</v>
@@ -16464,7 +16464,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G555" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H555" t="n">
         <v>3867</v>
@@ -16493,7 +16493,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G556" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H556" t="n">
         <v>4442</v>
@@ -16522,7 +16522,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G557" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H557" t="n">
         <v>13819</v>
@@ -16551,7 +16551,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G558" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H558" t="n">
         <v>20885</v>
@@ -16725,7 +16725,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H564" t="n">
         <v>2151</v>
@@ -16754,7 +16754,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H565" t="n">
         <v>6946</v>
@@ -16783,7 +16783,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H566" t="n">
         <v>6002</v>
@@ -16870,7 +16870,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H569" t="n">
         <v>8874</v>
@@ -16899,7 +16899,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G570" t="n">
-        <v>5.69971656799316</v>
+        <v>5.69971704483032</v>
       </c>
       <c r="H570" t="n">
         <v>10333</v>
@@ -16986,7 +16986,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.82295417785645</v>
+        <v>5.82295370101929</v>
       </c>
       <c r="H573" t="n">
         <v>2375</v>
@@ -17160,7 +17160,7 @@
         <v>7.11510801315308</v>
       </c>
       <c r="G579" t="n">
-        <v>5.83835887908936</v>
+        <v>5.8383584022522</v>
       </c>
       <c r="H579" t="n">
         <v>7254</v>
@@ -17363,7 +17363,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G586" t="n">
-        <v>5.6843113899231</v>
+        <v>5.68431234359741</v>
       </c>
       <c r="H586" t="n">
         <v>1097</v>
@@ -17392,7 +17392,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G587" t="n">
-        <v>5.6689076423645</v>
+        <v>5.66890716552734</v>
       </c>
       <c r="H587" t="n">
         <v>10990</v>
@@ -17450,7 +17450,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H589" t="n">
         <v>5812</v>
@@ -17479,7 +17479,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G590" t="n">
-        <v>5.6689076423645</v>
+        <v>5.66890716552734</v>
       </c>
       <c r="H590" t="n">
         <v>7426</v>
@@ -17508,7 +17508,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.57647943496704</v>
+        <v>5.5764799118042</v>
       </c>
       <c r="H591" t="n">
         <v>11995</v>
@@ -17595,7 +17595,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H594" t="n">
         <v>5028</v>
@@ -17827,7 +17827,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G602" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H602" t="n">
         <v>5214</v>
@@ -18001,7 +18001,7 @@
         <v>6.30785322189331</v>
       </c>
       <c r="G608" t="n">
-        <v>5.17595911026001</v>
+        <v>5.17595863342285</v>
       </c>
       <c r="H608" t="n">
         <v>11796</v>
@@ -18117,7 +18117,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G612" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H612" t="n">
         <v>17032</v>
@@ -18436,7 +18436,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G623" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H623" t="n">
         <v>4481</v>
@@ -18465,7 +18465,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G624" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H624" t="n">
         <v>11485</v>
@@ -18610,7 +18610,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H629" t="n">
         <v>53531</v>
@@ -18639,7 +18639,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G630" t="n">
-        <v>5.6843113899231</v>
+        <v>5.68431234359741</v>
       </c>
       <c r="H630" t="n">
         <v>81260</v>
@@ -18668,7 +18668,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H631" t="n">
         <v>34982</v>
@@ -18784,7 +18784,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54567003250122</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H635" t="n">
         <v>39040</v>
@@ -18929,7 +18929,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G640" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H640" t="n">
         <v>38746</v>
@@ -18958,7 +18958,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G641" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H641" t="n">
         <v>12988</v>
@@ -19451,7 +19451,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G658" t="n">
-        <v>5.1913628578186</v>
+        <v>5.19136333465576</v>
       </c>
       <c r="H658" t="n">
         <v>3495</v>
@@ -19509,7 +19509,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G660" t="n">
-        <v>5.1913628578186</v>
+        <v>5.19136333465576</v>
       </c>
       <c r="H660" t="n">
         <v>37725</v>
@@ -19712,7 +19712,7 @@
         <v>6.10134601593018</v>
       </c>
       <c r="G667" t="n">
-        <v>5.00650835037231</v>
+        <v>5.00650787353516</v>
       </c>
       <c r="H667" t="n">
         <v>97565</v>
@@ -19741,7 +19741,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06812572479248</v>
+        <v>5.06812620162964</v>
       </c>
       <c r="H668" t="n">
         <v>18182</v>
@@ -19770,7 +19770,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G669" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974452972412</v>
       </c>
       <c r="H669" t="n">
         <v>4938</v>
@@ -19886,7 +19886,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G673" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974452972412</v>
       </c>
       <c r="H673" t="n">
         <v>7144</v>
@@ -20089,7 +20089,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G680" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H680" t="n">
         <v>192872</v>
@@ -20234,7 +20234,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G685" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H685" t="n">
         <v>67173</v>
@@ -20321,7 +20321,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G688" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H688" t="n">
         <v>23554</v>
@@ -20437,7 +20437,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G692" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H692" t="n">
         <v>9073</v>
@@ -20466,7 +20466,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G693" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H693" t="n">
         <v>65443</v>
@@ -20524,7 +20524,7 @@
         <v>6.60822677612305</v>
       </c>
       <c r="G695" t="n">
-        <v>5.42243337631226</v>
+        <v>5.4224328994751</v>
       </c>
       <c r="H695" t="n">
         <v>13441</v>
@@ -20553,7 +20553,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H696" t="n">
         <v>21135</v>
@@ -20640,7 +20640,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G699" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H699" t="n">
         <v>7492</v>
@@ -20756,7 +20756,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G703" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H703" t="n">
         <v>59216</v>
@@ -20814,7 +20814,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H705" t="n">
         <v>4626</v>
@@ -20930,7 +20930,7 @@
         <v>6.58945417404175</v>
       </c>
       <c r="G709" t="n">
-        <v>5.40702867507935</v>
+        <v>5.4070291519165</v>
       </c>
       <c r="H709" t="n">
         <v>14955</v>
@@ -20959,7 +20959,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G710" t="n">
-        <v>5.37621927261353</v>
+        <v>5.37621974945068</v>
       </c>
       <c r="H710" t="n">
         <v>22162</v>
@@ -21104,7 +21104,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G715" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H715" t="n">
         <v>49349</v>
@@ -21133,7 +21133,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G716" t="n">
-        <v>5.34541034698486</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H716" t="n">
         <v>22905</v>
@@ -21423,7 +21423,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G726" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974452972412</v>
       </c>
       <c r="H726" t="n">
         <v>34937</v>
@@ -21452,7 +21452,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G727" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974452972412</v>
       </c>
       <c r="H727" t="n">
         <v>45598</v>
@@ -21481,7 +21481,7 @@
         <v>6.12011909484863</v>
       </c>
       <c r="G728" t="n">
-        <v>5.02191209793091</v>
+        <v>5.02191257476807</v>
       </c>
       <c r="H728" t="n">
         <v>128887</v>
@@ -21510,7 +21510,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G729" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H729" t="n">
         <v>214334</v>
@@ -21539,7 +21539,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434125900269</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H730" t="n">
         <v>4041</v>
@@ -21568,7 +21568,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G731" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974452972412</v>
       </c>
       <c r="H731" t="n">
         <v>7136</v>
@@ -21597,7 +21597,7 @@
         <v>6.25153303146362</v>
       </c>
       <c r="G732" t="n">
-        <v>5.12974500656128</v>
+        <v>5.12974452972412</v>
       </c>
       <c r="H732" t="n">
         <v>47543</v>
@@ -21626,7 +21626,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434125900269</v>
+        <v>5.11434078216553</v>
       </c>
       <c r="H733" t="n">
         <v>5204</v>
@@ -21684,7 +21684,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G735" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H735" t="n">
         <v>12753</v>
@@ -21713,7 +21713,7 @@
         <v>6.17643880844116</v>
       </c>
       <c r="G736" t="n">
-        <v>5.06812572479248</v>
+        <v>5.06812620162964</v>
       </c>
       <c r="H736" t="n">
         <v>5420</v>
@@ -21800,7 +21800,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G739" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H739" t="n">
         <v>9338</v>
@@ -21829,7 +21829,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G740" t="n">
-        <v>5.05272150039673</v>
+        <v>5.05272197723389</v>
       </c>
       <c r="H740" t="n">
         <v>18125</v>
@@ -21945,7 +21945,7 @@
         <v>6.13889312744141</v>
       </c>
       <c r="G744" t="n">
-        <v>5.03731775283813</v>
+        <v>5.03731822967529</v>
       </c>
       <c r="H744" t="n">
         <v>78631</v>
@@ -22003,7 +22003,7 @@
         <v>5.83851909637451</v>
       </c>
       <c r="G746" t="n">
-        <v>4.79084348678589</v>
+        <v>4.79084300994873</v>
       </c>
       <c r="H746" t="n">
         <v>6996</v>
@@ -22119,7 +22119,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436922073364</v>
+        <v>4.5443696975708</v>
       </c>
       <c r="H750" t="n">
         <v>20273</v>
@@ -22235,7 +22235,7 @@
         <v>5.29409122467041</v>
       </c>
       <c r="G754" t="n">
-        <v>4.34410905838013</v>
+        <v>4.34410858154297</v>
       </c>
       <c r="H754" t="n">
         <v>96598</v>
@@ -22264,7 +22264,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08222961425781</v>
+        <v>4.08223009109497</v>
       </c>
       <c r="H755" t="n">
         <v>42542</v>
@@ -22351,7 +22351,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468602180481</v>
+        <v>3.60468554496765</v>
       </c>
       <c r="H758" t="n">
         <v>114780</v>
@@ -22409,7 +22409,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G760" t="n">
-        <v>3.23497462272644</v>
+        <v>3.23497438430786</v>
       </c>
       <c r="H760" t="n">
         <v>9678</v>
@@ -22438,7 +22438,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G761" t="n">
-        <v>3.20416498184204</v>
+        <v>3.20416474342346</v>
       </c>
       <c r="H761" t="n">
         <v>10734</v>
@@ -22554,7 +22554,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G765" t="n">
-        <v>3.25808119773865</v>
+        <v>3.25808143615723</v>
       </c>
       <c r="H765" t="n">
         <v>2694</v>
@@ -22583,7 +22583,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G766" t="n">
-        <v>3.30429458618164</v>
+        <v>3.30429482460022</v>
       </c>
       <c r="H766" t="n">
         <v>13344</v>
@@ -22699,7 +22699,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G770" t="n">
-        <v>3.2657835483551</v>
+        <v>3.26578378677368</v>
       </c>
       <c r="H770" t="n">
         <v>7733</v>
@@ -22728,7 +22728,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G771" t="n">
-        <v>3.31199741363525</v>
+        <v>3.31199765205383</v>
       </c>
       <c r="H771" t="n">
         <v>19489</v>
@@ -22757,7 +22757,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G772" t="n">
-        <v>3.20416498184204</v>
+        <v>3.20416474342346</v>
       </c>
       <c r="H772" t="n">
         <v>20777</v>
@@ -22786,7 +22786,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G773" t="n">
-        <v>3.23497462272644</v>
+        <v>3.23497438430786</v>
       </c>
       <c r="H773" t="n">
         <v>20307</v>
@@ -22815,7 +22815,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G774" t="n">
-        <v>3.23497462272644</v>
+        <v>3.23497438430786</v>
       </c>
       <c r="H774" t="n">
         <v>8024</v>
@@ -22844,7 +22844,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G775" t="n">
-        <v>3.30429458618164</v>
+        <v>3.30429482460022</v>
       </c>
       <c r="H775" t="n">
         <v>11885</v>
@@ -22873,7 +22873,7 @@
         <v>4.13952779769897</v>
       </c>
       <c r="G776" t="n">
-        <v>3.39672255516052</v>
+        <v>3.39672231674194</v>
       </c>
       <c r="H776" t="n">
         <v>23048</v>
@@ -22902,7 +22902,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G777" t="n">
-        <v>3.31199741363525</v>
+        <v>3.31199765205383</v>
       </c>
       <c r="H777" t="n">
         <v>10983</v>
@@ -22960,7 +22960,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306626319885</v>
+        <v>3.54306650161743</v>
       </c>
       <c r="H779" t="n">
         <v>19181</v>
@@ -22989,7 +22989,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G780" t="n">
-        <v>3.3890209197998</v>
+        <v>3.38902068138123</v>
       </c>
       <c r="H780" t="n">
         <v>14969</v>
@@ -23105,7 +23105,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G784" t="n">
-        <v>3.3890209197998</v>
+        <v>3.38902068138123</v>
       </c>
       <c r="H784" t="n">
         <v>15845</v>
@@ -23163,7 +23163,7 @@
         <v>4.19584894180298</v>
       </c>
       <c r="G786" t="n">
-        <v>3.44293737411499</v>
+        <v>3.44293713569641</v>
       </c>
       <c r="H786" t="n">
         <v>21547</v>
@@ -23221,7 +23221,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.77413630485535</v>
+        <v>3.7741367816925</v>
       </c>
       <c r="H788" t="n">
         <v>79040</v>
@@ -23250,7 +23250,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035064697266</v>
+        <v>3.82035088539124</v>
       </c>
       <c r="H789" t="n">
         <v>103597</v>
@@ -23308,7 +23308,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.81264758110046</v>
+        <v>3.81264805793762</v>
       </c>
       <c r="H791" t="n">
         <v>43347</v>
@@ -23337,7 +23337,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.77413630485535</v>
+        <v>3.7741367816925</v>
       </c>
       <c r="H792" t="n">
         <v>60664</v>
@@ -23366,7 +23366,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.83575558662415</v>
+        <v>3.83575582504272</v>
       </c>
       <c r="H793" t="n">
         <v>20249</v>
@@ -23424,7 +23424,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.82035064697266</v>
+        <v>3.82035088539124</v>
       </c>
       <c r="H795" t="n">
         <v>37010</v>
@@ -23482,7 +23482,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G797" t="n">
-        <v>3.89737367630005</v>
+        <v>3.89737319946289</v>
       </c>
       <c r="H797" t="n">
         <v>14230</v>
@@ -23511,7 +23511,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818331718445</v>
+        <v>3.92818307876587</v>
       </c>
       <c r="H798" t="n">
         <v>44285</v>
@@ -23569,7 +23569,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.83575558662415</v>
+        <v>3.83575582504272</v>
       </c>
       <c r="H800" t="n">
         <v>42258</v>
@@ -23627,7 +23627,7 @@
         <v>4.40235614776611</v>
       </c>
       <c r="G802" t="n">
-        <v>3.86765432357788</v>
+        <v>3.8676540851593</v>
       </c>
       <c r="H802" t="n">
         <v>51949</v>
@@ -23656,7 +23656,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H803" t="n">
         <v>26953</v>
@@ -23743,7 +23743,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291386604309</v>
+        <v>3.84291410446167</v>
       </c>
       <c r="H806" t="n">
         <v>94227</v>
@@ -23801,7 +23801,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G808" t="n">
-        <v>4.11505174636841</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H808" t="n">
         <v>72299</v>
@@ -23917,7 +23917,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10680532455444</v>
+        <v>4.10680484771729</v>
       </c>
       <c r="H812" t="n">
         <v>23474</v>
@@ -23946,7 +23946,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.10680532455444</v>
+        <v>4.10680484771729</v>
       </c>
       <c r="H813" t="n">
         <v>40978</v>
@@ -23975,7 +23975,7 @@
         <v>4.66518306732178</v>
       </c>
       <c r="G814" t="n">
-        <v>4.09855842590332</v>
+        <v>4.09855794906616</v>
       </c>
       <c r="H814" t="n">
         <v>59049</v>
@@ -24004,7 +24004,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G815" t="n">
-        <v>4.11505174636841</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H815" t="n">
         <v>40504</v>
@@ -24033,7 +24033,7 @@
         <v>4.66518306732178</v>
       </c>
       <c r="G816" t="n">
-        <v>4.09855842590332</v>
+        <v>4.09855794906616</v>
       </c>
       <c r="H816" t="n">
         <v>42310</v>
@@ -24091,7 +24091,7 @@
         <v>5.05003690719604</v>
       </c>
       <c r="G818" t="n">
-        <v>4.43666839599609</v>
+        <v>4.43666887283325</v>
       </c>
       <c r="H818" t="n">
         <v>171756</v>
@@ -24149,7 +24149,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G820" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H820" t="n">
         <v>76661</v>
@@ -24178,7 +24178,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G821" t="n">
-        <v>4.30472326278687</v>
+        <v>4.30472278594971</v>
       </c>
       <c r="H821" t="n">
         <v>71502</v>
@@ -24207,7 +24207,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G822" t="n">
-        <v>4.27173662185669</v>
+        <v>4.27173614501953</v>
       </c>
       <c r="H822" t="n">
         <v>24302</v>
@@ -24265,7 +24265,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G824" t="n">
-        <v>4.28823041915894</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H824" t="n">
         <v>56130</v>
@@ -24381,7 +24381,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G828" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H828" t="n">
         <v>25450</v>
@@ -24555,7 +24555,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G834" t="n">
-        <v>4.11505174636841</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H834" t="n">
         <v>7566</v>
@@ -24584,7 +24584,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G835" t="n">
-        <v>4.13979053497314</v>
+        <v>4.1397910118103</v>
       </c>
       <c r="H835" t="n">
         <v>12122</v>
@@ -24613,7 +24613,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G836" t="n">
-        <v>4.13979053497314</v>
+        <v>4.1397910118103</v>
       </c>
       <c r="H836" t="n">
         <v>40720</v>
@@ -24642,7 +24642,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H837" t="n">
         <v>17076</v>
@@ -24729,7 +24729,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H840" t="n">
         <v>4918</v>
@@ -24758,7 +24758,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28823041915894</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H841" t="n">
         <v>29013</v>
@@ -24787,7 +24787,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H842" t="n">
         <v>14939</v>
@@ -24874,7 +24874,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H845" t="n">
         <v>6786</v>
@@ -24932,7 +24932,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H847" t="n">
         <v>5286</v>
@@ -24961,7 +24961,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H848" t="n">
         <v>24096</v>
@@ -24990,7 +24990,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G849" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H849" t="n">
         <v>13952</v>
@@ -25048,7 +25048,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G851" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H851" t="n">
         <v>10827</v>
@@ -25077,7 +25077,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G852" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H852" t="n">
         <v>6470</v>
@@ -25106,7 +25106,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G853" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H853" t="n">
         <v>46882</v>
@@ -25135,7 +25135,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G854" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H854" t="n">
         <v>24267</v>
@@ -25164,7 +25164,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G855" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H855" t="n">
         <v>53288</v>
@@ -25193,7 +25193,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G856" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H856" t="n">
         <v>122348</v>
@@ -25222,7 +25222,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G857" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H857" t="n">
         <v>31914</v>
@@ -25251,7 +25251,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G858" t="n">
-        <v>4.13979053497314</v>
+        <v>4.1397910118103</v>
       </c>
       <c r="H858" t="n">
         <v>20200</v>
@@ -25280,7 +25280,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G859" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H859" t="n">
         <v>20156</v>
@@ -25338,7 +25338,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G861" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H861" t="n">
         <v>7702</v>
@@ -25454,7 +25454,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G865" t="n">
-        <v>4.27173662185669</v>
+        <v>4.27173614501953</v>
       </c>
       <c r="H865" t="n">
         <v>17734</v>
@@ -25570,7 +25570,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H869" t="n">
         <v>6800</v>
@@ -25599,7 +25599,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G870" t="n">
-        <v>4.28823041915894</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H870" t="n">
         <v>12725</v>
@@ -25773,7 +25773,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G876" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H876" t="n">
         <v>18056</v>
@@ -25802,7 +25802,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G877" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H877" t="n">
         <v>14094</v>
@@ -25831,7 +25831,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G878" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H878" t="n">
         <v>29761</v>
@@ -25889,7 +25889,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G880" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H880" t="n">
         <v>4103</v>
@@ -25947,7 +25947,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H882" t="n">
         <v>10955</v>
@@ -25976,7 +25976,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G883" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H883" t="n">
         <v>5879</v>
@@ -26005,7 +26005,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G884" t="n">
-        <v>4.20576429367065</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H884" t="n">
         <v>9707</v>
@@ -26034,7 +26034,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927049636841</v>
+        <v>4.18927001953125</v>
       </c>
       <c r="H885" t="n">
         <v>4939</v>
@@ -26208,7 +26208,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G891" t="n">
-        <v>4.10680532455444</v>
+        <v>4.10680484771729</v>
       </c>
       <c r="H891" t="n">
         <v>4752</v>
@@ -26237,7 +26237,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258514404297</v>
+        <v>4.03258562088013</v>
       </c>
       <c r="H892" t="n">
         <v>19963</v>
@@ -26266,7 +26266,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G893" t="n">
-        <v>4.04083156585693</v>
+        <v>4.04083204269409</v>
       </c>
       <c r="H893" t="n">
         <v>7436</v>
@@ -26411,7 +26411,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G898" t="n">
-        <v>4.11505174636841</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H898" t="n">
         <v>13328</v>
@@ -26469,7 +26469,7 @@
         <v>4.52438306808472</v>
       </c>
       <c r="G900" t="n">
-        <v>3.97485995292664</v>
+        <v>3.97485947608948</v>
       </c>
       <c r="H900" t="n">
         <v>7883</v>
@@ -26527,7 +26527,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H902" t="n">
         <v>27440</v>
@@ -26585,7 +26585,7 @@
         <v>4.4305157661438</v>
       </c>
       <c r="G904" t="n">
-        <v>3.8923933506012</v>
+        <v>3.89239287376404</v>
       </c>
       <c r="H904" t="n">
         <v>57694</v>
@@ -26643,7 +26643,7 @@
         <v>4.32726192474365</v>
       </c>
       <c r="G906" t="n">
-        <v>3.80168056488037</v>
+        <v>3.80168032646179</v>
       </c>
       <c r="H906" t="n">
         <v>16851</v>
@@ -26672,7 +26672,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H907" t="n">
         <v>21206</v>
@@ -26730,7 +26730,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G909" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H909" t="n">
         <v>12272</v>
@@ -26759,7 +26759,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H910" t="n">
         <v>221384</v>
@@ -26846,7 +26846,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G913" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H913" t="n">
         <v>26785</v>
@@ -26875,7 +26875,7 @@
         <v>3.85792803764343</v>
       </c>
       <c r="G914" t="n">
-        <v>3.38935112953186</v>
+        <v>3.38935089111328</v>
       </c>
       <c r="H914" t="n">
         <v>126936</v>
@@ -26933,7 +26933,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G916" t="n">
-        <v>3.43058371543884</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H916" t="n">
         <v>30575</v>
@@ -26991,7 +26991,7 @@
         <v>3.78283405303955</v>
       </c>
       <c r="G918" t="n">
-        <v>3.32337808609009</v>
+        <v>3.32337784767151</v>
       </c>
       <c r="H918" t="n">
         <v>20342</v>
@@ -27484,7 +27484,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G935" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H935" t="n">
         <v>48632</v>
@@ -27600,7 +27600,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G939" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H939" t="n">
         <v>25861</v>
@@ -27745,7 +27745,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H944" t="n">
         <v>39463</v>
@@ -27832,7 +27832,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G947" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H947" t="n">
         <v>47814</v>
@@ -27861,7 +27861,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G948" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H948" t="n">
         <v>31997</v>
@@ -27890,7 +27890,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H949" t="n">
         <v>106760</v>
@@ -27919,7 +27919,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G950" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H950" t="n">
         <v>10561</v>
@@ -28122,7 +28122,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G957" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H957" t="n">
         <v>34099</v>
@@ -28383,7 +28383,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G966" t="n">
-        <v>3.85116028785706</v>
+        <v>3.8511598110199</v>
       </c>
       <c r="H966" t="n">
         <v>80934</v>
@@ -28470,7 +28470,7 @@
         <v>4.48683595657349</v>
       </c>
       <c r="G969" t="n">
-        <v>3.9418728351593</v>
+        <v>3.94187307357788</v>
       </c>
       <c r="H969" t="n">
         <v>25574</v>
@@ -28557,7 +28557,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G972" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518724441528</v>
       </c>
       <c r="H972" t="n">
         <v>13653</v>
@@ -28644,7 +28644,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G975" t="n">
-        <v>3.85116028785706</v>
+        <v>3.8511598110199</v>
       </c>
       <c r="H975" t="n">
         <v>12119</v>
@@ -28673,7 +28673,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992746353149</v>
+        <v>3.80992770195007</v>
       </c>
       <c r="H976" t="n">
         <v>12393</v>
@@ -28702,7 +28702,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H977" t="n">
         <v>18818</v>
@@ -28934,7 +28934,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G985" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H985" t="n">
         <v>21733</v>
@@ -29079,7 +29079,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G990" t="n">
-        <v>3.76044821739197</v>
+        <v>3.76044797897339</v>
       </c>
       <c r="H990" t="n">
         <v>34076</v>
@@ -29108,7 +29108,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G991" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H991" t="n">
         <v>31203</v>
@@ -29166,7 +29166,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992746353149</v>
+        <v>3.80992770195007</v>
       </c>
       <c r="H993" t="n">
         <v>25930</v>
@@ -29195,7 +29195,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G994" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518724441528</v>
       </c>
       <c r="H994" t="n">
         <v>29512</v>
@@ -29224,7 +29224,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G995" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518724441528</v>
       </c>
       <c r="H995" t="n">
         <v>32878</v>
@@ -29282,7 +29282,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G997" t="n">
-        <v>3.76044821739197</v>
+        <v>3.76044797897339</v>
       </c>
       <c r="H997" t="n">
         <v>27938</v>
@@ -29311,7 +29311,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H998" t="n">
         <v>7194</v>
@@ -29398,7 +29398,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1001" t="n">
         <v>15073</v>
@@ -29456,7 +29456,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1003" t="n">
         <v>38443</v>
@@ -29485,7 +29485,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1004" t="n">
         <v>11715</v>
@@ -29514,7 +29514,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1005" t="n">
         <v>24094</v>
@@ -29630,7 +29630,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1009" t="n">
         <v>21917</v>
@@ -29659,7 +29659,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1010" t="n">
         <v>40769</v>
@@ -29688,7 +29688,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1011" t="n">
         <v>16281</v>
@@ -29717,7 +29717,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1012" t="n">
         <v>21537</v>
@@ -29746,7 +29746,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1013" t="n">
         <v>21737</v>
@@ -29775,7 +29775,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1014" t="n">
         <v>18825</v>
@@ -29833,7 +29833,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1016" t="n">
         <v>29025</v>
@@ -29891,7 +29891,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1018" t="n">
         <v>34727</v>
@@ -29920,7 +29920,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1019" t="n">
         <v>21560</v>
@@ -29978,7 +29978,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1021" t="n">
         <v>27672</v>
@@ -30036,7 +30036,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1023" t="n">
         <v>100775</v>
@@ -30094,7 +30094,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1025" t="n">
         <v>37874</v>
@@ -30152,7 +30152,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1027" t="n">
         <v>25372</v>
@@ -30181,7 +30181,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1028" t="n">
         <v>29741</v>
@@ -30210,7 +30210,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1029" t="n">
         <v>11946</v>
@@ -30239,7 +30239,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1030" t="n">
         <v>28499</v>
@@ -30268,7 +30268,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1031" t="n">
         <v>19835</v>
@@ -30384,7 +30384,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1035" t="n">
         <v>20652</v>
@@ -30413,7 +30413,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1036" t="n">
         <v>25907</v>
@@ -30471,7 +30471,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.71921443939209</v>
+        <v>3.71921467781067</v>
       </c>
       <c r="H1038" t="n">
         <v>51341</v>
@@ -30558,7 +30558,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1041" t="n">
         <v>33432</v>
@@ -30587,7 +30587,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1042" t="n">
         <v>29677</v>
@@ -30674,7 +30674,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.76044821739197</v>
+        <v>3.76044797897339</v>
       </c>
       <c r="H1045" t="n">
         <v>26734</v>
@@ -30703,7 +30703,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1046" t="n">
         <v>8805</v>
@@ -30761,7 +30761,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518724441528</v>
       </c>
       <c r="H1048" t="n">
         <v>18325</v>
@@ -30790,7 +30790,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1049" t="n">
         <v>11760</v>
@@ -30819,7 +30819,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1050" t="n">
         <v>3012</v>
@@ -30848,7 +30848,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1051" t="n">
         <v>3548</v>
@@ -30877,7 +30877,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.76044821739197</v>
+        <v>3.76044797897339</v>
       </c>
       <c r="H1052" t="n">
         <v>6158</v>
@@ -31022,7 +31022,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1057" t="n">
         <v>30443</v>
@@ -31051,7 +31051,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1058" t="n">
         <v>12928</v>
@@ -31167,7 +31167,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1062" t="n">
         <v>48219</v>
@@ -31196,7 +31196,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1063" t="n">
         <v>25919</v>
@@ -31225,7 +31225,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.76044821739197</v>
+        <v>3.76044797897339</v>
       </c>
       <c r="H1064" t="n">
         <v>11044</v>
@@ -31254,7 +31254,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1065" t="n">
         <v>24230</v>
@@ -31283,7 +31283,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.76044821739197</v>
+        <v>3.76044797897339</v>
       </c>
       <c r="H1066" t="n">
         <v>19508</v>
@@ -31312,7 +31312,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1067" t="n">
         <v>39186</v>
@@ -31370,7 +31370,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1069" t="n">
         <v>58800</v>
@@ -31399,7 +31399,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.7439546585083</v>
+        <v>3.74395442008972</v>
       </c>
       <c r="H1070" t="n">
         <v>56554</v>
@@ -31428,7 +31428,7 @@
         <v>4.3084888458252</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.78518772125244</v>
+        <v>3.78518724441528</v>
       </c>
       <c r="H1071" t="n">
         <v>50468</v>
@@ -31457,7 +31457,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1072" t="n">
         <v>42884</v>
@@ -31486,7 +31486,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1073" t="n">
         <v>22042</v>
@@ -31515,7 +31515,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1074" t="n">
         <v>65157</v>
@@ -31660,7 +31660,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1079" t="n">
         <v>14510</v>
@@ -31834,7 +31834,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1085" t="n">
         <v>9140</v>
@@ -31892,7 +31892,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1087" t="n">
         <v>42401</v>
@@ -31921,7 +31921,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1088" t="n">
         <v>11524</v>
@@ -31950,7 +31950,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1089" t="n">
         <v>6676</v>
@@ -32037,7 +32037,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1092" t="n">
         <v>27747</v>
@@ -32066,7 +32066,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1093" t="n">
         <v>24635</v>
@@ -32095,7 +32095,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1094" t="n">
         <v>30142</v>
@@ -32153,7 +32153,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1096" t="n">
         <v>9429</v>
@@ -32182,7 +32182,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1097" t="n">
         <v>890</v>
@@ -32240,7 +32240,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1099" t="n">
         <v>2287</v>
@@ -32298,7 +32298,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1101" t="n">
         <v>18207</v>
@@ -32356,7 +32356,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1103" t="n">
         <v>8811</v>
@@ -32443,7 +32443,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532321929932</v>
       </c>
       <c r="H1106" t="n">
         <v>12193</v>
@@ -32559,7 +32559,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1110" t="n">
         <v>6715</v>
@@ -32588,7 +32588,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532321929932</v>
       </c>
       <c r="H1111" t="n">
         <v>8326</v>
@@ -32617,7 +32617,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883061408997</v>
+        <v>3.43883037567139</v>
       </c>
       <c r="H1112" t="n">
         <v>3066</v>
@@ -32704,7 +32704,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285757064819</v>
       </c>
       <c r="H1115" t="n">
         <v>45530</v>
@@ -32733,7 +32733,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532321929932</v>
       </c>
       <c r="H1116" t="n">
         <v>10368</v>
@@ -32849,7 +32849,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220155715942</v>
+        <v>3.75220108032227</v>
       </c>
       <c r="H1120" t="n">
         <v>74582</v>
@@ -32907,7 +32907,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.71921443939209</v>
+        <v>3.71921467781067</v>
       </c>
       <c r="H1122" t="n">
         <v>40624</v>
@@ -32936,7 +32936,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1123" t="n">
         <v>50758</v>
@@ -33139,7 +33139,7 @@
         <v>4.3554220199585</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.82642030715942</v>
+        <v>3.826420545578</v>
       </c>
       <c r="H1130" t="n">
         <v>37637</v>
@@ -33197,7 +33197,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.7686939239502</v>
+        <v>3.76869368553162</v>
       </c>
       <c r="H1132" t="n">
         <v>13639</v>
@@ -33226,7 +33226,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1133" t="n">
         <v>63296</v>
@@ -33400,7 +33400,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.69447493553162</v>
+        <v>3.69447469711304</v>
       </c>
       <c r="H1139" t="n">
         <v>9634</v>
@@ -33487,7 +33487,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1142" t="n">
         <v>70144</v>
@@ -33516,7 +33516,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1143" t="n">
         <v>71574</v>
@@ -33545,7 +33545,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1144" t="n">
         <v>12460</v>
@@ -33574,7 +33574,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1145" t="n">
         <v>11043</v>
@@ -33603,7 +33603,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1146" t="n">
         <v>13893</v>
@@ -33632,7 +33632,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1147" t="n">
         <v>5028</v>
@@ -33748,7 +33748,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1151" t="n">
         <v>24839</v>
@@ -33777,7 +33777,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1152" t="n">
         <v>10052</v>
@@ -34038,7 +34038,7 @@
         <v>4.14891481399536</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.64499521255493</v>
+        <v>3.64499497413635</v>
       </c>
       <c r="H1161" t="n">
         <v>5965</v>
@@ -34096,7 +34096,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428338050842</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1163" t="n">
         <v>36527</v>
@@ -34125,7 +34125,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1164" t="n">
         <v>32377</v>
@@ -34183,7 +34183,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1166" t="n">
         <v>8226</v>
@@ -34241,7 +34241,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1168" t="n">
         <v>10241</v>
@@ -34270,7 +34270,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1169" t="n">
         <v>8390</v>
@@ -34299,7 +34299,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1170" t="n">
         <v>23775</v>
@@ -34328,7 +34328,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1171" t="n">
         <v>4856</v>
@@ -34357,7 +34357,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252932548523</v>
+        <v>3.56252908706665</v>
       </c>
       <c r="H1172" t="n">
         <v>22682</v>
@@ -34386,7 +34386,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1173" t="n">
         <v>9266</v>
@@ -34415,7 +34415,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1174" t="n">
         <v>82581</v>
@@ -34502,7 +34502,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1177" t="n">
         <v>14799</v>
@@ -34589,7 +34589,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1180" t="n">
         <v>27262</v>
@@ -34618,7 +34618,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.43058371543884</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H1181" t="n">
         <v>8590</v>
@@ -34676,7 +34676,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1183" t="n">
         <v>24607</v>
@@ -34792,7 +34792,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1187" t="n">
         <v>17346</v>
@@ -34850,7 +34850,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798161506653</v>
       </c>
       <c r="H1189" t="n">
         <v>48866</v>
@@ -34879,7 +34879,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1190" t="n">
         <v>25104</v>
@@ -34908,7 +34908,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077598571777</v>
+        <v>3.57077574729919</v>
       </c>
       <c r="H1191" t="n">
         <v>5698</v>
@@ -34966,7 +34966,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1193" t="n">
         <v>19889</v>
@@ -34995,7 +34995,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551596641541</v>
+        <v>3.59551572799683</v>
       </c>
       <c r="H1194" t="n">
         <v>16241</v>
@@ -35024,7 +35024,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1195" t="n">
         <v>20816</v>
@@ -35111,7 +35111,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1198" t="n">
         <v>11291</v>
@@ -35140,7 +35140,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1199" t="n">
         <v>6078</v>
@@ -35169,7 +35169,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1200" t="n">
         <v>7176</v>
@@ -35198,7 +35198,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1201" t="n">
         <v>8294</v>
@@ -35227,7 +35227,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428338050842</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1202" t="n">
         <v>5435</v>
@@ -35285,7 +35285,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1204" t="n">
         <v>12073</v>
@@ -35314,7 +35314,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1205" t="n">
         <v>19359</v>
@@ -35343,7 +35343,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1206" t="n">
         <v>10703</v>
@@ -35401,7 +35401,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1208" t="n">
         <v>1693</v>
@@ -35517,7 +35517,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1212" t="n">
         <v>12870</v>
@@ -35575,7 +35575,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1214" t="n">
         <v>5806</v>
@@ -35633,7 +35633,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.5460364818573</v>
+        <v>3.54603600502014</v>
       </c>
       <c r="H1216" t="n">
         <v>8971</v>
@@ -35720,7 +35720,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428338050842</v>
+        <v>3.55428314208984</v>
       </c>
       <c r="H1219" t="n">
         <v>41335</v>
@@ -35749,7 +35749,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1220" t="n">
         <v>7491</v>
@@ -35778,7 +35778,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1221" t="n">
         <v>5316</v>
@@ -35807,7 +35807,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1222" t="n">
         <v>6029</v>
@@ -35836,7 +35836,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1223" t="n">
         <v>22676</v>
@@ -35865,7 +35865,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1224" t="n">
         <v>10519</v>
@@ -35894,7 +35894,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1225" t="n">
         <v>9180</v>
@@ -35981,7 +35981,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1228" t="n">
         <v>9896</v>
@@ -36010,7 +36010,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.52954244613647</v>
+        <v>3.52954268455505</v>
       </c>
       <c r="H1229" t="n">
         <v>21602</v>
@@ -36039,7 +36039,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1230" t="n">
         <v>20614</v>
@@ -36068,7 +36068,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1231" t="n">
         <v>12772</v>
@@ -36097,7 +36097,7 @@
         <v>3.933021068573</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.4553234577179</v>
+        <v>3.45532321929932</v>
       </c>
       <c r="H1232" t="n">
         <v>23015</v>
@@ -36126,7 +36126,7 @@
         <v>3.90486097335815</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.43058371543884</v>
+        <v>3.43058347702026</v>
       </c>
       <c r="H1233" t="n">
         <v>26288</v>
@@ -36155,7 +36155,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.44707751274109</v>
+        <v>3.44707727432251</v>
       </c>
       <c r="H1234" t="n">
         <v>49691</v>
@@ -36271,7 +36271,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285757064819</v>
       </c>
       <c r="H1238" t="n">
         <v>1560</v>
@@ -36358,7 +36358,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409087181091</v>
+        <v>3.41409063339233</v>
       </c>
       <c r="H1241" t="n">
         <v>8107</v>
@@ -36532,7 +36532,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.28214550018311</v>
+        <v>3.28214502334595</v>
       </c>
       <c r="H1247" t="n">
         <v>87521</v>
@@ -36590,7 +36590,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1249" t="n">
         <v>48472</v>
@@ -36619,7 +36619,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1250" t="n">
         <v>14068</v>
@@ -36706,7 +36706,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721277236938</v>
       </c>
       <c r="H1253" t="n">
         <v>6186</v>
@@ -36735,7 +36735,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721277236938</v>
       </c>
       <c r="H1254" t="n">
         <v>7022</v>
@@ -36764,7 +36764,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.21617197990417</v>
+        <v>3.2161717414856</v>
       </c>
       <c r="H1255" t="n">
         <v>41768</v>
@@ -36851,7 +36851,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.21617197990417</v>
+        <v>3.2161717414856</v>
       </c>
       <c r="H1258" t="n">
         <v>26713</v>
@@ -36880,7 +36880,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1259" t="n">
         <v>13331</v>
@@ -37025,7 +37025,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351406097412</v>
       </c>
       <c r="H1264" t="n">
         <v>42973</v>
@@ -37054,7 +37054,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90280151367188</v>
+        <v>2.9028012752533</v>
       </c>
       <c r="H1265" t="n">
         <v>33527</v>
@@ -37083,7 +37083,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.90280151367188</v>
+        <v>2.9028012752533</v>
       </c>
       <c r="H1266" t="n">
         <v>13521</v>
@@ -37141,7 +37141,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1268" t="n">
         <v>2663</v>
@@ -37170,7 +37170,7 @@
         <v>3.32288694381714</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.91929531097412</v>
+        <v>2.91929507255554</v>
       </c>
       <c r="H1269" t="n">
         <v>2212</v>
@@ -37228,7 +37228,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877479553223</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1271" t="n">
         <v>8955</v>
@@ -37257,7 +37257,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.9935142993927</v>
+        <v>2.99351406097412</v>
       </c>
       <c r="H1272" t="n">
         <v>11850</v>
@@ -37286,7 +37286,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.90280151367188</v>
+        <v>2.9028012752533</v>
       </c>
       <c r="H1273" t="n">
         <v>76645</v>
@@ -37315,7 +37315,7 @@
         <v>3.3416600227356</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.93578791618347</v>
+        <v>2.93578815460205</v>
       </c>
       <c r="H1274" t="n">
         <v>32956</v>
@@ -37402,7 +37402,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.05948686599731</v>
+        <v>3.05948662757874</v>
       </c>
       <c r="H1277" t="n">
         <v>5110</v>
@@ -37460,7 +37460,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.08422660827637</v>
+        <v>3.08422684669495</v>
       </c>
       <c r="H1279" t="n">
         <v>6287</v>
@@ -37489,7 +37489,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.08422660827637</v>
+        <v>3.08422684669495</v>
       </c>
       <c r="H1280" t="n">
         <v>2125</v>
@@ -37518,7 +37518,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1281" t="n">
         <v>186455</v>
@@ -37547,7 +37547,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1282" t="n">
         <v>37331</v>
@@ -37576,7 +37576,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12546014785767</v>
+        <v>3.12545990943909</v>
       </c>
       <c r="H1283" t="n">
         <v>6914</v>
@@ -37605,7 +37605,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.10072016716003</v>
+        <v>3.10071992874146</v>
       </c>
       <c r="H1284" t="n">
         <v>4412</v>
@@ -37895,7 +37895,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.05948686599731</v>
+        <v>3.05948662757874</v>
       </c>
       <c r="H1294" t="n">
         <v>7283</v>
@@ -37924,7 +37924,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.05948686599731</v>
+        <v>3.05948662757874</v>
       </c>
       <c r="H1295" t="n">
         <v>3328</v>
@@ -38127,7 +38127,7 @@
         <v>3.35104703903198</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.94403481483459</v>
+        <v>2.94403457641602</v>
       </c>
       <c r="H1302" t="n">
         <v>14106</v>
@@ -38156,7 +38156,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877479553223</v>
+        <v>2.96877431869507</v>
       </c>
       <c r="H1303" t="n">
         <v>16267</v>
@@ -38214,7 +38214,7 @@
         <v>3.24779295921326</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.85332202911377</v>
+        <v>2.85332179069519</v>
       </c>
       <c r="H1305" t="n">
         <v>46001</v>
@@ -38243,7 +38243,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630843162537</v>
+        <v>2.88630867004395</v>
       </c>
       <c r="H1306" t="n">
         <v>18867</v>
@@ -38330,7 +38330,7 @@
         <v>3.85792803764343</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.38935112953186</v>
+        <v>3.38935089111328</v>
       </c>
       <c r="H1309" t="n">
         <v>54861</v>
@@ -38446,7 +38446,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1313" t="n">
         <v>8922</v>
@@ -38475,7 +38475,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.504802942276</v>
+        <v>3.50480270385742</v>
       </c>
       <c r="H1314" t="n">
         <v>9692</v>
@@ -38591,7 +38591,7 @@
         <v>4.01720809936523</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.57294178009033</v>
+        <v>3.57294154167175</v>
       </c>
       <c r="H1318" t="n">
         <v>31505</v>
@@ -38620,7 +38620,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.56433176994324</v>
+        <v>3.56433200836182</v>
       </c>
       <c r="H1319" t="n">
         <v>20606</v>
@@ -38678,7 +38678,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1321" t="n">
         <v>19899</v>
@@ -38707,7 +38707,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.56433176994324</v>
+        <v>3.56433200836182</v>
       </c>
       <c r="H1322" t="n">
         <v>34453</v>
@@ -38736,7 +38736,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1323" t="n">
         <v>8362</v>
@@ -38765,7 +38765,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1324" t="n">
         <v>8377</v>
@@ -38794,7 +38794,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1325" t="n">
         <v>624</v>
@@ -38823,7 +38823,7 @@
         <v>4.06560802459717</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.61598896980286</v>
+        <v>3.61598873138428</v>
       </c>
       <c r="H1326" t="n">
         <v>58609</v>
@@ -38968,7 +38968,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1331" t="n">
         <v>44773</v>
@@ -38997,7 +38997,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.55572247505188</v>
+        <v>3.55572271347046</v>
       </c>
       <c r="H1332" t="n">
         <v>36069</v>
@@ -39026,7 +39026,7 @@
         <v>3.96880793571472</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.52989411354065</v>
+        <v>3.52989387512207</v>
       </c>
       <c r="H1333" t="n">
         <v>15175</v>
@@ -39055,7 +39055,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1334" t="n">
         <v>13459</v>
@@ -39113,7 +39113,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.50406575202942</v>
+        <v>3.50406551361084</v>
       </c>
       <c r="H1336" t="n">
         <v>37524</v>
@@ -39142,7 +39142,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1337" t="n">
         <v>4129</v>
@@ -39287,7 +39287,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1342" t="n">
         <v>5320</v>
@@ -39374,7 +39374,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1345" t="n">
         <v>36756</v>
@@ -39403,7 +39403,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.52128458023071</v>
+        <v>3.52128434181213</v>
       </c>
       <c r="H1346" t="n">
         <v>3230</v>
@@ -39519,7 +39519,7 @@
         <v>3.85264801979065</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.42658042907715</v>
+        <v>3.42658019065857</v>
       </c>
       <c r="H1350" t="n">
         <v>51255</v>
@@ -39780,7 +39780,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1359" t="n">
         <v>170543</v>
@@ -39838,7 +39838,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1361" t="n">
         <v>9312</v>
@@ -39867,7 +39867,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1362" t="n">
         <v>5877</v>
@@ -39896,7 +39896,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1363" t="n">
         <v>10464</v>
@@ -39983,7 +39983,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1366" t="n">
         <v>6495</v>
@@ -40012,7 +40012,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1367" t="n">
         <v>24029</v>
@@ -40041,7 +40041,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1368" t="n">
         <v>1065</v>
@@ -40070,7 +40070,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1369" t="n">
         <v>3932</v>
@@ -40099,7 +40099,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1370" t="n">
         <v>24459</v>
@@ -40186,7 +40186,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1373" t="n">
         <v>6080</v>
@@ -40215,7 +40215,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1374" t="n">
         <v>434</v>
@@ -40244,7 +40244,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1375" t="n">
         <v>33412</v>
@@ -40273,7 +40273,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1376" t="n">
         <v>17128</v>
@@ -40331,7 +40331,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1378" t="n">
         <v>10186</v>
@@ -40360,7 +40360,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1379" t="n">
         <v>42590</v>
@@ -40389,7 +40389,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1380" t="n">
         <v>1765</v>
@@ -40418,7 +40418,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1381" t="n">
         <v>37987</v>
@@ -40447,7 +40447,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1382" t="n">
         <v>73173</v>
@@ -40505,7 +40505,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1384" t="n">
         <v>415</v>
@@ -40621,7 +40621,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1388" t="n">
         <v>7459</v>
@@ -40650,7 +40650,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1389" t="n">
         <v>16272</v>
@@ -40766,7 +40766,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1393" t="n">
         <v>29155</v>
@@ -40795,7 +40795,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1394" t="n">
         <v>9851</v>
@@ -40853,7 +40853,7 @@
         <v>3.63000702857971</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.22856163978577</v>
+        <v>3.22856140136719</v>
       </c>
       <c r="H1396" t="n">
         <v>7770</v>
@@ -40911,7 +40911,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1398" t="n">
         <v>25070</v>
@@ -40940,7 +40940,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1399" t="n">
         <v>65695</v>
@@ -40969,7 +40969,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1400" t="n">
         <v>12081</v>
@@ -40998,7 +40998,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1401" t="n">
         <v>66836</v>
@@ -41056,7 +41056,7 @@
         <v>3.63968706130981</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.23717093467712</v>
+        <v>3.2371711730957</v>
       </c>
       <c r="H1403" t="n">
         <v>209305</v>
@@ -41085,7 +41085,7 @@
         <v>3.63000702857971</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22856163978577</v>
+        <v>3.22856140136719</v>
       </c>
       <c r="H1404" t="n">
         <v>35126</v>
@@ -41114,7 +41114,7 @@
         <v>3.61064696311951</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.21134233474731</v>
+        <v>3.21134257316589</v>
       </c>
       <c r="H1405" t="n">
         <v>27111</v>
@@ -41259,7 +41259,7 @@
         <v>3.57192707061768</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.17690467834473</v>
+        <v>3.17690443992615</v>
       </c>
       <c r="H1410" t="n">
         <v>12551</v>
@@ -41288,7 +41288,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1411" t="n">
         <v>27549</v>
@@ -41317,7 +41317,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1412" t="n">
         <v>29335</v>
@@ -41346,7 +41346,7 @@
         <v>3.5912868976593</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.19412350654602</v>
+        <v>3.19412326812744</v>
       </c>
       <c r="H1413" t="n">
         <v>30134</v>
@@ -41375,7 +41375,7 @@
         <v>3.63000702857971</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.22856163978577</v>
+        <v>3.22856140136719</v>
       </c>
       <c r="H1414" t="n">
         <v>130837</v>
@@ -41433,7 +41433,7 @@
         <v>3.63000702857971</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.22856163978577</v>
+        <v>3.22856140136719</v>
       </c>
       <c r="H1416" t="n">
         <v>119361</v>
@@ -41578,7 +41578,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.68616318702698</v>
+        <v>2.6861629486084</v>
       </c>
       <c r="H1421" t="n">
         <v>294760</v>
@@ -41694,7 +41694,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.73782014846802</v>
+        <v>2.7378203868866</v>
       </c>
       <c r="H1425" t="n">
         <v>51368</v>
@@ -41752,7 +41752,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.73782014846802</v>
+        <v>2.7378203868866</v>
       </c>
       <c r="H1427" t="n">
         <v>44531</v>
@@ -41781,7 +41781,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.68616318702698</v>
+        <v>2.6861629486084</v>
       </c>
       <c r="H1428" t="n">
         <v>64646</v>
@@ -41810,7 +41810,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.68616318702698</v>
+        <v>2.6861629486084</v>
       </c>
       <c r="H1429" t="n">
         <v>11887</v>
@@ -42129,7 +42129,7 @@
         <v>3.02016592025757</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.68616318702698</v>
+        <v>2.6861629486084</v>
       </c>
       <c r="H1440" t="n">
         <v>12710</v>
@@ -42216,7 +42216,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1443" t="n">
         <v>16328</v>
@@ -42245,7 +42245,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1444" t="n">
         <v>8029</v>
@@ -42361,7 +42361,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.625896692276</v>
+        <v>2.62589693069458</v>
       </c>
       <c r="H1448" t="n">
         <v>10321</v>
@@ -42448,7 +42448,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1451" t="n">
         <v>26990</v>
@@ -42535,7 +42535,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1454" t="n">
         <v>18616</v>
@@ -42593,7 +42593,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1456" t="n">
         <v>9511</v>
@@ -42622,7 +42622,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.625896692276</v>
+        <v>2.62589693069458</v>
       </c>
       <c r="H1457" t="n">
         <v>19285</v>
@@ -42651,7 +42651,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1458" t="n">
         <v>7087</v>
@@ -42680,7 +42680,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1459" t="n">
         <v>0</v>
@@ -42767,7 +42767,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1462" t="n">
         <v>8485</v>
@@ -42883,7 +42883,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1466" t="n">
         <v>22210</v>
@@ -42912,7 +42912,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1467" t="n">
         <v>39470</v>
@@ -42970,7 +42970,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1469" t="n">
         <v>4860</v>
@@ -42999,7 +42999,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1470" t="n">
         <v>14149</v>
@@ -43028,7 +43028,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1471" t="n">
         <v>7824</v>
@@ -43057,7 +43057,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1472" t="n">
         <v>309</v>
@@ -43086,7 +43086,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1473" t="n">
         <v>4257</v>
@@ -43115,7 +43115,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1474" t="n">
         <v>4029</v>
@@ -43144,7 +43144,7 @@
         <v>2.82656598091125</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.51397371292114</v>
+        <v>2.51397347450256</v>
       </c>
       <c r="H1475" t="n">
         <v>18078</v>
@@ -43173,7 +43173,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1476" t="n">
         <v>9918</v>
@@ -43202,7 +43202,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1477" t="n">
         <v>1399</v>
@@ -43289,7 +43289,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1480" t="n">
         <v>17076</v>
@@ -43405,7 +43405,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1484" t="n">
         <v>24519</v>
@@ -43434,7 +43434,7 @@
         <v>3.14600610733032</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.79808664321899</v>
+        <v>2.79808640480042</v>
       </c>
       <c r="H1485" t="n">
         <v>143477</v>
@@ -43492,7 +43492,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.73782014846802</v>
+        <v>2.7378203868866</v>
       </c>
       <c r="H1487" t="n">
         <v>26058</v>
@@ -43695,7 +43695,7 @@
         <v>3.07824611663818</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.73782014846802</v>
+        <v>2.7378203868866</v>
       </c>
       <c r="H1494" t="n">
         <v>57457</v>
@@ -43782,7 +43782,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.625896692276</v>
+        <v>2.62589693069458</v>
       </c>
       <c r="H1497" t="n">
         <v>42894</v>
@@ -43869,7 +43869,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1500" t="n">
         <v>22756</v>
@@ -44043,7 +44043,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1506" t="n">
         <v>20996</v>
@@ -44101,7 +44101,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1508" t="n">
         <v>6712</v>
@@ -44130,7 +44130,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1509" t="n">
         <v>1581</v>
@@ -44159,7 +44159,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1510" t="n">
         <v>8075</v>
@@ -44304,7 +44304,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1515" t="n">
         <v>32516</v>
@@ -44333,7 +44333,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1516" t="n">
         <v>46577</v>
@@ -44391,7 +44391,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1518" t="n">
         <v>29111</v>
@@ -44449,7 +44449,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1520" t="n">
         <v>17400</v>
@@ -44478,7 +44478,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1521" t="n">
         <v>46845</v>
@@ -44565,7 +44565,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1524" t="n">
         <v>40680</v>
@@ -44594,7 +44594,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1525" t="n">
         <v>22382</v>
@@ -44623,7 +44623,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1526" t="n">
         <v>3220</v>
@@ -44652,7 +44652,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1527" t="n">
         <v>21079</v>
@@ -44710,7 +44710,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1529" t="n">
         <v>39356</v>
@@ -44768,7 +44768,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1531" t="n">
         <v>13812</v>
@@ -44855,7 +44855,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1534" t="n">
         <v>3396</v>
@@ -44884,7 +44884,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1535" t="n">
         <v>298</v>
@@ -44913,7 +44913,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.625896692276</v>
+        <v>2.62589693069458</v>
       </c>
       <c r="H1536" t="n">
         <v>6092</v>
@@ -45087,7 +45087,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1542" t="n">
         <v>23641</v>
@@ -45116,7 +45116,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.625896692276</v>
+        <v>2.62589693069458</v>
       </c>
       <c r="H1543" t="n">
         <v>16346</v>
@@ -45145,7 +45145,7 @@
         <v>2.97176599502563</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.64311599731445</v>
+        <v>2.64311575889587</v>
       </c>
       <c r="H1544" t="n">
         <v>64626</v>
@@ -45174,7 +45174,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1545" t="n">
         <v>35279</v>
@@ -45203,7 +45203,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867810249329</v>
+        <v>2.60867786407471</v>
       </c>
       <c r="H1546" t="n">
         <v>1556</v>
@@ -45261,7 +45261,7 @@
         <v>2.95240592956543</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.625896692276</v>
+        <v>2.62589693069458</v>
       </c>
       <c r="H1548" t="n">
         <v>40237</v>
@@ -45290,7 +45290,7 @@
         <v>2.9233660697937</v>
       </c>
       <c r="G1549" t="n">
-        <v>2.60006833076477</v>
+        <v>2.60006856918335</v>
       </c>
       <c r="H1549" t="n">
         <v>33069</v>
@@ -45464,7 +45464,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1555" t="n">
         <v>2918</v>
@@ -45493,7 +45493,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1556" t="n">
         <v>2071</v>
@@ -45522,7 +45522,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1557" t="n">
         <v>8550</v>
@@ -45580,7 +45580,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1559" t="n">
         <v>5144</v>
@@ -45638,7 +45638,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1561" t="n">
         <v>4172</v>
@@ -45667,7 +45667,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1562" t="n">
         <v>3173</v>
@@ -45696,7 +45696,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1563" t="n">
         <v>46081</v>
@@ -45725,7 +45725,7 @@
         <v>2.87496590614319</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.55702090263367</v>
+        <v>2.55702114105225</v>
       </c>
       <c r="H1564" t="n">
         <v>60925</v>
@@ -45754,7 +45754,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53980207443237</v>
+        <v>2.53980183601379</v>
       </c>
       <c r="H1565" t="n">
         <v>19052</v>
@@ -45783,7 +45783,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1566" t="n">
         <v>15762</v>
@@ -45812,7 +45812,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.58284950256348</v>
+        <v>2.58284974098206</v>
       </c>
       <c r="H1567" t="n">
         <v>4363</v>
@@ -45957,7 +45957,7 @@
         <v>2.778165102005</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.4709255695343</v>
+        <v>2.47092533111572</v>
       </c>
       <c r="H1572" t="n">
         <v>11420</v>
@@ -46044,7 +46044,7 @@
         <v>2.7684850692749</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.46231579780579</v>
+        <v>2.46231603622437</v>
       </c>
       <c r="H1575" t="n">
         <v>2078</v>
@@ -46102,7 +46102,7 @@
         <v>2.72976493835449</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.42787766456604</v>
+        <v>2.42787790298462</v>
       </c>
       <c r="H1577" t="n">
         <v>7789</v>
@@ -46218,7 +46218,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1581" t="n">
         <v>32796</v>
@@ -46421,7 +46421,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1588" t="n">
         <v>3414</v>
@@ -46479,7 +46479,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1590" t="n">
         <v>4907</v>
@@ -46653,7 +46653,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1596" t="n">
         <v>20064</v>
@@ -46682,7 +46682,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.35039281845093</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1597" t="n">
         <v>15617</v>
@@ -46711,7 +46711,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1598" t="n">
         <v>1874</v>
@@ -46740,7 +46740,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1599" t="n">
         <v>1891</v>
@@ -46856,7 +46856,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1603" t="n">
         <v>1960</v>
@@ -47001,7 +47001,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.33317375183105</v>
+        <v>2.33317351341248</v>
       </c>
       <c r="H1608" t="n">
         <v>17007</v>
@@ -47030,7 +47030,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.31595492362976</v>
+        <v>2.31595468521118</v>
       </c>
       <c r="H1609" t="n">
         <v>2565</v>
@@ -47059,7 +47059,7 @@
         <v>2.58456492424011</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.29873585700989</v>
+        <v>2.29873561859131</v>
       </c>
       <c r="H1610" t="n">
         <v>6882</v>
@@ -47088,7 +47088,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.31595492362976</v>
+        <v>2.31595468521118</v>
       </c>
       <c r="H1611" t="n">
         <v>32982</v>
@@ -47146,7 +47146,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1613" t="n">
         <v>29869</v>
@@ -47204,7 +47204,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1615" t="n">
         <v>7674</v>
@@ -47233,7 +47233,7 @@
         <v>2.53616499900818</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.25568819046021</v>
+        <v>2.25568842887878</v>
       </c>
       <c r="H1616" t="n">
         <v>12621</v>
@@ -47320,7 +47320,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.31595492362976</v>
+        <v>2.31595468521118</v>
       </c>
       <c r="H1619" t="n">
         <v>51766</v>
@@ -47349,7 +47349,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1620" t="n">
         <v>9318</v>
@@ -47407,7 +47407,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.26429796218872</v>
+        <v>2.26429772377014</v>
       </c>
       <c r="H1622" t="n">
         <v>10065</v>
@@ -47436,7 +47436,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1623" t="n">
         <v>4589</v>
@@ -47465,7 +47465,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1624" t="n">
         <v>1019</v>
@@ -47494,7 +47494,7 @@
         <v>2.53616499900818</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.25568819046021</v>
+        <v>2.25568842887878</v>
       </c>
       <c r="H1625" t="n">
         <v>4983</v>
@@ -47581,7 +47581,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1628" t="n">
         <v>14751</v>
@@ -47610,7 +47610,7 @@
         <v>2.53616499900818</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.25568819046021</v>
+        <v>2.25568842887878</v>
       </c>
       <c r="H1629" t="n">
         <v>9865</v>
@@ -47726,7 +47726,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542217254639</v>
+        <v>2.19542193412781</v>
       </c>
       <c r="H1633" t="n">
         <v>21458</v>
@@ -47755,7 +47755,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1634" t="n">
         <v>5717</v>
@@ -47784,7 +47784,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542217254639</v>
+        <v>2.19542193412781</v>
       </c>
       <c r="H1635" t="n">
         <v>12502</v>
@@ -47813,7 +47813,7 @@
         <v>2.44904494285583</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.17820310592651</v>
+        <v>2.17820286750793</v>
       </c>
       <c r="H1636" t="n">
         <v>8399</v>
@@ -47842,7 +47842,7 @@
         <v>2.44904494285583</v>
       </c>
       <c r="G1637" t="n">
-        <v>2.17820310592651</v>
+        <v>2.17820286750793</v>
       </c>
       <c r="H1637" t="n">
         <v>13308</v>
@@ -47871,7 +47871,7 @@
         <v>2.42968511581421</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.16098403930664</v>
+        <v>2.16098427772522</v>
       </c>
       <c r="H1638" t="n">
         <v>21499</v>
@@ -47900,7 +47900,7 @@
         <v>2.42968511581421</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.16098403930664</v>
+        <v>2.16098427772522</v>
       </c>
       <c r="H1639" t="n">
         <v>53308</v>
@@ -48016,7 +48016,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.09210824966431</v>
+        <v>2.09210848808289</v>
       </c>
       <c r="H1643" t="n">
         <v>3904</v>
@@ -48132,7 +48132,7 @@
         <v>2.34256505966187</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.08349871635437</v>
+        <v>2.08349895477295</v>
       </c>
       <c r="H1647" t="n">
         <v>19328</v>
@@ -48190,7 +48190,7 @@
         <v>2.03280401229858</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.80799448490143</v>
+        <v>1.80799436569214</v>
       </c>
       <c r="H1649" t="n">
         <v>181839</v>
@@ -48364,7 +48364,7 @@
         <v>2.236083984375</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.9887934923172</v>
+        <v>1.98879337310791</v>
       </c>
       <c r="H1655" t="n">
         <v>10660</v>
@@ -48393,7 +48393,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1656" t="n">
         <v>18678</v>
@@ -48596,7 +48596,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1663" t="n">
         <v>4546</v>
@@ -48625,7 +48625,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1664" t="n">
         <v>7148</v>
@@ -48654,7 +48654,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157466411591</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1665" t="n">
         <v>13211</v>
@@ -48683,7 +48683,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157466411591</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1666" t="n">
         <v>1802</v>
@@ -48799,7 +48799,7 @@
         <v>2.19736409187317</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.95435559749603</v>
+        <v>1.95435547828674</v>
       </c>
       <c r="H1670" t="n">
         <v>12022</v>
@@ -48828,7 +48828,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1671" t="n">
         <v>9132</v>
@@ -48886,7 +48886,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1673" t="n">
         <v>6434</v>
@@ -49031,7 +49031,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1678" t="n">
         <v>989</v>
@@ -49060,7 +49060,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157466411591</v>
+        <v>1.97157454490662</v>
       </c>
       <c r="H1679" t="n">
         <v>11494</v>
@@ -49234,7 +49234,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713676929474</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1685" t="n">
         <v>2206</v>
@@ -49292,7 +49292,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.92852711677551</v>
+        <v>1.92852735519409</v>
       </c>
       <c r="H1687" t="n">
         <v>8509</v>
@@ -49321,7 +49321,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.92852711677551</v>
+        <v>1.92852735519409</v>
       </c>
       <c r="H1688" t="n">
         <v>1787</v>
@@ -49350,7 +49350,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130793094635</v>
       </c>
       <c r="H1689" t="n">
         <v>2827</v>
@@ -49379,7 +49379,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713676929474</v>
+        <v>1.93713665008545</v>
       </c>
       <c r="H1690" t="n">
         <v>6351</v>
@@ -49408,7 +49408,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130793094635</v>
       </c>
       <c r="H1691" t="n">
         <v>11205</v>
@@ -49437,7 +49437,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.92852711677551</v>
+        <v>1.92852735519409</v>
       </c>
       <c r="H1692" t="n">
         <v>13</v>
@@ -49524,7 +49524,7 @@
         <v>2.16832399368286</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.92852711677551</v>
+        <v>1.92852735519409</v>
       </c>
       <c r="H1695" t="n">
         <v>4200</v>
@@ -49553,7 +49553,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.91130816936493</v>
+        <v>1.91130793094635</v>
       </c>
       <c r="H1696" t="n">
         <v>8700</v>
@@ -49582,7 +49582,7 @@
         <v>2.19736409187317</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.95435559749603</v>
+        <v>1.95435547828674</v>
       </c>
       <c r="H1697" t="n">
         <v>7025</v>
@@ -49669,7 +49669,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1700" t="n">
         <v>18468</v>
@@ -49698,7 +49698,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1701" t="n">
         <v>24585</v>
@@ -49814,7 +49814,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1705" t="n">
         <v>17809</v>
@@ -50017,7 +50017,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1712" t="n">
         <v>2050</v>
@@ -50162,7 +50162,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1717" t="n">
         <v>7314</v>
@@ -50249,7 +50249,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1720" t="n">
         <v>13618</v>
@@ -50278,7 +50278,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1721" t="n">
         <v>17819</v>
@@ -50307,7 +50307,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1722" t="n">
         <v>4243</v>
@@ -50365,7 +50365,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1724" t="n">
         <v>14445</v>
@@ -50394,7 +50394,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1725" t="n">
         <v>30310</v>
@@ -50452,7 +50452,7 @@
         <v>2.25544404983521</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.00601267814636</v>
+        <v>2.00601243972778</v>
       </c>
       <c r="H1727" t="n">
         <v>8079</v>
@@ -50510,7 +50510,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1729" t="n">
         <v>65398</v>
@@ -50597,7 +50597,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1732" t="n">
         <v>1549</v>
@@ -50655,7 +50655,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1734" t="n">
         <v>31099</v>
@@ -50684,7 +50684,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1735" t="n">
         <v>43518</v>
@@ -50713,7 +50713,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1736" t="n">
         <v>14137</v>
@@ -50771,7 +50771,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1738" t="n">
         <v>18680</v>
@@ -50800,7 +50800,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1739" t="n">
         <v>19421</v>
@@ -50829,7 +50829,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1740" t="n">
         <v>2244</v>
@@ -50858,7 +50858,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.02323174476624</v>
+        <v>2.02323150634766</v>
       </c>
       <c r="H1741" t="n">
         <v>28106</v>
@@ -51061,7 +51061,7 @@
         <v>2.42968511581421</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.16098403930664</v>
+        <v>2.16098427772522</v>
       </c>
       <c r="H1748" t="n">
         <v>38106</v>
@@ -51090,7 +51090,7 @@
         <v>2.42000508308411</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.1523745059967</v>
+        <v>2.15237474441528</v>
       </c>
       <c r="H1749" t="n">
         <v>10433</v>
@@ -51119,7 +51119,7 @@
         <v>2.42000508308411</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.1523745059967</v>
+        <v>2.15237474441528</v>
       </c>
       <c r="H1750" t="n">
         <v>27892</v>
@@ -51148,7 +51148,7 @@
         <v>2.42000508308411</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.1523745059967</v>
+        <v>2.15237474441528</v>
       </c>
       <c r="H1751" t="n">
         <v>88617</v>
@@ -51235,7 +51235,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1754" t="n">
         <v>28322</v>
@@ -51293,7 +51293,7 @@
         <v>2.56520509719849</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.28151702880859</v>
+        <v>2.28151679039001</v>
       </c>
       <c r="H1756" t="n">
         <v>20023</v>
@@ -51322,7 +51322,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.22985982894897</v>
+        <v>2.22986006736755</v>
       </c>
       <c r="H1757" t="n">
         <v>34411</v>
@@ -51351,7 +51351,7 @@
         <v>2.60392498970032</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.31595492362976</v>
+        <v>2.31595468521118</v>
       </c>
       <c r="H1758" t="n">
         <v>35729</v>
@@ -51380,7 +51380,7 @@
         <v>2.58456492424011</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.29873585700989</v>
+        <v>2.29873561859131</v>
       </c>
       <c r="H1759" t="n">
         <v>32149</v>
@@ -51438,7 +51438,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1761" t="n">
         <v>46109</v>
@@ -51467,7 +51467,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178328514099</v>
+        <v>2.34178304672241</v>
       </c>
       <c r="H1762" t="n">
         <v>39976</v>
@@ -51496,7 +51496,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1763" t="n">
         <v>42243</v>
@@ -51612,7 +51612,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1767" t="n">
         <v>46462</v>
@@ -51641,7 +51641,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1768" t="n">
         <v>78393</v>
@@ -51670,7 +51670,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.49675464630127</v>
+        <v>2.49675440788269</v>
       </c>
       <c r="H1769" t="n">
         <v>37445</v>
@@ -51931,7 +51931,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1778" t="n">
         <v>39347</v>
@@ -51960,7 +51960,7 @@
         <v>2.778165102005</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.4709255695343</v>
+        <v>2.47092533111572</v>
       </c>
       <c r="H1779" t="n">
         <v>9965</v>
@@ -52018,7 +52018,7 @@
         <v>2.72976493835449</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.42787766456604</v>
+        <v>2.42787790298462</v>
       </c>
       <c r="H1781" t="n">
         <v>44312</v>
@@ -52192,7 +52192,7 @@
         <v>2.7588050365448</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.45370650291443</v>
+        <v>2.45370626449585</v>
       </c>
       <c r="H1787" t="n">
         <v>21255</v>
@@ -52221,7 +52221,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1788" t="n">
         <v>16442</v>
@@ -52250,7 +52250,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1789" t="n">
         <v>12324</v>
@@ -52279,7 +52279,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1790" t="n">
         <v>4506</v>
@@ -52337,7 +52337,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1792" t="n">
         <v>4191</v>
@@ -52424,7 +52424,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1795" t="n">
         <v>15184</v>
@@ -52569,7 +52569,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1800" t="n">
         <v>4610</v>
@@ -52598,7 +52598,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1801" t="n">
         <v>10103</v>
@@ -52656,7 +52656,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1803" t="n">
         <v>9157</v>
@@ -52685,7 +52685,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1804" t="n">
         <v>1740</v>
@@ -52743,7 +52743,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1806" t="n">
         <v>13043</v>
@@ -52772,7 +52772,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1807" t="n">
         <v>1109</v>
@@ -52801,7 +52801,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.35039281845093</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1808" t="n">
         <v>13121</v>
@@ -52830,7 +52830,7 @@
         <v>2.66200494766235</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.36761164665222</v>
+        <v>2.36761140823364</v>
       </c>
       <c r="H1809" t="n">
         <v>2711</v>
@@ -52859,7 +52859,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.35039281845093</v>
+        <v>2.35039258003235</v>
       </c>
       <c r="H1810" t="n">
         <v>982</v>
@@ -52917,7 +52917,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1812" t="n">
         <v>8492</v>
@@ -53207,7 +53207,7 @@
         <v>2.69104504585266</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.39344000816345</v>
+        <v>2.39344024658203</v>
       </c>
       <c r="H1822" t="n">
         <v>32573</v>
@@ -53497,7 +53497,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H1832" t="n">
         <v>59454</v>
@@ -53526,7 +53526,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1833" t="n">
         <v>33795</v>
@@ -53555,7 +53555,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H1834" t="n">
         <v>2101</v>
@@ -53758,7 +53758,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H1841" t="n">
         <v>1854</v>
@@ -53845,7 +53845,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1844" t="n">
         <v>10237</v>
@@ -54106,7 +54106,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1853" t="n">
         <v>5483</v>
@@ -54135,7 +54135,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1854" t="n">
         <v>0</v>
@@ -54164,7 +54164,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1855" t="n">
         <v>9470</v>
@@ -54338,7 +54338,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1861" t="n">
         <v>7040</v>
@@ -54483,7 +54483,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1866" t="n">
         <v>903</v>
@@ -54512,7 +54512,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H1867" t="n">
         <v>2527</v>
@@ -54541,7 +54541,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1868" t="n">
         <v>3611</v>
@@ -54628,7 +54628,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1871" t="n">
         <v>3931</v>
@@ -54686,7 +54686,7 @@
         <v>2.43936491012573</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.2389121055603</v>
+        <v>2.23891186714172</v>
       </c>
       <c r="H1873" t="n">
         <v>23672</v>
@@ -54802,7 +54802,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H1877" t="n">
         <v>13900</v>
@@ -54831,7 +54831,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1878" t="n">
         <v>9018</v>
@@ -54860,7 +54860,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1879" t="n">
         <v>17810</v>
@@ -54918,7 +54918,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1881" t="n">
         <v>8259</v>
@@ -54947,7 +54947,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1882" t="n">
         <v>11793</v>
@@ -55353,7 +55353,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H1896" t="n">
         <v>4769</v>
@@ -55382,7 +55382,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1897" t="n">
         <v>1451</v>
@@ -55411,7 +55411,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H1898" t="n">
         <v>8092</v>
@@ -55440,7 +55440,7 @@
         <v>2.58456492424011</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.37218046188354</v>
+        <v>2.37218022346497</v>
       </c>
       <c r="H1899" t="n">
         <v>4228</v>
@@ -55469,7 +55469,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1900" t="n">
         <v>12044</v>
@@ -55498,7 +55498,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1901" t="n">
         <v>4069</v>
@@ -55556,7 +55556,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1903" t="n">
         <v>4074</v>
@@ -55614,7 +55614,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1905" t="n">
         <v>6653</v>
@@ -55701,7 +55701,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.25668120384216</v>
+        <v>2.25668096542358</v>
       </c>
       <c r="H1908" t="n">
         <v>27521</v>
@@ -55788,7 +55788,7 @@
         <v>2.58456492424011</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.37218046188354</v>
+        <v>2.37218022346497</v>
       </c>
       <c r="H1911" t="n">
         <v>20490</v>
@@ -55817,7 +55817,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.40771865844727</v>
+        <v>2.40771842002869</v>
       </c>
       <c r="H1912" t="n">
         <v>23722</v>
@@ -56020,7 +56020,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1919" t="n">
         <v>16639</v>
@@ -56078,7 +56078,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1921" t="n">
         <v>9518</v>
@@ -56165,7 +56165,7 @@
         <v>2.43936491012573</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.2389121055603</v>
+        <v>2.23891186714172</v>
       </c>
       <c r="H1924" t="n">
         <v>3915</v>
@@ -56281,7 +56281,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H1928" t="n">
         <v>17337</v>
@@ -56310,7 +56310,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H1929" t="n">
         <v>4189</v>
@@ -56368,7 +56368,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1931" t="n">
         <v>14759</v>
@@ -56397,7 +56397,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1932" t="n">
         <v>5678</v>
@@ -56513,7 +56513,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1936" t="n">
         <v>2578</v>
@@ -56542,7 +56542,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1937" t="n">
         <v>971</v>
@@ -56571,7 +56571,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H1938" t="n">
         <v>5236</v>
@@ -56716,7 +56716,7 @@
         <v>2.43936491012573</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.2389121055603</v>
+        <v>2.23891186714172</v>
       </c>
       <c r="H1943" t="n">
         <v>14865</v>
@@ -56745,7 +56745,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1944" t="n">
         <v>34951</v>
@@ -56803,7 +56803,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.25668120384216</v>
+        <v>2.25668096542358</v>
       </c>
       <c r="H1946" t="n">
         <v>20252</v>
@@ -56832,7 +56832,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1947" t="n">
         <v>23413</v>
@@ -56861,7 +56861,7 @@
         <v>2.43936491012573</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.2389121055603</v>
+        <v>2.23891186714172</v>
       </c>
       <c r="H1948" t="n">
         <v>29182</v>
@@ -56890,7 +56890,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.15895128250122</v>
+        <v>2.15895104408264</v>
       </c>
       <c r="H1949" t="n">
         <v>11476</v>
@@ -56919,7 +56919,7 @@
         <v>2.37160491943359</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.1767201423645</v>
+        <v>2.17671990394592</v>
       </c>
       <c r="H1950" t="n">
         <v>11295</v>
@@ -56948,7 +56948,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.15895128250122</v>
+        <v>2.15895104408264</v>
       </c>
       <c r="H1951" t="n">
         <v>4521</v>
@@ -56977,7 +56977,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1952" t="n">
         <v>16380</v>
@@ -57006,7 +57006,7 @@
         <v>2.410325050354</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.2122585773468</v>
+        <v>2.21225833892822</v>
       </c>
       <c r="H1953" t="n">
         <v>17845</v>
@@ -57093,7 +57093,7 @@
         <v>2.37160491943359</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.1767201423645</v>
+        <v>2.17671990394592</v>
       </c>
       <c r="H1956" t="n">
         <v>6953</v>
@@ -57180,7 +57180,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.13229656219482</v>
+        <v>2.13229632377625</v>
       </c>
       <c r="H1959" t="n">
         <v>14034</v>
@@ -57209,7 +57209,7 @@
         <v>2.32320404052734</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.13229656219482</v>
+        <v>2.13229632377625</v>
       </c>
       <c r="H1960" t="n">
         <v>4541</v>
@@ -57267,7 +57267,7 @@
         <v>2.30384397506714</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.11452746391296</v>
+        <v>2.11452722549438</v>
       </c>
       <c r="H1962" t="n">
         <v>13074</v>
@@ -57296,7 +57296,7 @@
         <v>2.30384397506714</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.11452746391296</v>
+        <v>2.11452722549438</v>
       </c>
       <c r="H1963" t="n">
         <v>209</v>
@@ -57325,7 +57325,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1964" t="n">
         <v>15269</v>
@@ -57354,7 +57354,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1965" t="n">
         <v>12872</v>
@@ -57383,7 +57383,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1966" t="n">
         <v>23652</v>
@@ -57412,7 +57412,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1967" t="n">
         <v>20448</v>
@@ -57441,7 +57441,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1968" t="n">
         <v>35340</v>
@@ -57470,7 +57470,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1969" t="n">
         <v>24002</v>
@@ -57499,7 +57499,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1970" t="n">
         <v>36918</v>
@@ -57528,7 +57528,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1971" t="n">
         <v>27120</v>
@@ -57615,7 +57615,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1974" t="n">
         <v>34163</v>
@@ -57673,7 +57673,7 @@
         <v>2.27480411529541</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.08787393569946</v>
+        <v>2.08787369728088</v>
       </c>
       <c r="H1976" t="n">
         <v>16917</v>
@@ -57789,7 +57789,7 @@
         <v>2.236083984375</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.05233550071716</v>
+        <v>2.05233526229858</v>
       </c>
       <c r="H1980" t="n">
         <v>9568</v>
@@ -57934,7 +57934,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H1985" t="n">
         <v>55841</v>
@@ -58021,7 +58021,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H1988" t="n">
         <v>43616</v>
@@ -58050,7 +58050,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H1989" t="n">
         <v>58455</v>
@@ -58166,7 +58166,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.25668120384216</v>
+        <v>2.25668096542358</v>
       </c>
       <c r="H1993" t="n">
         <v>19024</v>
@@ -58224,7 +58224,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1995" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H1995" t="n">
         <v>14714</v>
@@ -58253,7 +58253,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1996" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H1996" t="n">
         <v>31596</v>
@@ -58311,7 +58311,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H1998" t="n">
         <v>7615</v>
@@ -58369,7 +58369,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G2000" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H2000" t="n">
         <v>2168</v>
@@ -58514,7 +58514,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2005" t="n">
         <v>41791</v>
@@ -58543,7 +58543,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2006" t="n">
         <v>14896</v>
@@ -58601,7 +58601,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H2008" t="n">
         <v>27423</v>
@@ -58659,7 +58659,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2010" t="n">
         <v>5419</v>
@@ -58746,7 +58746,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H2013" t="n">
         <v>30285</v>
@@ -58775,7 +58775,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H2014" t="n">
         <v>43588</v>
@@ -58862,7 +58862,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2017" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2017" t="n">
         <v>39236</v>
@@ -58891,7 +58891,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2018" t="n">
         <v>9889</v>
@@ -58920,7 +58920,7 @@
         <v>2.52648496627808</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.31887316703796</v>
+        <v>2.31887292861938</v>
       </c>
       <c r="H2019" t="n">
         <v>7853</v>
@@ -58949,7 +58949,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H2020" t="n">
         <v>17003</v>
@@ -58978,7 +58978,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G2021" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H2021" t="n">
         <v>28514</v>
@@ -59065,7 +59065,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H2024" t="n">
         <v>7013</v>
@@ -59094,7 +59094,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H2025" t="n">
         <v>10324</v>
@@ -59210,7 +59210,7 @@
         <v>2.48776507377625</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.28333497047424</v>
+        <v>2.28333473205566</v>
       </c>
       <c r="H2029" t="n">
         <v>102293</v>
@@ -59326,7 +59326,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.33664226531982</v>
+        <v>2.33664202690125</v>
       </c>
       <c r="H2033" t="n">
         <v>40125</v>
@@ -59674,7 +59674,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.25668120384216</v>
+        <v>2.25668096542358</v>
       </c>
       <c r="H2045" t="n">
         <v>6582</v>
@@ -59761,7 +59761,7 @@
         <v>2.37160491943359</v>
       </c>
       <c r="G2048" t="n">
-        <v>2.1767201423645</v>
+        <v>2.17671990394592</v>
       </c>
       <c r="H2048" t="n">
         <v>21499</v>
@@ -59790,7 +59790,7 @@
         <v>2.30384397506714</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.11452746391296</v>
+        <v>2.11452722549438</v>
       </c>
       <c r="H2049" t="n">
         <v>8476</v>
@@ -59848,7 +59848,7 @@
         <v>2.35224509239197</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.15895128250122</v>
+        <v>2.15895104408264</v>
       </c>
       <c r="H2051" t="n">
         <v>10865</v>
@@ -60138,7 +60138,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G2061" t="n">
-        <v>2.25668120384216</v>
+        <v>2.25668096542358</v>
       </c>
       <c r="H2061" t="n">
         <v>11223</v>
@@ -60254,7 +60254,7 @@
         <v>2.45872497558594</v>
       </c>
       <c r="G2065" t="n">
-        <v>2.25668120384216</v>
+        <v>2.25668096542358</v>
       </c>
       <c r="H2065" t="n">
         <v>231306</v>
@@ -60312,7 +60312,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2067" t="n">
         <v>7954</v>
@@ -60341,7 +60341,7 @@
         <v>2.49744510650635</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.29221963882446</v>
+        <v>2.29221940040588</v>
       </c>
       <c r="H2068" t="n">
         <v>45547</v>
@@ -60428,7 +60428,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H2071" t="n">
         <v>64047</v>
@@ -60457,7 +60457,7 @@
         <v>2.58456492424011</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.37218046188354</v>
+        <v>2.37218022346497</v>
       </c>
       <c r="H2072" t="n">
         <v>111463</v>
@@ -60515,7 +60515,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.34552693367004</v>
+        <v>2.34552669525146</v>
       </c>
       <c r="H2074" t="n">
         <v>24088</v>
@@ -60544,7 +60544,7 @@
         <v>2.57488489151001</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.36329579353333</v>
+        <v>2.36329555511475</v>
       </c>
       <c r="H2075" t="n">
         <v>34358</v>
@@ -71106,6 +71106,35 @@
         <v>4161</v>
       </c>
       <c r="I2439" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2440" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2440" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G2440" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="H2440" t="n">
+        <v>22535</v>
+      </c>
+      <c r="I2440" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G3" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H3" t="n">
         <v>6711</v>
@@ -485,7 +485,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269636154175</v>
+        <v>7.41269588470459</v>
       </c>
       <c r="H4" t="n">
         <v>14488</v>
@@ -543,7 +543,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G6" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H6" t="n">
         <v>3089</v>
@@ -572,7 +572,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G7" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H8" t="n">
         <v>532</v>
@@ -630,7 +630,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H9" t="n">
         <v>213</v>
@@ -659,7 +659,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H10" t="n">
         <v>1917</v>
@@ -717,7 +717,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G12" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H12" t="n">
         <v>1065</v>
@@ -746,7 +746,7 @@
         <v>9.34914016723633</v>
       </c>
       <c r="G13" t="n">
-        <v>7.35363054275513</v>
+        <v>7.35362911224365</v>
       </c>
       <c r="H13" t="n">
         <v>2450</v>
@@ -775,7 +775,7 @@
         <v>9.56503295898438</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52344179153442</v>
+        <v>7.52344226837158</v>
       </c>
       <c r="H14" t="n">
         <v>532</v>
@@ -804,7 +804,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G15" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H15" t="n">
         <v>1384</v>
@@ -833,7 +833,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G16" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H16" t="n">
         <v>213</v>
@@ -862,7 +862,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H17" t="n">
         <v>106</v>
@@ -891,7 +891,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302213668823</v>
+        <v>7.31302261352539</v>
       </c>
       <c r="H18" t="n">
         <v>7244</v>
@@ -920,7 +920,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G19" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H19" t="n">
         <v>7776</v>
@@ -949,7 +949,7 @@
         <v>9.3585262298584</v>
       </c>
       <c r="G20" t="n">
-        <v>7.36101293563843</v>
+        <v>7.36101245880127</v>
       </c>
       <c r="H20" t="n">
         <v>1065</v>
@@ -978,7 +978,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512521743774</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H21" t="n">
         <v>3302</v>
@@ -1007,7 +1007,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G22" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H22" t="n">
         <v>2450</v>
@@ -1036,7 +1036,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484401702881</v>
+        <v>7.43484449386597</v>
       </c>
       <c r="H23" t="n">
         <v>1065</v>
@@ -1094,7 +1094,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G25" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H25" t="n">
         <v>1384</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H26" t="n">
         <v>4154</v>
@@ -1152,7 +1152,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H27" t="n">
         <v>639</v>
@@ -1181,7 +1181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H30" t="n">
         <v>1704</v>
@@ -1297,7 +1297,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437644958496</v>
       </c>
       <c r="H32" t="n">
         <v>4580</v>
@@ -1326,7 +1326,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H33" t="n">
         <v>426</v>
@@ -1355,7 +1355,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G35" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727478027344</v>
       </c>
       <c r="H35" t="n">
         <v>2769</v>
@@ -1529,7 +1529,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G40" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H40" t="n">
         <v>1598</v>
@@ -1558,7 +1558,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H41" t="n">
         <v>15021</v>
@@ -1587,7 +1587,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H42" t="n">
         <v>12784</v>
@@ -1616,7 +1616,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H43" t="n">
         <v>5326</v>
@@ -1645,7 +1645,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H44" t="n">
         <v>12357</v>
@@ -1674,7 +1674,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H45" t="n">
         <v>10014</v>
@@ -1703,7 +1703,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H46" t="n">
         <v>1598</v>
@@ -1732,7 +1732,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H47" t="n">
         <v>3089</v>
@@ -1761,7 +1761,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4791431427002</v>
+        <v>7.47914361953735</v>
       </c>
       <c r="H48" t="n">
         <v>3941</v>
@@ -1790,7 +1790,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H49" t="n">
         <v>9588</v>
@@ -1848,7 +1848,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H51" t="n">
         <v>13103</v>
@@ -1877,7 +1877,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437740325928</v>
+        <v>7.46437644958496</v>
       </c>
       <c r="H52" t="n">
         <v>2982</v>
@@ -1906,7 +1906,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H53" t="n">
         <v>7776</v>
@@ -1935,7 +1935,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H54" t="n">
         <v>319</v>
@@ -1964,7 +1964,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H55" t="n">
         <v>21306</v>
@@ -1993,7 +1993,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H56" t="n">
         <v>4261</v>
@@ -2080,7 +2080,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H59" t="n">
         <v>106</v>
@@ -2167,7 +2167,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587350845337</v>
       </c>
       <c r="H62" t="n">
         <v>1065</v>
@@ -2196,7 +2196,7 @@
         <v>9.94050121307373</v>
       </c>
       <c r="G63" t="n">
-        <v>7.81876945495605</v>
+        <v>7.81876850128174</v>
       </c>
       <c r="H63" t="n">
         <v>16725</v>
@@ -2225,7 +2225,7 @@
         <v>9.86540699005127</v>
       </c>
       <c r="G64" t="n">
-        <v>7.75970411300659</v>
+        <v>7.75970315933228</v>
       </c>
       <c r="H64" t="n">
         <v>12570</v>
@@ -2254,7 +2254,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G65" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568523406982</v>
       </c>
       <c r="H65" t="n">
         <v>22052</v>
@@ -2283,7 +2283,7 @@
         <v>9.98743438720703</v>
       </c>
       <c r="G66" t="n">
-        <v>7.85568475723267</v>
+        <v>7.85568523406982</v>
       </c>
       <c r="H66" t="n">
         <v>4261</v>
@@ -2312,7 +2312,7 @@
         <v>10.1188478469849</v>
       </c>
       <c r="G67" t="n">
-        <v>7.95904970169067</v>
+        <v>7.95904874801636</v>
       </c>
       <c r="H67" t="n">
         <v>7137</v>
@@ -2341,7 +2341,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G68" t="n">
-        <v>7.8704514503479</v>
+        <v>7.87045049667358</v>
       </c>
       <c r="H68" t="n">
         <v>1704</v>
@@ -2457,7 +2457,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G72" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998435974121</v>
       </c>
       <c r="H72" t="n">
         <v>2343</v>
@@ -2486,7 +2486,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.94428396224976</v>
+        <v>7.94428300857544</v>
       </c>
       <c r="H73" t="n">
         <v>5326</v>
@@ -2515,7 +2515,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G74" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998435974121</v>
       </c>
       <c r="H74" t="n">
         <v>6924</v>
@@ -2544,7 +2544,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998435974121</v>
       </c>
       <c r="H75" t="n">
         <v>1065</v>
@@ -2631,7 +2631,7 @@
         <v>10.0062084197998</v>
       </c>
       <c r="G78" t="n">
-        <v>7.8704514503479</v>
+        <v>7.87045049667358</v>
       </c>
       <c r="H78" t="n">
         <v>639</v>
@@ -2718,7 +2718,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G81" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372156143188</v>
       </c>
       <c r="H81" t="n">
         <v>6072</v>
@@ -3037,7 +3037,7 @@
         <v>9.93111419677734</v>
       </c>
       <c r="G92" t="n">
-        <v>7.81138467788696</v>
+        <v>7.81138563156128</v>
       </c>
       <c r="H92" t="n">
         <v>7457</v>
@@ -3153,7 +3153,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H96" t="n">
         <v>1598</v>
@@ -3182,7 +3182,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73755407333374</v>
+        <v>7.73755311965942</v>
       </c>
       <c r="H97" t="n">
         <v>2556</v>
@@ -3240,7 +3240,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G99" t="n">
-        <v>7.73755407333374</v>
+        <v>7.73755311965942</v>
       </c>
       <c r="H99" t="n">
         <v>11612</v>
@@ -3269,7 +3269,7 @@
         <v>9.78092670440674</v>
       </c>
       <c r="G100" t="n">
-        <v>7.69325542449951</v>
+        <v>7.6932544708252</v>
       </c>
       <c r="H100" t="n">
         <v>1811</v>
@@ -3327,7 +3327,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H102" t="n">
         <v>1065</v>
@@ -3356,7 +3356,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587350845337</v>
       </c>
       <c r="H103" t="n">
         <v>852</v>
@@ -3559,7 +3559,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G110" t="n">
-        <v>7.73755407333374</v>
+        <v>7.73755311965942</v>
       </c>
       <c r="H110" t="n">
         <v>319</v>
@@ -3646,7 +3646,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H113" t="n">
         <v>2237</v>
@@ -3675,7 +3675,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G114" t="n">
-        <v>7.73755407333374</v>
+        <v>7.73755311965942</v>
       </c>
       <c r="H114" t="n">
         <v>4687</v>
@@ -3704,7 +3704,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G115" t="n">
-        <v>7.73755407333374</v>
+        <v>7.73755311965942</v>
       </c>
       <c r="H115" t="n">
         <v>213</v>
@@ -3733,7 +3733,7 @@
         <v>9.83724689483643</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73755407333374</v>
+        <v>7.73755311965942</v>
       </c>
       <c r="H116" t="n">
         <v>319</v>
@@ -3791,7 +3791,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063924789429</v>
+        <v>7.70063829421997</v>
       </c>
       <c r="H118" t="n">
         <v>50070</v>
@@ -3820,7 +3820,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G119" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H119" t="n">
         <v>5326</v>
@@ -3878,7 +3878,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H121" t="n">
         <v>4580</v>
@@ -3907,7 +3907,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H122" t="n">
         <v>213</v>
@@ -3936,7 +3936,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278833389282</v>
+        <v>7.72278738021851</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>9.74337959289551</v>
       </c>
       <c r="G125" t="n">
-        <v>7.6637225151062</v>
+        <v>7.66372156143188</v>
       </c>
       <c r="H125" t="n">
         <v>426</v>
@@ -4023,7 +4023,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65634059906006</v>
       </c>
       <c r="H126" t="n">
         <v>426</v>
@@ -4168,7 +4168,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H131" t="n">
         <v>1811</v>
@@ -4197,7 +4197,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G132" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680578231812</v>
       </c>
       <c r="H132" t="n">
         <v>1704</v>
@@ -4226,7 +4226,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G133" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680578231812</v>
       </c>
       <c r="H133" t="n">
         <v>2769</v>
@@ -4255,7 +4255,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67110538482666</v>
+        <v>7.67110443115234</v>
       </c>
       <c r="H134" t="n">
         <v>852</v>
@@ -4284,7 +4284,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157438278198</v>
+        <v>7.64157342910767</v>
       </c>
       <c r="H135" t="n">
         <v>1384</v>
@@ -4313,7 +4313,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512521743774</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H136" t="n">
         <v>2556</v>
@@ -4342,7 +4342,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H137" t="n">
         <v>10440</v>
@@ -4371,7 +4371,7 @@
         <v>9.54625988006592</v>
       </c>
       <c r="G138" t="n">
-        <v>7.50867652893066</v>
+        <v>7.50867557525635</v>
       </c>
       <c r="H138" t="n">
         <v>3302</v>
@@ -4400,7 +4400,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H139" t="n">
         <v>6498</v>
@@ -4429,7 +4429,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G140" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727478027344</v>
       </c>
       <c r="H140" t="n">
         <v>7457</v>
@@ -4458,7 +4458,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G141" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727478027344</v>
       </c>
       <c r="H141" t="n">
         <v>18323</v>
@@ -4516,7 +4516,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H143" t="n">
         <v>8629</v>
@@ -4545,7 +4545,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G144" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H144" t="n">
         <v>213</v>
@@ -4574,7 +4574,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H145" t="n">
         <v>1065</v>
@@ -4603,7 +4603,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H146" t="n">
         <v>106</v>
@@ -4632,7 +4632,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H149" t="n">
         <v>2663</v>
@@ -4719,7 +4719,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H150" t="n">
         <v>2769</v>
@@ -4748,7 +4748,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H151" t="n">
         <v>12997</v>
@@ -4777,7 +4777,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G152" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H152" t="n">
         <v>13742</v>
@@ -4806,7 +4806,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G153" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680578231812</v>
       </c>
       <c r="H153" t="n">
         <v>639</v>
@@ -4835,7 +4835,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G154" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727478027344</v>
       </c>
       <c r="H154" t="n">
         <v>3409</v>
@@ -4893,7 +4893,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G156" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65634059906006</v>
       </c>
       <c r="H156" t="n">
         <v>426</v>
@@ -4922,7 +4922,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G157" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680578231812</v>
       </c>
       <c r="H157" t="n">
         <v>2343</v>
@@ -4951,7 +4951,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G158" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680578231812</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G159" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H159" t="n">
         <v>22691</v>
@@ -5009,7 +5009,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G160" t="n">
-        <v>7.61942481994629</v>
+        <v>7.61942386627197</v>
       </c>
       <c r="H160" t="n">
         <v>26953</v>
@@ -5038,7 +5038,7 @@
         <v>9.68706035614014</v>
       </c>
       <c r="G161" t="n">
-        <v>7.61942481994629</v>
+        <v>7.61942386627197</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063924789429</v>
+        <v>7.70063829421997</v>
       </c>
       <c r="H163" t="n">
         <v>1171</v>
@@ -5154,7 +5154,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G165" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65634059906006</v>
       </c>
       <c r="H165" t="n">
         <v>2343</v>
@@ -5183,7 +5183,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G166" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65634059906006</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540355682373</v>
       </c>
       <c r="H167" t="n">
         <v>745</v>
@@ -5241,7 +5241,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G168" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65634059906006</v>
       </c>
       <c r="H168" t="n">
         <v>46022</v>
@@ -5328,7 +5328,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587350845337</v>
       </c>
       <c r="H171" t="n">
         <v>21519</v>
@@ -5357,7 +5357,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587255477905</v>
+        <v>7.68587350845337</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540355682373</v>
       </c>
       <c r="H173" t="n">
         <v>5433</v>
@@ -5415,7 +5415,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G174" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H174" t="n">
         <v>32918</v>
@@ -5444,7 +5444,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H175" t="n">
         <v>1278</v>
@@ -5473,7 +5473,7 @@
         <v>9.65890026092529</v>
       </c>
       <c r="G176" t="n">
-        <v>7.59727334976196</v>
+        <v>7.59727478027344</v>
       </c>
       <c r="H176" t="n">
         <v>745</v>
@@ -5502,7 +5502,7 @@
         <v>9.73399353027344</v>
       </c>
       <c r="G177" t="n">
-        <v>7.65633869171143</v>
+        <v>7.65634059906006</v>
       </c>
       <c r="H177" t="n">
         <v>5859</v>
@@ -5531,7 +5531,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H178" t="n">
         <v>10653</v>
@@ -5560,7 +5560,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G179" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H179" t="n">
         <v>13210</v>
@@ -5589,7 +5589,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H180" t="n">
         <v>11079</v>
@@ -5618,7 +5618,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774282455444</v>
+        <v>7.56774187088013</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>9.58380699157715</v>
       </c>
       <c r="G184" t="n">
-        <v>7.53820848464966</v>
+        <v>7.53820943832397</v>
       </c>
       <c r="H184" t="n">
         <v>7457</v>
@@ -5734,7 +5734,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391078948975</v>
       </c>
       <c r="H185" t="n">
         <v>11718</v>
@@ -5763,7 +5763,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H186" t="n">
         <v>7137</v>
@@ -5821,7 +5821,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H188" t="n">
         <v>3196</v>
@@ -5850,7 +5850,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512521743774</v>
+        <v>7.57512474060059</v>
       </c>
       <c r="H189" t="n">
         <v>106</v>
@@ -5937,7 +5937,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H192" t="n">
         <v>213</v>
@@ -5966,7 +5966,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G193" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H193" t="n">
         <v>9481</v>
@@ -5995,7 +5995,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G194" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H194" t="n">
         <v>8735</v>
@@ -6024,7 +6024,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G195" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H195" t="n">
         <v>3196</v>
@@ -6111,7 +6111,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G198" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H198" t="n">
         <v>10653</v>
@@ -6140,7 +6140,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G199" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H199" t="n">
         <v>15553</v>
@@ -6169,7 +6169,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H201" t="n">
         <v>745</v>
@@ -6227,7 +6227,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H203" t="n">
         <v>1384</v>
@@ -6314,7 +6314,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G205" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H205" t="n">
         <v>106</v>
@@ -6343,7 +6343,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G206" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H206" t="n">
         <v>5220</v>
@@ -6372,7 +6372,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G207" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H207" t="n">
         <v>3728</v>
@@ -6401,7 +6401,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G208" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H208" t="n">
         <v>2130</v>
@@ -6430,7 +6430,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H209" t="n">
         <v>319</v>
@@ -6459,7 +6459,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G210" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H210" t="n">
         <v>1171</v>
@@ -6488,7 +6488,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H211" t="n">
         <v>3728</v>
@@ -6517,7 +6517,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H212" t="n">
         <v>958</v>
@@ -6546,7 +6546,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G213" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H213" t="n">
         <v>27379</v>
@@ -6575,7 +6575,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G214" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H214" t="n">
         <v>12357</v>
@@ -6604,7 +6604,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H215" t="n">
         <v>639</v>
@@ -6633,7 +6633,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H216" t="n">
         <v>11612</v>
@@ -6778,7 +6778,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G221" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998435974121</v>
       </c>
       <c r="H221" t="n">
         <v>44637</v>
@@ -6807,7 +6807,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G222" t="n">
-        <v>7.89998340606689</v>
+        <v>7.89998435974121</v>
       </c>
       <c r="H222" t="n">
         <v>38565</v>
@@ -7039,7 +7039,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G230" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H230" t="n">
         <v>24076</v>
@@ -7068,7 +7068,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H231" t="n">
         <v>3089</v>
@@ -7097,7 +7097,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H232" t="n">
         <v>7883</v>
@@ -7126,7 +7126,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H233" t="n">
         <v>23970</v>
@@ -7155,7 +7155,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G234" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H234" t="n">
         <v>54864</v>
@@ -7184,7 +7184,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H235" t="n">
         <v>9055</v>
@@ -7213,7 +7213,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H236" t="n">
         <v>8203</v>
@@ -7242,7 +7242,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G237" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H237" t="n">
         <v>4794</v>
@@ -7271,7 +7271,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G238" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H238" t="n">
         <v>14062</v>
@@ -7329,7 +7329,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G240" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H240" t="n">
         <v>21413</v>
@@ -7358,7 +7358,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H241" t="n">
         <v>39630</v>
@@ -7387,7 +7387,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H242" t="n">
         <v>19495</v>
@@ -7416,7 +7416,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H243" t="n">
         <v>23650</v>
@@ -7445,7 +7445,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H244" t="n">
         <v>36967</v>
@@ -7474,7 +7474,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.45699405670166</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H245" t="n">
         <v>35049</v>
@@ -7503,7 +7503,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082513809204</v>
+        <v>7.53082418441772</v>
       </c>
       <c r="H246" t="n">
         <v>35688</v>
@@ -7532,7 +7532,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G247" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H247" t="n">
         <v>25674</v>
@@ -7561,7 +7561,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G248" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H248" t="n">
         <v>1598</v>
@@ -7590,7 +7590,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G249" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H249" t="n">
         <v>42400</v>
@@ -7619,7 +7619,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H250" t="n">
         <v>13742</v>
@@ -7648,7 +7648,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G251" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H251" t="n">
         <v>2982</v>
@@ -7677,7 +7677,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G252" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H252" t="n">
         <v>3089</v>
@@ -7706,7 +7706,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G253" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H253" t="n">
         <v>2769</v>
@@ -7735,7 +7735,7 @@
         <v>9.38668632507324</v>
       </c>
       <c r="G254" t="n">
-        <v>7.38316297531128</v>
+        <v>7.38316249847412</v>
       </c>
       <c r="H254" t="n">
         <v>1065</v>
@@ -7764,7 +7764,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G255" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H255" t="n">
         <v>24502</v>
@@ -7793,7 +7793,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H256" t="n">
         <v>53586</v>
@@ -7822,7 +7822,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G258" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H258" t="n">
         <v>1384</v>
@@ -7880,7 +7880,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G259" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H259" t="n">
         <v>29296</v>
@@ -7909,7 +7909,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H260" t="n">
         <v>2343</v>
@@ -7938,7 +7938,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G261" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H261" t="n">
         <v>319</v>
@@ -7967,7 +7967,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H262" t="n">
         <v>14062</v>
@@ -7996,7 +7996,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H263" t="n">
         <v>1598</v>
@@ -8025,7 +8025,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G264" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H264" t="n">
         <v>532</v>
@@ -8054,7 +8054,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G265" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H265" t="n">
         <v>6498</v>
@@ -8083,7 +8083,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G266" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H266" t="n">
         <v>36114</v>
@@ -8112,7 +8112,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G267" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H267" t="n">
         <v>7457</v>
@@ -8141,7 +8141,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G268" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H268" t="n">
         <v>11825</v>
@@ -8170,7 +8170,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624671936035</v>
+        <v>7.34624767303467</v>
       </c>
       <c r="H269" t="n">
         <v>4474</v>
@@ -8199,7 +8199,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G270" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H270" t="n">
         <v>22478</v>
@@ -8228,7 +8228,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G271" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H271" t="n">
         <v>2130</v>
@@ -8257,7 +8257,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G272" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H272" t="n">
         <v>20880</v>
@@ -8286,7 +8286,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G273" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H273" t="n">
         <v>5326</v>
@@ -8315,7 +8315,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G274" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H274" t="n">
         <v>6072</v>
@@ -8344,7 +8344,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G275" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H275" t="n">
         <v>2663</v>
@@ -8373,7 +8373,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G276" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H276" t="n">
         <v>426</v>
@@ -8402,7 +8402,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G277" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H277" t="n">
         <v>19176</v>
@@ -8431,7 +8431,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G278" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H278" t="n">
         <v>532</v>
@@ -8460,7 +8460,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G279" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H279" t="n">
         <v>6392</v>
@@ -8489,7 +8489,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G280" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H280" t="n">
         <v>1171</v>
@@ -8518,7 +8518,7 @@
         <v>9.24588584899902</v>
       </c>
       <c r="G281" t="n">
-        <v>7.2724142074585</v>
+        <v>7.27241516113281</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>9.29281902313232</v>
       </c>
       <c r="G286" t="n">
-        <v>7.30933094024658</v>
+        <v>7.30932950973511</v>
       </c>
       <c r="H286" t="n">
         <v>106</v>
@@ -8692,7 +8692,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G287" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H287" t="n">
         <v>7244</v>
@@ -8721,7 +8721,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G288" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H288" t="n">
         <v>1065</v>
@@ -8750,7 +8750,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G289" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H289" t="n">
         <v>745</v>
@@ -8779,7 +8779,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G290" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H290" t="n">
         <v>6818</v>
@@ -8808,7 +8808,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G291" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H291" t="n">
         <v>1065</v>
@@ -8837,7 +8837,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G292" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H292" t="n">
         <v>3728</v>
@@ -8953,7 +8953,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G296" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H296" t="n">
         <v>14595</v>
@@ -8982,7 +8982,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G297" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H297" t="n">
         <v>8629</v>
@@ -9011,7 +9011,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G298" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H298" t="n">
         <v>532</v>
@@ -9040,7 +9040,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G299" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>8.91735172271729</v>
       </c>
       <c r="G303" t="n">
-        <v>7.01400375366211</v>
+        <v>7.01400423049927</v>
       </c>
       <c r="H303" t="n">
         <v>639</v>
@@ -9185,7 +9185,7 @@
         <v>9.10508632659912</v>
       </c>
       <c r="G304" t="n">
-        <v>7.16166877746582</v>
+        <v>7.16166830062866</v>
       </c>
       <c r="H304" t="n">
         <v>3941</v>
@@ -9359,7 +9359,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H310" t="n">
         <v>4048</v>
@@ -9417,7 +9417,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H312" t="n">
         <v>2663</v>
@@ -9475,7 +9475,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H314" t="n">
         <v>51349</v>
@@ -9562,7 +9562,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017314910889</v>
       </c>
       <c r="H317" t="n">
         <v>54438</v>
@@ -9620,7 +9620,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867799758911</v>
+        <v>6.71867847442627</v>
       </c>
       <c r="H319" t="n">
         <v>12144</v>
@@ -9649,7 +9649,7 @@
         <v>8.63575077056885</v>
       </c>
       <c r="G320" t="n">
-        <v>6.79250907897949</v>
+        <v>6.79250860214233</v>
       </c>
       <c r="H320" t="n">
         <v>9907</v>
@@ -9678,7 +9678,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G321" t="n">
-        <v>6.75559425354004</v>
+        <v>6.75559282302856</v>
       </c>
       <c r="H321" t="n">
         <v>745</v>
@@ -9707,7 +9707,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G322" t="n">
-        <v>6.75559425354004</v>
+        <v>6.75559282302856</v>
       </c>
       <c r="H322" t="n">
         <v>532</v>
@@ -9765,7 +9765,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.6079306602478</v>
+        <v>6.60793018341064</v>
       </c>
       <c r="H324" t="n">
         <v>5859</v>
@@ -9794,7 +9794,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G325" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H325" t="n">
         <v>9161</v>
@@ -9881,7 +9881,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G328" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H328" t="n">
         <v>25568</v>
@@ -9910,7 +9910,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G329" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H329" t="n">
         <v>958</v>
@@ -9939,7 +9939,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G330" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G332" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H332" t="n">
         <v>4367</v>
@@ -10026,7 +10026,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G333" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H333" t="n">
         <v>6924</v>
@@ -10055,7 +10055,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G334" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H334" t="n">
         <v>2343</v>
@@ -10084,7 +10084,7 @@
         <v>8.30721664428711</v>
       </c>
       <c r="G335" t="n">
-        <v>6.53409862518311</v>
+        <v>6.53409767150879</v>
       </c>
       <c r="H335" t="n">
         <v>3089</v>
@@ -10113,7 +10113,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G336" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H336" t="n">
         <v>2556</v>
@@ -10142,7 +10142,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G337" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H337" t="n">
         <v>7563</v>
@@ -10171,7 +10171,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G338" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G339" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H339" t="n">
         <v>6285</v>
@@ -10229,7 +10229,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G340" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H340" t="n">
         <v>532</v>
@@ -10258,7 +10258,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G341" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H341" t="n">
         <v>5539</v>
@@ -10287,7 +10287,7 @@
         <v>8.26028442382812</v>
       </c>
       <c r="G342" t="n">
-        <v>6.49718379974365</v>
+        <v>6.49718332290649</v>
       </c>
       <c r="H342" t="n">
         <v>2556</v>
@@ -10345,7 +10345,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G344" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H344" t="n">
         <v>3409</v>
@@ -10374,7 +10374,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G345" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G348" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H348" t="n">
         <v>12677</v>
@@ -10490,7 +10490,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G349" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H349" t="n">
         <v>19389</v>
@@ -10519,7 +10519,7 @@
         <v>8.11948394775391</v>
       </c>
       <c r="G350" t="n">
-        <v>6.38643598556519</v>
+        <v>6.38643550872803</v>
       </c>
       <c r="H350" t="n">
         <v>6605</v>
@@ -10548,7 +10548,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G351" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H351" t="n">
         <v>13316</v>
@@ -10577,7 +10577,7 @@
         <v>8.16641712188721</v>
       </c>
       <c r="G352" t="n">
-        <v>6.4233512878418</v>
+        <v>6.42335176467896</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G356" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H356" t="n">
         <v>1065</v>
@@ -10722,7 +10722,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G357" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G361" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H361" t="n">
         <v>532</v>
@@ -11215,7 +11215,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H374" t="n">
         <v>2556</v>
@@ -11244,7 +11244,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H375" t="n">
         <v>3196</v>
@@ -11273,7 +11273,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G376" t="n">
-        <v>6.01727724075317</v>
+        <v>6.01727771759033</v>
       </c>
       <c r="H376" t="n">
         <v>213</v>
@@ -11302,7 +11302,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H377" t="n">
         <v>15340</v>
@@ -11331,7 +11331,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G378" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H378" t="n">
         <v>74147</v>
@@ -11360,7 +11360,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G379" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G384" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H384" t="n">
         <v>532</v>
@@ -11534,7 +11534,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G385" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H385" t="n">
         <v>532</v>
@@ -11563,7 +11563,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G386" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G387" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H387" t="n">
         <v>532</v>
@@ -11621,7 +11621,7 @@
         <v>7.74401617050171</v>
       </c>
       <c r="G388" t="n">
-        <v>6.09110927581787</v>
+        <v>6.09110879898071</v>
       </c>
       <c r="H388" t="n">
         <v>2663</v>
@@ -11650,7 +11650,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.0541934967041</v>
+        <v>6.05419301986694</v>
       </c>
       <c r="H389" t="n">
         <v>3196</v>
@@ -11679,7 +11679,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G390" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H390" t="n">
         <v>8203</v>
@@ -11708,7 +11708,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G391" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H391" t="n">
         <v>5433</v>
@@ -11911,7 +11911,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G398" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H398" t="n">
         <v>18749</v>
@@ -11998,7 +11998,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G401" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H401" t="n">
         <v>958</v>
@@ -12056,7 +12056,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G403" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H403" t="n">
         <v>4580</v>
@@ -12259,7 +12259,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G410" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H410" t="n">
         <v>9588</v>
@@ -12375,7 +12375,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G414" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H414" t="n">
         <v>19282</v>
@@ -12491,7 +12491,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G418" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H418" t="n">
         <v>639</v>
@@ -12520,7 +12520,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G419" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H419" t="n">
         <v>3089</v>
@@ -12607,7 +12607,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G422" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H422" t="n">
         <v>6818</v>
@@ -12665,7 +12665,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G424" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H424" t="n">
         <v>5113</v>
@@ -12781,7 +12781,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H428" t="n">
         <v>24183</v>
@@ -12839,7 +12839,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G430" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H430" t="n">
         <v>2024</v>
@@ -12868,7 +12868,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G431" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H431" t="n">
         <v>13955</v>
@@ -12955,7 +12955,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G434" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H434" t="n">
         <v>6498</v>
@@ -12984,7 +12984,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G435" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H435" t="n">
         <v>13103</v>
@@ -13013,7 +13013,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G436" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H436" t="n">
         <v>13636</v>
@@ -13042,7 +13042,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G437" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H437" t="n">
         <v>1598</v>
@@ -13071,7 +13071,7 @@
         <v>7.65014886856079</v>
       </c>
       <c r="G438" t="n">
-        <v>6.01727724075317</v>
+        <v>6.01727771759033</v>
       </c>
       <c r="H438" t="n">
         <v>1278</v>
@@ -13158,7 +13158,7 @@
         <v>7.55628204345703</v>
       </c>
       <c r="G441" t="n">
-        <v>5.94344520568848</v>
+        <v>5.94344568252563</v>
       </c>
       <c r="H441" t="n">
         <v>33664</v>
@@ -13245,7 +13245,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G444" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H444" t="n">
         <v>958</v>
@@ -13274,7 +13274,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G445" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H445" t="n">
         <v>5007</v>
@@ -13361,7 +13361,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G448" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H448" t="n">
         <v>2343</v>
@@ -13506,7 +13506,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G453" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H453" t="n">
         <v>2343</v>
@@ -13651,7 +13651,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G458" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H458" t="n">
         <v>1065</v>
@@ -13680,7 +13680,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G459" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H459" t="n">
         <v>3089</v>
@@ -13709,7 +13709,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H460" t="n">
         <v>1704</v>
@@ -13767,7 +13767,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G462" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H462" t="n">
         <v>1065</v>
@@ -13854,7 +13854,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G465" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H465" t="n">
         <v>1065</v>
@@ -13970,7 +13970,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G469" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H469" t="n">
         <v>2663</v>
@@ -13999,7 +13999,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H470" t="n">
         <v>852</v>
@@ -14028,7 +14028,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G471" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H471" t="n">
         <v>2343</v>
@@ -14260,7 +14260,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811897277832</v>
       </c>
       <c r="H479" t="n">
         <v>6605</v>
@@ -14289,7 +14289,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G480" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H480" t="n">
         <v>2130</v>
@@ -14318,7 +14318,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737211227417</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H481" t="n">
         <v>20241</v>
@@ -14492,7 +14492,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G487" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H487" t="n">
         <v>26846</v>
@@ -14521,7 +14521,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G488" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H488" t="n">
         <v>11931</v>
@@ -14550,7 +14550,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G489" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H489" t="n">
         <v>2556</v>
@@ -14579,7 +14579,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G490" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H490" t="n">
         <v>13849</v>
@@ -14695,7 +14695,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G494" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H494" t="n">
         <v>15873</v>
@@ -14811,7 +14811,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G498" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H498" t="n">
         <v>6392</v>
@@ -14840,7 +14840,7 @@
         <v>6.89921379089355</v>
       </c>
       <c r="G499" t="n">
-        <v>5.42662334442139</v>
+        <v>5.42662382125854</v>
       </c>
       <c r="H499" t="n">
         <v>106533</v>
@@ -14927,7 +14927,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587600708008</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H502" t="n">
         <v>12251</v>
@@ -14956,7 +14956,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G503" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H503" t="n">
         <v>20561</v>
@@ -15043,7 +15043,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587600708008</v>
+        <v>5.31587696075439</v>
       </c>
       <c r="H506" t="n">
         <v>11399</v>
@@ -15072,7 +15072,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G507" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H507" t="n">
         <v>45703</v>
@@ -15217,7 +15217,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G512" t="n">
-        <v>5.16821432113647</v>
+        <v>5.16821336746216</v>
       </c>
       <c r="H512" t="n">
         <v>25248</v>
@@ -15246,7 +15246,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G513" t="n">
-        <v>5.16821432113647</v>
+        <v>5.16821336746216</v>
       </c>
       <c r="H513" t="n">
         <v>33877</v>
@@ -15275,7 +15275,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G514" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H514" t="n">
         <v>35582</v>
@@ -15304,7 +15304,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G515" t="n">
-        <v>5.20512962341309</v>
+        <v>5.20512914657593</v>
       </c>
       <c r="H515" t="n">
         <v>9374</v>
@@ -15333,7 +15333,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G516" t="n">
-        <v>5.20512962341309</v>
+        <v>5.20512914657593</v>
       </c>
       <c r="H516" t="n">
         <v>8203</v>
@@ -15362,7 +15362,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G517" t="n">
-        <v>5.20512962341309</v>
+        <v>5.20512914657593</v>
       </c>
       <c r="H517" t="n">
         <v>11931</v>
@@ -15391,7 +15391,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G518" t="n">
-        <v>5.2420449256897</v>
+        <v>5.24204540252686</v>
       </c>
       <c r="H518" t="n">
         <v>33451</v>
@@ -15420,7 +15420,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G519" t="n">
-        <v>5.28634357452393</v>
+        <v>5.28634405136108</v>
       </c>
       <c r="H519" t="n">
         <v>9268</v>
@@ -15478,7 +15478,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G521" t="n">
-        <v>5.28634357452393</v>
+        <v>5.28634405136108</v>
       </c>
       <c r="H521" t="n">
         <v>22691</v>
@@ -15565,7 +15565,7 @@
         <v>6.83350801467896</v>
       </c>
       <c r="G524" t="n">
-        <v>5.37494277954102</v>
+        <v>5.37494230270386</v>
       </c>
       <c r="H524" t="n">
         <v>3302</v>
@@ -15652,7 +15652,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737211227417</v>
+        <v>5.53737258911133</v>
       </c>
       <c r="H527" t="n">
         <v>16193</v>
@@ -15710,7 +15710,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G529" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H529" t="n">
         <v>9791</v>
@@ -15884,7 +15884,7 @@
         <v>7.37793493270874</v>
       </c>
       <c r="G535" t="n">
-        <v>5.80316543579102</v>
+        <v>5.80316495895386</v>
       </c>
       <c r="H535" t="n">
         <v>4634</v>
@@ -15971,7 +15971,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G538" t="n">
-        <v>5.61120414733887</v>
+        <v>5.61120367050171</v>
       </c>
       <c r="H538" t="n">
         <v>8909</v>
@@ -16145,7 +16145,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G544" t="n">
-        <v>5.41924238204956</v>
+        <v>5.41924142837524</v>
       </c>
       <c r="H544" t="n">
         <v>37583</v>
@@ -16232,7 +16232,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G547" t="n">
-        <v>5.41924238204956</v>
+        <v>5.41924142837524</v>
       </c>
       <c r="H547" t="n">
         <v>16722</v>
@@ -16261,7 +16261,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G548" t="n">
-        <v>5.38970899581909</v>
+        <v>5.38970851898193</v>
       </c>
       <c r="H548" t="n">
         <v>3390</v>
@@ -16290,7 +16290,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G549" t="n">
-        <v>5.41924238204956</v>
+        <v>5.41924142837524</v>
       </c>
       <c r="H549" t="n">
         <v>2049</v>
@@ -16319,7 +16319,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G550" t="n">
-        <v>5.34540939331055</v>
+        <v>5.34540987014771</v>
       </c>
       <c r="H550" t="n">
         <v>4911</v>
@@ -16348,7 +16348,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G551" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405265808105</v>
       </c>
       <c r="H551" t="n">
         <v>3089</v>
@@ -16377,7 +16377,7 @@
         <v>6.68332099914551</v>
       </c>
       <c r="G552" t="n">
-        <v>5.4840521812439</v>
+        <v>5.48405265808105</v>
       </c>
       <c r="H552" t="n">
         <v>9976</v>
@@ -16435,7 +16435,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G554" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H554" t="n">
         <v>5577</v>
@@ -16638,7 +16638,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G561" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H561" t="n">
         <v>4176</v>
@@ -16667,7 +16667,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G562" t="n">
-        <v>5.5148606300354</v>
+        <v>5.51486110687256</v>
       </c>
       <c r="H562" t="n">
         <v>2780</v>
@@ -16696,7 +16696,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G563" t="n">
-        <v>5.5148606300354</v>
+        <v>5.51486110687256</v>
       </c>
       <c r="H563" t="n">
         <v>2546</v>
@@ -16725,7 +16725,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H564" t="n">
         <v>2151</v>
@@ -16812,7 +16812,7 @@
         <v>6.64577388763428</v>
       </c>
       <c r="G567" t="n">
-        <v>5.45324277877808</v>
+        <v>5.45324230194092</v>
       </c>
       <c r="H567" t="n">
         <v>8224</v>
@@ -16841,7 +16841,7 @@
         <v>6.72086715698242</v>
       </c>
       <c r="G568" t="n">
-        <v>5.5148606300354</v>
+        <v>5.51486110687256</v>
       </c>
       <c r="H568" t="n">
         <v>3556</v>
@@ -16928,7 +16928,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G571" t="n">
-        <v>5.77674055099487</v>
+        <v>5.77674102783203</v>
       </c>
       <c r="H571" t="n">
         <v>3259</v>
@@ -16986,7 +16986,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.82295417785645</v>
+        <v>5.82295370101929</v>
       </c>
       <c r="H573" t="n">
         <v>2375</v>
@@ -17015,7 +17015,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G574" t="n">
-        <v>5.77674055099487</v>
+        <v>5.77674102783203</v>
       </c>
       <c r="H574" t="n">
         <v>4794</v>
@@ -17189,7 +17189,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G580" t="n">
-        <v>5.85376405715942</v>
+        <v>5.85376358032227</v>
       </c>
       <c r="H580" t="n">
         <v>2840</v>
@@ -17276,7 +17276,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G583" t="n">
-        <v>5.77674055099487</v>
+        <v>5.77674102783203</v>
       </c>
       <c r="H583" t="n">
         <v>1715</v>
@@ -17305,7 +17305,7 @@
         <v>7.02124118804932</v>
       </c>
       <c r="G584" t="n">
-        <v>5.7613353729248</v>
+        <v>5.76133489608765</v>
       </c>
       <c r="H584" t="n">
         <v>1672</v>
@@ -17334,7 +17334,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593067169189</v>
+        <v>5.74593114852905</v>
       </c>
       <c r="H585" t="n">
         <v>1301</v>
@@ -17363,7 +17363,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G586" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H586" t="n">
         <v>1097</v>
@@ -17421,7 +17421,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G588" t="n">
-        <v>5.62269401550293</v>
+        <v>5.62269353866577</v>
       </c>
       <c r="H588" t="n">
         <v>2162</v>
@@ -17450,7 +17450,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H589" t="n">
         <v>5812</v>
@@ -17537,7 +17537,7 @@
         <v>6.88982820510864</v>
       </c>
       <c r="G592" t="n">
-        <v>5.65350389480591</v>
+        <v>5.65350341796875</v>
       </c>
       <c r="H592" t="n">
         <v>12357</v>
@@ -17595,7 +17595,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H594" t="n">
         <v>5028</v>
@@ -17624,7 +17624,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G595" t="n">
-        <v>5.62269401550293</v>
+        <v>5.62269353866577</v>
       </c>
       <c r="H595" t="n">
         <v>33809</v>
@@ -17798,7 +17798,7 @@
         <v>6.64577388763428</v>
       </c>
       <c r="G601" t="n">
-        <v>5.45324277877808</v>
+        <v>5.45324230194092</v>
       </c>
       <c r="H601" t="n">
         <v>14021</v>
@@ -17885,7 +17885,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G604" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H604" t="n">
         <v>16874</v>
@@ -17914,7 +17914,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G605" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H605" t="n">
         <v>2935</v>
@@ -18001,7 +18001,7 @@
         <v>6.30785322189331</v>
       </c>
       <c r="G608" t="n">
-        <v>5.17595863342285</v>
+        <v>5.17595911026001</v>
       </c>
       <c r="H608" t="n">
         <v>11796</v>
@@ -18146,7 +18146,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G613" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H613" t="n">
         <v>5312</v>
@@ -18175,7 +18175,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G614" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H614" t="n">
         <v>5545</v>
@@ -18204,7 +18204,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G615" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H615" t="n">
         <v>3749</v>
@@ -18233,7 +18233,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G616" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H616" t="n">
         <v>3536</v>
@@ -18262,7 +18262,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G617" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H617" t="n">
         <v>2524</v>
@@ -18291,7 +18291,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G618" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H618" t="n">
         <v>2151</v>
@@ -18320,7 +18320,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G619" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H619" t="n">
         <v>2993</v>
@@ -18349,7 +18349,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G620" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H620" t="n">
         <v>2684</v>
@@ -18407,7 +18407,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H622" t="n">
         <v>3398</v>
@@ -18436,7 +18436,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G623" t="n">
-        <v>5.34540939331055</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H623" t="n">
         <v>4481</v>
@@ -18494,7 +18494,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G625" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H625" t="n">
         <v>2743</v>
@@ -18523,7 +18523,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G626" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H626" t="n">
         <v>8590</v>
@@ -18552,7 +18552,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G627" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H627" t="n">
         <v>166729</v>
@@ -18581,7 +18581,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G628" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H628" t="n">
         <v>147791</v>
@@ -18610,7 +18610,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H629" t="n">
         <v>53531</v>
@@ -18639,7 +18639,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G630" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H630" t="n">
         <v>81260</v>
@@ -18668,7 +18668,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H631" t="n">
         <v>34982</v>
@@ -18726,7 +18726,7 @@
         <v>6.64577388763428</v>
       </c>
       <c r="G633" t="n">
-        <v>5.45324277877808</v>
+        <v>5.45324230194092</v>
       </c>
       <c r="H633" t="n">
         <v>70645</v>
@@ -18755,7 +18755,7 @@
         <v>6.64577388763428</v>
       </c>
       <c r="G634" t="n">
-        <v>5.45324277877808</v>
+        <v>5.45324230194092</v>
       </c>
       <c r="H634" t="n">
         <v>108552</v>
@@ -18784,7 +18784,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54566955566406</v>
+        <v>5.54567050933838</v>
       </c>
       <c r="H635" t="n">
         <v>39040</v>
@@ -18871,7 +18871,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G638" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H638" t="n">
         <v>28392</v>
@@ -18900,7 +18900,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G639" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H639" t="n">
         <v>41973</v>
@@ -19016,7 +19016,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G643" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H643" t="n">
         <v>20473</v>
@@ -19248,7 +19248,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H651" t="n">
         <v>8630</v>
@@ -19451,7 +19451,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G658" t="n">
-        <v>5.19136381149292</v>
+        <v>5.19136333465576</v>
       </c>
       <c r="H658" t="n">
         <v>3495</v>
@@ -19509,7 +19509,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G660" t="n">
-        <v>5.19136381149292</v>
+        <v>5.19136333465576</v>
       </c>
       <c r="H660" t="n">
         <v>37725</v>
@@ -19538,7 +19538,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H661" t="n">
         <v>10675</v>
@@ -19567,7 +19567,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H662" t="n">
         <v>33870</v>
@@ -19596,7 +19596,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H663" t="n">
         <v>10127</v>
@@ -19625,7 +19625,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H664" t="n">
         <v>26802</v>
@@ -19683,7 +19683,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G666" t="n">
-        <v>5.09893560409546</v>
+        <v>5.0989351272583</v>
       </c>
       <c r="H666" t="n">
         <v>29799</v>
@@ -19799,7 +19799,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H670" t="n">
         <v>5550</v>
@@ -19857,7 +19857,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G672" t="n">
-        <v>5.09893560409546</v>
+        <v>5.0989351272583</v>
       </c>
       <c r="H672" t="n">
         <v>11699</v>
@@ -20292,7 +20292,7 @@
         <v>6.64577388763428</v>
       </c>
       <c r="G687" t="n">
-        <v>5.45324277877808</v>
+        <v>5.45324230194092</v>
       </c>
       <c r="H687" t="n">
         <v>47806</v>
@@ -20350,7 +20350,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H689" t="n">
         <v>14741</v>
@@ -20379,7 +20379,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G690" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H690" t="n">
         <v>23361</v>
@@ -20495,7 +20495,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G694" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H694" t="n">
         <v>62988</v>
@@ -20524,7 +20524,7 @@
         <v>6.60822677612305</v>
       </c>
       <c r="G695" t="n">
-        <v>5.42243337631226</v>
+        <v>5.4224328994751</v>
       </c>
       <c r="H695" t="n">
         <v>13441</v>
@@ -20640,7 +20640,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G699" t="n">
-        <v>5.34540939331055</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H699" t="n">
         <v>7492</v>
@@ -20872,7 +20872,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G707" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H707" t="n">
         <v>16991</v>
@@ -20901,7 +20901,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G708" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H708" t="n">
         <v>26773</v>
@@ -20988,7 +20988,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G711" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H711" t="n">
         <v>17810</v>
@@ -21046,7 +21046,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G713" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H713" t="n">
         <v>10302</v>
@@ -21075,7 +21075,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G714" t="n">
-        <v>5.39162445068359</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H714" t="n">
         <v>21490</v>
@@ -21133,7 +21133,7 @@
         <v>6.51435995101929</v>
       </c>
       <c r="G716" t="n">
-        <v>5.34540939331055</v>
+        <v>5.34541034698486</v>
       </c>
       <c r="H716" t="n">
         <v>22905</v>
@@ -21162,7 +21162,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H717" t="n">
         <v>11988</v>
@@ -21307,7 +21307,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H722" t="n">
         <v>8101</v>
@@ -21365,7 +21365,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379154205322</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H724" t="n">
         <v>158873</v>
@@ -21539,7 +21539,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G730" t="n">
-        <v>5.11434078216553</v>
+        <v>5.11434125900269</v>
       </c>
       <c r="H730" t="n">
         <v>4041</v>
@@ -21626,7 +21626,7 @@
         <v>6.23275995254517</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11434078216553</v>
+        <v>5.11434125900269</v>
       </c>
       <c r="H733" t="n">
         <v>5204</v>
@@ -21655,7 +21655,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H734" t="n">
         <v>11911</v>
@@ -21742,7 +21742,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H737" t="n">
         <v>10868</v>
@@ -21771,7 +21771,7 @@
         <v>6.21398591995239</v>
       </c>
       <c r="G738" t="n">
-        <v>5.09893560409546</v>
+        <v>5.0989351272583</v>
       </c>
       <c r="H738" t="n">
         <v>24352</v>
@@ -21858,7 +21858,7 @@
         <v>5.98870611190796</v>
       </c>
       <c r="G741" t="n">
-        <v>4.91408014297485</v>
+        <v>4.91408061981201</v>
       </c>
       <c r="H741" t="n">
         <v>84527</v>
@@ -22003,7 +22003,7 @@
         <v>5.83851909637451</v>
       </c>
       <c r="G746" t="n">
-        <v>4.79084300994873</v>
+        <v>4.79084253311157</v>
       </c>
       <c r="H746" t="n">
         <v>6996</v>
@@ -22032,7 +22032,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760635375977</v>
+        <v>4.66760587692261</v>
       </c>
       <c r="H747" t="n">
         <v>45629</v>
@@ -22061,7 +22061,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760635375977</v>
+        <v>4.66760587692261</v>
       </c>
       <c r="H748" t="n">
         <v>24857</v>
@@ -22119,7 +22119,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436874389648</v>
+        <v>4.54436922073364</v>
       </c>
       <c r="H750" t="n">
         <v>20273</v>
@@ -22148,7 +22148,7 @@
         <v>5.63201189041138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.62139225006104</v>
+        <v>4.62139272689819</v>
       </c>
       <c r="H751" t="n">
         <v>11601</v>
@@ -22177,7 +22177,7 @@
         <v>5.55691814422607</v>
       </c>
       <c r="G752" t="n">
-        <v>4.55977344512939</v>
+        <v>4.55977296829224</v>
       </c>
       <c r="H752" t="n">
         <v>19277</v>
@@ -22206,7 +22206,7 @@
         <v>5.4442777633667</v>
       </c>
       <c r="G753" t="n">
-        <v>4.46734523773193</v>
+        <v>4.46734571456909</v>
       </c>
       <c r="H753" t="n">
         <v>30856</v>
@@ -22351,7 +22351,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468602180481</v>
+        <v>3.60468578338623</v>
       </c>
       <c r="H758" t="n">
         <v>114780</v>
@@ -22380,7 +22380,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G759" t="n">
-        <v>3.59698295593262</v>
+        <v>3.59698367118835</v>
       </c>
       <c r="H759" t="n">
         <v>59239</v>
@@ -22525,7 +22525,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G764" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H764" t="n">
         <v>23305</v>
@@ -22641,7 +22641,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G768" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H768" t="n">
         <v>8286</v>
@@ -22931,7 +22931,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G778" t="n">
-        <v>3.48915123939514</v>
+        <v>3.48915100097656</v>
       </c>
       <c r="H778" t="n">
         <v>94813</v>
@@ -22989,7 +22989,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G780" t="n">
-        <v>3.38902115821838</v>
+        <v>3.3890209197998</v>
       </c>
       <c r="H780" t="n">
         <v>14969</v>
@@ -23018,7 +23018,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G781" t="n">
-        <v>3.45063877105713</v>
+        <v>3.45063900947571</v>
       </c>
       <c r="H781" t="n">
         <v>5436</v>
@@ -23047,7 +23047,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G782" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H782" t="n">
         <v>12018</v>
@@ -23105,7 +23105,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G784" t="n">
-        <v>3.38902115821838</v>
+        <v>3.3890209197998</v>
       </c>
       <c r="H784" t="n">
         <v>15845</v>
@@ -23279,7 +23279,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G790" t="n">
-        <v>3.86656451225281</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H790" t="n">
         <v>21030</v>
@@ -23308,7 +23308,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.8126482963562</v>
+        <v>3.81264734268188</v>
       </c>
       <c r="H791" t="n">
         <v>43347</v>
@@ -23366,7 +23366,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575510978699</v>
       </c>
       <c r="H793" t="n">
         <v>20249</v>
@@ -23395,7 +23395,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G794" t="n">
-        <v>3.86656451225281</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H794" t="n">
         <v>52761</v>
@@ -23453,7 +23453,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G796" t="n">
-        <v>3.85116052627563</v>
+        <v>3.85116004943848</v>
       </c>
       <c r="H796" t="n">
         <v>6620</v>
@@ -23482,7 +23482,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G797" t="n">
-        <v>3.89737367630005</v>
+        <v>3.89737319946289</v>
       </c>
       <c r="H797" t="n">
         <v>14230</v>
@@ -23511,7 +23511,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818307876587</v>
+        <v>3.92818260192871</v>
       </c>
       <c r="H798" t="n">
         <v>44285</v>
@@ -23569,7 +23569,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575510978699</v>
       </c>
       <c r="H800" t="n">
         <v>42258</v>
@@ -23598,7 +23598,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85116052627563</v>
+        <v>3.85116004943848</v>
       </c>
       <c r="H801" t="n">
         <v>45469</v>
@@ -23656,7 +23656,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G803" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H803" t="n">
         <v>26953</v>
@@ -23743,7 +23743,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291386604309</v>
+        <v>3.84291434288025</v>
       </c>
       <c r="H806" t="n">
         <v>94227</v>
@@ -23772,7 +23772,7 @@
         <v>4.57131576538086</v>
       </c>
       <c r="G807" t="n">
-        <v>4.01609230041504</v>
+        <v>4.01609182357788</v>
       </c>
       <c r="H807" t="n">
         <v>66075</v>
@@ -23801,7 +23801,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G808" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H808" t="n">
         <v>72299</v>
@@ -23830,7 +23830,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G809" t="n">
-        <v>4.09031200408936</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H809" t="n">
         <v>25175</v>
@@ -23888,7 +23888,7 @@
         <v>4.60886287689209</v>
       </c>
       <c r="G811" t="n">
-        <v>4.04907894134521</v>
+        <v>4.04907846450806</v>
       </c>
       <c r="H811" t="n">
         <v>16762</v>
@@ -24004,7 +24004,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G815" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H815" t="n">
         <v>40504</v>
@@ -24149,7 +24149,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G820" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H820" t="n">
         <v>76661</v>
@@ -24178,7 +24178,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G821" t="n">
-        <v>4.30472326278687</v>
+        <v>4.30472278594971</v>
       </c>
       <c r="H821" t="n">
         <v>71502</v>
@@ -24236,7 +24236,7 @@
         <v>4.95617008209229</v>
       </c>
       <c r="G823" t="n">
-        <v>4.35420274734497</v>
+        <v>4.35420227050781</v>
       </c>
       <c r="H823" t="n">
         <v>29222</v>
@@ -24265,7 +24265,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G824" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H824" t="n">
         <v>56130</v>
@@ -24381,7 +24381,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G828" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H828" t="n">
         <v>25450</v>
@@ -24439,7 +24439,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G830" t="n">
-        <v>4.09031200408936</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H830" t="n">
         <v>8227</v>
@@ -24468,7 +24468,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G831" t="n">
-        <v>4.09031200408936</v>
+        <v>4.0903115272522</v>
       </c>
       <c r="H831" t="n">
         <v>6924</v>
@@ -24555,7 +24555,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G834" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H834" t="n">
         <v>7566</v>
@@ -24729,7 +24729,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H840" t="n">
         <v>4918</v>
@@ -24758,7 +24758,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G841" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H841" t="n">
         <v>29013</v>
@@ -24816,7 +24816,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H843" t="n">
         <v>12791</v>
@@ -24874,7 +24874,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H845" t="n">
         <v>6786</v>
@@ -24932,7 +24932,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H847" t="n">
         <v>5286</v>
@@ -24961,7 +24961,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H848" t="n">
         <v>24096</v>
@@ -24990,7 +24990,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G849" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H849" t="n">
         <v>13952</v>
@@ -25048,7 +25048,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G851" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H851" t="n">
         <v>10827</v>
@@ -25077,7 +25077,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G852" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H852" t="n">
         <v>6470</v>
@@ -25106,7 +25106,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G853" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H853" t="n">
         <v>46882</v>
@@ -25135,7 +25135,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G854" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H854" t="n">
         <v>24267</v>
@@ -25164,7 +25164,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G855" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H855" t="n">
         <v>53288</v>
@@ -25193,7 +25193,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G856" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H856" t="n">
         <v>122348</v>
@@ -25222,7 +25222,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G857" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H857" t="n">
         <v>31914</v>
@@ -25280,7 +25280,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G859" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H859" t="n">
         <v>20156</v>
@@ -25338,7 +25338,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G861" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H861" t="n">
         <v>7702</v>
@@ -25512,7 +25512,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H867" t="n">
         <v>1044</v>
@@ -25541,7 +25541,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G868" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H868" t="n">
         <v>7727</v>
@@ -25599,7 +25599,7 @@
         <v>4.88107681274414</v>
       </c>
       <c r="G870" t="n">
-        <v>4.28822946548462</v>
+        <v>4.28822994232178</v>
       </c>
       <c r="H870" t="n">
         <v>12725</v>
@@ -25657,7 +25657,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G872" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H872" t="n">
         <v>7867</v>
@@ -25715,7 +25715,7 @@
         <v>4.82475709915161</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23875045776367</v>
+        <v>4.23875093460083</v>
       </c>
       <c r="H874" t="n">
         <v>23224</v>
@@ -25773,7 +25773,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G876" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H876" t="n">
         <v>18056</v>
@@ -25802,7 +25802,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G877" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H877" t="n">
         <v>14094</v>
@@ -25831,7 +25831,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G878" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H878" t="n">
         <v>29761</v>
@@ -25889,7 +25889,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G880" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H880" t="n">
         <v>4103</v>
@@ -25947,7 +25947,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277765274048</v>
+        <v>4.17277717590332</v>
       </c>
       <c r="H882" t="n">
         <v>10955</v>
@@ -25976,7 +25976,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G883" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H883" t="n">
         <v>5879</v>
@@ -26005,7 +26005,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G884" t="n">
-        <v>4.20576333999634</v>
+        <v>4.2057638168335</v>
       </c>
       <c r="H884" t="n">
         <v>9707</v>
@@ -26237,7 +26237,7 @@
         <v>4.59008884429932</v>
       </c>
       <c r="G892" t="n">
-        <v>4.03258514404297</v>
+        <v>4.03258419036865</v>
       </c>
       <c r="H892" t="n">
         <v>19963</v>
@@ -26353,7 +26353,7 @@
         <v>4.54315614700317</v>
       </c>
       <c r="G896" t="n">
-        <v>3.99135279655457</v>
+        <v>3.99135231971741</v>
       </c>
       <c r="H896" t="n">
         <v>9674</v>
@@ -26382,7 +26382,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959921836853</v>
       </c>
       <c r="H897" t="n">
         <v>21516</v>
@@ -26411,7 +26411,7 @@
         <v>4.68395614624023</v>
       </c>
       <c r="G898" t="n">
-        <v>4.11505079269409</v>
+        <v>4.11505126953125</v>
       </c>
       <c r="H898" t="n">
         <v>13328</v>
@@ -26440,7 +26440,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959921836853</v>
       </c>
       <c r="H899" t="n">
         <v>13100</v>
@@ -26672,7 +26672,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G907" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H907" t="n">
         <v>21206</v>
@@ -26759,7 +26759,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G910" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H910" t="n">
         <v>221384</v>
@@ -26788,7 +26788,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G911" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H911" t="n">
         <v>26515</v>
@@ -27020,7 +27020,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G919" t="n">
-        <v>3.3151319026947</v>
+        <v>3.31513166427612</v>
       </c>
       <c r="H919" t="n">
         <v>19199</v>
@@ -27049,7 +27049,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G920" t="n">
-        <v>3.3151319026947</v>
+        <v>3.31513166427612</v>
       </c>
       <c r="H920" t="n">
         <v>6182</v>
@@ -27136,7 +27136,7 @@
         <v>3.75467395782471</v>
       </c>
       <c r="G923" t="n">
-        <v>3.29863786697388</v>
+        <v>3.29863810539246</v>
       </c>
       <c r="H923" t="n">
         <v>6991</v>
@@ -27194,7 +27194,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G925" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H925" t="n">
         <v>60383</v>
@@ -27281,7 +27281,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H928" t="n">
         <v>18937</v>
@@ -27310,7 +27310,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G929" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H929" t="n">
         <v>55594</v>
@@ -27339,7 +27339,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H930" t="n">
         <v>14164</v>
@@ -27368,7 +27368,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G931" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H931" t="n">
         <v>15744</v>
@@ -27397,7 +27397,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G932" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H932" t="n">
         <v>78843</v>
@@ -27426,7 +27426,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G933" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H933" t="n">
         <v>20415</v>
@@ -27455,7 +27455,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G934" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H934" t="n">
         <v>82776</v>
@@ -27513,7 +27513,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H936" t="n">
         <v>20128</v>
@@ -27542,7 +27542,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G937" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H937" t="n">
         <v>127295</v>
@@ -27600,7 +27600,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G939" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H939" t="n">
         <v>25861</v>
@@ -27658,7 +27658,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G941" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H941" t="n">
         <v>84865</v>
@@ -27687,7 +27687,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G942" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H942" t="n">
         <v>31672</v>
@@ -27716,7 +27716,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G943" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H943" t="n">
         <v>39520</v>
@@ -27803,7 +27803,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G946" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H946" t="n">
         <v>23231</v>
@@ -27977,7 +27977,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G952" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H952" t="n">
         <v>37331</v>
@@ -28006,7 +28006,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G953" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H953" t="n">
         <v>3250</v>
@@ -28035,7 +28035,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G954" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H954" t="n">
         <v>11668</v>
@@ -28122,7 +28122,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G957" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H957" t="n">
         <v>34099</v>
@@ -28209,7 +28209,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H960" t="n">
         <v>23384</v>
@@ -28238,7 +28238,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G961" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H961" t="n">
         <v>231929</v>
@@ -28296,7 +28296,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959969520569</v>
+        <v>3.99959921836853</v>
       </c>
       <c r="H963" t="n">
         <v>98447</v>
@@ -28354,7 +28354,7 @@
         <v>4.50560903549194</v>
       </c>
       <c r="G965" t="n">
-        <v>3.95836567878723</v>
+        <v>3.95836615562439</v>
       </c>
       <c r="H965" t="n">
         <v>25228</v>
@@ -28412,7 +28412,7 @@
         <v>4.56192922592163</v>
       </c>
       <c r="G967" t="n">
-        <v>4.00784587860107</v>
+        <v>4.00784540176392</v>
       </c>
       <c r="H967" t="n">
         <v>56555</v>
@@ -28499,7 +28499,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85940742492676</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H970" t="n">
         <v>23554</v>
@@ -28528,7 +28528,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.85940742492676</v>
+        <v>3.8594069480896</v>
       </c>
       <c r="H971" t="n">
         <v>26341</v>
@@ -28615,7 +28615,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G974" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H974" t="n">
         <v>14226</v>
@@ -28673,7 +28673,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992794036865</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H976" t="n">
         <v>12393</v>
@@ -28760,7 +28760,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G979" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H979" t="n">
         <v>17023</v>
@@ -28934,7 +28934,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G985" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H985" t="n">
         <v>21733</v>
@@ -28992,7 +28992,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H987" t="n">
         <v>32827</v>
@@ -29079,7 +29079,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G990" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H990" t="n">
         <v>34076</v>
@@ -29166,7 +29166,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992794036865</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H993" t="n">
         <v>25930</v>
@@ -29253,7 +29253,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G996" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H996" t="n">
         <v>22397</v>
@@ -29282,7 +29282,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G997" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H997" t="n">
         <v>27938</v>
@@ -29369,7 +29369,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1000" t="n">
         <v>15235</v>
@@ -29456,7 +29456,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1003" t="n">
         <v>38443</v>
@@ -29485,7 +29485,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1004" t="n">
         <v>11715</v>
@@ -29543,7 +29543,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1006" t="n">
         <v>54190</v>
@@ -29572,7 +29572,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1007" t="n">
         <v>37625</v>
@@ -29659,7 +29659,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1010" t="n">
         <v>40769</v>
@@ -29688,7 +29688,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1011" t="n">
         <v>16281</v>
@@ -29746,7 +29746,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1013" t="n">
         <v>21737</v>
@@ -29775,7 +29775,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1014" t="n">
         <v>18825</v>
@@ -29833,7 +29833,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1016" t="n">
         <v>29025</v>
@@ -29891,7 +29891,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1018" t="n">
         <v>34727</v>
@@ -29920,7 +29920,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1019" t="n">
         <v>21560</v>
@@ -29978,7 +29978,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1021" t="n">
         <v>27672</v>
@@ -30065,7 +30065,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1024" t="n">
         <v>24801</v>
@@ -30094,7 +30094,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1025" t="n">
         <v>37874</v>
@@ -30152,7 +30152,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1027" t="n">
         <v>25372</v>
@@ -30181,7 +30181,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1028" t="n">
         <v>29741</v>
@@ -30210,7 +30210,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1029" t="n">
         <v>11946</v>
@@ -30297,7 +30297,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1032" t="n">
         <v>39883</v>
@@ -30471,7 +30471,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921443939209</v>
       </c>
       <c r="H1038" t="n">
         <v>51341</v>
@@ -30500,7 +30500,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1039" t="n">
         <v>43496</v>
@@ -30616,7 +30616,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1043" t="n">
         <v>11883</v>
@@ -30674,7 +30674,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1045" t="n">
         <v>26734</v>
@@ -30732,7 +30732,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1047" t="n">
         <v>25237</v>
@@ -30877,7 +30877,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1052" t="n">
         <v>6158</v>
@@ -30906,7 +30906,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1053" t="n">
         <v>8465</v>
@@ -31167,7 +31167,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1062" t="n">
         <v>48219</v>
@@ -31225,7 +31225,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1064" t="n">
         <v>11044</v>
@@ -31283,7 +31283,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.76044797897339</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1066" t="n">
         <v>19508</v>
@@ -31312,7 +31312,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1067" t="n">
         <v>39186</v>
@@ -31341,7 +31341,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1068" t="n">
         <v>17426</v>
@@ -31486,7 +31486,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1073" t="n">
         <v>22042</v>
@@ -31515,7 +31515,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1074" t="n">
         <v>65157</v>
@@ -31602,7 +31602,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1077" t="n">
         <v>94343</v>
@@ -31805,7 +31805,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1084" t="n">
         <v>20412</v>
@@ -31892,7 +31892,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1087" t="n">
         <v>42401</v>
@@ -31979,7 +31979,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H1090" t="n">
         <v>13072</v>
@@ -32008,7 +32008,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1091" t="n">
         <v>1611</v>
@@ -32182,7 +32182,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1097" t="n">
         <v>890</v>
@@ -32269,7 +32269,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1100" t="n">
         <v>19929</v>
@@ -32298,7 +32298,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.43883037567139</v>
+        <v>3.43883061408997</v>
       </c>
       <c r="H1101" t="n">
         <v>18207</v>
@@ -32356,7 +32356,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1103" t="n">
         <v>8811</v>
@@ -32414,7 +32414,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H1105" t="n">
         <v>6136</v>
@@ -32501,7 +32501,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1108" t="n">
         <v>11339</v>
@@ -32530,7 +32530,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1109" t="n">
         <v>1861</v>
@@ -32559,7 +32559,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1110" t="n">
         <v>6715</v>
@@ -32617,7 +32617,7 @@
         <v>3.91424798965454</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.43883037567139</v>
+        <v>3.43883061408997</v>
       </c>
       <c r="H1112" t="n">
         <v>3066</v>
@@ -32646,7 +32646,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1113" t="n">
         <v>2815</v>
@@ -32675,7 +32675,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1114" t="n">
         <v>5118</v>
@@ -32704,7 +32704,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285757064819</v>
+        <v>3.37285733222961</v>
       </c>
       <c r="H1115" t="n">
         <v>45530</v>
@@ -32791,7 +32791,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H1118" t="n">
         <v>8601</v>
@@ -32907,7 +32907,7 @@
         <v>4.23339509963989</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.71921467781067</v>
+        <v>3.71921443939209</v>
       </c>
       <c r="H1122" t="n">
         <v>40624</v>
@@ -32936,7 +32936,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.73570823669434</v>
+        <v>3.73570799827576</v>
       </c>
       <c r="H1123" t="n">
         <v>50758</v>
@@ -32994,7 +32994,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1125" t="n">
         <v>30453</v>
@@ -33023,7 +33023,7 @@
         <v>4.29910182952881</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.77694082260132</v>
+        <v>3.77694058418274</v>
       </c>
       <c r="H1126" t="n">
         <v>56617</v>
@@ -33052,7 +33052,7 @@
         <v>4.36480903625488</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.83466696739197</v>
+        <v>3.83466744422913</v>
       </c>
       <c r="H1127" t="n">
         <v>98755</v>
@@ -33226,7 +33226,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272183418274</v>
+        <v>3.70272135734558</v>
       </c>
       <c r="H1133" t="n">
         <v>63296</v>
@@ -33284,7 +33284,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1135" t="n">
         <v>25711</v>
@@ -33400,7 +33400,7 @@
         <v>4.20523500442505</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.69447469711304</v>
+        <v>3.69447445869446</v>
       </c>
       <c r="H1139" t="n">
         <v>9634</v>
@@ -33487,7 +33487,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1142" t="n">
         <v>70144</v>
@@ -33516,7 +33516,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1143" t="n">
         <v>71574</v>
@@ -33545,7 +33545,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1144" t="n">
         <v>12460</v>
@@ -33574,7 +33574,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1145" t="n">
         <v>11043</v>
@@ -33632,7 +33632,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1147" t="n">
         <v>5028</v>
@@ -33719,7 +33719,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1150" t="n">
         <v>35755</v>
@@ -33864,7 +33864,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1155" t="n">
         <v>8816</v>
@@ -33893,7 +33893,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.62850260734558</v>
+        <v>3.628502368927</v>
       </c>
       <c r="H1156" t="n">
         <v>2307</v>
@@ -33951,7 +33951,7 @@
         <v>4.11136817932129</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.61200881004333</v>
+        <v>3.61200857162476</v>
       </c>
       <c r="H1158" t="n">
         <v>16226</v>
@@ -34212,7 +34212,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.57902312278748</v>
+        <v>3.5790228843689</v>
       </c>
       <c r="H1167" t="n">
         <v>10482</v>
@@ -34241,7 +34241,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1168" t="n">
         <v>10241</v>
@@ -34270,7 +34270,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1169" t="n">
         <v>8390</v>
@@ -34299,7 +34299,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1170" t="n">
         <v>23775</v>
@@ -34328,7 +34328,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1171" t="n">
         <v>4856</v>
@@ -34415,7 +34415,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1174" t="n">
         <v>82581</v>
@@ -34560,7 +34560,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1179" t="n">
         <v>10695</v>
@@ -34734,7 +34734,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1185" t="n">
         <v>40153</v>
@@ -34821,7 +34821,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.66973495483398</v>
+        <v>3.66973519325256</v>
       </c>
       <c r="H1188" t="n">
         <v>64523</v>
@@ -34908,7 +34908,7 @@
         <v>4.06443500518799</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.57077598571777</v>
+        <v>3.57077622413635</v>
       </c>
       <c r="H1191" t="n">
         <v>5698</v>
@@ -34966,7 +34966,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1193" t="n">
         <v>19889</v>
@@ -35082,7 +35082,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H1197" t="n">
         <v>17683</v>
@@ -35111,7 +35111,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1198" t="n">
         <v>11291</v>
@@ -35169,7 +35169,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1200" t="n">
         <v>7176</v>
@@ -35198,7 +35198,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1201" t="n">
         <v>8294</v>
@@ -35343,7 +35343,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1206" t="n">
         <v>10703</v>
@@ -35372,7 +35372,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1207" t="n">
         <v>26510</v>
@@ -35401,7 +35401,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1208" t="n">
         <v>1693</v>
@@ -35430,7 +35430,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1209" t="n">
         <v>10093</v>
@@ -35459,7 +35459,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1210" t="n">
         <v>7512</v>
@@ -35488,7 +35488,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1211" t="n">
         <v>51874</v>
@@ -35517,7 +35517,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1212" t="n">
         <v>12870</v>
@@ -35575,7 +35575,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1214" t="n">
         <v>5806</v>
@@ -35633,7 +35633,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1216" t="n">
         <v>8971</v>
@@ -35749,7 +35749,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1220" t="n">
         <v>7491</v>
@@ -35778,7 +35778,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1221" t="n">
         <v>5316</v>
@@ -35807,7 +35807,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1222" t="n">
         <v>6029</v>
@@ -35836,7 +35836,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1223" t="n">
         <v>22676</v>
@@ -35865,7 +35865,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1224" t="n">
         <v>10519</v>
@@ -35894,7 +35894,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1225" t="n">
         <v>9180</v>
@@ -35923,7 +35923,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1226" t="n">
         <v>12826</v>
@@ -35981,7 +35981,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1228" t="n">
         <v>9896</v>
@@ -36010,7 +36010,7 @@
         <v>4.01750087738037</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.52954268455505</v>
+        <v>3.52954244613647</v>
       </c>
       <c r="H1229" t="n">
         <v>21602</v>
@@ -36039,7 +36039,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1230" t="n">
         <v>20614</v>
@@ -36068,7 +36068,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.49655699729919</v>
+        <v>3.49655675888062</v>
       </c>
       <c r="H1231" t="n">
         <v>12772</v>
@@ -36271,7 +36271,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285757064819</v>
+        <v>3.37285733222961</v>
       </c>
       <c r="H1238" t="n">
         <v>1560</v>
@@ -36358,7 +36358,7 @@
         <v>3.8860878944397</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.41409063339233</v>
+        <v>3.41409087181091</v>
       </c>
       <c r="H1241" t="n">
         <v>8107</v>
@@ -36503,7 +36503,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.35636448860168</v>
+        <v>3.35636425018311</v>
       </c>
       <c r="H1246" t="n">
         <v>8528</v>
@@ -36532,7 +36532,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.28214502334595</v>
+        <v>3.28214526176453</v>
       </c>
       <c r="H1247" t="n">
         <v>87521</v>
@@ -36561,7 +36561,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493939399719</v>
+        <v>3.17493915557861</v>
       </c>
       <c r="H1248" t="n">
         <v>97339</v>
@@ -36590,7 +36590,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072040557861</v>
       </c>
       <c r="H1249" t="n">
         <v>48472</v>
@@ -36793,7 +36793,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493939399719</v>
+        <v>3.17493915557861</v>
       </c>
       <c r="H1256" t="n">
         <v>43078</v>
@@ -36880,7 +36880,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072040557861</v>
       </c>
       <c r="H1259" t="n">
         <v>13331</v>
@@ -36909,7 +36909,7 @@
         <v>3.59510111808777</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.15844655036926</v>
+        <v>3.15844631195068</v>
       </c>
       <c r="H1260" t="n">
         <v>19893</v>
@@ -37025,7 +37025,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.99351406097412</v>
+        <v>2.9935142993927</v>
       </c>
       <c r="H1264" t="n">
         <v>42973</v>
@@ -37228,7 +37228,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877431869507</v>
+        <v>2.96877455711365</v>
       </c>
       <c r="H1271" t="n">
         <v>8955</v>
@@ -37257,7 +37257,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.99351406097412</v>
+        <v>2.9935142993927</v>
       </c>
       <c r="H1272" t="n">
         <v>11850</v>
@@ -37373,7 +37373,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.06773376464844</v>
+        <v>3.06773352622986</v>
       </c>
       <c r="H1276" t="n">
         <v>18660</v>
@@ -37402,7 +37402,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.05948662757874</v>
+        <v>3.05948686599731</v>
       </c>
       <c r="H1277" t="n">
         <v>5110</v>
@@ -37460,7 +37460,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.08422684669495</v>
+        <v>3.08422660827637</v>
       </c>
       <c r="H1279" t="n">
         <v>6287</v>
@@ -37489,7 +37489,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.08422684669495</v>
+        <v>3.08422660827637</v>
       </c>
       <c r="H1280" t="n">
         <v>2125</v>
@@ -37518,7 +37518,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072040557861</v>
       </c>
       <c r="H1281" t="n">
         <v>186455</v>
@@ -37547,7 +37547,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072040557861</v>
       </c>
       <c r="H1282" t="n">
         <v>37331</v>
@@ -37605,7 +37605,7 @@
         <v>3.52939391136169</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.10071992874146</v>
+        <v>3.10072040557861</v>
       </c>
       <c r="H1284" t="n">
         <v>4412</v>
@@ -37634,7 +37634,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.06773376464844</v>
+        <v>3.06773352622986</v>
       </c>
       <c r="H1285" t="n">
         <v>6703</v>
@@ -37663,7 +37663,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.06773376464844</v>
+        <v>3.06773352622986</v>
       </c>
       <c r="H1286" t="n">
         <v>11272</v>
@@ -37808,7 +37808,7 @@
         <v>3.41675400733948</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.0017614364624</v>
+        <v>3.00176119804382</v>
       </c>
       <c r="H1291" t="n">
         <v>10469</v>
@@ -37837,7 +37837,7 @@
         <v>3.4636869430542</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.04299402236938</v>
+        <v>3.04299378395081</v>
       </c>
       <c r="H1292" t="n">
         <v>2450</v>
@@ -37895,7 +37895,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.05948662757874</v>
+        <v>3.05948686599731</v>
       </c>
       <c r="H1294" t="n">
         <v>7283</v>
@@ -37924,7 +37924,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.05948662757874</v>
+        <v>3.05948686599731</v>
       </c>
       <c r="H1295" t="n">
         <v>3328</v>
@@ -38156,7 +38156,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877431869507</v>
+        <v>2.96877455711365</v>
       </c>
       <c r="H1303" t="n">
         <v>16267</v>
@@ -38243,7 +38243,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630867004395</v>
+        <v>2.88630843162537</v>
       </c>
       <c r="H1306" t="n">
         <v>18867</v>
@@ -38272,7 +38272,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.35636448860168</v>
+        <v>3.35636425018311</v>
       </c>
       <c r="H1307" t="n">
         <v>245895</v>
@@ -38388,7 +38388,7 @@
         <v>3.95179510116577</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.47181725502014</v>
+        <v>3.47181701660156</v>
       </c>
       <c r="H1311" t="n">
         <v>32028</v>
@@ -38417,7 +38417,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48831009864807</v>
+        <v>3.48830986022949</v>
       </c>
       <c r="H1312" t="n">
         <v>43094</v>
@@ -38504,7 +38504,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.46357035636902</v>
+        <v>3.46357011795044</v>
       </c>
       <c r="H1315" t="n">
         <v>17985</v>
@@ -38620,7 +38620,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.56433200836182</v>
+        <v>3.56433176994324</v>
       </c>
       <c r="H1319" t="n">
         <v>20606</v>
@@ -38678,7 +38678,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1321" t="n">
         <v>19899</v>
@@ -38707,7 +38707,7 @@
         <v>4.00752782821655</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.56433200836182</v>
+        <v>3.56433176994324</v>
       </c>
       <c r="H1322" t="n">
         <v>34453</v>
@@ -38736,7 +38736,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1323" t="n">
         <v>8362</v>
@@ -38765,7 +38765,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1324" t="n">
         <v>8377</v>
@@ -38794,7 +38794,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1325" t="n">
         <v>624</v>
@@ -38823,7 +38823,7 @@
         <v>4.06560802459717</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.61598873138428</v>
+        <v>3.61598896980286</v>
       </c>
       <c r="H1326" t="n">
         <v>58609</v>
@@ -38968,7 +38968,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1331" t="n">
         <v>44773</v>
@@ -38997,7 +38997,7 @@
         <v>3.99784803390503</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.55572271347046</v>
+        <v>3.55572247505188</v>
       </c>
       <c r="H1332" t="n">
         <v>36069</v>
@@ -39026,7 +39026,7 @@
         <v>3.96880793571472</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.52989387512207</v>
+        <v>3.52989411354065</v>
       </c>
       <c r="H1333" t="n">
         <v>15175</v>
@@ -39055,7 +39055,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.50406551361084</v>
+        <v>3.50406575202942</v>
       </c>
       <c r="H1334" t="n">
         <v>13459</v>
@@ -39113,7 +39113,7 @@
         <v>3.93976807594299</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.50406551361084</v>
+        <v>3.50406575202942</v>
       </c>
       <c r="H1336" t="n">
         <v>37524</v>
@@ -39142,7 +39142,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1337" t="n">
         <v>4129</v>
@@ -39287,7 +39287,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1342" t="n">
         <v>5320</v>
@@ -39316,7 +39316,7 @@
         <v>3.98816800117493</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.54711318016052</v>
+        <v>3.54711294174194</v>
       </c>
       <c r="H1343" t="n">
         <v>14766</v>
@@ -39345,7 +39345,7 @@
         <v>3.98816800117493</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.54711318016052</v>
+        <v>3.54711294174194</v>
       </c>
       <c r="H1344" t="n">
         <v>2895</v>
@@ -39374,7 +39374,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1345" t="n">
         <v>36756</v>
@@ -39403,7 +39403,7 @@
         <v>3.95912790298462</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.52128434181213</v>
+        <v>3.52128458023071</v>
       </c>
       <c r="H1346" t="n">
         <v>3230</v>
@@ -39490,7 +39490,7 @@
         <v>3.88168811798096</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.45240879058838</v>
+        <v>3.45240902900696</v>
       </c>
       <c r="H1349" t="n">
         <v>17363</v>
@@ -39519,7 +39519,7 @@
         <v>3.85264801979065</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.42658019065857</v>
+        <v>3.42658042907715</v>
       </c>
       <c r="H1350" t="n">
         <v>51255</v>
@@ -40128,7 +40128,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.16829514503479</v>
+        <v>3.16829490661621</v>
       </c>
       <c r="H1371" t="n">
         <v>4983</v>
@@ -40824,7 +40824,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21995186805725</v>
+        <v>3.21995210647583</v>
       </c>
       <c r="H1395" t="n">
         <v>1030</v>
@@ -40882,7 +40882,7 @@
         <v>3.62032699584961</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21995186805725</v>
+        <v>3.21995210647583</v>
       </c>
       <c r="H1397" t="n">
         <v>13064</v>
@@ -41056,7 +41056,7 @@
         <v>3.63968706130981</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.2371711730957</v>
+        <v>3.23717093467712</v>
       </c>
       <c r="H1403" t="n">
         <v>209305</v>
@@ -41839,7 +41839,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1430" t="n">
         <v>9533</v>
@@ -41868,7 +41868,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1431" t="n">
         <v>6011</v>
@@ -41897,7 +41897,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1432" t="n">
         <v>3304</v>
@@ -41926,7 +41926,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.72921061515808</v>
+        <v>2.72921085357666</v>
       </c>
       <c r="H1433" t="n">
         <v>10331</v>
@@ -41955,7 +41955,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1434" t="n">
         <v>98460</v>
@@ -41984,7 +41984,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1435" t="n">
         <v>11831</v>
@@ -42013,7 +42013,7 @@
         <v>3.08792591094971</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.74642968177795</v>
+        <v>2.74642944335938</v>
       </c>
       <c r="H1436" t="n">
         <v>11904</v>
@@ -42042,7 +42042,7 @@
         <v>3.06856608390808</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.72921061515808</v>
+        <v>2.72921085357666</v>
       </c>
       <c r="H1437" t="n">
         <v>11573</v>
@@ -42071,7 +42071,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1438" t="n">
         <v>12728</v>
@@ -42100,7 +42100,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1439" t="n">
         <v>15913</v>
@@ -42158,7 +42158,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1441" t="n">
         <v>7860</v>
@@ -42187,7 +42187,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1442" t="n">
         <v>13772</v>
@@ -42535,7 +42535,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1454" t="n">
         <v>18616</v>
@@ -42564,7 +42564,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1455" t="n">
         <v>24438</v>
@@ -42593,7 +42593,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1456" t="n">
         <v>9511</v>
@@ -42651,7 +42651,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1458" t="n">
         <v>7087</v>
@@ -42680,7 +42680,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1459" t="n">
         <v>0</v>
@@ -42767,7 +42767,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1462" t="n">
         <v>8485</v>
@@ -42825,7 +42825,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1464" t="n">
         <v>7001</v>
@@ -42854,7 +42854,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1465" t="n">
         <v>35035</v>
@@ -42912,7 +42912,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1467" t="n">
         <v>39470</v>
@@ -42941,7 +42941,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1468" t="n">
         <v>26594</v>
@@ -42970,7 +42970,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1469" t="n">
         <v>4860</v>
@@ -42999,7 +42999,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1470" t="n">
         <v>14149</v>
@@ -43086,7 +43086,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1473" t="n">
         <v>4257</v>
@@ -43173,7 +43173,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1476" t="n">
         <v>9918</v>
@@ -43202,7 +43202,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1477" t="n">
         <v>1399</v>
@@ -43260,7 +43260,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1479" t="n">
         <v>198</v>
@@ -43289,7 +43289,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1480" t="n">
         <v>17076</v>
@@ -43318,7 +43318,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1481" t="n">
         <v>8595</v>
@@ -43347,7 +43347,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1482" t="n">
         <v>13838</v>
@@ -43405,7 +43405,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1484" t="n">
         <v>24519</v>
@@ -43434,7 +43434,7 @@
         <v>3.14600610733032</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.79808640480042</v>
+        <v>2.79808664321899</v>
       </c>
       <c r="H1485" t="n">
         <v>143477</v>
@@ -43550,7 +43550,7 @@
         <v>3.01048588752747</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.67755365371704</v>
+        <v>2.67755341529846</v>
       </c>
       <c r="H1489" t="n">
         <v>23880</v>
@@ -43579,7 +43579,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1490" t="n">
         <v>8748</v>
@@ -43724,7 +43724,7 @@
         <v>3.02984595298767</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.69477272033691</v>
+        <v>2.69477248191833</v>
       </c>
       <c r="H1495" t="n">
         <v>7764</v>
@@ -43753,7 +43753,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1496" t="n">
         <v>28832</v>
@@ -43927,7 +43927,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1502" t="n">
         <v>30040</v>
@@ -44014,7 +44014,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1505" t="n">
         <v>14841</v>
@@ -44043,7 +44043,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1506" t="n">
         <v>20996</v>
@@ -44072,7 +44072,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1507" t="n">
         <v>3357</v>
@@ -44246,7 +44246,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1513" t="n">
         <v>8695</v>
@@ -44449,7 +44449,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1520" t="n">
         <v>17400</v>
@@ -44565,7 +44565,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1524" t="n">
         <v>40680</v>
@@ -44652,7 +44652,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1527" t="n">
         <v>21079</v>
@@ -44710,7 +44710,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1529" t="n">
         <v>39356</v>
@@ -44768,7 +44768,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1531" t="n">
         <v>13812</v>
@@ -44855,7 +44855,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1534" t="n">
         <v>3396</v>
@@ -44884,7 +44884,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1535" t="n">
         <v>298</v>
@@ -44942,7 +44942,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1537" t="n">
         <v>47394</v>
@@ -44971,7 +44971,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1538" t="n">
         <v>53293</v>
@@ -45000,7 +45000,7 @@
         <v>3.00080609321594</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.66894435882568</v>
+        <v>2.6689441204071</v>
       </c>
       <c r="H1539" t="n">
         <v>1340</v>
@@ -45203,7 +45203,7 @@
         <v>2.9330461025238</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.60867786407471</v>
+        <v>2.60867810249329</v>
       </c>
       <c r="H1546" t="n">
         <v>1556</v>
@@ -45348,7 +45348,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1551" t="n">
         <v>12634</v>
@@ -45377,7 +45377,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1552" t="n">
         <v>42728</v>
@@ -45406,7 +45406,7 @@
         <v>2.88464593887329</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.5656304359436</v>
+        <v>2.56563067436218</v>
       </c>
       <c r="H1553" t="n">
         <v>7867</v>
@@ -45493,7 +45493,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1556" t="n">
         <v>2071</v>
@@ -45522,7 +45522,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1557" t="n">
         <v>8550</v>
@@ -45580,7 +45580,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1559" t="n">
         <v>5144</v>
@@ -45609,7 +45609,7 @@
         <v>2.89432597160339</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.57423996925354</v>
+        <v>2.57424020767212</v>
       </c>
       <c r="H1560" t="n">
         <v>5682</v>
@@ -45638,7 +45638,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1561" t="n">
         <v>4172</v>
@@ -45667,7 +45667,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1562" t="n">
         <v>3173</v>
@@ -45696,7 +45696,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1563" t="n">
         <v>46081</v>
@@ -45754,7 +45754,7 @@
         <v>2.85560607910156</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.53980183601379</v>
+        <v>2.53980207443237</v>
       </c>
       <c r="H1565" t="n">
         <v>19052</v>
@@ -45783,7 +45783,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1566" t="n">
         <v>15762</v>
@@ -45812,7 +45812,7 @@
         <v>2.9040060043335</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.58284974098206</v>
+        <v>2.58284950256348</v>
       </c>
       <c r="H1567" t="n">
         <v>4363</v>
@@ -45986,7 +45986,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1573" t="n">
         <v>9765</v>
@@ -46015,7 +46015,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1574" t="n">
         <v>13419</v>
@@ -46044,7 +46044,7 @@
         <v>2.7684850692749</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.46231603622437</v>
+        <v>2.46231579780579</v>
       </c>
       <c r="H1575" t="n">
         <v>2078</v>
@@ -46073,7 +46073,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1576" t="n">
         <v>14992</v>
@@ -46131,7 +46131,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1578" t="n">
         <v>3766</v>
@@ -46160,7 +46160,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1579" t="n">
         <v>4333</v>
@@ -46189,7 +46189,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1580" t="n">
         <v>3340</v>
@@ -46276,7 +46276,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1583" t="n">
         <v>4884</v>
@@ -46392,7 +46392,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1587" t="n">
         <v>9909</v>
@@ -46450,7 +46450,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1589" t="n">
         <v>10979</v>
@@ -46508,7 +46508,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1591" t="n">
         <v>10038</v>
@@ -46537,7 +46537,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1592" t="n">
         <v>2788</v>
@@ -46566,7 +46566,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1593" t="n">
         <v>1012</v>
@@ -46595,7 +46595,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1594" t="n">
         <v>2066</v>
@@ -46682,7 +46682,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.35039258003235</v>
+        <v>2.35039234161377</v>
       </c>
       <c r="H1597" t="n">
         <v>15617</v>
@@ -46798,7 +46798,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1601" t="n">
         <v>10946</v>
@@ -46827,7 +46827,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1602" t="n">
         <v>344</v>
@@ -46856,7 +46856,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.33317351341248</v>
+        <v>2.33317375183105</v>
       </c>
       <c r="H1603" t="n">
         <v>1960</v>
@@ -47001,7 +47001,7 @@
         <v>2.62328505516052</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.33317351341248</v>
+        <v>2.33317375183105</v>
       </c>
       <c r="H1608" t="n">
         <v>17007</v>
@@ -47175,7 +47175,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.27290749549866</v>
+        <v>2.27290725708008</v>
       </c>
       <c r="H1614" t="n">
         <v>8963</v>
@@ -47204,7 +47204,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.26429772377014</v>
+        <v>2.26429796218872</v>
       </c>
       <c r="H1615" t="n">
         <v>7674</v>
@@ -47378,7 +47378,7 @@
         <v>2.55552506446838</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.27290749549866</v>
+        <v>2.27290725708008</v>
       </c>
       <c r="H1621" t="n">
         <v>2200</v>
@@ -47407,7 +47407,7 @@
         <v>2.54584503173828</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.26429772377014</v>
+        <v>2.26429796218872</v>
       </c>
       <c r="H1622" t="n">
         <v>10065</v>
@@ -47581,7 +47581,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1628" t="n">
         <v>14751</v>
@@ -47668,7 +47668,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1631" t="n">
         <v>47603</v>
@@ -47697,7 +47697,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1632" t="n">
         <v>2350</v>
@@ -47726,7 +47726,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.19542193412781</v>
+        <v>2.19542169570923</v>
       </c>
       <c r="H1633" t="n">
         <v>21458</v>
@@ -47755,7 +47755,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1634" t="n">
         <v>5717</v>
@@ -47784,7 +47784,7 @@
         <v>2.46840500831604</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.19542193412781</v>
+        <v>2.19542169570923</v>
       </c>
       <c r="H1635" t="n">
         <v>12502</v>
@@ -47958,7 +47958,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.10071754455566</v>
+        <v>2.10071778297424</v>
       </c>
       <c r="H1641" t="n">
         <v>12225</v>
@@ -48190,7 +48190,7 @@
         <v>2.03280401229858</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.80799436569214</v>
+        <v>1.80799448490143</v>
       </c>
       <c r="H1649" t="n">
         <v>181839</v>
@@ -48219,7 +48219,7 @@
         <v>2.13928389549255</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.9026985168457</v>
+        <v>1.90269863605499</v>
       </c>
       <c r="H1650" t="n">
         <v>284242</v>
@@ -48277,7 +48277,7 @@
         <v>2.11024403572083</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.87687027454376</v>
+        <v>1.87687039375305</v>
       </c>
       <c r="H1652" t="n">
         <v>30327</v>
@@ -48422,7 +48422,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1657" t="n">
         <v>22469</v>
@@ -48480,7 +48480,7 @@
         <v>2.29416394233704</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.04045057296753</v>
+        <v>2.04045033454895</v>
       </c>
       <c r="H1659" t="n">
         <v>10060</v>
@@ -48654,7 +48654,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.97157454490662</v>
+        <v>1.97157430648804</v>
       </c>
       <c r="H1665" t="n">
         <v>13211</v>
@@ -48683,7 +48683,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.97157454490662</v>
+        <v>1.97157430648804</v>
       </c>
       <c r="H1666" t="n">
         <v>1802</v>
@@ -48741,7 +48741,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574642181396</v>
       </c>
       <c r="H1668" t="n">
         <v>5866</v>
@@ -48770,7 +48770,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574642181396</v>
       </c>
       <c r="H1669" t="n">
         <v>16104</v>
@@ -48915,7 +48915,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1674" t="n">
         <v>1074</v>
@@ -48944,7 +48944,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1675" t="n">
         <v>10649</v>
@@ -48973,7 +48973,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1676" t="n">
         <v>11045</v>
@@ -49002,7 +49002,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1677" t="n">
         <v>5075</v>
@@ -49060,7 +49060,7 @@
         <v>2.21672391891479</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.97157454490662</v>
+        <v>1.97157430648804</v>
       </c>
       <c r="H1679" t="n">
         <v>11494</v>
@@ -49089,7 +49089,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.96296501159668</v>
+        <v>1.9629647731781</v>
       </c>
       <c r="H1680" t="n">
         <v>5364</v>
@@ -49118,7 +49118,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.96296501159668</v>
+        <v>1.9629647731781</v>
       </c>
       <c r="H1681" t="n">
         <v>2066</v>
@@ -49205,7 +49205,7 @@
         <v>2.18768405914307</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.94574618339539</v>
+        <v>1.94574642181396</v>
       </c>
       <c r="H1684" t="n">
         <v>37</v>
@@ -49234,7 +49234,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.93713665008545</v>
+        <v>1.93713688850403</v>
       </c>
       <c r="H1685" t="n">
         <v>2206</v>
@@ -49263,7 +49263,7 @@
         <v>2.10056400299072</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.86826074123383</v>
+        <v>1.86826086044312</v>
       </c>
       <c r="H1686" t="n">
         <v>3905</v>
@@ -49350,7 +49350,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.91130793094635</v>
+        <v>1.91130816936493</v>
       </c>
       <c r="H1689" t="n">
         <v>2827</v>
@@ -49379,7 +49379,7 @@
         <v>2.17800402641296</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.93713665008545</v>
+        <v>1.93713688850403</v>
       </c>
       <c r="H1690" t="n">
         <v>6351</v>
@@ -49408,7 +49408,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.91130793094635</v>
+        <v>1.91130816936493</v>
       </c>
       <c r="H1691" t="n">
         <v>11205</v>
@@ -49553,7 +49553,7 @@
         <v>2.14896392822266</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.91130793094635</v>
+        <v>1.91130816936493</v>
       </c>
       <c r="H1696" t="n">
         <v>8700</v>
@@ -49611,7 +49611,7 @@
         <v>2.20704388618469</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.96296501159668</v>
+        <v>1.9629647731781</v>
       </c>
       <c r="H1698" t="n">
         <v>11966</v>
@@ -49640,7 +49640,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1699" t="n">
         <v>12812</v>
@@ -49727,7 +49727,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1702" t="n">
         <v>37919</v>
@@ -49872,7 +49872,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1707" t="n">
         <v>15181</v>
@@ -50046,7 +50046,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1713" t="n">
         <v>23525</v>
@@ -50104,7 +50104,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1715" t="n">
         <v>7005</v>
@@ -50133,7 +50133,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1716" t="n">
         <v>3434</v>
@@ -50191,7 +50191,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1718" t="n">
         <v>41646</v>
@@ -50220,7 +50220,7 @@
         <v>2.2457640171051</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.99740314483643</v>
+        <v>1.99740302562714</v>
       </c>
       <c r="H1719" t="n">
         <v>15121</v>
@@ -50887,7 +50887,7 @@
         <v>2.29416394233704</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.04045057296753</v>
+        <v>2.04045033454895</v>
       </c>
       <c r="H1742" t="n">
         <v>13973</v>
@@ -50945,7 +50945,7 @@
         <v>2.36192488670349</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.10071754455566</v>
+        <v>2.10071778297424</v>
       </c>
       <c r="H1744" t="n">
         <v>16458</v>
@@ -50974,7 +50974,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1745" t="n">
         <v>73553</v>
@@ -51003,7 +51003,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1746" t="n">
         <v>21182</v>
@@ -51177,7 +51177,7 @@
         <v>2.47808504104614</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.20403146743774</v>
+        <v>2.20403122901917</v>
       </c>
       <c r="H1752" t="n">
         <v>66956</v>
@@ -51235,7 +51235,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1754" t="n">
         <v>28322</v>
@@ -51322,7 +51322,7 @@
         <v>2.50712490081787</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.22986006736755</v>
+        <v>2.22985982894897</v>
       </c>
       <c r="H1757" t="n">
         <v>34411</v>
@@ -51467,7 +51467,7 @@
         <v>2.63296508789062</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.34178304672241</v>
+        <v>2.34178328514099</v>
       </c>
       <c r="H1762" t="n">
         <v>39976</v>
@@ -51525,7 +51525,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1764" t="n">
         <v>25977</v>
@@ -51612,7 +51612,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.49675440788269</v>
+        <v>2.49675464630127</v>
       </c>
       <c r="H1767" t="n">
         <v>46462</v>
@@ -51641,7 +51641,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49675440788269</v>
+        <v>2.49675464630127</v>
       </c>
       <c r="H1768" t="n">
         <v>78393</v>
@@ -51670,7 +51670,7 @@
         <v>2.80720591545105</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.49675440788269</v>
+        <v>2.49675464630127</v>
       </c>
       <c r="H1769" t="n">
         <v>37445</v>
@@ -51902,7 +51902,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1777" t="n">
         <v>19559</v>
@@ -51989,7 +51989,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1780" t="n">
         <v>21413</v>
@@ -52076,7 +52076,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1783" t="n">
         <v>84665</v>
@@ -52105,7 +52105,7 @@
         <v>2.7491250038147</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.44509696960449</v>
+        <v>2.44509673118591</v>
       </c>
       <c r="H1784" t="n">
         <v>6025</v>
@@ -52134,7 +52134,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1785" t="n">
         <v>36419</v>
@@ -52163,7 +52163,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1786" t="n">
         <v>20786</v>
@@ -52366,7 +52366,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1793" t="n">
         <v>3563</v>
@@ -52395,7 +52395,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1794" t="n">
         <v>4978</v>
@@ -52453,7 +52453,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1796" t="n">
         <v>9261</v>
@@ -52482,7 +52482,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1797" t="n">
         <v>8670</v>
@@ -52511,7 +52511,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1798" t="n">
         <v>277</v>
@@ -52540,7 +52540,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1799" t="n">
         <v>8141</v>
@@ -52627,7 +52627,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1802" t="n">
         <v>5605</v>
@@ -52801,7 +52801,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.35039258003235</v>
+        <v>2.35039234161377</v>
       </c>
       <c r="H1808" t="n">
         <v>13121</v>
@@ -52859,7 +52859,7 @@
         <v>2.64264488220215</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.35039258003235</v>
+        <v>2.35039234161377</v>
       </c>
       <c r="H1810" t="n">
         <v>982</v>
@@ -52946,7 +52946,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1813" t="n">
         <v>28535</v>
@@ -52975,7 +52975,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1814" t="n">
         <v>3215</v>
@@ -53004,7 +53004,7 @@
         <v>2.70072507858276</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.40204954147339</v>
+        <v>2.40204977989197</v>
       </c>
       <c r="H1815" t="n">
         <v>3758</v>
@@ -53062,7 +53062,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1817" t="n">
         <v>21384</v>
@@ -53091,7 +53091,7 @@
         <v>2.73944497108459</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.43648743629456</v>
+        <v>2.43648719787598</v>
       </c>
       <c r="H1818" t="n">
         <v>22026</v>
@@ -53120,7 +53120,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1819" t="n">
         <v>15508</v>
@@ -53149,7 +53149,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1820" t="n">
         <v>60205</v>
@@ -53178,7 +53178,7 @@
         <v>2.67168498039246</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.37622094154358</v>
+        <v>2.37622117996216</v>
       </c>
       <c r="H1821" t="n">
         <v>18850</v>
@@ -53236,7 +53236,7 @@
         <v>2.71040511131287</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.41065907478333</v>
+        <v>2.4106593132019</v>
       </c>
       <c r="H1823" t="n">
         <v>8939</v>
@@ -53265,7 +53265,7 @@
         <v>2.72008490562439</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.41926860809326</v>
+        <v>2.41926836967468</v>
       </c>
       <c r="H1824" t="n">
         <v>2472</v>
@@ -71193,6 +71193,35 @@
         <v>12740</v>
       </c>
       <c r="I2442" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2443" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2443" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2443" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="E2443" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="G2443" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="H2443" t="n">
+        <v>19180</v>
+      </c>
+      <c r="I2443" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CELL.MI.xlsx
+++ b/data/CELL.MI.xlsx
@@ -485,7 +485,7 @@
         <v>9.42423343658447</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41269493103027</v>
+        <v>7.41269445419312</v>
       </c>
       <c r="H4" t="n">
         <v>14488</v>
@@ -514,7 +514,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G5" t="n">
-        <v>7.42007875442505</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H5" t="n">
         <v>319</v>
@@ -630,7 +630,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G9" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H9" t="n">
         <v>213</v>
@@ -659,7 +659,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G10" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H10" t="n">
         <v>1917</v>
@@ -746,7 +746,7 @@
         <v>9.34914016723633</v>
       </c>
       <c r="G13" t="n">
-        <v>7.35363101959229</v>
+        <v>7.35363006591797</v>
       </c>
       <c r="H13" t="n">
         <v>2450</v>
@@ -862,7 +862,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G17" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H17" t="n">
         <v>106</v>
@@ -891,7 +891,7 @@
         <v>9.29751300811768</v>
       </c>
       <c r="G18" t="n">
-        <v>7.31302213668823</v>
+        <v>7.31302309036255</v>
       </c>
       <c r="H18" t="n">
         <v>7244</v>
@@ -949,7 +949,7 @@
         <v>9.3585262298584</v>
       </c>
       <c r="G20" t="n">
-        <v>7.36101198196411</v>
+        <v>7.36101293563843</v>
       </c>
       <c r="H20" t="n">
         <v>1065</v>
@@ -978,7 +978,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G21" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H21" t="n">
         <v>3302</v>
@@ -1036,7 +1036,7 @@
         <v>9.452392578125</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43484449386597</v>
+        <v>7.43484544754028</v>
       </c>
       <c r="H23" t="n">
         <v>1065</v>
@@ -1065,7 +1065,7 @@
         <v>9.44300556182861</v>
       </c>
       <c r="G24" t="n">
-        <v>7.42746067047119</v>
+        <v>7.42746019363403</v>
       </c>
       <c r="H24" t="n">
         <v>319</v>
@@ -1123,7 +1123,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G26" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H26" t="n">
         <v>4154</v>
@@ -1152,7 +1152,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G27" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H27" t="n">
         <v>639</v>
@@ -1181,7 +1181,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G28" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G29" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G30" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H30" t="n">
         <v>1704</v>
@@ -1297,7 +1297,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G32" t="n">
-        <v>7.46437788009644</v>
+        <v>7.46437740325928</v>
       </c>
       <c r="H32" t="n">
         <v>4580</v>
@@ -1326,7 +1326,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G33" t="n">
-        <v>7.47914266586304</v>
+        <v>7.47914409637451</v>
       </c>
       <c r="H33" t="n">
         <v>426</v>
@@ -1355,7 +1355,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G34" t="n">
-        <v>7.47914266586304</v>
+        <v>7.47914409637451</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>9.70583438873291</v>
       </c>
       <c r="G36" t="n">
-        <v>7.63419103622437</v>
+        <v>7.63419151306152</v>
       </c>
       <c r="H36" t="n">
         <v>3196</v>
@@ -1471,7 +1471,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G38" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H38" t="n">
         <v>21413</v>
@@ -1500,7 +1500,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G39" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H39" t="n">
         <v>11186</v>
@@ -1558,7 +1558,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G41" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H41" t="n">
         <v>15021</v>
@@ -1587,7 +1587,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G42" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H42" t="n">
         <v>12784</v>
@@ -1616,7 +1616,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G43" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H43" t="n">
         <v>5326</v>
@@ -1645,7 +1645,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G44" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H44" t="n">
         <v>12357</v>
@@ -1674,7 +1674,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G45" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H45" t="n">
         <v>10014</v>
@@ -1703,7 +1703,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G46" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H46" t="n">
         <v>1598</v>
@@ -1732,7 +1732,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G47" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391031265259</v>
       </c>
       <c r="H47" t="n">
         <v>3089</v>
@@ -1761,7 +1761,7 @@
         <v>9.50871276855469</v>
       </c>
       <c r="G48" t="n">
-        <v>7.47914266586304</v>
+        <v>7.47914409637451</v>
       </c>
       <c r="H48" t="n">
         <v>3941</v>
@@ -1790,7 +1790,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G49" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H49" t="n">
         <v>9588</v>
@@ -1819,7 +1819,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G50" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H50" t="n">
         <v>2556</v>
@@ -1848,7 +1848,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G51" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391031265259</v>
       </c>
       <c r="H51" t="n">
         <v>13103</v>
@@ -1877,7 +1877,7 @@
         <v>9.48993968963623</v>
       </c>
       <c r="G52" t="n">
-        <v>7.46437788009644</v>
+        <v>7.46437740325928</v>
       </c>
       <c r="H52" t="n">
         <v>2982</v>
@@ -1906,7 +1906,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G53" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391031265259</v>
       </c>
       <c r="H53" t="n">
         <v>7776</v>
@@ -1935,7 +1935,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G54" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391031265259</v>
       </c>
       <c r="H54" t="n">
         <v>319</v>
@@ -1964,7 +1964,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G55" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H55" t="n">
         <v>21306</v>
@@ -1993,7 +1993,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G56" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H56" t="n">
         <v>4261</v>
@@ -2080,7 +2080,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H59" t="n">
         <v>106</v>
@@ -2167,7 +2167,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G62" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H62" t="n">
         <v>1065</v>
@@ -2312,7 +2312,7 @@
         <v>10.1188478469849</v>
       </c>
       <c r="G67" t="n">
-        <v>7.9590482711792</v>
+        <v>7.95905017852783</v>
       </c>
       <c r="H67" t="n">
         <v>7137</v>
@@ -2457,7 +2457,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G72" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H72" t="n">
         <v>2343</v>
@@ -2486,7 +2486,7 @@
         <v>10.1000747680664</v>
       </c>
       <c r="G73" t="n">
-        <v>7.94428396224976</v>
+        <v>7.94428300857544</v>
       </c>
       <c r="H73" t="n">
         <v>5326</v>
@@ -2515,7 +2515,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G74" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H74" t="n">
         <v>6924</v>
@@ -2544,7 +2544,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H75" t="n">
         <v>1065</v>
@@ -2660,7 +2660,7 @@
         <v>9.9029541015625</v>
       </c>
       <c r="G79" t="n">
-        <v>7.78923654556274</v>
+        <v>7.78923559188843</v>
       </c>
       <c r="H79" t="n">
         <v>5007</v>
@@ -2747,7 +2747,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G82" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H82" t="n">
         <v>4367</v>
@@ -2776,7 +2776,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G83" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G84" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H84" t="n">
         <v>10653</v>
@@ -2921,7 +2921,7 @@
         <v>9.97804832458496</v>
       </c>
       <c r="G88" t="n">
-        <v>7.84830141067505</v>
+        <v>7.84830236434937</v>
       </c>
       <c r="H88" t="n">
         <v>2982</v>
@@ -2950,7 +2950,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G89" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H89" t="n">
         <v>15021</v>
@@ -2979,7 +2979,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G90" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H90" t="n">
         <v>5859</v>
@@ -3008,7 +3008,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G91" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H91" t="n">
         <v>2450</v>
@@ -3037,7 +3037,7 @@
         <v>9.93111419677734</v>
       </c>
       <c r="G92" t="n">
-        <v>7.81138610839844</v>
+        <v>7.81138706207275</v>
       </c>
       <c r="H92" t="n">
         <v>7457</v>
@@ -3066,7 +3066,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G93" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H93" t="n">
         <v>958</v>
@@ -3124,7 +3124,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G95" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H95" t="n">
         <v>2556</v>
@@ -3153,7 +3153,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G96" t="n">
-        <v>7.72278785705566</v>
+        <v>7.72278690338135</v>
       </c>
       <c r="H96" t="n">
         <v>1598</v>
@@ -3327,7 +3327,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G102" t="n">
-        <v>7.72278785705566</v>
+        <v>7.72278690338135</v>
       </c>
       <c r="H102" t="n">
         <v>1065</v>
@@ -3356,7 +3356,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G103" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H103" t="n">
         <v>852</v>
@@ -3385,7 +3385,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G104" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H104" t="n">
         <v>1065</v>
@@ -3414,7 +3414,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G105" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G113" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H113" t="n">
         <v>2237</v>
@@ -3791,7 +3791,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G118" t="n">
-        <v>7.70063781738281</v>
+        <v>7.70063829421997</v>
       </c>
       <c r="H118" t="n">
         <v>50070</v>
@@ -3820,7 +3820,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G119" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H119" t="n">
         <v>5326</v>
@@ -3878,7 +3878,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G121" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H121" t="n">
         <v>4580</v>
@@ -3907,7 +3907,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G122" t="n">
-        <v>7.72278785705566</v>
+        <v>7.72278690338135</v>
       </c>
       <c r="H122" t="n">
         <v>213</v>
@@ -3936,7 +3936,7 @@
         <v>9.81847381591797</v>
       </c>
       <c r="G123" t="n">
-        <v>7.72278785705566</v>
+        <v>7.72278690338135</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G124" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H124" t="n">
         <v>7137</v>
@@ -4168,7 +4168,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G131" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H131" t="n">
         <v>1811</v>
@@ -4197,7 +4197,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G132" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H132" t="n">
         <v>1704</v>
@@ -4226,7 +4226,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G133" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H133" t="n">
         <v>2769</v>
@@ -4255,7 +4255,7 @@
         <v>9.75276660919189</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67110538482666</v>
+        <v>7.6711049079895</v>
       </c>
       <c r="H134" t="n">
         <v>852</v>
@@ -4284,7 +4284,7 @@
         <v>9.71522045135498</v>
       </c>
       <c r="G135" t="n">
-        <v>7.64157295227051</v>
+        <v>7.64157247543335</v>
       </c>
       <c r="H135" t="n">
         <v>1384</v>
@@ -4313,7 +4313,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G136" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H136" t="n">
         <v>2556</v>
@@ -4342,7 +4342,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G137" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H137" t="n">
         <v>10440</v>
@@ -4371,7 +4371,7 @@
         <v>9.54625988006592</v>
       </c>
       <c r="G138" t="n">
-        <v>7.50867652893066</v>
+        <v>7.50867557525635</v>
       </c>
       <c r="H138" t="n">
         <v>3302</v>
@@ -4400,7 +4400,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G139" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H139" t="n">
         <v>6498</v>
@@ -4487,7 +4487,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58250761032104</v>
+        <v>7.58250856399536</v>
       </c>
       <c r="H142" t="n">
         <v>639</v>
@@ -4516,7 +4516,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G143" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H143" t="n">
         <v>8629</v>
@@ -4574,7 +4574,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G145" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H145" t="n">
         <v>1065</v>
@@ -4603,7 +4603,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G146" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H146" t="n">
         <v>106</v>
@@ -4632,7 +4632,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G147" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G148" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G149" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H149" t="n">
         <v>2663</v>
@@ -4719,7 +4719,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G150" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H150" t="n">
         <v>2769</v>
@@ -4748,7 +4748,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G151" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H151" t="n">
         <v>12997</v>
@@ -4806,7 +4806,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G153" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H153" t="n">
         <v>639</v>
@@ -4864,7 +4864,7 @@
         <v>9.60258007049561</v>
       </c>
       <c r="G155" t="n">
-        <v>7.55297613143921</v>
+        <v>7.55297565460205</v>
       </c>
       <c r="H155" t="n">
         <v>2130</v>
@@ -4922,7 +4922,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G157" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H157" t="n">
         <v>2343</v>
@@ -4951,7 +4951,7 @@
         <v>9.69644737243652</v>
       </c>
       <c r="G158" t="n">
-        <v>7.62680768966675</v>
+        <v>7.62680721282959</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G159" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H159" t="n">
         <v>22691</v>
@@ -5096,7 +5096,7 @@
         <v>9.79031372070312</v>
       </c>
       <c r="G163" t="n">
-        <v>7.70063781738281</v>
+        <v>7.70063829421997</v>
       </c>
       <c r="H163" t="n">
         <v>1171</v>
@@ -5212,7 +5212,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G167" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540498733521</v>
       </c>
       <c r="H167" t="n">
         <v>745</v>
@@ -5328,7 +5328,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G171" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H171" t="n">
         <v>21519</v>
@@ -5357,7 +5357,7 @@
         <v>9.77154064178467</v>
       </c>
       <c r="G172" t="n">
-        <v>7.68587160110474</v>
+        <v>7.68587255477905</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>9.80908679962158</v>
       </c>
       <c r="G173" t="n">
-        <v>7.71540451049805</v>
+        <v>7.71540498733521</v>
       </c>
       <c r="H173" t="n">
         <v>5433</v>
@@ -5444,7 +5444,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G175" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H175" t="n">
         <v>1278</v>
@@ -5531,7 +5531,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G178" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H178" t="n">
         <v>10653</v>
@@ -5589,7 +5589,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G180" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H180" t="n">
         <v>11079</v>
@@ -5618,7 +5618,7 @@
         <v>9.62135410308838</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56774234771729</v>
+        <v>7.56774139404297</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G182" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H182" t="n">
         <v>6072</v>
@@ -5676,7 +5676,7 @@
         <v>9.59319305419922</v>
       </c>
       <c r="G183" t="n">
-        <v>7.54559230804443</v>
+        <v>7.54559183120728</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>9.52748680114746</v>
       </c>
       <c r="G185" t="n">
-        <v>7.49390983581543</v>
+        <v>7.49391031265259</v>
       </c>
       <c r="H185" t="n">
         <v>11718</v>
@@ -5763,7 +5763,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G186" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H186" t="n">
         <v>7137</v>
@@ -5792,7 +5792,7 @@
         <v>9.64012718200684</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58250761032104</v>
+        <v>7.58250856399536</v>
       </c>
       <c r="H187" t="n">
         <v>10014</v>
@@ -5821,7 +5821,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G188" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H188" t="n">
         <v>3196</v>
@@ -5850,7 +5850,7 @@
         <v>9.63074016571045</v>
       </c>
       <c r="G189" t="n">
-        <v>7.57512474060059</v>
+        <v>7.57512426376343</v>
       </c>
       <c r="H189" t="n">
         <v>106</v>
@@ -5879,7 +5879,7 @@
         <v>9.61196708679199</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56035852432251</v>
+        <v>7.56035804748535</v>
       </c>
       <c r="H190" t="n">
         <v>1065</v>
@@ -5908,7 +5908,7 @@
         <v>9.47116661071777</v>
       </c>
       <c r="G191" t="n">
-        <v>7.44961071014404</v>
+        <v>7.4496111869812</v>
       </c>
       <c r="H191" t="n">
         <v>106</v>
@@ -5937,7 +5937,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G192" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H192" t="n">
         <v>213</v>
@@ -6198,7 +6198,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G201" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H201" t="n">
         <v>745</v>
@@ -6227,7 +6227,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G202" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G203" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H203" t="n">
         <v>1384</v>
@@ -6285,7 +6285,7 @@
         <v>9.43362045288086</v>
       </c>
       <c r="G204" t="n">
-        <v>7.42007875442505</v>
+        <v>7.42007923126221</v>
       </c>
       <c r="H204" t="n">
         <v>958</v>
@@ -6430,7 +6430,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G209" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H209" t="n">
         <v>319</v>
@@ -6488,7 +6488,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G211" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H211" t="n">
         <v>3728</v>
@@ -6517,7 +6517,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G212" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H212" t="n">
         <v>958</v>
@@ -6604,7 +6604,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G215" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H215" t="n">
         <v>639</v>
@@ -6633,7 +6633,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G216" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H216" t="n">
         <v>11612</v>
@@ -6662,7 +6662,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G217" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H217" t="n">
         <v>192826</v>
@@ -6749,7 +6749,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G220" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H220" t="n">
         <v>61683</v>
@@ -6778,7 +6778,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G221" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H221" t="n">
         <v>44637</v>
@@ -6807,7 +6807,7 @@
         <v>10.0437536239624</v>
       </c>
       <c r="G222" t="n">
-        <v>7.89998245239258</v>
+        <v>7.89998340606689</v>
       </c>
       <c r="H222" t="n">
         <v>38565</v>
@@ -6923,7 +6923,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G226" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H226" t="n">
         <v>16086</v>
@@ -6952,7 +6952,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G227" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H227" t="n">
         <v>63174</v>
@@ -6981,7 +6981,7 @@
         <v>9.8560209274292</v>
       </c>
       <c r="G228" t="n">
-        <v>7.75232028961182</v>
+        <v>7.75232124328613</v>
       </c>
       <c r="H228" t="n">
         <v>21200</v>
@@ -7039,7 +7039,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G230" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H230" t="n">
         <v>24076</v>
@@ -7068,7 +7068,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G231" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H231" t="n">
         <v>3089</v>
@@ -7097,7 +7097,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G232" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H232" t="n">
         <v>7883</v>
@@ -7126,7 +7126,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G233" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H233" t="n">
         <v>23970</v>
@@ -7155,7 +7155,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G234" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H234" t="n">
         <v>54864</v>
@@ -7184,7 +7184,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G235" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H235" t="n">
         <v>9055</v>
@@ -7213,7 +7213,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G236" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H236" t="n">
         <v>8203</v>
@@ -7242,7 +7242,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G237" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H237" t="n">
         <v>4794</v>
@@ -7271,7 +7271,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G238" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H238" t="n">
         <v>14062</v>
@@ -7329,7 +7329,7 @@
         <v>9.66828727722168</v>
       </c>
       <c r="G240" t="n">
-        <v>7.6046576499939</v>
+        <v>7.60465717315674</v>
       </c>
       <c r="H240" t="n">
         <v>21413</v>
@@ -7358,7 +7358,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H241" t="n">
         <v>39630</v>
@@ -7387,7 +7387,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G242" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H242" t="n">
         <v>19495</v>
@@ -7416,7 +7416,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G243" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H243" t="n">
         <v>23650</v>
@@ -7445,7 +7445,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G244" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H244" t="n">
         <v>36967</v>
@@ -7474,7 +7474,7 @@
         <v>9.48055267333984</v>
       </c>
       <c r="G245" t="n">
-        <v>7.45699310302734</v>
+        <v>7.4569935798645</v>
       </c>
       <c r="H245" t="n">
         <v>35049</v>
@@ -7503,7 +7503,7 @@
         <v>9.57441997528076</v>
       </c>
       <c r="G246" t="n">
-        <v>7.53082513809204</v>
+        <v>7.5308256149292</v>
       </c>
       <c r="H246" t="n">
         <v>35688</v>
@@ -7619,7 +7619,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G250" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H250" t="n">
         <v>13742</v>
@@ -7793,7 +7793,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G256" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H256" t="n">
         <v>53586</v>
@@ -7822,7 +7822,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G257" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G260" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H260" t="n">
         <v>2343</v>
@@ -7967,7 +7967,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G262" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H262" t="n">
         <v>14062</v>
@@ -7996,7 +7996,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G263" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H263" t="n">
         <v>1598</v>
@@ -8170,7 +8170,7 @@
         <v>9.33975315093994</v>
       </c>
       <c r="G269" t="n">
-        <v>7.34624767303467</v>
+        <v>7.34624671936035</v>
       </c>
       <c r="H269" t="n">
         <v>4474</v>
@@ -8866,7 +8866,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G293" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475109100342</v>
       </c>
       <c r="H293" t="n">
         <v>1917</v>
@@ -8895,7 +8895,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G294" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475109100342</v>
       </c>
       <c r="H294" t="n">
         <v>4474</v>
@@ -8924,7 +8924,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G295" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475109100342</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G300" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325689315796</v>
       </c>
       <c r="H300" t="n">
         <v>23011</v>
@@ -9098,7 +9098,7 @@
         <v>9.0581521987915</v>
       </c>
       <c r="G301" t="n">
-        <v>7.12475156784058</v>
+        <v>7.12475109100342</v>
       </c>
       <c r="H301" t="n">
         <v>2237</v>
@@ -9243,7 +9243,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G306" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H306" t="n">
         <v>8309</v>
@@ -9272,7 +9272,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G307" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325689315796</v>
       </c>
       <c r="H307" t="n">
         <v>2130</v>
@@ -9301,7 +9301,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G308" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H308" t="n">
         <v>9588</v>
@@ -9330,7 +9330,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G309" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H309" t="n">
         <v>11825</v>
@@ -9359,7 +9359,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G310" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017362594604</v>
       </c>
       <c r="H310" t="n">
         <v>4048</v>
@@ -9388,7 +9388,7 @@
         <v>8.87041854858398</v>
       </c>
       <c r="G311" t="n">
-        <v>6.9770884513855</v>
+        <v>6.97708892822266</v>
       </c>
       <c r="H311" t="n">
         <v>10866</v>
@@ -9417,7 +9417,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G312" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017362594604</v>
       </c>
       <c r="H312" t="n">
         <v>2663</v>
@@ -9475,7 +9475,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G314" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017362594604</v>
       </c>
       <c r="H314" t="n">
         <v>51349</v>
@@ -9504,7 +9504,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G315" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325689315796</v>
       </c>
       <c r="H315" t="n">
         <v>958</v>
@@ -9533,7 +9533,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G316" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325689315796</v>
       </c>
       <c r="H316" t="n">
         <v>213</v>
@@ -9562,7 +9562,7 @@
         <v>8.82348537445068</v>
       </c>
       <c r="G317" t="n">
-        <v>6.94017267227173</v>
+        <v>6.94017362594604</v>
       </c>
       <c r="H317" t="n">
         <v>54438</v>
@@ -9591,7 +9591,7 @@
         <v>8.77655220031738</v>
       </c>
       <c r="G318" t="n">
-        <v>6.90325736999512</v>
+        <v>6.90325689315796</v>
       </c>
       <c r="H318" t="n">
         <v>27379</v>
@@ -9620,7 +9620,7 @@
         <v>8.54188537597656</v>
       </c>
       <c r="G319" t="n">
-        <v>6.71867799758911</v>
+        <v>6.71867847442627</v>
       </c>
       <c r="H319" t="n">
         <v>12144</v>
@@ -9678,7 +9678,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G321" t="n">
-        <v>6.75559329986572</v>
+        <v>6.75559377670288</v>
       </c>
       <c r="H321" t="n">
         <v>745</v>
@@ -9707,7 +9707,7 @@
         <v>8.58881759643555</v>
       </c>
       <c r="G322" t="n">
-        <v>6.75559329986572</v>
+        <v>6.75559377670288</v>
       </c>
       <c r="H322" t="n">
         <v>532</v>
@@ -9736,7 +9736,7 @@
         <v>8.35415077209473</v>
       </c>
       <c r="G323" t="n">
-        <v>6.57101488113403</v>
+        <v>6.57101440429688</v>
       </c>
       <c r="H323" t="n">
         <v>20561</v>
@@ -9765,7 +9765,7 @@
         <v>8.40108394622803</v>
       </c>
       <c r="G324" t="n">
-        <v>6.60793018341064</v>
+        <v>6.60792970657349</v>
       </c>
       <c r="H324" t="n">
         <v>5859</v>
@@ -9823,7 +9823,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G326" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H326" t="n">
         <v>44424</v>
@@ -9852,7 +9852,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G327" t="n">
-        <v>6.34951972961426</v>
+        <v>6.3495192527771</v>
       </c>
       <c r="H327" t="n">
         <v>3089</v>
@@ -9968,7 +9968,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G331" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H331" t="n">
         <v>20134</v>
@@ -10084,7 +10084,7 @@
         <v>8.30721664428711</v>
       </c>
       <c r="G335" t="n">
-        <v>6.53409862518311</v>
+        <v>6.53409767150879</v>
       </c>
       <c r="H335" t="n">
         <v>3089</v>
@@ -10316,7 +10316,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G343" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H343" t="n">
         <v>745</v>
@@ -10345,7 +10345,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G344" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H344" t="n">
         <v>3409</v>
@@ -10374,7 +10374,7 @@
         <v>7.93174982070923</v>
       </c>
       <c r="G345" t="n">
-        <v>6.23877191543579</v>
+        <v>6.23877239227295</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>8.02561664581299</v>
       </c>
       <c r="G346" t="n">
-        <v>6.31260395050049</v>
+        <v>6.31260347366333</v>
       </c>
       <c r="H346" t="n">
         <v>852</v>
@@ -10432,7 +10432,7 @@
         <v>8.07254981994629</v>
       </c>
       <c r="G347" t="n">
-        <v>6.34951972961426</v>
+        <v>6.3495192527771</v>
       </c>
       <c r="H347" t="n">
         <v>852</v>
@@ -11215,7 +11215,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G374" t="n">
-        <v>6.05419397354126</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H374" t="n">
         <v>2556</v>
@@ -11244,7 +11244,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G375" t="n">
-        <v>6.05419397354126</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H375" t="n">
         <v>3196</v>
@@ -11302,7 +11302,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G377" t="n">
-        <v>6.05419397354126</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H377" t="n">
         <v>15340</v>
@@ -11650,7 +11650,7 @@
         <v>7.69708299636841</v>
       </c>
       <c r="G389" t="n">
-        <v>6.05419397354126</v>
+        <v>6.0541934967041</v>
       </c>
       <c r="H389" t="n">
         <v>3196</v>
@@ -11911,7 +11911,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G398" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H398" t="n">
         <v>18749</v>
@@ -11998,7 +11998,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G401" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H401" t="n">
         <v>958</v>
@@ -12056,7 +12056,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G403" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H403" t="n">
         <v>4580</v>
@@ -12085,7 +12085,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G404" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428789138794</v>
       </c>
       <c r="H404" t="n">
         <v>20454</v>
@@ -12259,7 +12259,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G410" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H410" t="n">
         <v>9588</v>
@@ -12375,7 +12375,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G414" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H414" t="n">
         <v>19282</v>
@@ -12607,7 +12607,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G422" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H422" t="n">
         <v>6818</v>
@@ -12665,7 +12665,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G424" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H424" t="n">
         <v>5113</v>
@@ -12781,7 +12781,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G428" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H428" t="n">
         <v>24183</v>
@@ -12810,7 +12810,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G429" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428789138794</v>
       </c>
       <c r="H429" t="n">
         <v>7990</v>
@@ -12839,7 +12839,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G430" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H430" t="n">
         <v>2024</v>
@@ -12868,7 +12868,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G431" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H431" t="n">
         <v>13955</v>
@@ -12955,7 +12955,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G434" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H434" t="n">
         <v>6498</v>
@@ -13100,7 +13100,7 @@
         <v>7.97868299484253</v>
       </c>
       <c r="G439" t="n">
-        <v>6.27568769454956</v>
+        <v>6.27568864822388</v>
       </c>
       <c r="H439" t="n">
         <v>3089</v>
@@ -13129,7 +13129,7 @@
         <v>7.97868299484253</v>
       </c>
       <c r="G440" t="n">
-        <v>6.27568769454956</v>
+        <v>6.27568864822388</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G444" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H444" t="n">
         <v>958</v>
@@ -13274,7 +13274,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G445" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H445" t="n">
         <v>5007</v>
@@ -13361,7 +13361,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G448" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H448" t="n">
         <v>2343</v>
@@ -13390,7 +13390,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G449" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428789138794</v>
       </c>
       <c r="H449" t="n">
         <v>4261</v>
@@ -13419,7 +13419,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G450" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428789138794</v>
       </c>
       <c r="H450" t="n">
         <v>5752</v>
@@ -13448,7 +13448,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G451" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428789138794</v>
       </c>
       <c r="H451" t="n">
         <v>8735</v>
@@ -13506,7 +13506,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G453" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H453" t="n">
         <v>2343</v>
@@ -13535,7 +13535,7 @@
         <v>7.08694791793823</v>
       </c>
       <c r="G454" t="n">
-        <v>5.57428741455078</v>
+        <v>5.57428789138794</v>
       </c>
       <c r="H454" t="n">
         <v>2769</v>
@@ -13651,7 +13651,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G458" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H458" t="n">
         <v>1065</v>
@@ -13680,7 +13680,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G459" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H459" t="n">
         <v>3089</v>
@@ -13709,7 +13709,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G460" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H460" t="n">
         <v>1704</v>
@@ -13767,7 +13767,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G462" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H462" t="n">
         <v>1065</v>
@@ -13854,7 +13854,7 @@
         <v>7.36854887008667</v>
       </c>
       <c r="G465" t="n">
-        <v>5.79578256607056</v>
+        <v>5.79578304290771</v>
       </c>
       <c r="H465" t="n">
         <v>1065</v>
@@ -13970,7 +13970,7 @@
         <v>7.27468204498291</v>
       </c>
       <c r="G469" t="n">
-        <v>5.72195100784302</v>
+        <v>5.72195148468018</v>
       </c>
       <c r="H469" t="n">
         <v>2663</v>
@@ -13999,7 +13999,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G470" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H470" t="n">
         <v>852</v>
@@ -14028,7 +14028,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G471" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H471" t="n">
         <v>2343</v>
@@ -14260,7 +14260,7 @@
         <v>7.18081521987915</v>
       </c>
       <c r="G479" t="n">
-        <v>5.64811992645264</v>
+        <v>5.64811944961548</v>
       </c>
       <c r="H479" t="n">
         <v>6605</v>
@@ -14289,7 +14289,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G480" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H480" t="n">
         <v>2130</v>
@@ -14318,7 +14318,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G481" t="n">
-        <v>5.53737258911133</v>
+        <v>5.53737211227417</v>
       </c>
       <c r="H481" t="n">
         <v>20241</v>
@@ -14376,7 +14376,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G483" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H483" t="n">
         <v>3409</v>
@@ -14405,7 +14405,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G484" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H484" t="n">
         <v>2343</v>
@@ -14434,7 +14434,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G485" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H485" t="n">
         <v>19176</v>
@@ -14463,7 +14463,7 @@
         <v>6.99308109283447</v>
       </c>
       <c r="G486" t="n">
-        <v>5.5004563331604</v>
+        <v>5.50045585632324</v>
       </c>
       <c r="H486" t="n">
         <v>4154</v>
@@ -14608,7 +14608,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G491" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H491" t="n">
         <v>2343</v>
@@ -14637,7 +14637,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G492" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H492" t="n">
         <v>2876</v>
@@ -14666,7 +14666,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G493" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H493" t="n">
         <v>3089</v>
@@ -14724,7 +14724,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G495" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H495" t="n">
         <v>3515</v>
@@ -14753,7 +14753,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G496" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H496" t="n">
         <v>8948</v>
@@ -14782,7 +14782,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G497" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H497" t="n">
         <v>9268</v>
@@ -14869,7 +14869,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G500" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H500" t="n">
         <v>50603</v>
@@ -14898,7 +14898,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G501" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H501" t="n">
         <v>18856</v>
@@ -14927,7 +14927,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G502" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587648391724</v>
       </c>
       <c r="H502" t="n">
         <v>12251</v>
@@ -14985,7 +14985,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G504" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H504" t="n">
         <v>36754</v>
@@ -15014,7 +15014,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G505" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H505" t="n">
         <v>23757</v>
@@ -15043,7 +15043,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G506" t="n">
-        <v>5.31587696075439</v>
+        <v>5.31587648391724</v>
       </c>
       <c r="H506" t="n">
         <v>11399</v>
@@ -15101,7 +15101,7 @@
         <v>6.80534696578979</v>
       </c>
       <c r="G508" t="n">
-        <v>5.35279226303101</v>
+        <v>5.35279273986816</v>
       </c>
       <c r="H508" t="n">
         <v>25035</v>
@@ -15130,7 +15130,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G509" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H509" t="n">
         <v>39417</v>
@@ -15159,7 +15159,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G510" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H510" t="n">
         <v>33345</v>
@@ -15188,7 +15188,7 @@
         <v>6.71148109436035</v>
       </c>
       <c r="G511" t="n">
-        <v>5.27896118164062</v>
+        <v>5.27896165847778</v>
       </c>
       <c r="H511" t="n">
         <v>12251</v>
@@ -15304,7 +15304,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G515" t="n">
-        <v>5.20512914657593</v>
+        <v>5.20512962341309</v>
       </c>
       <c r="H515" t="n">
         <v>9374</v>
@@ -15333,7 +15333,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G516" t="n">
-        <v>5.20512914657593</v>
+        <v>5.20512962341309</v>
       </c>
       <c r="H516" t="n">
         <v>8203</v>
@@ -15362,7 +15362,7 @@
         <v>6.61761379241943</v>
       </c>
       <c r="G517" t="n">
-        <v>5.20512914657593</v>
+        <v>5.20512962341309</v>
       </c>
       <c r="H517" t="n">
         <v>11931</v>
@@ -15507,7 +15507,7 @@
         <v>6.70209407806396</v>
       </c>
       <c r="G522" t="n">
-        <v>5.27157878875732</v>
+        <v>5.27157831192017</v>
       </c>
       <c r="H522" t="n">
         <v>7990</v>
@@ -15536,7 +15536,7 @@
         <v>6.81473398208618</v>
       </c>
       <c r="G523" t="n">
-        <v>5.36017608642578</v>
+        <v>5.36017560958862</v>
       </c>
       <c r="H523" t="n">
         <v>11505</v>
@@ -15594,7 +15594,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G525" t="n">
-        <v>5.43400764465332</v>
+        <v>5.43400716781616</v>
       </c>
       <c r="H525" t="n">
         <v>20028</v>
@@ -15652,7 +15652,7 @@
         <v>7.04001522064209</v>
       </c>
       <c r="G527" t="n">
-        <v>5.53737258911133</v>
+        <v>5.53737211227417</v>
       </c>
       <c r="H527" t="n">
         <v>16193</v>
@@ -15681,7 +15681,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49307298660278</v>
+        <v>5.49307346343994</v>
       </c>
       <c r="H528" t="n">
         <v>4048</v>
@@ -15710,7 +15710,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G529" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H529" t="n">
         <v>9791</v>
@@ -15855,7 +15855,7 @@
         <v>7.28406810760498</v>
       </c>
       <c r="G534" t="n">
-        <v>5.72933340072632</v>
+        <v>5.72933387756348</v>
       </c>
       <c r="H534" t="n">
         <v>17724</v>
@@ -15913,7 +15913,7 @@
         <v>7.30284214019775</v>
       </c>
       <c r="G536" t="n">
-        <v>5.74410104751587</v>
+        <v>5.74410057067871</v>
       </c>
       <c r="H536" t="n">
         <v>10126</v>
@@ -15971,7 +15971,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G538" t="n">
-        <v>5.61120367050171</v>
+        <v>5.61120319366455</v>
       </c>
       <c r="H538" t="n">
         <v>8909</v>
@@ -16000,7 +16000,7 @@
         <v>7.17142820358276</v>
       </c>
       <c r="G539" t="n">
-        <v>5.64073657989502</v>
+        <v>5.6407356262207</v>
       </c>
       <c r="H539" t="n">
         <v>7267</v>
@@ -16029,7 +16029,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G540" t="n">
-        <v>5.58167123794556</v>
+        <v>5.5816707611084</v>
       </c>
       <c r="H540" t="n">
         <v>33206</v>
@@ -16058,7 +16058,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G541" t="n">
-        <v>5.50783920288086</v>
+        <v>5.50784015655518</v>
       </c>
       <c r="H541" t="n">
         <v>31068</v>
@@ -16116,7 +16116,7 @@
         <v>6.9836950302124</v>
       </c>
       <c r="G543" t="n">
-        <v>5.49307298660278</v>
+        <v>5.49307346343994</v>
       </c>
       <c r="H543" t="n">
         <v>13326</v>
@@ -16319,7 +16319,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G550" t="n">
-        <v>5.34540987014771</v>
+        <v>5.34540939331055</v>
       </c>
       <c r="H550" t="n">
         <v>4911</v>
@@ -16406,7 +16406,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G553" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H553" t="n">
         <v>3539</v>
@@ -16435,7 +16435,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G554" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H554" t="n">
         <v>5577</v>
@@ -16493,7 +16493,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G556" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H556" t="n">
         <v>4442</v>
@@ -16522,7 +16522,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G557" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H557" t="n">
         <v>13819</v>
@@ -16551,7 +16551,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G558" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H558" t="n">
         <v>20885</v>
@@ -16580,7 +16580,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G559" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H559" t="n">
         <v>3355</v>
@@ -16609,7 +16609,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G560" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H560" t="n">
         <v>6240</v>
@@ -16638,7 +16638,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G561" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H561" t="n">
         <v>4176</v>
@@ -16725,7 +16725,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G564" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H564" t="n">
         <v>2151</v>
@@ -16754,7 +16754,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G565" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57647943496704</v>
       </c>
       <c r="H565" t="n">
         <v>6946</v>
@@ -16783,7 +16783,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G566" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57647943496704</v>
       </c>
       <c r="H566" t="n">
         <v>6002</v>
@@ -16870,7 +16870,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G569" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57647943496704</v>
       </c>
       <c r="H569" t="n">
         <v>8874</v>
@@ -16899,7 +16899,7 @@
         <v>6.94614791870117</v>
       </c>
       <c r="G570" t="n">
-        <v>5.69971656799316</v>
+        <v>5.69971704483032</v>
       </c>
       <c r="H570" t="n">
         <v>10333</v>
@@ -16957,7 +16957,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G572" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H572" t="n">
         <v>2151</v>
@@ -16986,7 +16986,7 @@
         <v>7.09633493423462</v>
       </c>
       <c r="G573" t="n">
-        <v>5.82295417785645</v>
+        <v>5.82295370101929</v>
       </c>
       <c r="H573" t="n">
         <v>2375</v>
@@ -17044,7 +17044,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G575" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H575" t="n">
         <v>1619</v>
@@ -17073,7 +17073,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G576" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H576" t="n">
         <v>1608</v>
@@ -17102,7 +17102,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G577" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H577" t="n">
         <v>4644</v>
@@ -17131,7 +17131,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G578" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H578" t="n">
         <v>4303</v>
@@ -17160,7 +17160,7 @@
         <v>7.11510801315308</v>
       </c>
       <c r="G579" t="n">
-        <v>5.8383584022522</v>
+        <v>5.83835887908936</v>
       </c>
       <c r="H579" t="n">
         <v>7254</v>
@@ -17189,7 +17189,7 @@
         <v>7.13388204574585</v>
       </c>
       <c r="G580" t="n">
-        <v>5.85376405715942</v>
+        <v>5.85376310348511</v>
       </c>
       <c r="H580" t="n">
         <v>2840</v>
@@ -17247,7 +17247,7 @@
         <v>7.05878782272339</v>
       </c>
       <c r="G582" t="n">
-        <v>5.79214477539062</v>
+        <v>5.79214429855347</v>
       </c>
       <c r="H582" t="n">
         <v>356</v>
@@ -17305,7 +17305,7 @@
         <v>7.02124118804932</v>
       </c>
       <c r="G584" t="n">
-        <v>5.76133584976196</v>
+        <v>5.7613353729248</v>
       </c>
       <c r="H584" t="n">
         <v>1672</v>
@@ -17334,7 +17334,7 @@
         <v>7.00246810913086</v>
       </c>
       <c r="G585" t="n">
-        <v>5.74593067169189</v>
+        <v>5.74593162536621</v>
       </c>
       <c r="H585" t="n">
         <v>1301</v>
@@ -17363,7 +17363,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G586" t="n">
-        <v>5.6843113899231</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H586" t="n">
         <v>1097</v>
@@ -17392,7 +17392,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G587" t="n">
-        <v>5.66890668869019</v>
+        <v>5.66890716552734</v>
       </c>
       <c r="H587" t="n">
         <v>10990</v>
@@ -17421,7 +17421,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G588" t="n">
-        <v>5.62269353866577</v>
+        <v>5.62269306182861</v>
       </c>
       <c r="H588" t="n">
         <v>2162</v>
@@ -17450,7 +17450,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G589" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H589" t="n">
         <v>5812</v>
@@ -17479,7 +17479,7 @@
         <v>6.90860080718994</v>
       </c>
       <c r="G590" t="n">
-        <v>5.66890668869019</v>
+        <v>5.66890716552734</v>
       </c>
       <c r="H590" t="n">
         <v>7426</v>
@@ -17508,7 +17508,7 @@
         <v>6.79596090316772</v>
       </c>
       <c r="G591" t="n">
-        <v>5.5764799118042</v>
+        <v>5.57647943496704</v>
       </c>
       <c r="H591" t="n">
         <v>11995</v>
@@ -17566,7 +17566,7 @@
         <v>6.77718687057495</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56107521057129</v>
+        <v>5.56107473373413</v>
       </c>
       <c r="H593" t="n">
         <v>10592</v>
@@ -17595,7 +17595,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G594" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H594" t="n">
         <v>5028</v>
@@ -17624,7 +17624,7 @@
         <v>6.85228109359741</v>
       </c>
       <c r="G595" t="n">
-        <v>5.62269353866577</v>
+        <v>5.62269306182861</v>
       </c>
       <c r="H595" t="n">
         <v>33809</v>
@@ -17711,7 +17711,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G598" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H598" t="n">
         <v>14734</v>
@@ -17740,7 +17740,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G599" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H599" t="n">
         <v>10813</v>
@@ -17769,7 +17769,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G600" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H600" t="n">
         <v>12230</v>
@@ -17827,7 +17827,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G602" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H602" t="n">
         <v>5214</v>
@@ -17885,7 +17885,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G604" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H604" t="n">
         <v>16874</v>
@@ -17914,7 +17914,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G605" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H605" t="n">
         <v>2935</v>
@@ -17972,7 +17972,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G607" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H607" t="n">
         <v>7436</v>
@@ -18117,7 +18117,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G612" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H612" t="n">
         <v>17032</v>
@@ -18146,7 +18146,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G613" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H613" t="n">
         <v>5312</v>
@@ -18175,7 +18175,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G614" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H614" t="n">
         <v>5545</v>
@@ -18204,7 +18204,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G615" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H615" t="n">
         <v>3749</v>
@@ -18233,7 +18233,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G616" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H616" t="n">
         <v>3536</v>
@@ -18262,7 +18262,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G617" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H617" t="n">
         <v>2524</v>
@@ -18291,7 +18291,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G618" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H618" t="n">
         <v>2151</v>
@@ -18320,7 +18320,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G619" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H619" t="n">
         <v>2993</v>
@@ -18349,7 +18349,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G620" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H620" t="n">
         <v>2684</v>
@@ -18378,7 +18378,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G621" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H621" t="n">
         <v>2910</v>
@@ -18407,7 +18407,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H622" t="n">
         <v>3398</v>
@@ -18465,7 +18465,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G624" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H624" t="n">
         <v>11485</v>
@@ -18494,7 +18494,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G625" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H625" t="n">
         <v>2743</v>
@@ -18523,7 +18523,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G626" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H626" t="n">
         <v>8590</v>
@@ -18552,7 +18552,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G627" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H627" t="n">
         <v>166729</v>
@@ -18581,7 +18581,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G628" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H628" t="n">
         <v>147791</v>
@@ -18610,7 +18610,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G629" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H629" t="n">
         <v>53531</v>
@@ -18639,7 +18639,7 @@
         <v>6.9273738861084</v>
       </c>
       <c r="G630" t="n">
-        <v>5.6843113899231</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H630" t="n">
         <v>81260</v>
@@ -18668,7 +18668,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G631" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H631" t="n">
         <v>34982</v>
@@ -18784,7 +18784,7 @@
         <v>6.75841379165649</v>
       </c>
       <c r="G635" t="n">
-        <v>5.54567050933838</v>
+        <v>5.54567003250122</v>
       </c>
       <c r="H635" t="n">
         <v>39040</v>
@@ -18813,7 +18813,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G636" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H636" t="n">
         <v>58339</v>
@@ -18842,7 +18842,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G637" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H637" t="n">
         <v>41909</v>
@@ -18871,7 +18871,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G638" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H638" t="n">
         <v>28392</v>
@@ -18900,7 +18900,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G639" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H639" t="n">
         <v>41973</v>
@@ -18929,7 +18929,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G640" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H640" t="n">
         <v>38746</v>
@@ -18958,7 +18958,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G641" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H641" t="n">
         <v>12988</v>
@@ -18987,7 +18987,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G642" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H642" t="n">
         <v>20150</v>
@@ -19016,7 +19016,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G643" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H643" t="n">
         <v>20473</v>
@@ -19074,7 +19074,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G645" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H645" t="n">
         <v>19543</v>
@@ -19103,7 +19103,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G646" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H646" t="n">
         <v>12266</v>
@@ -19190,7 +19190,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G649" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H649" t="n">
         <v>1693</v>
@@ -19248,7 +19248,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H651" t="n">
         <v>8630</v>
@@ -19277,7 +19277,7 @@
         <v>6.42049312591553</v>
       </c>
       <c r="G652" t="n">
-        <v>5.26838684082031</v>
+        <v>5.26838636398315</v>
       </c>
       <c r="H652" t="n">
         <v>6863</v>
@@ -19306,7 +19306,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G653" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H653" t="n">
         <v>3865</v>
@@ -19451,7 +19451,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G658" t="n">
-        <v>5.19136333465576</v>
+        <v>5.1913628578186</v>
       </c>
       <c r="H658" t="n">
         <v>3495</v>
@@ -19509,7 +19509,7 @@
         <v>6.32662582397461</v>
       </c>
       <c r="G660" t="n">
-        <v>5.19136333465576</v>
+        <v>5.1913628578186</v>
       </c>
       <c r="H660" t="n">
         <v>37725</v>
@@ -19538,7 +19538,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G661" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H661" t="n">
         <v>10675</v>
@@ -19567,7 +19567,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G662" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H662" t="n">
         <v>33870</v>
@@ -19596,7 +19596,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H663" t="n">
         <v>10127</v>
@@ -19625,7 +19625,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G664" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H664" t="n">
         <v>26802</v>
@@ -19654,7 +19654,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G665" t="n">
-        <v>5.14514923095703</v>
+        <v>5.14514970779419</v>
       </c>
       <c r="H665" t="n">
         <v>4770</v>
@@ -19799,7 +19799,7 @@
         <v>6.28908014297485</v>
       </c>
       <c r="G670" t="n">
-        <v>5.16055488586426</v>
+        <v>5.1605544090271</v>
       </c>
       <c r="H670" t="n">
         <v>5550</v>
@@ -19828,7 +19828,7 @@
         <v>6.34539985656738</v>
       </c>
       <c r="G671" t="n">
-        <v>5.20676803588867</v>
+        <v>5.20676851272583</v>
       </c>
       <c r="H671" t="n">
         <v>10523</v>
@@ -19915,7 +19915,7 @@
         <v>6.27030611038208</v>
       </c>
       <c r="G674" t="n">
-        <v>5.14514923095703</v>
+        <v>5.14514970779419</v>
       </c>
       <c r="H674" t="n">
         <v>11895</v>
@@ -20089,7 +20089,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G680" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H680" t="n">
         <v>192872</v>
@@ -20118,7 +20118,7 @@
         <v>6.42049312591553</v>
       </c>
       <c r="G681" t="n">
-        <v>5.26838684082031</v>
+        <v>5.26838636398315</v>
       </c>
       <c r="H681" t="n">
         <v>24663</v>
@@ -20147,7 +20147,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G682" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H682" t="n">
         <v>7075</v>
@@ -20234,7 +20234,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G685" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H685" t="n">
         <v>67173</v>
@@ -20263,7 +20263,7 @@
         <v>6.66454696655273</v>
       </c>
       <c r="G686" t="n">
-        <v>5.46864652633667</v>
+        <v>5.46864700317383</v>
       </c>
       <c r="H686" t="n">
         <v>133072</v>
@@ -20350,7 +20350,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H689" t="n">
         <v>14741</v>
@@ -20379,7 +20379,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G690" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H690" t="n">
         <v>23361</v>
@@ -20408,7 +20408,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G691" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H691" t="n">
         <v>12241</v>
@@ -20437,7 +20437,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G692" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H692" t="n">
         <v>9073</v>
@@ -20495,7 +20495,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G694" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H694" t="n">
         <v>62988</v>
@@ -20582,7 +20582,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G697" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H697" t="n">
         <v>12834</v>
@@ -20611,7 +20611,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G698" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H698" t="n">
         <v>13447</v>
@@ -20756,7 +20756,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G703" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H703" t="n">
         <v>59216</v>
@@ -20814,7 +20814,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H705" t="n">
         <v>4626</v>
@@ -20843,7 +20843,7 @@
         <v>6.53313398361206</v>
       </c>
       <c r="G706" t="n">
-        <v>5.36081504821777</v>
+        <v>5.36081552505493</v>
       </c>
       <c r="H706" t="n">
         <v>15942</v>
@@ -20872,7 +20872,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G707" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H707" t="n">
         <v>16991</v>
@@ -20901,7 +20901,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G708" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H708" t="n">
         <v>26773</v>
@@ -20959,7 +20959,7 @@
         <v>6.55190706253052</v>
       </c>
       <c r="G710" t="n">
-        <v>5.37621879577637</v>
+        <v>5.37621927261353</v>
       </c>
       <c r="H710" t="n">
         <v>22162</v>
@@ -20988,7 +20988,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G711" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H711" t="n">
         <v>17810</v>
@@ -21046,7 +21046,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G713" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H713" t="n">
         <v>10302</v>
@@ -21075,7 +21075,7 @@
         <v>6.57068014144897</v>
       </c>
       <c r="G714" t="n">
-        <v>5.39162397384644</v>
+        <v>5.39162349700928</v>
       </c>
       <c r="H714" t="n">
         <v>21490</v>
@@ -21104,7 +21104,7 @@
         <v>6.49558687210083</v>
       </c>
       <c r="G715" t="n">
-        <v>5.33000564575195</v>
+        <v>5.33000516891479</v>
       </c>
       <c r="H715" t="n">
         <v>49349</v>
@@ -21162,7 +21162,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G717" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H717" t="n">
         <v>11988</v>
@@ -21191,7 +21191,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G718" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H718" t="n">
         <v>2084</v>
@@ -21249,7 +21249,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G720" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H720" t="n">
         <v>3936</v>
@@ -21278,7 +21278,7 @@
         <v>6.45804023742676</v>
       </c>
       <c r="G721" t="n">
-        <v>5.29919672012329</v>
+        <v>5.29919576644897</v>
       </c>
       <c r="H721" t="n">
         <v>3313</v>
@@ -21307,7 +21307,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G722" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H722" t="n">
         <v>8101</v>
@@ -21365,7 +21365,7 @@
         <v>6.4392671585083</v>
       </c>
       <c r="G724" t="n">
-        <v>5.28379201889038</v>
+        <v>5.28379249572754</v>
       </c>
       <c r="H724" t="n">
         <v>158873</v>
@@ -21510,7 +21510,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G729" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272245407104</v>
       </c>
       <c r="H729" t="n">
         <v>214334</v>
@@ -21655,7 +21655,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G734" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H734" t="n">
         <v>11911</v>
@@ -21684,7 +21684,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G735" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272245407104</v>
       </c>
       <c r="H735" t="n">
         <v>12753</v>
@@ -21742,7 +21742,7 @@
         <v>6.19521284103394</v>
       </c>
       <c r="G737" t="n">
-        <v>5.08353090286255</v>
+        <v>5.08353137969971</v>
       </c>
       <c r="H737" t="n">
         <v>10868</v>
@@ -21800,7 +21800,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G739" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272245407104</v>
       </c>
       <c r="H739" t="n">
         <v>9338</v>
@@ -21829,7 +21829,7 @@
         <v>6.15766620635986</v>
       </c>
       <c r="G740" t="n">
-        <v>5.05272197723389</v>
+        <v>5.05272245407104</v>
       </c>
       <c r="H740" t="n">
         <v>18125</v>
@@ -21945,7 +21945,7 @@
         <v>6.13889312744141</v>
       </c>
       <c r="G744" t="n">
-        <v>5.03731727600098</v>
+        <v>5.03731775283813</v>
       </c>
       <c r="H744" t="n">
         <v>78631</v>
@@ -22032,7 +22032,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G747" t="n">
-        <v>4.66760635375977</v>
+        <v>4.66760540008545</v>
       </c>
       <c r="H747" t="n">
         <v>45629</v>
@@ -22061,7 +22061,7 @@
         <v>5.68833208084106</v>
       </c>
       <c r="G748" t="n">
-        <v>4.66760635375977</v>
+        <v>4.66760540008545</v>
       </c>
       <c r="H748" t="n">
         <v>24857</v>
@@ -22090,7 +22090,7 @@
         <v>5.65078496932983</v>
       </c>
       <c r="G749" t="n">
-        <v>4.63679695129395</v>
+        <v>4.63679647445679</v>
       </c>
       <c r="H749" t="n">
         <v>47792</v>
@@ -22119,7 +22119,7 @@
         <v>5.53814506530762</v>
       </c>
       <c r="G750" t="n">
-        <v>4.54436874389648</v>
+        <v>4.54436922073364</v>
       </c>
       <c r="H750" t="n">
         <v>20273</v>
@@ -22148,7 +22148,7 @@
         <v>5.63201189041138</v>
       </c>
       <c r="G751" t="n">
-        <v>4.62139177322388</v>
+        <v>4.62139225006104</v>
       </c>
       <c r="H751" t="n">
         <v>11601</v>
@@ -22177,7 +22177,7 @@
         <v>5.55691814422607</v>
       </c>
       <c r="G752" t="n">
-        <v>4.55977296829224</v>
+        <v>4.55977344512939</v>
       </c>
       <c r="H752" t="n">
         <v>19277</v>
@@ -22264,7 +22264,7 @@
         <v>4.97494411468506</v>
       </c>
       <c r="G755" t="n">
-        <v>4.08222961425781</v>
+        <v>4.08223009109497</v>
       </c>
       <c r="H755" t="n">
         <v>42542</v>
@@ -22293,7 +22293,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02061033248901</v>
+        <v>4.02061128616333</v>
       </c>
       <c r="H756" t="n">
         <v>118566</v>
@@ -22322,7 +22322,7 @@
         <v>4.73088979721069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.88196897506714</v>
+        <v>3.8819694519043</v>
       </c>
       <c r="H757" t="n">
         <v>69358</v>
@@ -22351,7 +22351,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60468578338623</v>
+        <v>3.60468554496765</v>
       </c>
       <c r="H758" t="n">
         <v>114780</v>
@@ -22380,7 +22380,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G759" t="n">
-        <v>3.59698295593262</v>
+        <v>3.59698343276978</v>
       </c>
       <c r="H759" t="n">
         <v>59239</v>
@@ -22409,7 +22409,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G760" t="n">
-        <v>3.23497438430786</v>
+        <v>3.23497462272644</v>
       </c>
       <c r="H760" t="n">
         <v>9678</v>
@@ -22467,7 +22467,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G762" t="n">
-        <v>3.06552314758301</v>
+        <v>3.06552338600159</v>
       </c>
       <c r="H762" t="n">
         <v>9266</v>
@@ -22496,7 +22496,7 @@
         <v>3.73590111732483</v>
       </c>
       <c r="G763" t="n">
-        <v>3.06552314758301</v>
+        <v>3.06552338600159</v>
       </c>
       <c r="H763" t="n">
         <v>15127</v>
@@ -22525,7 +22525,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G764" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H764" t="n">
         <v>23305</v>
@@ -22554,7 +22554,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G765" t="n">
-        <v>3.25808119773865</v>
+        <v>3.25808143615723</v>
       </c>
       <c r="H765" t="n">
         <v>2694</v>
@@ -22583,7 +22583,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G766" t="n">
-        <v>3.30429482460022</v>
+        <v>3.3042950630188</v>
       </c>
       <c r="H766" t="n">
         <v>13344</v>
@@ -22641,7 +22641,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G768" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H768" t="n">
         <v>8286</v>
@@ -22786,7 +22786,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G773" t="n">
-        <v>3.23497438430786</v>
+        <v>3.23497462272644</v>
       </c>
       <c r="H773" t="n">
         <v>20307</v>
@@ -22815,7 +22815,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G774" t="n">
-        <v>3.23497438430786</v>
+        <v>3.23497462272644</v>
       </c>
       <c r="H774" t="n">
         <v>8024</v>
@@ -22844,7 +22844,7 @@
         <v>4.02688789367676</v>
       </c>
       <c r="G775" t="n">
-        <v>3.30429482460022</v>
+        <v>3.3042950630188</v>
       </c>
       <c r="H775" t="n">
         <v>11885</v>
@@ -22931,7 +22931,7 @@
         <v>4.25216913223267</v>
       </c>
       <c r="G778" t="n">
-        <v>3.48915100097656</v>
+        <v>3.48915076255798</v>
       </c>
       <c r="H778" t="n">
         <v>94813</v>
@@ -22960,7 +22960,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G779" t="n">
-        <v>3.54306674003601</v>
+        <v>3.54306626319885</v>
       </c>
       <c r="H779" t="n">
         <v>19181</v>
@@ -23047,7 +23047,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G782" t="n">
-        <v>3.42753219604492</v>
+        <v>3.42753195762634</v>
       </c>
       <c r="H782" t="n">
         <v>12018</v>
@@ -23221,7 +23221,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G788" t="n">
-        <v>3.7741367816925</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H788" t="n">
         <v>79040</v>
@@ -23250,7 +23250,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035040855408</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H789" t="n">
         <v>103597</v>
@@ -23279,7 +23279,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G790" t="n">
-        <v>3.86656427383423</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H790" t="n">
         <v>21030</v>
@@ -23308,7 +23308,7 @@
         <v>4.646409034729</v>
       </c>
       <c r="G791" t="n">
-        <v>3.81264805793762</v>
+        <v>3.81264758110046</v>
       </c>
       <c r="H791" t="n">
         <v>43347</v>
@@ -23337,7 +23337,7 @@
         <v>4.5994758605957</v>
       </c>
       <c r="G792" t="n">
-        <v>3.7741367816925</v>
+        <v>3.77413654327393</v>
       </c>
       <c r="H792" t="n">
         <v>60664</v>
@@ -23366,7 +23366,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G793" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H793" t="n">
         <v>20249</v>
@@ -23395,7 +23395,7 @@
         <v>4.71211576461792</v>
       </c>
       <c r="G794" t="n">
-        <v>3.86656427383423</v>
+        <v>3.86656403541565</v>
       </c>
       <c r="H794" t="n">
         <v>52761</v>
@@ -23424,7 +23424,7 @@
         <v>4.65579605102539</v>
       </c>
       <c r="G795" t="n">
-        <v>3.82035040855408</v>
+        <v>3.82035064697266</v>
       </c>
       <c r="H795" t="n">
         <v>37010</v>
@@ -23453,7 +23453,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G796" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116052627563</v>
       </c>
       <c r="H796" t="n">
         <v>6620</v>
@@ -23511,7 +23511,7 @@
         <v>4.78720998764038</v>
       </c>
       <c r="G798" t="n">
-        <v>3.92818307876587</v>
+        <v>3.92818355560303</v>
       </c>
       <c r="H798" t="n">
         <v>44285</v>
@@ -23569,7 +23569,7 @@
         <v>4.67457008361816</v>
       </c>
       <c r="G800" t="n">
-        <v>3.8357560634613</v>
+        <v>3.83575558662415</v>
       </c>
       <c r="H800" t="n">
         <v>42258</v>
@@ -23598,7 +23598,7 @@
         <v>4.69334316253662</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116052627563</v>
       </c>
       <c r="H801" t="n">
         <v>45469</v>
@@ -23627,7 +23627,7 @@
         <v>4.40235614776611</v>
       </c>
       <c r="G802" t="n">
-        <v>3.86765384674072</v>
+        <v>3.86765432357788</v>
       </c>
       <c r="H802" t="n">
         <v>51949</v>
@@ -23714,7 +23714,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G805" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H805" t="n">
         <v>26480</v>
@@ -23743,7 +23743,7 @@
         <v>4.37419605255127</v>
       </c>
       <c r="G806" t="n">
-        <v>3.84291434288025</v>
+        <v>3.84291386604309</v>
       </c>
       <c r="H806" t="n">
         <v>94227</v>
@@ -24062,7 +24062,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G817" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H817" t="n">
         <v>604873</v>
@@ -24178,7 +24178,7 @@
         <v>4.8998498916626</v>
       </c>
       <c r="G821" t="n">
-        <v>4.30472278594971</v>
+        <v>4.30472326278687</v>
       </c>
       <c r="H821" t="n">
         <v>71502</v>
@@ -24207,7 +24207,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G822" t="n">
-        <v>4.27173614501953</v>
+        <v>4.27173662185669</v>
       </c>
       <c r="H822" t="n">
         <v>24302</v>
@@ -24236,7 +24236,7 @@
         <v>4.95617008209229</v>
       </c>
       <c r="G823" t="n">
-        <v>4.35420322418213</v>
+        <v>4.35420274734497</v>
       </c>
       <c r="H823" t="n">
         <v>29222</v>
@@ -24294,7 +24294,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G825" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H825" t="n">
         <v>35941</v>
@@ -24352,7 +24352,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G827" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H827" t="n">
         <v>16261</v>
@@ -24642,7 +24642,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G837" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H837" t="n">
         <v>17076</v>
@@ -24729,7 +24729,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G840" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H840" t="n">
         <v>4918</v>
@@ -24787,7 +24787,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G842" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H842" t="n">
         <v>14939</v>
@@ -24874,7 +24874,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H845" t="n">
         <v>6786</v>
@@ -24932,7 +24932,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G847" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H847" t="n">
         <v>5286</v>
@@ -24961,7 +24961,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G848" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H848" t="n">
         <v>24096</v>
@@ -25019,7 +25019,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G850" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H850" t="n">
         <v>14912</v>
@@ -25309,7 +25309,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G860" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H860" t="n">
         <v>8024</v>
@@ -25454,7 +25454,7 @@
         <v>4.86230278015137</v>
       </c>
       <c r="G865" t="n">
-        <v>4.27173614501953</v>
+        <v>4.27173662185669</v>
       </c>
       <c r="H865" t="n">
         <v>17734</v>
@@ -25483,7 +25483,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G866" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H866" t="n">
         <v>18582</v>
@@ -25570,7 +25570,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G869" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H869" t="n">
         <v>6800</v>
@@ -25628,7 +25628,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G871" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H871" t="n">
         <v>2654</v>
@@ -25744,7 +25744,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H875" t="n">
         <v>16903</v>
@@ -25918,7 +25918,7 @@
         <v>4.80598306655884</v>
       </c>
       <c r="G881" t="n">
-        <v>4.22225666046143</v>
+        <v>4.22225713729858</v>
       </c>
       <c r="H881" t="n">
         <v>56962</v>
@@ -25947,7 +25947,7 @@
         <v>4.74966287612915</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17277717590332</v>
+        <v>4.17277765274048</v>
       </c>
       <c r="H882" t="n">
         <v>10955</v>
@@ -26034,7 +26034,7 @@
         <v>4.76843595504761</v>
       </c>
       <c r="G885" t="n">
-        <v>4.18927001953125</v>
+        <v>4.18927049636841</v>
       </c>
       <c r="H885" t="n">
         <v>4939</v>
@@ -26324,7 +26324,7 @@
         <v>4.61824893951416</v>
       </c>
       <c r="G895" t="n">
-        <v>4.05732440948486</v>
+        <v>4.05732488632202</v>
       </c>
       <c r="H895" t="n">
         <v>14416</v>
@@ -26353,7 +26353,7 @@
         <v>4.54315614700317</v>
       </c>
       <c r="G896" t="n">
-        <v>3.99135255813599</v>
+        <v>3.99135303497314</v>
       </c>
       <c r="H896" t="n">
         <v>9674</v>
@@ -26382,7 +26382,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G897" t="n">
-        <v>3.99959921836853</v>
+        <v>3.99959969520569</v>
       </c>
       <c r="H897" t="n">
         <v>21516</v>
@@ -26440,7 +26440,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99959921836853</v>
+        <v>3.99959969520569</v>
       </c>
       <c r="H899" t="n">
         <v>13100</v>
@@ -26498,7 +26498,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G901" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H901" t="n">
         <v>23762</v>
@@ -26527,7 +26527,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G902" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H902" t="n">
         <v>27440</v>
@@ -26556,7 +26556,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G903" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H903" t="n">
         <v>30505</v>
@@ -26730,7 +26730,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H909" t="n">
         <v>12272</v>
@@ -26846,7 +26846,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G913" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H913" t="n">
         <v>26785</v>
@@ -26875,7 +26875,7 @@
         <v>3.85792803764343</v>
       </c>
       <c r="G914" t="n">
-        <v>3.38935089111328</v>
+        <v>3.38935112953186</v>
       </c>
       <c r="H914" t="n">
         <v>126936</v>
@@ -26962,7 +26962,7 @@
         <v>3.80160808563232</v>
       </c>
       <c r="G917" t="n">
-        <v>3.33987164497375</v>
+        <v>3.33987188339233</v>
       </c>
       <c r="H917" t="n">
         <v>10305</v>
@@ -26991,7 +26991,7 @@
         <v>3.78283405303955</v>
       </c>
       <c r="G918" t="n">
-        <v>3.32337784767151</v>
+        <v>3.32337808609009</v>
       </c>
       <c r="H918" t="n">
         <v>20342</v>
@@ -27020,7 +27020,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G919" t="n">
-        <v>3.31513166427612</v>
+        <v>3.3151319026947</v>
       </c>
       <c r="H919" t="n">
         <v>19199</v>
@@ -27049,7 +27049,7 @@
         <v>3.77344799041748</v>
       </c>
       <c r="G920" t="n">
-        <v>3.31513166427612</v>
+        <v>3.3151319026947</v>
       </c>
       <c r="H920" t="n">
         <v>6182</v>
@@ -27194,7 +27194,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G925" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H925" t="n">
         <v>60383</v>
@@ -27281,7 +27281,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G928" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H928" t="n">
         <v>18937</v>
@@ -27310,7 +27310,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G929" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H929" t="n">
         <v>55594</v>
@@ -27339,7 +27339,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G930" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H930" t="n">
         <v>14164</v>
@@ -27368,7 +27368,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G931" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H931" t="n">
         <v>15744</v>
@@ -27426,7 +27426,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G933" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H933" t="n">
         <v>20415</v>
@@ -27484,7 +27484,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G935" t="n">
-        <v>3.44707727432251</v>
+        <v>3.44707751274109</v>
       </c>
       <c r="H935" t="n">
         <v>48632</v>
@@ -27513,7 +27513,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G936" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H936" t="n">
         <v>20128</v>
@@ -27600,7 +27600,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G939" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H939" t="n">
         <v>25861</v>
@@ -27629,7 +27629,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G940" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H940" t="n">
         <v>204103</v>
@@ -27716,7 +27716,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G943" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H943" t="n">
         <v>39520</v>
@@ -27745,7 +27745,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G944" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H944" t="n">
         <v>39463</v>
@@ -27774,7 +27774,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G945" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148829460144</v>
       </c>
       <c r="H945" t="n">
         <v>38359</v>
@@ -27803,7 +27803,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G946" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H946" t="n">
         <v>23231</v>
@@ -27832,7 +27832,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G947" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H947" t="n">
         <v>47814</v>
@@ -27861,7 +27861,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G948" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H948" t="n">
         <v>31997</v>
@@ -27890,7 +27890,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G949" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H949" t="n">
         <v>106760</v>
@@ -27919,7 +27919,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G950" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H950" t="n">
         <v>10561</v>
@@ -27948,7 +27948,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G951" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H951" t="n">
         <v>23800</v>
@@ -28006,7 +28006,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G953" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H953" t="n">
         <v>3250</v>
@@ -28035,7 +28035,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G954" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H954" t="n">
         <v>11668</v>
@@ -28209,7 +28209,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G960" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H960" t="n">
         <v>23384</v>
@@ -28267,7 +28267,7 @@
         <v>4.61824893951416</v>
       </c>
       <c r="G962" t="n">
-        <v>4.05732440948486</v>
+        <v>4.05732488632202</v>
       </c>
       <c r="H962" t="n">
         <v>450636</v>
@@ -28296,7 +28296,7 @@
         <v>4.55254316329956</v>
       </c>
       <c r="G963" t="n">
-        <v>3.99959921836853</v>
+        <v>3.99959969520569</v>
       </c>
       <c r="H963" t="n">
         <v>98447</v>
@@ -28325,7 +28325,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G964" t="n">
-        <v>3.96661257743835</v>
+        <v>3.96661305427551</v>
       </c>
       <c r="H964" t="n">
         <v>39821</v>
@@ -28354,7 +28354,7 @@
         <v>4.50560903549194</v>
       </c>
       <c r="G965" t="n">
-        <v>3.95836591720581</v>
+        <v>3.95836639404297</v>
       </c>
       <c r="H965" t="n">
         <v>25228</v>
@@ -28383,7 +28383,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G966" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116052627563</v>
       </c>
       <c r="H966" t="n">
         <v>80934</v>
@@ -28441,7 +28441,7 @@
         <v>4.51499605178833</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96661257743835</v>
+        <v>3.96661305427551</v>
       </c>
       <c r="H968" t="n">
         <v>98913</v>
@@ -28499,7 +28499,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85940670967102</v>
+        <v>3.85940718650818</v>
       </c>
       <c r="H970" t="n">
         <v>23554</v>
@@ -28528,7 +28528,7 @@
         <v>4.39296913146973</v>
       </c>
       <c r="G971" t="n">
-        <v>3.85940670967102</v>
+        <v>3.85940718650818</v>
       </c>
       <c r="H971" t="n">
         <v>26341</v>
@@ -28586,7 +28586,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G973" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H973" t="n">
         <v>30963</v>
@@ -28644,7 +28644,7 @@
         <v>4.38358211517334</v>
       </c>
       <c r="G975" t="n">
-        <v>3.85116004943848</v>
+        <v>3.85116052627563</v>
       </c>
       <c r="H975" t="n">
         <v>12119</v>
@@ -28673,7 +28673,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G976" t="n">
-        <v>3.80992770195007</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H976" t="n">
         <v>12393</v>
@@ -28702,7 +28702,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G977" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H977" t="n">
         <v>18818</v>
@@ -28876,7 +28876,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G983" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H983" t="n">
         <v>19501</v>
@@ -28963,7 +28963,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G986" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H986" t="n">
         <v>14453</v>
@@ -28992,7 +28992,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H987" t="n">
         <v>32827</v>
@@ -29021,7 +29021,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G988" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H988" t="n">
         <v>105272</v>
@@ -29050,7 +29050,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G989" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H989" t="n">
         <v>29551</v>
@@ -29079,7 +29079,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G990" t="n">
-        <v>3.76044845581055</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H990" t="n">
         <v>34076</v>
@@ -29108,7 +29108,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G991" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H991" t="n">
         <v>31203</v>
@@ -29137,7 +29137,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G992" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H992" t="n">
         <v>77453</v>
@@ -29166,7 +29166,7 @@
         <v>4.33664894104004</v>
       </c>
       <c r="G993" t="n">
-        <v>3.80992770195007</v>
+        <v>3.80992746353149</v>
       </c>
       <c r="H993" t="n">
         <v>25930</v>
@@ -29282,7 +29282,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G997" t="n">
-        <v>3.76044845581055</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H997" t="n">
         <v>27938</v>
@@ -29311,7 +29311,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G998" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H998" t="n">
         <v>7194</v>
@@ -29398,7 +29398,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H1001" t="n">
         <v>15073</v>
@@ -29456,7 +29456,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1003" t="n">
         <v>38443</v>
@@ -29514,7 +29514,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H1005" t="n">
         <v>24094</v>
@@ -29572,7 +29572,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1007" t="n">
         <v>37625</v>
@@ -29630,7 +29630,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H1009" t="n">
         <v>21917</v>
@@ -29717,7 +29717,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H1012" t="n">
         <v>21537</v>
@@ -29775,7 +29775,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1014" t="n">
         <v>18825</v>
@@ -29804,7 +29804,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1015" t="n">
         <v>18095</v>
@@ -29833,7 +29833,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1016" t="n">
         <v>29025</v>
@@ -29862,7 +29862,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H1017" t="n">
         <v>56350</v>
@@ -29920,7 +29920,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1019" t="n">
         <v>21560</v>
@@ -29949,7 +29949,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1020" t="n">
         <v>23255</v>
@@ -30007,7 +30007,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1022" t="n">
         <v>23587</v>
@@ -30036,7 +30036,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1023" t="n">
         <v>100775</v>
@@ -30094,7 +30094,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1025" t="n">
         <v>37874</v>
@@ -30123,7 +30123,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1026" t="n">
         <v>14221</v>
@@ -30152,7 +30152,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1027" t="n">
         <v>25372</v>
@@ -30239,7 +30239,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H1030" t="n">
         <v>28499</v>
@@ -30297,7 +30297,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1032" t="n">
         <v>39883</v>
@@ -30355,7 +30355,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1034" t="n">
         <v>41320</v>
@@ -30384,7 +30384,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1035" t="n">
         <v>20652</v>
@@ -30413,7 +30413,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1036" t="n">
         <v>25907</v>
@@ -30442,7 +30442,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1037" t="n">
         <v>103283</v>
@@ -30529,7 +30529,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1040" t="n">
         <v>37918</v>
@@ -30558,7 +30558,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1041" t="n">
         <v>33432</v>
@@ -30587,7 +30587,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H1042" t="n">
         <v>29677</v>
@@ -30645,7 +30645,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1044" t="n">
         <v>60916</v>
@@ -30674,7 +30674,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.76044845581055</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1045" t="n">
         <v>26734</v>
@@ -30703,7 +30703,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1046" t="n">
         <v>8805</v>
@@ -30790,7 +30790,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1049" t="n">
         <v>11760</v>
@@ -30819,7 +30819,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1050" t="n">
         <v>3012</v>
@@ -30848,7 +30848,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1051" t="n">
         <v>3548</v>
@@ -30877,7 +30877,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.76044845581055</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1052" t="n">
         <v>6158</v>
@@ -30964,7 +30964,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1055" t="n">
         <v>12152</v>
@@ -30993,7 +30993,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1056" t="n">
         <v>13789</v>
@@ -31022,7 +31022,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H1057" t="n">
         <v>30443</v>
@@ -31051,7 +31051,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H1058" t="n">
         <v>12928</v>
@@ -31080,7 +31080,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1059" t="n">
         <v>5829</v>
@@ -31138,7 +31138,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1061" t="n">
         <v>16774</v>
@@ -31196,7 +31196,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1063" t="n">
         <v>25919</v>
@@ -31225,7 +31225,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.76044845581055</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1064" t="n">
         <v>11044</v>
@@ -31254,7 +31254,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1065" t="n">
         <v>24230</v>
@@ -31283,7 +31283,7 @@
         <v>4.28032922744751</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.76044845581055</v>
+        <v>3.76044821739197</v>
       </c>
       <c r="H1066" t="n">
         <v>19508</v>
@@ -31312,7 +31312,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1067" t="n">
         <v>39186</v>
@@ -31370,7 +31370,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1069" t="n">
         <v>58800</v>
@@ -31399,7 +31399,7 @@
         <v>4.26155519485474</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.74395418167114</v>
+        <v>3.7439546585083</v>
       </c>
       <c r="H1070" t="n">
         <v>56554</v>
@@ -31457,7 +31457,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1072" t="n">
         <v>42884</v>
@@ -31515,7 +31515,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1074" t="n">
         <v>65157</v>
@@ -31602,7 +31602,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1077" t="n">
         <v>94343</v>
@@ -31631,7 +31631,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1078" t="n">
         <v>6907</v>
@@ -31660,7 +31660,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H1079" t="n">
         <v>14510</v>
@@ -31805,7 +31805,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1084" t="n">
         <v>20412</v>
@@ -31834,7 +31834,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1085" t="n">
         <v>9140</v>
@@ -31892,7 +31892,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1087" t="n">
         <v>42401</v>
@@ -31921,7 +31921,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.56252908706665</v>
+        <v>3.56252932548523</v>
       </c>
       <c r="H1088" t="n">
         <v>11524</v>
@@ -31950,7 +31950,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1089" t="n">
         <v>6676</v>
@@ -31979,7 +31979,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H1090" t="n">
         <v>13072</v>
@@ -32037,7 +32037,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1092" t="n">
         <v>27747</v>
@@ -32066,7 +32066,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.56252908706665</v>
+        <v>3.56252932548523</v>
       </c>
       <c r="H1093" t="n">
         <v>24635</v>
@@ -32095,7 +32095,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1094" t="n">
         <v>30142</v>
@@ -32153,7 +32153,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1096" t="n">
         <v>9429</v>
@@ -32240,7 +32240,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1099" t="n">
         <v>2287</v>
@@ -32269,7 +32269,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1100" t="n">
         <v>19929</v>
@@ -32356,7 +32356,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1103" t="n">
         <v>8811</v>
@@ -32501,7 +32501,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1108" t="n">
         <v>11339</v>
@@ -32530,7 +32530,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1109" t="n">
         <v>1861</v>
@@ -32646,7 +32646,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1113" t="n">
         <v>2815</v>
@@ -32675,7 +32675,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1114" t="n">
         <v>5118</v>
@@ -32704,7 +32704,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285709381104</v>
       </c>
       <c r="H1115" t="n">
         <v>45530</v>
@@ -32820,7 +32820,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1119" t="n">
         <v>119353</v>
@@ -32849,7 +32849,7 @@
         <v>4.27094221115112</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.75220131874084</v>
+        <v>3.75220155715942</v>
       </c>
       <c r="H1120" t="n">
         <v>74582</v>
@@ -32965,7 +32965,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1124" t="n">
         <v>70251</v>
@@ -33081,7 +33081,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1128" t="n">
         <v>62441</v>
@@ -33110,7 +33110,7 @@
         <v>4.34603595733643</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.81817412376404</v>
+        <v>3.81817436218262</v>
       </c>
       <c r="H1129" t="n">
         <v>47955</v>
@@ -33139,7 +33139,7 @@
         <v>4.3554220199585</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.82642030715942</v>
+        <v>3.82642006874084</v>
       </c>
       <c r="H1130" t="n">
         <v>37637</v>
@@ -33168,7 +33168,7 @@
         <v>4.31787490844727</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.79343342781067</v>
+        <v>3.79343366622925</v>
       </c>
       <c r="H1131" t="n">
         <v>33720</v>
@@ -33197,7 +33197,7 @@
         <v>4.28971481323242</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.76869344711304</v>
+        <v>3.7686939239502</v>
       </c>
       <c r="H1132" t="n">
         <v>13639</v>
@@ -33226,7 +33226,7 @@
         <v>4.21462202072144</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.70272159576416</v>
+        <v>3.70272183418274</v>
       </c>
       <c r="H1133" t="n">
         <v>63296</v>
@@ -33284,7 +33284,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1135" t="n">
         <v>25711</v>
@@ -33342,7 +33342,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148829460144</v>
       </c>
       <c r="H1137" t="n">
         <v>26693</v>
@@ -33371,7 +33371,7 @@
         <v>4.22400903701782</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71096873283386</v>
+        <v>3.71096849441528</v>
       </c>
       <c r="H1138" t="n">
         <v>28849</v>
@@ -33429,7 +33429,7 @@
         <v>4.16768789291382</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.66148805618286</v>
+        <v>3.66148829460144</v>
       </c>
       <c r="H1140" t="n">
         <v>47855</v>
@@ -33487,7 +33487,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1142" t="n">
         <v>70144</v>
@@ -33516,7 +33516,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1143" t="n">
         <v>71574</v>
@@ -33574,7 +33574,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1145" t="n">
         <v>11043</v>
@@ -33603,7 +33603,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1146" t="n">
         <v>13893</v>
@@ -33632,7 +33632,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1147" t="n">
         <v>5028</v>
@@ -33719,7 +33719,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1150" t="n">
         <v>35755</v>
@@ -33893,7 +33893,7 @@
         <v>4.13014221191406</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.628502368927</v>
+        <v>3.62850260734558</v>
       </c>
       <c r="H1156" t="n">
         <v>2307</v>
@@ -33980,7 +33980,7 @@
         <v>4.10198211669922</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.60376262664795</v>
+        <v>3.60376286506653</v>
       </c>
       <c r="H1159" t="n">
         <v>20913</v>
@@ -34096,7 +34096,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428338050842</v>
       </c>
       <c r="H1163" t="n">
         <v>36527</v>
@@ -34125,7 +34125,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1164" t="n">
         <v>32377</v>
@@ -34183,7 +34183,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1166" t="n">
         <v>8226</v>
@@ -34212,7 +34212,7 @@
         <v>4.07382202148438</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.5790228843689</v>
+        <v>3.57902312278748</v>
       </c>
       <c r="H1167" t="n">
         <v>10482</v>
@@ -34241,7 +34241,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1168" t="n">
         <v>10241</v>
@@ -34270,7 +34270,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1169" t="n">
         <v>8390</v>
@@ -34299,7 +34299,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1170" t="n">
         <v>23775</v>
@@ -34328,7 +34328,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1171" t="n">
         <v>4856</v>
@@ -34357,7 +34357,7 @@
         <v>4.0550479888916</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.56252908706665</v>
+        <v>3.56252932548523</v>
       </c>
       <c r="H1172" t="n">
         <v>22682</v>
@@ -34386,7 +34386,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1173" t="n">
         <v>9266</v>
@@ -34502,7 +34502,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.44707727432251</v>
+        <v>3.44707751274109</v>
       </c>
       <c r="H1177" t="n">
         <v>14799</v>
@@ -34560,7 +34560,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1179" t="n">
         <v>10695</v>
@@ -34589,7 +34589,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.44707727432251</v>
+        <v>3.44707751274109</v>
       </c>
       <c r="H1180" t="n">
         <v>27262</v>
@@ -34676,7 +34676,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.44707727432251</v>
+        <v>3.44707751274109</v>
       </c>
       <c r="H1183" t="n">
         <v>24607</v>
@@ -34734,7 +34734,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1185" t="n">
         <v>40153</v>
@@ -34792,7 +34792,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1187" t="n">
         <v>17346</v>
@@ -34821,7 +34821,7 @@
         <v>4.17707490921021</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.66973519325256</v>
+        <v>3.66973495483398</v>
       </c>
       <c r="H1188" t="n">
         <v>64523</v>
@@ -34850,7 +34850,7 @@
         <v>4.18646192550659</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.67798185348511</v>
+        <v>3.67798209190369</v>
       </c>
       <c r="H1189" t="n">
         <v>48866</v>
@@ -34879,7 +34879,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1190" t="n">
         <v>25104</v>
@@ -34995,7 +34995,7 @@
         <v>4.09259510040283</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59551572799683</v>
+        <v>3.59551596641541</v>
       </c>
       <c r="H1194" t="n">
         <v>16241</v>
@@ -35024,7 +35024,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1195" t="n">
         <v>20816</v>
@@ -35111,7 +35111,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1198" t="n">
         <v>11291</v>
@@ -35140,7 +35140,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.44707727432251</v>
+        <v>3.44707751274109</v>
       </c>
       <c r="H1199" t="n">
         <v>6078</v>
@@ -35169,7 +35169,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1200" t="n">
         <v>7176</v>
@@ -35198,7 +35198,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1201" t="n">
         <v>8294</v>
@@ -35227,7 +35227,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428338050842</v>
       </c>
       <c r="H1202" t="n">
         <v>5435</v>
@@ -35285,7 +35285,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1204" t="n">
         <v>12073</v>
@@ -35314,7 +35314,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1205" t="n">
         <v>19359</v>
@@ -35343,7 +35343,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1206" t="n">
         <v>10703</v>
@@ -35372,7 +35372,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1207" t="n">
         <v>26510</v>
@@ -35401,7 +35401,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1208" t="n">
         <v>1693</v>
@@ -35430,7 +35430,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1209" t="n">
         <v>10093</v>
@@ -35459,7 +35459,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1210" t="n">
         <v>7512</v>
@@ -35488,7 +35488,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1211" t="n">
         <v>51874</v>
@@ -35517,7 +35517,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1212" t="n">
         <v>12870</v>
@@ -35633,7 +35633,7 @@
         <v>4.03627490997314</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.54603600502014</v>
+        <v>3.54603624343872</v>
       </c>
       <c r="H1216" t="n">
         <v>8971</v>
@@ -35720,7 +35720,7 @@
         <v>4.04566192626953</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.55428314208984</v>
+        <v>3.55428338050842</v>
       </c>
       <c r="H1219" t="n">
         <v>41335</v>
@@ -35778,7 +35778,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1221" t="n">
         <v>5316</v>
@@ -35807,7 +35807,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1222" t="n">
         <v>6029</v>
@@ -35836,7 +35836,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1223" t="n">
         <v>22676</v>
@@ -35865,7 +35865,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1224" t="n">
         <v>10519</v>
@@ -35894,7 +35894,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1225" t="n">
         <v>9180</v>
@@ -35923,7 +35923,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1226" t="n">
         <v>12826</v>
@@ -35981,7 +35981,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1228" t="n">
         <v>9896</v>
@@ -36039,7 +36039,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1230" t="n">
         <v>20614</v>
@@ -36068,7 +36068,7 @@
         <v>3.97995495796204</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.49655675888062</v>
+        <v>3.49655699729919</v>
       </c>
       <c r="H1231" t="n">
         <v>12772</v>
@@ -36155,7 +36155,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.44707727432251</v>
+        <v>3.44707751274109</v>
       </c>
       <c r="H1234" t="n">
         <v>49691</v>
@@ -36184,7 +36184,7 @@
         <v>3.82976794242859</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.36461114883423</v>
+        <v>3.36461138725281</v>
       </c>
       <c r="H1235" t="n">
         <v>21167</v>
@@ -36213,7 +36213,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.38110423088074</v>
+        <v>3.38110446929932</v>
       </c>
       <c r="H1236" t="n">
         <v>10413</v>
@@ -36271,7 +36271,7 @@
         <v>3.83915400505066</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.37285733222961</v>
+        <v>3.37285709381104</v>
       </c>
       <c r="H1238" t="n">
         <v>1560</v>
@@ -36300,7 +36300,7 @@
         <v>3.8673141002655</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.39759707450867</v>
+        <v>3.39759731292725</v>
       </c>
       <c r="H1239" t="n">
         <v>9280</v>
@@ -36329,7 +36329,7 @@
         <v>3.8673141002655</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.39759707450867</v>
+        <v>3.39759731292725</v>
       </c>
       <c r="H1240" t="n">
         <v>10099</v>
@@ -36445,7 +36445,7 @@
         <v>3.8673141002655</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.39759707450867</v>
+        <v>3.39759731292725</v>
       </c>
       <c r="H1244" t="n">
         <v>5268</v>
@@ -36503,7 +36503,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.35636425018311</v>
+        <v>3.35636448860168</v>
       </c>
       <c r="H1246" t="n">
         <v>8528</v>
@@ -36561,7 +36561,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.17493915557861</v>
+        <v>3.17493939399719</v>
       </c>
       <c r="H1248" t="n">
         <v>97339</v>
@@ -36619,7 +36619,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12545990943909</v>
+        <v>3.12546014785767</v>
       </c>
       <c r="H1250" t="n">
         <v>14068</v>
@@ -36648,7 +36648,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.09247326850891</v>
+        <v>3.09247303009033</v>
       </c>
       <c r="H1251" t="n">
         <v>38843</v>
@@ -36677,7 +36677,7 @@
         <v>3.52000689506531</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.09247326850891</v>
+        <v>3.09247303009033</v>
       </c>
       <c r="H1252" t="n">
         <v>10004</v>
@@ -36706,7 +36706,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721324920654</v>
       </c>
       <c r="H1253" t="n">
         <v>6186</v>
@@ -36735,7 +36735,7 @@
         <v>3.54816699028015</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.11721301078796</v>
+        <v>3.11721324920654</v>
       </c>
       <c r="H1254" t="n">
         <v>7022</v>
@@ -36764,7 +36764,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.2161717414856</v>
+        <v>3.21617197990417</v>
       </c>
       <c r="H1255" t="n">
         <v>41768</v>
@@ -36793,7 +36793,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.17493915557861</v>
+        <v>3.17493939399719</v>
       </c>
       <c r="H1256" t="n">
         <v>43078</v>
@@ -36851,7 +36851,7 @@
         <v>3.66080689430237</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.2161717414856</v>
+        <v>3.21617197990417</v>
       </c>
       <c r="H1258" t="n">
         <v>26713</v>
@@ -36938,7 +36938,7 @@
         <v>3.56694102287292</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.13370704650879</v>
+        <v>3.13370680809021</v>
       </c>
       <c r="H1261" t="n">
         <v>8025</v>
@@ -37025,7 +37025,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.99351453781128</v>
+        <v>2.9935142993927</v>
       </c>
       <c r="H1264" t="n">
         <v>42973</v>
@@ -37054,7 +37054,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280151367188</v>
       </c>
       <c r="H1265" t="n">
         <v>33527</v>
@@ -37083,7 +37083,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280151367188</v>
       </c>
       <c r="H1266" t="n">
         <v>13521</v>
@@ -37199,7 +37199,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1270" t="n">
         <v>2889</v>
@@ -37228,7 +37228,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877479553223</v>
       </c>
       <c r="H1271" t="n">
         <v>8955</v>
@@ -37257,7 +37257,7 @@
         <v>3.40736699104309</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.99351453781128</v>
+        <v>2.9935142993927</v>
       </c>
       <c r="H1272" t="n">
         <v>11850</v>
@@ -37286,7 +37286,7 @@
         <v>3.30411291122437</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.9028012752533</v>
+        <v>2.90280151367188</v>
       </c>
       <c r="H1273" t="n">
         <v>76645</v>
@@ -37344,7 +37344,7 @@
         <v>3.43552708625793</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.01825404167175</v>
+        <v>3.01825428009033</v>
       </c>
       <c r="H1275" t="n">
         <v>23501</v>
@@ -37373,7 +37373,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1276" t="n">
         <v>18660</v>
@@ -37402,7 +37402,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.05948662757874</v>
+        <v>3.05948686599731</v>
       </c>
       <c r="H1277" t="n">
         <v>5110</v>
@@ -37431,7 +37431,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.07598042488098</v>
+        <v>3.07598066329956</v>
       </c>
       <c r="H1278" t="n">
         <v>2623</v>
@@ -37576,7 +37576,7 @@
         <v>3.55755400657654</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.12545990943909</v>
+        <v>3.12546014785767</v>
       </c>
       <c r="H1283" t="n">
         <v>6914</v>
@@ -37634,7 +37634,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1285" t="n">
         <v>6703</v>
@@ -37663,7 +37663,7 @@
         <v>3.49184703826904</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.06773352622986</v>
+        <v>3.06773376464844</v>
       </c>
       <c r="H1286" t="n">
         <v>11272</v>
@@ -37750,7 +37750,7 @@
         <v>3.50123405456543</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.07598042488098</v>
+        <v>3.07598066329956</v>
       </c>
       <c r="H1289" t="n">
         <v>6377</v>
@@ -37895,7 +37895,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.05948662757874</v>
+        <v>3.05948686599731</v>
       </c>
       <c r="H1294" t="n">
         <v>7283</v>
@@ -37924,7 +37924,7 @@
         <v>3.48246002197266</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.05948662757874</v>
+        <v>3.05948686599731</v>
       </c>
       <c r="H1295" t="n">
         <v>3328</v>
@@ -38011,7 +38011,7 @@
         <v>3.3979799747467</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.98526763916016</v>
+        <v>2.98526740074158</v>
       </c>
       <c r="H1298" t="n">
         <v>2308</v>
@@ -38040,7 +38040,7 @@
         <v>3.43552708625793</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.01825404167175</v>
+        <v>3.01825428009033</v>
       </c>
       <c r="H1299" t="n">
         <v>6284</v>
@@ -38127,7 +38127,7 @@
         <v>3.35104703903198</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.94403505325317</v>
+        <v>2.94403481483459</v>
       </c>
       <c r="H1302" t="n">
         <v>14106</v>
@@ -38156,7 +38156,7 @@
         <v>3.37920689582825</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.96877455711365</v>
+        <v>2.96877479553223</v>
       </c>
       <c r="H1303" t="n">
         <v>16267</v>
@@ -38185,7 +38185,7 @@
         <v>3.31349992752075</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.91104817390442</v>
+        <v>2.911048412323</v>
       </c>
       <c r="H1304" t="n">
         <v>19090</v>
@@ -38243,7 +38243,7 @@
         <v>3.28534007072449</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.88630843162537</v>
+        <v>2.88630867004395</v>
       </c>
       <c r="H1306" t="n">
         <v>18867</v>
@@ -38272,7 +38272,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.35636425018311</v>
+        <v>3.35636448860168</v>
       </c>
       <c r="H1307" t="n">
         <v>245895</v>
@@ -38301,7 +38301,7 @@
         <v>3.84854102134705</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.38110423088074</v>
+        <v>3.38110446929932</v>
       </c>
       <c r="H1308" t="n">
         <v>82876</v>
@@ -38330,7 +38330,7 @@
         <v>3.85792803764343</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.38935089111328</v>
+        <v>3.38935112953186</v>
       </c>
       <c r="H1309" t="n">
         <v>54861</v>
@@ -38417,7 +38417,7 @@
         <v>3.97056794166565</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.48830986022949</v>
+        <v>3.48831009864807</v>
       </c>
       <c r="H1312" t="n">
         <v>43094</v>
@@ -38446,7 +38446,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1313" t="n">
         <v>8922</v>
@@ -38475,7 +38475,7 @@
         <v>3.98934102058411</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.50480270385742</v>
+        <v>3.50480318069458</v>
       </c>
       <c r="H1314" t="n">
         <v>9692</v>
@@ -38504,7 +38504,7 @@
         <v>3.94240808486938</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.46357035636902</v>
+        <v>3.4635705947876</v>
       </c>
       <c r="H1315" t="n">
         <v>17985</v>
@@ -71251,6 +71251,35 @@
         <v>103768</v>
       </c>
       <c r="I2444" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2445" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2445" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="G2445" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="H2445" t="n">
+        <v>324496</v>
+      </c>
+      <c r="I2445" t="s">
         <v>9</v>
       </c>
     </row>
